--- a/streamlit_data/regional_insights.xlsx
+++ b/streamlit_data/regional_insights.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E356"/>
+  <dimension ref="A1:E368"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -566,7 +566,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Lu</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -604,102 +604,102 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>De</t>
+          <t>Instorebakery</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E10" t="n">
-        <v>18.653</v>
+        <v>20.54408949352927</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Instorebakery</t>
+          <t>Jumbo</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C11" t="n">
         <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E11" t="n">
-        <v>20.54408949352927</v>
+        <v>17.87454087102899</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Jumbo</t>
+          <t>Gamesa</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>17.87454087102899</v>
+        <v>14.34406779661017</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Gamesa</t>
+          <t>La Panera</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E13" t="n">
-        <v>14.34406779661017</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>La Panera</t>
+          <t>Aviva</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>8.199999999999999</v>
+        <v>5.020416666666667</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Aviva</t>
+          <t>Hatuey</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -712,74 +712,74 @@
         <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>5.020416666666667</v>
+        <v>4.6105</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Hatuey</t>
+          <t>Food Club</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E16" t="n">
-        <v>4.6105</v>
+        <v>13.77359998911356</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Food Club</t>
+          <t>Molino Del Sol</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" t="n">
         <v>2</v>
       </c>
-      <c r="D17" t="n">
-        <v>4</v>
-      </c>
       <c r="E17" t="n">
-        <v>13.77359998911356</v>
+        <v>6.007045454545454</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Molino Del Sol</t>
+          <t>Bizcocho</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C18" t="n">
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>6.007045454545454</v>
+        <v>10.02074074074074</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Bizcocho</t>
+          <t>Dino</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="C19" t="n">
         <v>1</v>
@@ -788,26 +788,26 @@
         <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>10.02074074074074</v>
+        <v>4.624444444444444</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Dino</t>
+          <t>Fritolay</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C20" t="n">
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E20" t="n">
-        <v>4.624444444444444</v>
+        <v>24.1450861571947</v>
       </c>
     </row>
     <row r="21">
@@ -832,20 +832,20 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Fritolay</t>
+          <t>Nabisco</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D22" t="n">
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>24.1450861571947</v>
+        <v>13.06208846559279</v>
       </c>
     </row>
     <row r="23">
@@ -870,77 +870,77 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Nabisco</t>
+          <t>Ritz</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D24" t="n">
         <v>3</v>
       </c>
       <c r="E24" t="n">
-        <v>13.06208846559279</v>
+        <v>13.45669546927413</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Ritz</t>
+          <t>Pringles</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C25" t="n">
         <v>2</v>
       </c>
       <c r="D25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E25" t="n">
-        <v>13.45669546927413</v>
+        <v>30.28430124177305</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Pringles</t>
+          <t>Bermudez</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E26" t="n">
-        <v>30.28430124177305</v>
+        <v>9.901427320955712</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Bermudez</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C27" t="n">
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E27" t="n">
-        <v>9.901427320955712</v>
+        <v>14.89461538461538</v>
       </c>
     </row>
     <row r="28">
@@ -965,26 +965,26 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Colombina</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E29" t="n">
-        <v>14.89461538461538</v>
+        <v>12.91069444444445</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Colombina</t>
+          <t>Old El Paso</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -994,35 +994,35 @@
         <v>2</v>
       </c>
       <c r="D30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v>12.91069444444445</v>
+        <v>13.455</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Old El Paso</t>
+          <t>Duetto</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D31" t="n">
         <v>1</v>
       </c>
       <c r="E31" t="n">
-        <v>13.455</v>
+        <v>4.406190476190476</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Duetto</t>
+          <t>Mi Trigo</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -1032,10 +1032,10 @@
         <v>1</v>
       </c>
       <c r="D32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E32" t="n">
-        <v>4.406190476190476</v>
+        <v>7.743333333333332</v>
       </c>
     </row>
     <row r="33">
@@ -1060,20 +1060,20 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Mi Trigo</t>
+          <t>Chocolate</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C34" t="n">
         <v>1</v>
       </c>
       <c r="D34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E34" t="n">
-        <v>7.743333333333332</v>
+        <v>21.21722222222222</v>
       </c>
     </row>
     <row r="35">
@@ -1098,39 +1098,39 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Tostitos</t>
+          <t>Oh Snacks</t>
         </is>
       </c>
       <c r="B36" t="n">
         <v>18</v>
       </c>
       <c r="C36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E36" t="n">
-        <v>17.86079007336146</v>
+        <v>38.08068575758553</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Oh Snacks</t>
+          <t>Tostitos</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>18</v>
       </c>
       <c r="C37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E37" t="n">
-        <v>38.08068575758553</v>
+        <v>17.86079007336146</v>
       </c>
     </row>
     <row r="38">
@@ -1174,7 +1174,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Pc</t>
+          <t>Lays</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -1184,16 +1184,16 @@
         <v>1</v>
       </c>
       <c r="D40" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E40" t="n">
-        <v>5.189283551419543</v>
+        <v>33.99431564837405</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Lays</t>
+          <t>Pc</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -1203,10 +1203,10 @@
         <v>1</v>
       </c>
       <c r="D41" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E41" t="n">
-        <v>33.99431564837405</v>
+        <v>5.189283551419543</v>
       </c>
     </row>
     <row r="42">
@@ -1231,7 +1231,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Devon</t>
+          <t>Pita</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -1241,16 +1241,16 @@
         <v>1</v>
       </c>
       <c r="D43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E43" t="n">
-        <v>9.404842870544091</v>
+        <v>9.33</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Pita</t>
+          <t>Devon</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -1260,29 +1260,29 @@
         <v>1</v>
       </c>
       <c r="D44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E44" t="n">
-        <v>9.33</v>
+        <v>9.404842870544091</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Noel</t>
         </is>
       </c>
       <c r="B45" t="n">
         <v>13</v>
       </c>
       <c r="C45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D45" t="n">
         <v>3</v>
       </c>
       <c r="E45" t="n">
-        <v>3.208571428571429</v>
+        <v>18.95086616146494</v>
       </c>
     </row>
     <row r="46">
@@ -1326,20 +1326,20 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Noel</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="B48" t="n">
         <v>13</v>
       </c>
       <c r="C48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D48" t="n">
         <v>3</v>
       </c>
       <c r="E48" t="n">
-        <v>18.95086616146494</v>
+        <v>3.208571428571429</v>
       </c>
     </row>
     <row r="49">
@@ -1402,7 +1402,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Wow</t>
+          <t>Topper</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -1414,26 +1414,26 @@
       <c r="D52" t="n">
         <v>1</v>
       </c>
-      <c r="E52" t="n">
-        <v>9.494999999999999</v>
-      </c>
+      <c r="E52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Topper</t>
+          <t>Motto</t>
         </is>
       </c>
       <c r="B53" t="n">
         <v>11</v>
       </c>
       <c r="C53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D53" t="n">
         <v>1</v>
       </c>
-      <c r="E53" t="inlineStr"/>
+      <c r="E53" t="n">
+        <v>15.4472192513369</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1457,26 +1457,26 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Motto</t>
+          <t>Wow</t>
         </is>
       </c>
       <c r="B55" t="n">
         <v>11</v>
       </c>
       <c r="C55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D55" t="n">
         <v>1</v>
       </c>
       <c r="E55" t="n">
-        <v>15.4472192513369</v>
+        <v>9.494999999999999</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Shoon</t>
+          <t>Brownie</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -1489,13 +1489,13 @@
         <v>2</v>
       </c>
       <c r="E56" t="n">
-        <v>23.68495475113122</v>
+        <v>25.24</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Sandwich</t>
+          <t>Shoon</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -1508,25 +1508,27 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>4.321111111111112</v>
+        <v>23.68495475113122</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>El Charrito</t>
+          <t>Sandwich</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C58" t="n">
         <v>1</v>
       </c>
       <c r="D58" t="n">
-        <v>1</v>
-      </c>
-      <c r="E58" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="E58" t="n">
+        <v>4.321111111111112</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1550,7 +1552,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Flatbread</t>
+          <t>El Charrito</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -1562,37 +1564,35 @@
       <c r="D60" t="n">
         <v>1</v>
       </c>
-      <c r="E60" t="n">
-        <v>23.47111111111111</v>
-      </c>
+      <c r="E60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Chips Ahoy</t>
+          <t>Flatbread</t>
         </is>
       </c>
       <c r="B61" t="n">
         <v>10</v>
       </c>
       <c r="C61" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D61" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E61" t="n">
-        <v>12.98754379814598</v>
+        <v>23.47111111111111</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Siete</t>
+          <t>Chips Ahoy</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C62" t="n">
         <v>2</v>
@@ -1601,13 +1601,13 @@
         <v>2</v>
       </c>
       <c r="E62" t="n">
-        <v>35.46555757535778</v>
+        <v>12.98754379814598</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Wafer</t>
+          <t>Siete</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -1620,32 +1620,32 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>18.59</v>
+        <v>35.46555757535778</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Brownie</t>
+          <t>Wafer</t>
         </is>
       </c>
       <c r="B64" t="n">
         <v>9</v>
       </c>
       <c r="C64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D64" t="n">
         <v>2</v>
       </c>
       <c r="E64" t="n">
-        <v>28.15444444444444</v>
+        <v>18.59</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Brioche</t>
+          <t>Ml</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -1655,16 +1655,16 @@
         <v>1</v>
       </c>
       <c r="D65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E65" t="n">
-        <v>12.44571428571429</v>
+        <v>3.99665153267953</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Ml</t>
+          <t>Brioche</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -1674,10 +1674,10 @@
         <v>1</v>
       </c>
       <c r="D66" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E66" t="n">
-        <v>3.99665153267953</v>
+        <v>12.44571428571429</v>
       </c>
     </row>
     <row r="67">
@@ -1721,7 +1721,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Keebler</t>
+          <t>Avena</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -1731,16 +1731,16 @@
         <v>1</v>
       </c>
       <c r="D69" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E69" t="n">
-        <v>16.16</v>
+        <v>26.45333333333333</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Biskitop</t>
+          <t>Keebler</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -1752,31 +1752,31 @@
       <c r="D70" t="n">
         <v>2</v>
       </c>
-      <c r="E70" t="inlineStr"/>
+      <c r="E70" t="n">
+        <v>16.16</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Croissant</t>
+          <t>Biskitop</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C71" t="n">
         <v>1</v>
       </c>
       <c r="D71" t="n">
-        <v>1</v>
-      </c>
-      <c r="E71" t="n">
-        <v>8.3025</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="E71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Walkers</t>
+          <t>Biscotto</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -1789,13 +1789,13 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>97.43589743589745</v>
+        <v>25</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Nature'S Own</t>
+          <t>Kidsmania</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -1807,14 +1807,12 @@
       <c r="D73" t="n">
         <v>1</v>
       </c>
-      <c r="E73" t="n">
-        <v>7.755714285714285</v>
-      </c>
+      <c r="E73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Golden</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -1824,14 +1822,14 @@
         <v>1</v>
       </c>
       <c r="D74" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Waffer</t>
+          <t>Walkers</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -1841,33 +1839,35 @@
         <v>1</v>
       </c>
       <c r="D75" t="n">
-        <v>1</v>
-      </c>
-      <c r="E75" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="E75" t="n">
+        <v>97.43589743589745</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Hostess</t>
+          <t>Croissant</t>
         </is>
       </c>
       <c r="B76" t="n">
         <v>7</v>
       </c>
       <c r="C76" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D76" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E76" t="n">
-        <v>26.90605746209098</v>
+        <v>8.3025</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Members</t>
+          <t>Festival</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -1877,16 +1877,16 @@
         <v>1</v>
       </c>
       <c r="D77" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>13.74</v>
+        <v>9.385016025641024</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Biscotto</t>
+          <t>Members</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -1899,13 +1899,13 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>25</v>
+        <v>13.74</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Kidsmania</t>
+          <t>Waffer</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -1922,7 +1922,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Festival</t>
+          <t>Trigo</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -1934,56 +1934,54 @@
       <c r="D80" t="n">
         <v>1</v>
       </c>
-      <c r="E80" t="n">
-        <v>9.385016025641024</v>
-      </c>
+      <c r="E80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Barra</t>
+          <t>Nature'S Own</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C81" t="n">
         <v>1</v>
       </c>
       <c r="D81" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E81" t="n">
-        <v>70.74333333333334</v>
+        <v>7.755714285714285</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Cheetos</t>
+          <t>Hostess</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C82" t="n">
         <v>2</v>
       </c>
       <c r="D82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E82" t="n">
-        <v>24.41444882993455</v>
+        <v>26.90605746209098</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Buenhorno</t>
+          <t>Golden</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C83" t="n">
         <v>1</v>
@@ -1991,14 +1989,12 @@
       <c r="D83" t="n">
         <v>2</v>
       </c>
-      <c r="E83" t="n">
-        <v>7.76</v>
-      </c>
+      <c r="E83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Mr Bakewell</t>
+          <t>Kugi</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -2015,7 +2011,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Kugi</t>
+          <t>Ct</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -2025,14 +2021,16 @@
         <v>1</v>
       </c>
       <c r="D85" t="n">
-        <v>1</v>
-      </c>
-      <c r="E85" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E85" t="n">
+        <v>149.3495512238613</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Cadbury</t>
+          <t>Cupcake</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -2042,14 +2040,14 @@
         <v>1</v>
       </c>
       <c r="D86" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Sunshine</t>
+          <t>Schar</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -2059,16 +2057,16 @@
         <v>1</v>
       </c>
       <c r="D87" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>9.488333333333333</v>
+        <v>16.49046051697567</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Cupcake</t>
+          <t>Crich</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -2080,12 +2078,14 @@
       <c r="D88" t="n">
         <v>1</v>
       </c>
-      <c r="E88" t="inlineStr"/>
+      <c r="E88" t="n">
+        <v>10.99166666666667</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Schar</t>
+          <t>Sunshine</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -2095,16 +2095,16 @@
         <v>1</v>
       </c>
       <c r="D89" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E89" t="n">
-        <v>16.49046051697567</v>
+        <v>9.488333333333333</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Ct</t>
+          <t>Otis Spunkmeyer</t>
         </is>
       </c>
       <c r="B90" t="n">
@@ -2114,16 +2114,14 @@
         <v>1</v>
       </c>
       <c r="D90" t="n">
-        <v>3</v>
-      </c>
-      <c r="E90" t="n">
-        <v>149.3495512238613</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="E90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Princesa</t>
+          <t>Laurieri</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -2133,33 +2131,35 @@
         <v>1</v>
       </c>
       <c r="D91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E91" t="n">
-        <v>3.53</v>
+        <v>22.06756380315912</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Tiffany</t>
+          <t>Cheetos</t>
         </is>
       </c>
       <c r="B92" t="n">
         <v>6</v>
       </c>
       <c r="C92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D92" t="n">
         <v>1</v>
       </c>
-      <c r="E92" t="inlineStr"/>
+      <c r="E92" t="n">
+        <v>24.41444882993455</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Crich</t>
+          <t>Cadbury</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -2169,16 +2169,14 @@
         <v>1</v>
       </c>
       <c r="D93" t="n">
-        <v>1</v>
-      </c>
-      <c r="E93" t="n">
-        <v>10.99166666666667</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="E93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Laurieri</t>
+          <t>Buenhorno</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -2191,13 +2189,13 @@
         <v>2</v>
       </c>
       <c r="E94" t="n">
-        <v>22.06756380315912</v>
+        <v>7.76</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Bisco</t>
+          <t>Crav'N</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -2207,16 +2205,16 @@
         <v>1</v>
       </c>
       <c r="D95" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E95" t="n">
-        <v>5.82</v>
+        <v>31.21160437794628</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Oceanix</t>
+          <t>Mr Bakewell</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -2228,14 +2226,12 @@
       <c r="D96" t="n">
         <v>1</v>
       </c>
-      <c r="E96" t="n">
-        <v>10.86333333333334</v>
-      </c>
+      <c r="E96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Crav'N</t>
+          <t>Bisco</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -2245,16 +2241,16 @@
         <v>1</v>
       </c>
       <c r="D97" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E97" t="n">
-        <v>31.21160437794628</v>
+        <v>5.82</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Otis Spunkmeyer</t>
+          <t>Barra</t>
         </is>
       </c>
       <c r="B98" t="n">
@@ -2266,16 +2262,18 @@
       <c r="D98" t="n">
         <v>2</v>
       </c>
-      <c r="E98" t="inlineStr"/>
+      <c r="E98" t="n">
+        <v>70.74333333333334</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Wafers</t>
+          <t>Princesa</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C99" t="n">
         <v>1</v>
@@ -2284,17 +2282,17 @@
         <v>1</v>
       </c>
       <c r="E99" t="n">
-        <v>20.158</v>
+        <v>3.53</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Merba</t>
+          <t>Tiffany</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C100" t="n">
         <v>1</v>
@@ -2307,11 +2305,11 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Stiratini</t>
+          <t>Oceanix</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C101" t="n">
         <v>1</v>
@@ -2320,32 +2318,32 @@
         <v>1</v>
       </c>
       <c r="E101" t="n">
-        <v>17.48729886531608</v>
+        <v>10.86333333333334</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Bagel</t>
+          <t>Wafers</t>
         </is>
       </c>
       <c r="B102" t="n">
         <v>5</v>
       </c>
       <c r="C102" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D102" t="n">
         <v>1</v>
       </c>
       <c r="E102" t="n">
-        <v>15.8445892731972</v>
+        <v>20.158</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Kiss</t>
+          <t>Bagel</t>
         </is>
       </c>
       <c r="B103" t="n">
@@ -2355,16 +2353,16 @@
         <v>2</v>
       </c>
       <c r="D103" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E103" t="n">
-        <v>20.05506545869531</v>
+        <v>15.8445892731972</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Capacillos</t>
+          <t>Muffins</t>
         </is>
       </c>
       <c r="B104" t="n">
@@ -2381,7 +2379,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Muffins</t>
+          <t>Bolletje</t>
         </is>
       </c>
       <c r="B105" t="n">
@@ -2391,14 +2389,16 @@
         <v>1</v>
       </c>
       <c r="D105" t="n">
-        <v>1</v>
-      </c>
-      <c r="E105" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="E105" t="n">
+        <v>30.28979789236276</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Hosttes</t>
+          <t>Hamburguesa</t>
         </is>
       </c>
       <c r="B106" t="n">
@@ -2410,52 +2410,50 @@
       <c r="D106" t="n">
         <v>1</v>
       </c>
-      <c r="E106" t="n">
-        <v>36.83418646645511</v>
-      </c>
+      <c r="E106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Nestle</t>
+          <t>Hosttes</t>
         </is>
       </c>
       <c r="B107" t="n">
         <v>5</v>
       </c>
       <c r="C107" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D107" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E107" t="n">
-        <v>26.25212371338786</v>
+        <v>36.83418646645511</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Bolletje</t>
+          <t>Nestle</t>
         </is>
       </c>
       <c r="B108" t="n">
         <v>5</v>
       </c>
       <c r="C108" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D108" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E108" t="n">
-        <v>30.28979789236276</v>
+        <v>26.25212371338786</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Triskits</t>
+          <t>Capacillos</t>
         </is>
       </c>
       <c r="B109" t="n">
@@ -2472,7 +2470,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>La Libanesa</t>
+          <t>Stiratini</t>
         </is>
       </c>
       <c r="B110" t="n">
@@ -2484,145 +2482,141 @@
       <c r="D110" t="n">
         <v>1</v>
       </c>
-      <c r="E110" t="inlineStr"/>
+      <c r="E110" t="n">
+        <v>17.48729886531608</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Kinder</t>
+          <t>Triskits</t>
         </is>
       </c>
       <c r="B111" t="n">
         <v>5</v>
       </c>
       <c r="C111" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D111" t="n">
-        <v>2</v>
-      </c>
-      <c r="E111" t="n">
-        <v>11.20770469589525</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="E111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Choco</t>
+          <t>Merba</t>
         </is>
       </c>
       <c r="B112" t="n">
         <v>5</v>
       </c>
       <c r="C112" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D112" t="n">
-        <v>2</v>
-      </c>
-      <c r="E112" t="n">
-        <v>18.82562383612663</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="E112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Glutino</t>
+          <t>La Libanesa</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C113" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D113" t="n">
-        <v>3</v>
-      </c>
-      <c r="E113" t="n">
-        <v>23.58912056736007</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="E113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Brownies</t>
+          <t>Choco</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C114" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D114" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E114" t="n">
-        <v>13.575</v>
+        <v>18.82562383612663</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Betty</t>
+          <t>Kiss</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C115" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D115" t="n">
         <v>3</v>
       </c>
       <c r="E115" t="n">
-        <v>25.4104027048499</v>
+        <v>20.05506545869531</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Snyder’S</t>
+          <t>Kinder</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C116" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D116" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E116" t="n">
-        <v>21.8340355175269</v>
+        <v>11.20770469589525</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Florentinas</t>
+          <t>Glutino</t>
         </is>
       </c>
       <c r="B117" t="n">
         <v>4</v>
       </c>
       <c r="C117" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D117" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E117" t="n">
-        <v>12.265</v>
+        <v>23.58912056736007</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Keeber</t>
+          <t>Herrs</t>
         </is>
       </c>
       <c r="B118" t="n">
@@ -2632,35 +2626,35 @@
         <v>1</v>
       </c>
       <c r="D118" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E118" t="n">
-        <v>28.61772083892403</v>
+        <v>37.30902864926393</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>La</t>
+          <t>Snyder’S</t>
         </is>
       </c>
       <c r="B119" t="n">
         <v>4</v>
       </c>
       <c r="C119" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D119" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E119" t="n">
-        <v>14.53743481824682</v>
+        <v>21.8340355175269</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Herrs</t>
+          <t>Cubanas</t>
         </is>
       </c>
       <c r="B120" t="n">
@@ -2673,13 +2667,13 @@
         <v>1</v>
       </c>
       <c r="E120" t="n">
-        <v>37.30902864926393</v>
+        <v>7.470000000000001</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>St</t>
+          <t>Ovaltine</t>
         </is>
       </c>
       <c r="B121" t="n">
@@ -2689,14 +2683,16 @@
         <v>1</v>
       </c>
       <c r="D121" t="n">
-        <v>2</v>
-      </c>
-      <c r="E121" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E121" t="n">
+        <v>19.9445103354795</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Eggo</t>
+          <t>Florentinas</t>
         </is>
       </c>
       <c r="B122" t="n">
@@ -2709,32 +2705,32 @@
         <v>1</v>
       </c>
       <c r="E122" t="n">
-        <v>13.04942618420674</v>
+        <v>12.265</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Betty</t>
         </is>
       </c>
       <c r="B123" t="n">
         <v>4</v>
       </c>
       <c r="C123" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D123" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E123" t="n">
-        <v>39.34</v>
+        <v>25.4104027048499</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Muffin</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="B124" t="n">
@@ -2747,7 +2743,7 @@
         <v>1</v>
       </c>
       <c r="E124" t="n">
-        <v>10.45</v>
+        <v>39.34</v>
       </c>
     </row>
     <row r="125">
@@ -2770,26 +2766,24 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Takis</t>
+          <t>St</t>
         </is>
       </c>
       <c r="B126" t="n">
         <v>4</v>
       </c>
       <c r="C126" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D126" t="n">
         <v>2</v>
       </c>
-      <c r="E126" t="n">
-        <v>41.86</v>
-      </c>
+      <c r="E126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Cubanas</t>
+          <t>Muffin</t>
         </is>
       </c>
       <c r="B127" t="n">
@@ -2802,13 +2796,13 @@
         <v>1</v>
       </c>
       <c r="E127" t="n">
-        <v>7.470000000000001</v>
+        <v>10.45</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Eggo</t>
         </is>
       </c>
       <c r="B128" t="n">
@@ -2821,13 +2815,13 @@
         <v>1</v>
       </c>
       <c r="E128" t="n">
-        <v>25.6825</v>
+        <v>13.04942618420674</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Ovaltine</t>
+          <t>Keeber</t>
         </is>
       </c>
       <c r="B129" t="n">
@@ -2837,16 +2831,16 @@
         <v>1</v>
       </c>
       <c r="D129" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E129" t="n">
-        <v>19.9445103354795</v>
+        <v>28.61772083892403</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Dulcesol</t>
+          <t>Brownies</t>
         </is>
       </c>
       <c r="B130" t="n">
@@ -2859,17 +2853,17 @@
         <v>1</v>
       </c>
       <c r="E130" t="n">
-        <v>6.916666666666667</v>
+        <v>13.575</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Biscuit</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C131" t="n">
         <v>1</v>
@@ -2878,49 +2872,51 @@
         <v>1</v>
       </c>
       <c r="E131" t="n">
-        <v>20.18666666666667</v>
+        <v>25.6825</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Each</t>
+          <t>Dulcesol</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C132" t="n">
         <v>1</v>
       </c>
       <c r="D132" t="n">
-        <v>2</v>
-      </c>
-      <c r="E132" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E132" t="n">
+        <v>6.916666666666667</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Vigo</t>
+          <t>Takis</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C133" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D133" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E133" t="n">
-        <v>10.95246106181043</v>
+        <v>41.86</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Chocolate</t>
+          <t>Pizkas</t>
         </is>
       </c>
       <c r="B134" t="n">
@@ -2933,13 +2929,13 @@
         <v>1</v>
       </c>
       <c r="E134" t="n">
-        <v>15.33333333333333</v>
+        <v>4.146666666666667</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Nachos</t>
+          <t>Parreiro</t>
         </is>
       </c>
       <c r="B135" t="n">
@@ -2949,11 +2945,9 @@
         <v>1</v>
       </c>
       <c r="D135" t="n">
-        <v>1</v>
-      </c>
-      <c r="E135" t="n">
-        <v>5.466666666666666</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="E135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -2975,7 +2969,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Crix</t>
+          <t>Rm</t>
         </is>
       </c>
       <c r="B137" t="n">
@@ -2988,13 +2982,13 @@
         <v>1</v>
       </c>
       <c r="E137" t="n">
-        <v>7.160318629656713</v>
+        <v>19.81009679333702</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Sweet</t>
+          <t>Hamburguesas</t>
         </is>
       </c>
       <c r="B138" t="n">
@@ -3011,7 +3005,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Creamy</t>
+          <t>Pirucream</t>
         </is>
       </c>
       <c r="B139" t="n">
@@ -3021,14 +3015,16 @@
         <v>1</v>
       </c>
       <c r="D139" t="n">
-        <v>1</v>
-      </c>
-      <c r="E139" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="E139" t="n">
+        <v>11.47982243202111</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Parreiro</t>
+          <t>Nachos</t>
         </is>
       </c>
       <c r="B140" t="n">
@@ -3038,14 +3034,16 @@
         <v>1</v>
       </c>
       <c r="D140" t="n">
-        <v>2</v>
-      </c>
-      <c r="E140" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E140" t="n">
+        <v>5.466666666666666</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Wraps</t>
+          <t>Mantequilla</t>
         </is>
       </c>
       <c r="B141" t="n">
@@ -3058,7 +3056,7 @@
         <v>1</v>
       </c>
       <c r="E141" t="n">
-        <v>12.46588389137416</v>
+        <v>24.61</v>
       </c>
     </row>
     <row r="142">
@@ -3083,7 +3081,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Pizkas</t>
+          <t>Mars</t>
         </is>
       </c>
       <c r="B143" t="n">
@@ -3095,14 +3093,12 @@
       <c r="D143" t="n">
         <v>1</v>
       </c>
-      <c r="E143" t="n">
-        <v>4.146666666666667</v>
-      </c>
+      <c r="E143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Confetti</t>
+          <t>Helado</t>
         </is>
       </c>
       <c r="B144" t="n">
@@ -3119,7 +3115,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Werther’S</t>
+          <t>Flourish</t>
         </is>
       </c>
       <c r="B145" t="n">
@@ -3129,14 +3125,14 @@
         <v>1</v>
       </c>
       <c r="D145" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Rm</t>
+          <t>Verkade</t>
         </is>
       </c>
       <c r="B146" t="n">
@@ -3149,13 +3145,13 @@
         <v>1</v>
       </c>
       <c r="E146" t="n">
-        <v>19.81009679333702</v>
+        <v>18.10203109436577</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Verkade</t>
+          <t>Vigo</t>
         </is>
       </c>
       <c r="B147" t="n">
@@ -3168,13 +3164,13 @@
         <v>1</v>
       </c>
       <c r="E147" t="n">
-        <v>18.10203109436577</v>
+        <v>10.95246106181043</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Chetos</t>
+          <t>Cuetara</t>
         </is>
       </c>
       <c r="B148" t="n">
@@ -3186,12 +3182,14 @@
       <c r="D148" t="n">
         <v>1</v>
       </c>
-      <c r="E148" t="inlineStr"/>
+      <c r="E148" t="n">
+        <v>9.51</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Bonus</t>
+          <t>Sweet</t>
         </is>
       </c>
       <c r="B149" t="n">
@@ -3203,14 +3201,12 @@
       <c r="D149" t="n">
         <v>1</v>
       </c>
-      <c r="E149" t="n">
-        <v>10.17319787781675</v>
-      </c>
+      <c r="E149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Helado</t>
+          <t>Creamy</t>
         </is>
       </c>
       <c r="B150" t="n">
@@ -3227,7 +3223,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Cuetara</t>
+          <t>Confetti</t>
         </is>
       </c>
       <c r="B151" t="n">
@@ -3239,14 +3235,12 @@
       <c r="D151" t="n">
         <v>1</v>
       </c>
-      <c r="E151" t="n">
-        <v>9.51</v>
-      </c>
+      <c r="E151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Tuc</t>
+          <t>Chetos</t>
         </is>
       </c>
       <c r="B152" t="n">
@@ -3256,16 +3250,14 @@
         <v>1</v>
       </c>
       <c r="D152" t="n">
-        <v>2</v>
-      </c>
-      <c r="E152" t="n">
-        <v>12.76631956599985</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="E152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Dux</t>
+          <t>Del-E</t>
         </is>
       </c>
       <c r="B153" t="n">
@@ -3275,14 +3267,14 @@
         <v>1</v>
       </c>
       <c r="D153" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Flourish</t>
+          <t>Tuc</t>
         </is>
       </c>
       <c r="B154" t="n">
@@ -3292,9 +3284,11 @@
         <v>1</v>
       </c>
       <c r="D154" t="n">
-        <v>1</v>
-      </c>
-      <c r="E154" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="E154" t="n">
+        <v>12.76631956599985</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -3318,7 +3312,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Van Der Meulen</t>
+          <t>Caramelo</t>
         </is>
       </c>
       <c r="B156" t="n">
@@ -3331,13 +3325,13 @@
         <v>1</v>
       </c>
       <c r="E156" t="n">
-        <v>11.04698425260689</v>
+        <v>12.14333333333333</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Snyders</t>
+          <t>Van Der Meulen</t>
         </is>
       </c>
       <c r="B157" t="n">
@@ -3349,31 +3343,33 @@
       <c r="D157" t="n">
         <v>1</v>
       </c>
-      <c r="E157" t="inlineStr"/>
+      <c r="E157" t="n">
+        <v>11.04698425260689</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Frito</t>
+          <t>Bonus</t>
         </is>
       </c>
       <c r="B158" t="n">
         <v>3</v>
       </c>
       <c r="C158" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D158" t="n">
         <v>1</v>
       </c>
       <c r="E158" t="n">
-        <v>26.12234903090436</v>
+        <v>10.17319787781675</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Mars</t>
+          <t>Dux</t>
         </is>
       </c>
       <c r="B159" t="n">
@@ -3390,7 +3386,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Pirucream</t>
+          <t>Each</t>
         </is>
       </c>
       <c r="B160" t="n">
@@ -3402,14 +3398,12 @@
       <c r="D160" t="n">
         <v>2</v>
       </c>
-      <c r="E160" t="n">
-        <v>11.47982243202111</v>
-      </c>
+      <c r="E160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Trigo</t>
+          <t>Biscuit</t>
         </is>
       </c>
       <c r="B161" t="n">
@@ -3421,12 +3415,14 @@
       <c r="D161" t="n">
         <v>1</v>
       </c>
-      <c r="E161" t="inlineStr"/>
+      <c r="E161" t="n">
+        <v>20.18666666666667</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Del-E</t>
+          <t>Crix</t>
         </is>
       </c>
       <c r="B162" t="n">
@@ -3436,14 +3432,16 @@
         <v>1</v>
       </c>
       <c r="D162" t="n">
-        <v>2</v>
-      </c>
-      <c r="E162" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E162" t="n">
+        <v>7.160318629656713</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Wala</t>
+          <t>Snyders</t>
         </is>
       </c>
       <c r="B163" t="n">
@@ -3453,16 +3451,14 @@
         <v>1</v>
       </c>
       <c r="D163" t="n">
-        <v>2</v>
-      </c>
-      <c r="E163" t="n">
-        <v>5.32</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="E163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Waitrose</t>
+          <t>Soda</t>
         </is>
       </c>
       <c r="B164" t="n">
@@ -3472,18 +3468,20 @@
         <v>1</v>
       </c>
       <c r="D164" t="n">
-        <v>2</v>
-      </c>
-      <c r="E164" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E164" t="n">
+        <v>3.923333333333333</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Qiin</t>
+          <t>Wraps</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C165" t="n">
         <v>1</v>
@@ -3491,126 +3489,124 @@
       <c r="D165" t="n">
         <v>1</v>
       </c>
-      <c r="E165" t="inlineStr"/>
+      <c r="E165" t="n">
+        <v>12.46588389137416</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Wheat</t>
+          <t>Waitrose</t>
         </is>
       </c>
       <c r="B166" t="n">
+        <v>3</v>
+      </c>
+      <c r="C166" t="n">
+        <v>1</v>
+      </c>
+      <c r="D166" t="n">
         <v>2</v>
       </c>
-      <c r="C166" t="n">
-        <v>1</v>
-      </c>
-      <c r="D166" t="n">
-        <v>1</v>
-      </c>
-      <c r="E166" t="n">
-        <v>8.939329149136723</v>
-      </c>
+      <c r="E166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Pirulin</t>
+          <t>Werther’S</t>
         </is>
       </c>
       <c r="B167" t="n">
+        <v>3</v>
+      </c>
+      <c r="C167" t="n">
+        <v>1</v>
+      </c>
+      <c r="D167" t="n">
         <v>2</v>
       </c>
-      <c r="C167" t="n">
-        <v>1</v>
-      </c>
-      <c r="D167" t="n">
-        <v>1</v>
-      </c>
-      <c r="E167" t="n">
-        <v>11.60394936174618</v>
-      </c>
+      <c r="E167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Oscar Mayer</t>
+          <t>Frito</t>
         </is>
       </c>
       <c r="B168" t="n">
+        <v>3</v>
+      </c>
+      <c r="C168" t="n">
         <v>2</v>
       </c>
-      <c r="C168" t="n">
-        <v>1</v>
-      </c>
       <c r="D168" t="n">
         <v>1</v>
       </c>
       <c r="E168" t="n">
-        <v>22.51260705995357</v>
+        <v>26.12234903090436</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Pico</t>
+          <t>Wala</t>
         </is>
       </c>
       <c r="B169" t="n">
+        <v>3</v>
+      </c>
+      <c r="C169" t="n">
+        <v>1</v>
+      </c>
+      <c r="D169" t="n">
         <v>2</v>
       </c>
-      <c r="C169" t="n">
-        <v>1</v>
-      </c>
-      <c r="D169" t="n">
-        <v>1</v>
-      </c>
       <c r="E169" t="n">
-        <v>21.08728168019017</v>
+        <v>5.32</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Milka</t>
+          <t>Ajo</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C170" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D170" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E170" t="n">
-        <v>35.09695158172114</v>
+        <v>9.973333333333333</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Badia</t>
+          <t>Chobani</t>
         </is>
       </c>
       <c r="B171" t="n">
         <v>2</v>
       </c>
       <c r="C171" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D171" t="n">
         <v>1</v>
       </c>
       <c r="E171" t="n">
-        <v>29.48883103134886</v>
+        <v>17.1627724813966</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Moulind</t>
+          <t>Town</t>
         </is>
       </c>
       <c r="B172" t="n">
@@ -3623,13 +3619,13 @@
         <v>1</v>
       </c>
       <c r="E172" t="n">
-        <v>3.8</v>
+        <v>18.76376695929768</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Willie</t>
+          <t>Pirulin</t>
         </is>
       </c>
       <c r="B173" t="n">
@@ -3641,12 +3637,14 @@
       <c r="D173" t="n">
         <v>1</v>
       </c>
-      <c r="E173" t="inlineStr"/>
+      <c r="E173" t="n">
+        <v>11.60394936174618</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Nutella</t>
+          <t>Cole´s</t>
         </is>
       </c>
       <c r="B174" t="n">
@@ -3659,13 +3657,13 @@
         <v>1</v>
       </c>
       <c r="E174" t="n">
-        <v>14.10705314828377</v>
+        <v>21.94025264317509</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Lago</t>
+          <t>Barrel</t>
         </is>
       </c>
       <c r="B175" t="n">
@@ -3678,13 +3676,13 @@
         <v>1</v>
       </c>
       <c r="E175" t="n">
-        <v>13.945</v>
+        <v>32.87901755235749</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Napolitanas</t>
+          <t>Willie</t>
         </is>
       </c>
       <c r="B176" t="n">
@@ -3701,7 +3699,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Leche</t>
+          <t>Libanesa</t>
         </is>
       </c>
       <c r="B177" t="n">
@@ -3718,7 +3716,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Pillsbury</t>
+          <t>Papa</t>
         </is>
       </c>
       <c r="B178" t="n">
@@ -3731,13 +3729,13 @@
         <v>1</v>
       </c>
       <c r="E178" t="n">
-        <v>8.24</v>
+        <v>9.030000000000001</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Martin</t>
+          <t>Qiin</t>
         </is>
       </c>
       <c r="B179" t="n">
@@ -3749,14 +3747,12 @@
       <c r="D179" t="n">
         <v>1</v>
       </c>
-      <c r="E179" t="n">
-        <v>20.065</v>
-      </c>
+      <c r="E179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Beivita</t>
+          <t>Oscar Mayer</t>
         </is>
       </c>
       <c r="B180" t="n">
@@ -3769,13 +3765,13 @@
         <v>1</v>
       </c>
       <c r="E180" t="n">
-        <v>35.19230769230769</v>
+        <v>22.51260705995357</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Barrel</t>
+          <t>Lago</t>
         </is>
       </c>
       <c r="B181" t="n">
@@ -3788,13 +3784,13 @@
         <v>1</v>
       </c>
       <c r="E181" t="n">
-        <v>32.87901755235749</v>
+        <v>13.945</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Voortman</t>
+          <t>Martin</t>
         </is>
       </c>
       <c r="B182" t="n">
@@ -3807,13 +3803,13 @@
         <v>1</v>
       </c>
       <c r="E182" t="n">
-        <v>20.17345399698341</v>
+        <v>20.065</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>La Tortilla Factory</t>
+          <t>Wheat</t>
         </is>
       </c>
       <c r="B183" t="n">
@@ -3826,13 +3822,13 @@
         <v>1</v>
       </c>
       <c r="E183" t="n">
-        <v>21.71</v>
+        <v>8.939329149136723</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Sara Lee</t>
+          <t>Pillsbury</t>
         </is>
       </c>
       <c r="B184" t="n">
@@ -3845,13 +3841,13 @@
         <v>1</v>
       </c>
       <c r="E184" t="n">
-        <v>24.085</v>
+        <v>8.24</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Duo</t>
+          <t>Cheez</t>
         </is>
       </c>
       <c r="B185" t="n">
@@ -3868,7 +3864,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Chobani</t>
+          <t>Voortman</t>
         </is>
       </c>
       <c r="B186" t="n">
@@ -3881,13 +3877,13 @@
         <v>1</v>
       </c>
       <c r="E186" t="n">
-        <v>17.1627724813966</v>
+        <v>20.17345399698341</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Danesa</t>
+          <t>Pico</t>
         </is>
       </c>
       <c r="B187" t="n">
@@ -3900,30 +3896,32 @@
         <v>1</v>
       </c>
       <c r="E187" t="n">
-        <v>20.48</v>
+        <v>21.08728168019017</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Dairy</t>
+          <t>Milka</t>
         </is>
       </c>
       <c r="B188" t="n">
         <v>2</v>
       </c>
       <c r="C188" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D188" t="n">
-        <v>1</v>
-      </c>
-      <c r="E188" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="E188" t="n">
+        <v>35.09695158172114</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Dried</t>
+          <t>Moulind</t>
         </is>
       </c>
       <c r="B189" t="n">
@@ -3933,14 +3931,16 @@
         <v>1</v>
       </c>
       <c r="D189" t="n">
-        <v>2</v>
-      </c>
-      <c r="E189" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E189" t="n">
+        <v>3.8</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Cup</t>
+          <t>La Tortilla Factory</t>
         </is>
       </c>
       <c r="B190" t="n">
@@ -3953,13 +3953,13 @@
         <v>1</v>
       </c>
       <c r="E190" t="n">
-        <v>17.855</v>
+        <v>21.71</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Dulce</t>
+          <t>Nutella</t>
         </is>
       </c>
       <c r="B191" t="n">
@@ -3972,13 +3972,13 @@
         <v>1</v>
       </c>
       <c r="E191" t="n">
-        <v>11.635</v>
+        <v>14.10705314828377</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Knotts</t>
+          <t>Noni</t>
         </is>
       </c>
       <c r="B192" t="n">
@@ -3990,31 +3990,33 @@
       <c r="D192" t="n">
         <v>1</v>
       </c>
-      <c r="E192" t="inlineStr"/>
+      <c r="E192" t="n">
+        <v>3.96</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Feiny</t>
+          <t>Badia</t>
         </is>
       </c>
       <c r="B193" t="n">
         <v>2</v>
       </c>
       <c r="C193" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D193" t="n">
         <v>1</v>
       </c>
       <c r="E193" t="n">
-        <v>12.93854748603352</v>
+        <v>29.48883103134886</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Crunchmaster</t>
+          <t>Napolitanas</t>
         </is>
       </c>
       <c r="B194" t="n">
@@ -4026,14 +4028,12 @@
       <c r="D194" t="n">
         <v>1</v>
       </c>
-      <c r="E194" t="n">
-        <v>36.45078004731464</v>
-      </c>
+      <c r="E194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Cheez</t>
+          <t>Beivita</t>
         </is>
       </c>
       <c r="B195" t="n">
@@ -4045,31 +4045,33 @@
       <c r="D195" t="n">
         <v>1</v>
       </c>
-      <c r="E195" t="inlineStr"/>
+      <c r="E195" t="n">
+        <v>35.19230769230769</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Gerber</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="B196" t="n">
         <v>2</v>
       </c>
       <c r="C196" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D196" t="n">
         <v>1</v>
       </c>
       <c r="E196" t="n">
-        <v>19.6076093683384</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Glad</t>
+          <t>Leche</t>
         </is>
       </c>
       <c r="B197" t="n">
@@ -4086,7 +4088,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Haagen Daz</t>
+          <t>Dairy</t>
         </is>
       </c>
       <c r="B198" t="n">
@@ -4103,7 +4105,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Helados</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="B199" t="n">
@@ -4116,13 +4118,13 @@
         <v>1</v>
       </c>
       <c r="E199" t="n">
-        <v>14.575</v>
+        <v>14.39369043706868</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Hills</t>
         </is>
       </c>
       <c r="B200" t="n">
@@ -4134,9 +4136,7 @@
       <c r="D200" t="n">
         <v>1</v>
       </c>
-      <c r="E200" t="n">
-        <v>2.06</v>
-      </c>
+      <c r="E200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -4158,7 +4158,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Sabor</t>
+          <t>Sara Lee</t>
         </is>
       </c>
       <c r="B202" t="n">
@@ -4170,12 +4170,14 @@
       <c r="D202" t="n">
         <v>1</v>
       </c>
-      <c r="E202" t="inlineStr"/>
+      <c r="E202" t="n">
+        <v>24.085</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Hills</t>
+          <t>Dulcerita</t>
         </is>
       </c>
       <c r="B203" t="n">
@@ -4185,14 +4187,16 @@
         <v>1</v>
       </c>
       <c r="D203" t="n">
-        <v>1</v>
-      </c>
-      <c r="E203" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="E203" t="n">
+        <v>14.53743481824682</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Ready</t>
+          <t>Helados</t>
         </is>
       </c>
       <c r="B204" t="n">
@@ -4204,12 +4208,14 @@
       <c r="D204" t="n">
         <v>1</v>
       </c>
-      <c r="E204" t="inlineStr"/>
+      <c r="E204" t="n">
+        <v>14.575</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Town</t>
+          <t>Feiny</t>
         </is>
       </c>
       <c r="B205" t="n">
@@ -4222,13 +4228,13 @@
         <v>1</v>
       </c>
       <c r="E205" t="n">
-        <v>18.76376695929768</v>
+        <v>12.93854748603352</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Hinged</t>
+          <t>Sabor</t>
         </is>
       </c>
       <c r="B206" t="n">
@@ -4240,33 +4246,31 @@
       <c r="D206" t="n">
         <v>1</v>
       </c>
-      <c r="E206" t="n">
-        <v>1.907848055928269</v>
-      </c>
+      <c r="E206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Cole´s</t>
+          <t>Gerber</t>
         </is>
       </c>
       <c r="B207" t="n">
         <v>2</v>
       </c>
       <c r="C207" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D207" t="n">
         <v>1</v>
       </c>
       <c r="E207" t="n">
-        <v>21.94025264317509</v>
+        <v>19.6076093683384</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Danesa</t>
         </is>
       </c>
       <c r="B208" t="n">
@@ -4279,36 +4283,34 @@
         <v>1</v>
       </c>
       <c r="E208" t="n">
-        <v>14.39369043706868</v>
+        <v>20.48</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Triple</t>
+          <t>Dried</t>
         </is>
       </c>
       <c r="B209" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C209" t="n">
         <v>1</v>
       </c>
       <c r="D209" t="n">
-        <v>1</v>
-      </c>
-      <c r="E209" t="n">
-        <v>16.69444696384553</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="E209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Suiker</t>
+          <t>Haagen Daz</t>
         </is>
       </c>
       <c r="B210" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C210" t="n">
         <v>1</v>
@@ -4321,11 +4323,11 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Palacios</t>
+          <t>Knotts</t>
         </is>
       </c>
       <c r="B211" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C211" t="n">
         <v>1</v>
@@ -4333,18 +4335,16 @@
       <c r="D211" t="n">
         <v>1</v>
       </c>
-      <c r="E211" t="n">
-        <v>9.029999999999999</v>
-      </c>
+      <c r="E211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Tony</t>
+          <t>Crunchmaster</t>
         </is>
       </c>
       <c r="B212" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C212" t="n">
         <v>1</v>
@@ -4353,17 +4353,17 @@
         <v>1</v>
       </c>
       <c r="E212" t="n">
-        <v>101.8849369508442</v>
+        <v>36.45078004731464</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Paleta</t>
+          <t>Duo</t>
         </is>
       </c>
       <c r="B213" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C213" t="n">
         <v>1</v>
@@ -4376,11 +4376,11 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Toblerone</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="B214" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C214" t="n">
         <v>1</v>
@@ -4388,18 +4388,16 @@
       <c r="D214" t="n">
         <v>1</v>
       </c>
-      <c r="E214" t="n">
-        <v>16.06966809069997</v>
-      </c>
+      <c r="E214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Papagena</t>
+          <t>Glad</t>
         </is>
       </c>
       <c r="B215" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C215" t="n">
         <v>1</v>
@@ -4407,18 +4405,16 @@
       <c r="D215" t="n">
         <v>1</v>
       </c>
-      <c r="E215" t="n">
-        <v>30.69522036002483</v>
-      </c>
+      <c r="E215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Pcs</t>
+          <t>Dulce</t>
         </is>
       </c>
       <c r="B216" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C216" t="n">
         <v>1</v>
@@ -4426,16 +4422,18 @@
       <c r="D216" t="n">
         <v>1</v>
       </c>
-      <c r="E216" t="inlineStr"/>
+      <c r="E216" t="n">
+        <v>11.635</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Toast'Em</t>
+          <t>Cup</t>
         </is>
       </c>
       <c r="B217" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C217" t="n">
         <v>1</v>
@@ -4444,17 +4442,17 @@
         <v>1</v>
       </c>
       <c r="E217" t="n">
-        <v>7.369275296517468</v>
+        <v>17.855</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Sweetarts</t>
+          <t>Hinged</t>
         </is>
       </c>
       <c r="B218" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C218" t="n">
         <v>1</v>
@@ -4462,12 +4460,14 @@
       <c r="D218" t="n">
         <v>1</v>
       </c>
-      <c r="E218" t="inlineStr"/>
+      <c r="E218" t="n">
+        <v>1.907848055928269</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Pasta</t>
+          <t>Ruffles</t>
         </is>
       </c>
       <c r="B219" t="n">
@@ -4480,13 +4480,13 @@
         <v>1</v>
       </c>
       <c r="E219" t="n">
-        <v>53.49353332823143</v>
+        <v>20.12215858124287</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Taco</t>
+          <t>Santitas</t>
         </is>
       </c>
       <c r="B220" t="n">
@@ -4499,13 +4499,13 @@
         <v>1</v>
       </c>
       <c r="E220" t="n">
-        <v>5.52</v>
+        <v>23.62766194234949</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Tex</t>
+          <t>Pcs</t>
         </is>
       </c>
       <c r="B221" t="n">
@@ -4517,14 +4517,12 @@
       <c r="D221" t="n">
         <v>1</v>
       </c>
-      <c r="E221" t="n">
-        <v>9.264432029795158</v>
-      </c>
+      <c r="E221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Tn</t>
+          <t>Sustituto</t>
         </is>
       </c>
       <c r="B222" t="n">
@@ -4537,13 +4535,13 @@
         <v>1</v>
       </c>
       <c r="E222" t="n">
-        <v>27.87709497206704</v>
+        <v>53.09</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Sugar</t>
+          <t>Pasta</t>
         </is>
       </c>
       <c r="B223" t="n">
@@ -4555,12 +4553,14 @@
       <c r="D223" t="n">
         <v>1</v>
       </c>
-      <c r="E223" t="inlineStr"/>
+      <c r="E223" t="n">
+        <v>53.49353332823143</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Triscuit</t>
+          <t>Sazon</t>
         </is>
       </c>
       <c r="B224" t="n">
@@ -4573,13 +4573,13 @@
         <v>1</v>
       </c>
       <c r="E224" t="n">
-        <v>15.39664804469274</v>
+        <v>38.92</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Sustituto</t>
+          <t>Sponge</t>
         </is>
       </c>
       <c r="B225" t="n">
@@ -4591,14 +4591,12 @@
       <c r="D225" t="n">
         <v>1</v>
       </c>
-      <c r="E225" t="n">
-        <v>53.09</v>
-      </c>
+      <c r="E225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Rb</t>
+          <t>Spekkoek</t>
         </is>
       </c>
       <c r="B226" t="n">
@@ -4611,13 +4609,13 @@
         <v>1</v>
       </c>
       <c r="E226" t="n">
-        <v>31.81173473818277</v>
+        <v>37.62485187066193</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Twix</t>
+          <t>Soldanza</t>
         </is>
       </c>
       <c r="B227" t="n">
@@ -4629,14 +4627,12 @@
       <c r="D227" t="n">
         <v>1</v>
       </c>
-      <c r="E227" t="n">
-        <v>33.86584998558232</v>
-      </c>
+      <c r="E227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Smaakt</t>
+          <t>Scrocchi</t>
         </is>
       </c>
       <c r="B228" t="n">
@@ -4649,13 +4645,13 @@
         <v>1</v>
       </c>
       <c r="E228" t="n">
-        <v>50.39141531848635</v>
+        <v>14.05586592178771</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Papagena</t>
         </is>
       </c>
       <c r="B229" t="n">
@@ -4668,13 +4664,13 @@
         <v>1</v>
       </c>
       <c r="E229" t="n">
-        <v>20.44890996357828</v>
+        <v>30.69522036002483</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Relleno</t>
+          <t>Snickers</t>
         </is>
       </c>
       <c r="B230" t="n">
@@ -4687,13 +4683,13 @@
         <v>1</v>
       </c>
       <c r="E230" t="n">
-        <v>9.779999999999999</v>
+        <v>40.99</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Reynolds</t>
+          <t>Paleta</t>
         </is>
       </c>
       <c r="B231" t="n">
@@ -4710,7 +4706,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Ricola</t>
+          <t>Snapd</t>
         </is>
       </c>
       <c r="B232" t="n">
@@ -4723,13 +4719,13 @@
         <v>1</v>
       </c>
       <c r="E232" t="n">
-        <v>7.351955307262569</v>
+        <v>21.61</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Roll</t>
+          <t>Palacios</t>
         </is>
       </c>
       <c r="B233" t="n">
@@ -4741,12 +4737,14 @@
       <c r="D233" t="n">
         <v>1</v>
       </c>
-      <c r="E233" t="inlineStr"/>
+      <c r="E233" t="n">
+        <v>9.029999999999999</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Ruffles</t>
+          <t>Vegetarian</t>
         </is>
       </c>
       <c r="B234" t="n">
@@ -4758,14 +4756,12 @@
       <c r="D234" t="n">
         <v>1</v>
       </c>
-      <c r="E234" t="n">
-        <v>20.12215858124287</v>
-      </c>
+      <c r="E234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Vegetarian</t>
+          <t>Twizzlers</t>
         </is>
       </c>
       <c r="B235" t="n">
@@ -4782,7 +4778,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Santitas</t>
+          <t>Vegefarm</t>
         </is>
       </c>
       <c r="B236" t="n">
@@ -4795,13 +4791,13 @@
         <v>1</v>
       </c>
       <c r="E236" t="n">
-        <v>23.62766194234949</v>
+        <v>27.42714334124026</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Sazon</t>
+          <t>Relleno</t>
         </is>
       </c>
       <c r="B237" t="n">
@@ -4814,13 +4810,13 @@
         <v>1</v>
       </c>
       <c r="E237" t="n">
-        <v>38.92</v>
+        <v>9.779999999999999</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Scrocchi</t>
+          <t>Rb</t>
         </is>
       </c>
       <c r="B238" t="n">
@@ -4833,13 +4829,13 @@
         <v>1</v>
       </c>
       <c r="E238" t="n">
-        <v>14.05586592178771</v>
+        <v>31.81173473818277</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Pint</t>
+          <t>Sweetarts</t>
         </is>
       </c>
       <c r="B239" t="n">
@@ -4856,7 +4852,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Twizzlers</t>
+          <t>Smaakt</t>
         </is>
       </c>
       <c r="B240" t="n">
@@ -4868,12 +4864,14 @@
       <c r="D240" t="n">
         <v>1</v>
       </c>
-      <c r="E240" t="inlineStr"/>
+      <c r="E240" t="n">
+        <v>50.39141531848635</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Snapd</t>
+          <t>Proteina</t>
         </is>
       </c>
       <c r="B241" t="n">
@@ -4886,13 +4884,13 @@
         <v>1</v>
       </c>
       <c r="E241" t="n">
-        <v>21.61</v>
+        <v>49.31</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Pin</t>
+          <t>Taco</t>
         </is>
       </c>
       <c r="B242" t="n">
@@ -4904,12 +4902,14 @@
       <c r="D242" t="n">
         <v>1</v>
       </c>
-      <c r="E242" t="inlineStr"/>
+      <c r="E242" t="n">
+        <v>5.52</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Snickers</t>
+          <t>Tex</t>
         </is>
       </c>
       <c r="B243" t="n">
@@ -4922,13 +4922,13 @@
         <v>1</v>
       </c>
       <c r="E243" t="n">
-        <v>40.99</v>
+        <v>9.264432029795158</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Vegefarm</t>
+          <t>Suiker</t>
         </is>
       </c>
       <c r="B244" t="n">
@@ -4940,14 +4940,12 @@
       <c r="D244" t="n">
         <v>1</v>
       </c>
-      <c r="E244" t="n">
-        <v>27.42714334124026</v>
-      </c>
+      <c r="E244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Soldanza</t>
+          <t>Tn</t>
         </is>
       </c>
       <c r="B245" t="n">
@@ -4959,12 +4957,14 @@
       <c r="D245" t="n">
         <v>1</v>
       </c>
-      <c r="E245" t="inlineStr"/>
+      <c r="E245" t="n">
+        <v>27.87709497206704</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Spekkoek</t>
+          <t>Toast'Em</t>
         </is>
       </c>
       <c r="B246" t="n">
@@ -4977,13 +4977,13 @@
         <v>1</v>
       </c>
       <c r="E246" t="n">
-        <v>37.62485187066193</v>
+        <v>7.369275296517468</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Sponge</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="B247" t="n">
@@ -4995,12 +4995,14 @@
       <c r="D247" t="n">
         <v>1</v>
       </c>
-      <c r="E247" t="inlineStr"/>
+      <c r="E247" t="n">
+        <v>20.44890996357828</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Udis</t>
+          <t>Toblerone</t>
         </is>
       </c>
       <c r="B248" t="n">
@@ -5013,13 +5015,13 @@
         <v>1</v>
       </c>
       <c r="E248" t="n">
-        <v>8.562317859842246</v>
+        <v>16.06966809069997</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Stuk</t>
+          <t>Tony</t>
         </is>
       </c>
       <c r="B249" t="n">
@@ -5032,13 +5034,13 @@
         <v>1</v>
       </c>
       <c r="E249" t="n">
-        <v>24.46954478727046</v>
+        <v>101.8849369508442</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Stuks</t>
+          <t>Stuk</t>
         </is>
       </c>
       <c r="B250" t="n">
@@ -5050,12 +5052,14 @@
       <c r="D250" t="n">
         <v>1</v>
       </c>
-      <c r="E250" t="inlineStr"/>
+      <c r="E250" t="n">
+        <v>24.46954478727046</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>Reynolds</t>
         </is>
       </c>
       <c r="B251" t="n">
@@ -5072,7 +5076,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Kimberley's Bakeshoppe</t>
+          <t>Pint</t>
         </is>
       </c>
       <c r="B252" t="n">
@@ -5089,7 +5093,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Otis</t>
+          <t>Triple</t>
         </is>
       </c>
       <c r="B253" t="n">
@@ -5101,12 +5105,14 @@
       <c r="D253" t="n">
         <v>1</v>
       </c>
-      <c r="E253" t="inlineStr"/>
+      <c r="E253" t="n">
+        <v>16.69444696384553</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Oscar</t>
+          <t>Ricola</t>
         </is>
       </c>
       <c r="B254" t="n">
@@ -5119,13 +5125,13 @@
         <v>1</v>
       </c>
       <c r="E254" t="n">
-        <v>18.54852276596928</v>
+        <v>7.351955307262569</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Chiney</t>
+          <t>Pin</t>
         </is>
       </c>
       <c r="B255" t="n">
@@ -5142,7 +5148,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Cho Cho</t>
+          <t>Triscuit</t>
         </is>
       </c>
       <c r="B256" t="n">
@@ -5154,12 +5160,14 @@
       <c r="D256" t="n">
         <v>1</v>
       </c>
-      <c r="E256" t="inlineStr"/>
+      <c r="E256" t="n">
+        <v>15.39664804469274</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Chokis</t>
+          <t>Sugar</t>
         </is>
       </c>
       <c r="B257" t="n">
@@ -5171,14 +5179,12 @@
       <c r="D257" t="n">
         <v>1</v>
       </c>
-      <c r="E257" t="n">
-        <v>11.44</v>
-      </c>
+      <c r="E257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Choppers</t>
+          <t>Stuks</t>
         </is>
       </c>
       <c r="B258" t="n">
@@ -5195,7 +5201,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Chowmein</t>
+          <t>Roll</t>
         </is>
       </c>
       <c r="B259" t="n">
@@ -5212,7 +5218,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Cilantro</t>
+          <t>Twix</t>
         </is>
       </c>
       <c r="B260" t="n">
@@ -5224,12 +5230,14 @@
       <c r="D260" t="n">
         <v>1</v>
       </c>
-      <c r="E260" t="inlineStr"/>
+      <c r="E260" t="n">
+        <v>33.86584998558232</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Cloverhill</t>
+          <t>Udis</t>
         </is>
       </c>
       <c r="B261" t="n">
@@ -5241,12 +5249,14 @@
       <c r="D261" t="n">
         <v>1</v>
       </c>
-      <c r="E261" t="inlineStr"/>
+      <c r="E261" t="n">
+        <v>8.562317859842246</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>Coffee</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="B262" t="n">
@@ -5258,14 +5268,12 @@
       <c r="D262" t="n">
         <v>1</v>
       </c>
-      <c r="E262" t="n">
-        <v>35.25428458287176</v>
-      </c>
+      <c r="E262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>Colombian</t>
+          <t>Kimberley's Bakeshoppe</t>
         </is>
       </c>
       <c r="B263" t="n">
@@ -5277,14 +5285,12 @@
       <c r="D263" t="n">
         <v>1</v>
       </c>
-      <c r="E263" t="n">
-        <v>24.36534372833139</v>
-      </c>
+      <c r="E263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Condimento</t>
+          <t>Otis</t>
         </is>
       </c>
       <c r="B264" t="n">
@@ -5296,14 +5302,12 @@
       <c r="D264" t="n">
         <v>1</v>
       </c>
-      <c r="E264" t="n">
-        <v>17.28</v>
-      </c>
+      <c r="E264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Continental</t>
+          <t>Fernandes</t>
         </is>
       </c>
       <c r="B265" t="n">
@@ -5315,14 +5319,12 @@
       <c r="D265" t="n">
         <v>1</v>
       </c>
-      <c r="E265" t="n">
-        <v>14.487895716946</v>
-      </c>
+      <c r="E265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Count</t>
+          <t>Chiney</t>
         </is>
       </c>
       <c r="B266" t="n">
@@ -5339,7 +5341,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Cranberry</t>
+          <t>Cho Cho</t>
         </is>
       </c>
       <c r="B267" t="n">
@@ -5351,14 +5353,12 @@
       <c r="D267" t="n">
         <v>1</v>
       </c>
-      <c r="E267" t="n">
-        <v>19.55786211481664</v>
-      </c>
+      <c r="E267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Cream</t>
+          <t>Chokis</t>
         </is>
       </c>
       <c r="B268" t="n">
@@ -5371,13 +5371,13 @@
         <v>1</v>
       </c>
       <c r="E268" t="n">
-        <v>33.5</v>
+        <v>11.44</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Crema</t>
+          <t>Choppers</t>
         </is>
       </c>
       <c r="B269" t="n">
@@ -5389,14 +5389,12 @@
       <c r="D269" t="n">
         <v>1</v>
       </c>
-      <c r="E269" t="n">
-        <v>10.56</v>
-      </c>
+      <c r="E269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Cremosa</t>
+          <t>Chowmein</t>
         </is>
       </c>
       <c r="B270" t="n">
@@ -5413,7 +5411,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Cremy</t>
+          <t>Cilantro</t>
         </is>
       </c>
       <c r="B271" t="n">
@@ -5430,7 +5428,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>Croissants</t>
+          <t>Cloverhill</t>
         </is>
       </c>
       <c r="B272" t="n">
@@ -5447,7 +5445,7 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Cupcakes</t>
+          <t>Coffee</t>
         </is>
       </c>
       <c r="B273" t="n">
@@ -5459,12 +5457,14 @@
       <c r="D273" t="n">
         <v>1</v>
       </c>
-      <c r="E273" t="inlineStr"/>
+      <c r="E273" t="n">
+        <v>35.25428458287176</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>Cusano´s</t>
+          <t>Colombian</t>
         </is>
       </c>
       <c r="B274" t="n">
@@ -5476,12 +5476,14 @@
       <c r="D274" t="n">
         <v>1</v>
       </c>
-      <c r="E274" t="inlineStr"/>
+      <c r="E274" t="n">
+        <v>24.36534372833139</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Decorated</t>
+          <t>Condimento</t>
         </is>
       </c>
       <c r="B275" t="n">
@@ -5493,12 +5495,14 @@
       <c r="D275" t="n">
         <v>1</v>
       </c>
-      <c r="E275" t="inlineStr"/>
+      <c r="E275" t="n">
+        <v>17.28</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Double Duty</t>
+          <t>Continental</t>
         </is>
       </c>
       <c r="B276" t="n">
@@ -5510,12 +5514,14 @@
       <c r="D276" t="n">
         <v>1</v>
       </c>
-      <c r="E276" t="inlineStr"/>
+      <c r="E276" t="n">
+        <v>14.487895716946</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Ducales</t>
+          <t>Count</t>
         </is>
       </c>
       <c r="B277" t="n">
@@ -5527,14 +5533,12 @@
       <c r="D277" t="n">
         <v>1</v>
       </c>
-      <c r="E277" t="n">
-        <v>18.72440301815871</v>
-      </c>
+      <c r="E277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Chester</t>
+          <t>Cranberry</t>
         </is>
       </c>
       <c r="B278" t="n">
@@ -5546,12 +5550,14 @@
       <c r="D278" t="n">
         <v>1</v>
       </c>
-      <c r="E278" t="inlineStr"/>
+      <c r="E278" t="n">
+        <v>19.55786211481664</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>Cheez-It</t>
+          <t>Cream</t>
         </is>
       </c>
       <c r="B279" t="n">
@@ -5564,13 +5570,13 @@
         <v>1</v>
       </c>
       <c r="E279" t="n">
-        <v>28.26441564338176</v>
+        <v>33.5</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Cheese</t>
+          <t>Crema</t>
         </is>
       </c>
       <c r="B280" t="n">
@@ -5582,12 +5588,14 @@
       <c r="D280" t="n">
         <v>1</v>
       </c>
-      <c r="E280" t="inlineStr"/>
+      <c r="E280" t="n">
+        <v>10.56</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>Bakewell</t>
+          <t>Cremosa</t>
         </is>
       </c>
       <c r="B281" t="n">
@@ -5604,7 +5612,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>27Z</t>
+          <t>Cremy</t>
         </is>
       </c>
       <c r="B282" t="n">
@@ -5616,14 +5624,12 @@
       <c r="D282" t="n">
         <v>1</v>
       </c>
-      <c r="E282" t="n">
-        <v>27.47380304721075</v>
-      </c>
+      <c r="E282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>2Xram</t>
+          <t>Croissants</t>
         </is>
       </c>
       <c r="B283" t="n">
@@ -5635,14 +5641,12 @@
       <c r="D283" t="n">
         <v>1</v>
       </c>
-      <c r="E283" t="n">
-        <v>35.9842260926717</v>
-      </c>
+      <c r="E283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>3Xr</t>
+          <t>Cupcakes</t>
         </is>
       </c>
       <c r="B284" t="n">
@@ -5654,14 +5658,12 @@
       <c r="D284" t="n">
         <v>1</v>
       </c>
-      <c r="E284" t="n">
-        <v>32.66394886506618</v>
-      </c>
+      <c r="E284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>6Z</t>
+          <t>Cusano´s</t>
         </is>
       </c>
       <c r="B285" t="n">
@@ -5678,7 +5680,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>7Z</t>
+          <t>Decorated</t>
         </is>
       </c>
       <c r="B286" t="n">
@@ -5695,7 +5697,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>9”</t>
+          <t>Double Duty</t>
         </is>
       </c>
       <c r="B287" t="n">
@@ -5712,7 +5714,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>Afl.19.50</t>
+          <t>Ducales</t>
         </is>
       </c>
       <c r="B288" t="n">
@@ -5725,13 +5727,13 @@
         <v>1</v>
       </c>
       <c r="E288" t="n">
-        <v>10.89385474860335</v>
+        <v>18.72440301815871</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Algodon</t>
+          <t>Chester</t>
         </is>
       </c>
       <c r="B289" t="n">
@@ -5743,14 +5745,12 @@
       <c r="D289" t="n">
         <v>1</v>
       </c>
-      <c r="E289" t="n">
-        <v>54.03</v>
-      </c>
+      <c r="E289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Almond</t>
+          <t>Cheez-It</t>
         </is>
       </c>
       <c r="B290" t="n">
@@ -5762,12 +5762,14 @@
       <c r="D290" t="n">
         <v>1</v>
       </c>
-      <c r="E290" t="inlineStr"/>
+      <c r="E290" t="n">
+        <v>28.26441564338176</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Approx.</t>
+          <t>Cheese</t>
         </is>
       </c>
       <c r="B291" t="n">
@@ -5784,7 +5786,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Bandeja</t>
+          <t>Bakewell</t>
         </is>
       </c>
       <c r="B292" t="n">
@@ -5801,7 +5803,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Charmin</t>
+          <t>27Z</t>
         </is>
       </c>
       <c r="B293" t="n">
@@ -5814,13 +5816,13 @@
         <v>1</v>
       </c>
       <c r="E293" t="n">
-        <v>15.24047445634343</v>
+        <v>27.47380304721075</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Bayman</t>
+          <t>2Xram</t>
         </is>
       </c>
       <c r="B294" t="n">
@@ -5833,13 +5835,13 @@
         <v>1</v>
       </c>
       <c r="E294" t="n">
-        <v>13.45437616387337</v>
+        <v>35.9842260926717</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>Becky'S</t>
+          <t>3Xr</t>
         </is>
       </c>
       <c r="B295" t="n">
@@ -5852,13 +5854,13 @@
         <v>1</v>
       </c>
       <c r="E295" t="n">
-        <v>25.34916201117318</v>
+        <v>32.66394886506618</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Ben</t>
+          <t>6Z</t>
         </is>
       </c>
       <c r="B296" t="n">
@@ -5870,14 +5872,12 @@
       <c r="D296" t="n">
         <v>1</v>
       </c>
-      <c r="E296" t="n">
-        <v>33.79888268156424</v>
-      </c>
+      <c r="E296" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>7Z</t>
         </is>
       </c>
       <c r="B297" t="n">
@@ -5889,14 +5889,12 @@
       <c r="D297" t="n">
         <v>1</v>
       </c>
-      <c r="E297" t="n">
-        <v>31.69</v>
-      </c>
+      <c r="E297" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Bizcochos</t>
+          <t>9”</t>
         </is>
       </c>
       <c r="B298" t="n">
@@ -5908,14 +5906,12 @@
       <c r="D298" t="n">
         <v>1</v>
       </c>
-      <c r="E298" t="n">
-        <v>6.6</v>
-      </c>
+      <c r="E298" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Bridge</t>
+          <t>Afl.19.50</t>
         </is>
       </c>
       <c r="B299" t="n">
@@ -5928,13 +5924,13 @@
         <v>1</v>
       </c>
       <c r="E299" t="n">
-        <v>5.02</v>
+        <v>10.89385474860335</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Burrito</t>
+          <t>Algodon</t>
         </is>
       </c>
       <c r="B300" t="n">
@@ -5946,12 +5942,14 @@
       <c r="D300" t="n">
         <v>1</v>
       </c>
-      <c r="E300" t="inlineStr"/>
+      <c r="E300" t="n">
+        <v>54.03</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Cajuil</t>
+          <t>Almond</t>
         </is>
       </c>
       <c r="B301" t="n">
@@ -5963,14 +5961,12 @@
       <c r="D301" t="n">
         <v>1</v>
       </c>
-      <c r="E301" t="n">
-        <v>31.84</v>
-      </c>
+      <c r="E301" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Cassava</t>
+          <t>Approx.</t>
         </is>
       </c>
       <c r="B302" t="n">
@@ -5987,7 +5983,7 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Cbean</t>
+          <t>Bandeja</t>
         </is>
       </c>
       <c r="B303" t="n">
@@ -5999,14 +5995,12 @@
       <c r="D303" t="n">
         <v>1</v>
       </c>
-      <c r="E303" t="n">
-        <v>11.60477453580902</v>
-      </c>
+      <c r="E303" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Duncan</t>
+          <t>Charmin</t>
         </is>
       </c>
       <c r="B304" t="n">
@@ -6019,13 +6013,13 @@
         <v>1</v>
       </c>
       <c r="E304" t="n">
-        <v>7.12</v>
+        <v>15.24047445634343</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Fernandes</t>
+          <t>Bayman</t>
         </is>
       </c>
       <c r="B305" t="n">
@@ -6037,12 +6031,14 @@
       <c r="D305" t="n">
         <v>1</v>
       </c>
-      <c r="E305" t="inlineStr"/>
+      <c r="E305" t="n">
+        <v>13.45437616387337</v>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>Ferrero</t>
+          <t>Becky'S</t>
         </is>
       </c>
       <c r="B306" t="n">
@@ -6054,12 +6050,14 @@
       <c r="D306" t="n">
         <v>1</v>
       </c>
-      <c r="E306" t="inlineStr"/>
+      <c r="E306" t="n">
+        <v>25.34916201117318</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>Marie</t>
+          <t>Ben</t>
         </is>
       </c>
       <c r="B307" t="n">
@@ -6071,12 +6069,14 @@
       <c r="D307" t="n">
         <v>1</v>
       </c>
-      <c r="E307" t="inlineStr"/>
+      <c r="E307" t="n">
+        <v>33.79888268156424</v>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>Kraft</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B308" t="n">
@@ -6089,13 +6089,13 @@
         <v>1</v>
       </c>
       <c r="E308" t="n">
-        <v>9.264432029795158</v>
+        <v>31.69</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>Lampionwit</t>
+          <t>Bizcochos</t>
         </is>
       </c>
       <c r="B309" t="n">
@@ -6107,12 +6107,14 @@
       <c r="D309" t="n">
         <v>1</v>
       </c>
-      <c r="E309" t="inlineStr"/>
+      <c r="E309" t="n">
+        <v>6.6</v>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>Laureri</t>
+          <t>Bridge</t>
         </is>
       </c>
       <c r="B310" t="n">
@@ -6125,13 +6127,13 @@
         <v>1</v>
       </c>
       <c r="E310" t="n">
-        <v>7.575418994413408</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>Lenny</t>
+          <t>Burrito</t>
         </is>
       </c>
       <c r="B311" t="n">
@@ -6143,14 +6145,12 @@
       <c r="D311" t="n">
         <v>1</v>
       </c>
-      <c r="E311" t="n">
-        <v>26.41</v>
-      </c>
+      <c r="E311" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>Lewis</t>
+          <t>Cajuil</t>
         </is>
       </c>
       <c r="B312" t="n">
@@ -6163,13 +6163,13 @@
         <v>1</v>
       </c>
       <c r="E312" t="n">
-        <v>2.894339322587641</v>
+        <v>31.84</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Liga</t>
+          <t>Cassava</t>
         </is>
       </c>
       <c r="B313" t="n">
@@ -6181,14 +6181,12 @@
       <c r="D313" t="n">
         <v>1</v>
       </c>
-      <c r="E313" t="n">
-        <v>10.58305138091117</v>
-      </c>
+      <c r="E313" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Limited</t>
+          <t>Cbean</t>
         </is>
       </c>
       <c r="B314" t="n">
@@ -6201,13 +6199,13 @@
         <v>1</v>
       </c>
       <c r="E314" t="n">
-        <v>27.4172754619682</v>
+        <v>11.60477453580902</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>Liter</t>
+          <t>Duncan</t>
         </is>
       </c>
       <c r="B315" t="n">
@@ -6220,13 +6218,13 @@
         <v>1</v>
       </c>
       <c r="E315" t="n">
-        <v>45.93720207121603</v>
+        <v>7.12</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>M&amp;M'S</t>
+          <t>Ferrero</t>
         </is>
       </c>
       <c r="B316" t="n">
@@ -6238,14 +6236,12 @@
       <c r="D316" t="n">
         <v>1</v>
       </c>
-      <c r="E316" t="n">
-        <v>10.18156424581006</v>
-      </c>
+      <c r="E316" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>Madegood</t>
+          <t>Oscar</t>
         </is>
       </c>
       <c r="B317" t="n">
@@ -6258,13 +6254,13 @@
         <v>1</v>
       </c>
       <c r="E317" t="n">
-        <v>15.40363282035295</v>
+        <v>18.54852276596928</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>Mcvitie'S</t>
+          <t>Fjord</t>
         </is>
       </c>
       <c r="B318" t="n">
@@ -6277,13 +6273,13 @@
         <v>1</v>
       </c>
       <c r="E318" t="n">
-        <v>8.615941458808718</v>
+        <v>17.17877094972067</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>Kinnikinnick</t>
+          <t>Kraft</t>
         </is>
       </c>
       <c r="B319" t="n">
@@ -6296,13 +6292,13 @@
         <v>1</v>
       </c>
       <c r="E319" t="n">
-        <v>14.71802336379673</v>
+        <v>9.264432029795158</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Members Selection</t>
+          <t>Lampionwit</t>
         </is>
       </c>
       <c r="B320" t="n">
@@ -6319,7 +6315,7 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Milano</t>
+          <t>Laureri</t>
         </is>
       </c>
       <c r="B321" t="n">
@@ -6332,13 +6328,13 @@
         <v>1</v>
       </c>
       <c r="E321" t="n">
-        <v>15.6145251396648</v>
+        <v>7.575418994413408</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>Mjays</t>
+          <t>Lenny</t>
         </is>
       </c>
       <c r="B322" t="n">
@@ -6350,12 +6346,14 @@
       <c r="D322" t="n">
         <v>1</v>
       </c>
-      <c r="E322" t="inlineStr"/>
+      <c r="E322" t="n">
+        <v>26.41</v>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>Nature</t>
+          <t>Lewis</t>
         </is>
       </c>
       <c r="B323" t="n">
@@ -6368,13 +6366,13 @@
         <v>1</v>
       </c>
       <c r="E323" t="n">
-        <v>36.62321539416511</v>
+        <v>2.894339322587641</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>Nature Valley</t>
+          <t>Liga</t>
         </is>
       </c>
       <c r="B324" t="n">
@@ -6386,12 +6384,14 @@
       <c r="D324" t="n">
         <v>1</v>
       </c>
-      <c r="E324" t="inlineStr"/>
+      <c r="E324" t="n">
+        <v>10.58305138091117</v>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>Navidad</t>
+          <t>Limited</t>
         </is>
       </c>
       <c r="B325" t="n">
@@ -6404,13 +6404,13 @@
         <v>1</v>
       </c>
       <c r="E325" t="n">
-        <v>7.04</v>
+        <v>27.4172754619682</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>Nerds</t>
+          <t>Liter</t>
         </is>
       </c>
       <c r="B326" t="n">
@@ -6422,12 +6422,14 @@
       <c r="D326" t="n">
         <v>1</v>
       </c>
-      <c r="E326" t="inlineStr"/>
+      <c r="E326" t="n">
+        <v>45.93720207121603</v>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>Odorex</t>
+          <t>M&amp;M'S</t>
         </is>
       </c>
       <c r="B327" t="n">
@@ -6439,12 +6441,14 @@
       <c r="D327" t="n">
         <v>1</v>
       </c>
-      <c r="E327" t="inlineStr"/>
+      <c r="E327" t="n">
+        <v>10.18156424581006</v>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>Om</t>
+          <t>Madegood</t>
         </is>
       </c>
       <c r="B328" t="n">
@@ -6456,12 +6460,14 @@
       <c r="D328" t="n">
         <v>1</v>
       </c>
-      <c r="E328" t="inlineStr"/>
+      <c r="E328" t="n">
+        <v>15.40363282035295</v>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>Ortega</t>
+          <t>Maiz</t>
         </is>
       </c>
       <c r="B329" t="n">
@@ -6473,14 +6479,12 @@
       <c r="D329" t="n">
         <v>1</v>
       </c>
-      <c r="E329" t="n">
-        <v>10.91045974485786</v>
-      </c>
+      <c r="E329" t="inlineStr"/>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>Kokos</t>
+          <t>Marie</t>
         </is>
       </c>
       <c r="B330" t="n">
@@ -6492,14 +6496,12 @@
       <c r="D330" t="n">
         <v>1</v>
       </c>
-      <c r="E330" t="n">
-        <v>12.93854748603352</v>
-      </c>
+      <c r="E330" t="inlineStr"/>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>King's Hawaiian</t>
+          <t>Mcvitie'S</t>
         </is>
       </c>
       <c r="B331" t="n">
@@ -6511,12 +6513,14 @@
       <c r="D331" t="n">
         <v>1</v>
       </c>
-      <c r="E331" t="inlineStr"/>
+      <c r="E331" t="n">
+        <v>8.615941458808718</v>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>Fjord</t>
+          <t>Members Selection</t>
         </is>
       </c>
       <c r="B332" t="n">
@@ -6528,14 +6532,12 @@
       <c r="D332" t="n">
         <v>1</v>
       </c>
-      <c r="E332" t="n">
-        <v>17.17877094972067</v>
-      </c>
+      <c r="E332" t="inlineStr"/>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>Haribo</t>
+          <t>Milano</t>
         </is>
       </c>
       <c r="B333" t="n">
@@ -6547,12 +6549,14 @@
       <c r="D333" t="n">
         <v>1</v>
       </c>
-      <c r="E333" t="inlineStr"/>
+      <c r="E333" t="n">
+        <v>15.6145251396648</v>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>Fl</t>
+          <t>Mjays</t>
         </is>
       </c>
       <c r="B334" t="n">
@@ -6569,7 +6573,7 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>Food</t>
+          <t>Nature</t>
         </is>
       </c>
       <c r="B335" t="n">
@@ -6582,13 +6586,13 @@
         <v>1</v>
       </c>
       <c r="E335" t="n">
-        <v>17.08</v>
+        <v>36.62321539416511</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>French</t>
+          <t>Nature Valley</t>
         </is>
       </c>
       <c r="B336" t="n">
@@ -6600,14 +6604,12 @@
       <c r="D336" t="n">
         <v>1</v>
       </c>
-      <c r="E336" t="n">
-        <v>26.4006372976879</v>
-      </c>
+      <c r="E336" t="inlineStr"/>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>Gift</t>
+          <t>Navidad</t>
         </is>
       </c>
       <c r="B337" t="n">
@@ -6619,12 +6621,14 @@
       <c r="D337" t="n">
         <v>1</v>
       </c>
-      <c r="E337" t="inlineStr"/>
+      <c r="E337" t="n">
+        <v>7.04</v>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>Giftcard</t>
+          <t>Nerds</t>
         </is>
       </c>
       <c r="B338" t="n">
@@ -6641,7 +6645,7 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>Give &amp; Go</t>
+          <t>Odorex</t>
         </is>
       </c>
       <c r="B339" t="n">
@@ -6658,7 +6662,7 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>Goldfish</t>
+          <t>Om</t>
         </is>
       </c>
       <c r="B340" t="n">
@@ -6670,14 +6674,12 @@
       <c r="D340" t="n">
         <v>1</v>
       </c>
-      <c r="E340" t="n">
-        <v>29.31835727996105</v>
-      </c>
+      <c r="E340" t="inlineStr"/>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>Grande</t>
+          <t>Ortega</t>
         </is>
       </c>
       <c r="B341" t="n">
@@ -6690,13 +6692,13 @@
         <v>1</v>
       </c>
       <c r="E341" t="n">
-        <v>4.17</v>
+        <v>10.91045974485786</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>Haagen</t>
+          <t>Kokos</t>
         </is>
       </c>
       <c r="B342" t="n">
@@ -6709,13 +6711,13 @@
         <v>1</v>
       </c>
       <c r="E342" t="n">
-        <v>10.79896475763763</v>
+        <v>12.93854748603352</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>Hamburgesa</t>
+          <t>Kinnikinnick</t>
         </is>
       </c>
       <c r="B343" t="n">
@@ -6727,12 +6729,14 @@
       <c r="D343" t="n">
         <v>1</v>
       </c>
-      <c r="E343" t="inlineStr"/>
+      <c r="E343" t="n">
+        <v>14.71802336379673</v>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>Hershey</t>
+          <t>King's Hawaiian</t>
         </is>
       </c>
       <c r="B344" t="n">
@@ -6744,14 +6748,12 @@
       <c r="D344" t="n">
         <v>1</v>
       </c>
-      <c r="E344" t="n">
-        <v>19.07848055928269</v>
-      </c>
+      <c r="E344" t="inlineStr"/>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>Haribo</t>
         </is>
       </c>
       <c r="B345" t="n">
@@ -6763,14 +6765,12 @@
       <c r="D345" t="n">
         <v>1</v>
       </c>
-      <c r="E345" t="n">
-        <v>25.2651356623809</v>
-      </c>
+      <c r="E345" t="inlineStr"/>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>Highland</t>
+          <t>Fl</t>
         </is>
       </c>
       <c r="B346" t="n">
@@ -6787,7 +6787,7 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>Hol</t>
+          <t>Food</t>
         </is>
       </c>
       <c r="B347" t="n">
@@ -6800,13 +6800,13 @@
         <v>1</v>
       </c>
       <c r="E347" t="n">
-        <v>14.42307692307692</v>
+        <v>17.08</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>Holiday</t>
+          <t>French</t>
         </is>
       </c>
       <c r="B348" t="n">
@@ -6818,12 +6818,14 @@
       <c r="D348" t="n">
         <v>1</v>
       </c>
-      <c r="E348" t="inlineStr"/>
+      <c r="E348" t="n">
+        <v>26.4006372976879</v>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>Hollandia</t>
+          <t>Gift</t>
         </is>
       </c>
       <c r="B349" t="n">
@@ -6835,14 +6837,12 @@
       <c r="D349" t="n">
         <v>1</v>
       </c>
-      <c r="E349" t="n">
-        <v>52.34878150009826</v>
-      </c>
+      <c r="E349" t="inlineStr"/>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>Hummus</t>
+          <t>Giftcard</t>
         </is>
       </c>
       <c r="B350" t="n">
@@ -6854,14 +6854,12 @@
       <c r="D350" t="n">
         <v>1</v>
       </c>
-      <c r="E350" t="n">
-        <v>12.57</v>
-      </c>
+      <c r="E350" t="inlineStr"/>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>Igloo</t>
+          <t>Give &amp; Go</t>
         </is>
       </c>
       <c r="B351" t="n">
@@ -6878,7 +6876,7 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>Jos</t>
+          <t>Goldfish</t>
         </is>
       </c>
       <c r="B352" t="n">
@@ -6891,13 +6889,13 @@
         <v>1</v>
       </c>
       <c r="E352" t="n">
-        <v>27.90968342644321</v>
+        <v>29.31835727996105</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>Jumbo'S</t>
+          <t>Grande</t>
         </is>
       </c>
       <c r="B353" t="n">
@@ -6910,13 +6908,13 @@
         <v>1</v>
       </c>
       <c r="E353" t="n">
-        <v>5.352559263173788</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>Kc</t>
+          <t>Haagen</t>
         </is>
       </c>
       <c r="B354" t="n">
@@ -6928,12 +6926,14 @@
       <c r="D354" t="n">
         <v>1</v>
       </c>
-      <c r="E354" t="inlineStr"/>
+      <c r="E354" t="n">
+        <v>10.79896475763763</v>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>Kilo</t>
+          <t>Hamburgesa</t>
         </is>
       </c>
       <c r="B355" t="n">
@@ -6945,26 +6945,244 @@
       <c r="D355" t="n">
         <v>1</v>
       </c>
-      <c r="E355" t="n">
-        <v>14.25891435863968</v>
-      </c>
+      <c r="E355" t="inlineStr"/>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
+          <t>Hershey</t>
+        </is>
+      </c>
+      <c r="B356" t="n">
+        <v>1</v>
+      </c>
+      <c r="C356" t="n">
+        <v>1</v>
+      </c>
+      <c r="D356" t="n">
+        <v>1</v>
+      </c>
+      <c r="E356" t="n">
+        <v>19.07848055928269</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="B357" t="n">
+        <v>1</v>
+      </c>
+      <c r="C357" t="n">
+        <v>1</v>
+      </c>
+      <c r="D357" t="n">
+        <v>1</v>
+      </c>
+      <c r="E357" t="n">
+        <v>25.2651356623809</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>Highland</t>
+        </is>
+      </c>
+      <c r="B358" t="n">
+        <v>1</v>
+      </c>
+      <c r="C358" t="n">
+        <v>1</v>
+      </c>
+      <c r="D358" t="n">
+        <v>1</v>
+      </c>
+      <c r="E358" t="inlineStr"/>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>Hol</t>
+        </is>
+      </c>
+      <c r="B359" t="n">
+        <v>1</v>
+      </c>
+      <c r="C359" t="n">
+        <v>1</v>
+      </c>
+      <c r="D359" t="n">
+        <v>1</v>
+      </c>
+      <c r="E359" t="n">
+        <v>14.42307692307692</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>Holiday</t>
+        </is>
+      </c>
+      <c r="B360" t="n">
+        <v>1</v>
+      </c>
+      <c r="C360" t="n">
+        <v>1</v>
+      </c>
+      <c r="D360" t="n">
+        <v>1</v>
+      </c>
+      <c r="E360" t="inlineStr"/>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>Hollandia</t>
+        </is>
+      </c>
+      <c r="B361" t="n">
+        <v>1</v>
+      </c>
+      <c r="C361" t="n">
+        <v>1</v>
+      </c>
+      <c r="D361" t="n">
+        <v>1</v>
+      </c>
+      <c r="E361" t="n">
+        <v>52.34878150009826</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>Hummus</t>
+        </is>
+      </c>
+      <c r="B362" t="n">
+        <v>1</v>
+      </c>
+      <c r="C362" t="n">
+        <v>1</v>
+      </c>
+      <c r="D362" t="n">
+        <v>1</v>
+      </c>
+      <c r="E362" t="n">
+        <v>12.57</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>Igloo</t>
+        </is>
+      </c>
+      <c r="B363" t="n">
+        <v>1</v>
+      </c>
+      <c r="C363" t="n">
+        <v>1</v>
+      </c>
+      <c r="D363" t="n">
+        <v>1</v>
+      </c>
+      <c r="E363" t="inlineStr"/>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>Jos</t>
+        </is>
+      </c>
+      <c r="B364" t="n">
+        <v>1</v>
+      </c>
+      <c r="C364" t="n">
+        <v>1</v>
+      </c>
+      <c r="D364" t="n">
+        <v>1</v>
+      </c>
+      <c r="E364" t="n">
+        <v>27.90968342644321</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>Jumbo'S</t>
+        </is>
+      </c>
+      <c r="B365" t="n">
+        <v>1</v>
+      </c>
+      <c r="C365" t="n">
+        <v>1</v>
+      </c>
+      <c r="D365" t="n">
+        <v>1</v>
+      </c>
+      <c r="E365" t="n">
+        <v>5.352559263173788</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>Kc</t>
+        </is>
+      </c>
+      <c r="B366" t="n">
+        <v>1</v>
+      </c>
+      <c r="C366" t="n">
+        <v>1</v>
+      </c>
+      <c r="D366" t="n">
+        <v>1</v>
+      </c>
+      <c r="E366" t="inlineStr"/>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>Kilo</t>
+        </is>
+      </c>
+      <c r="B367" t="n">
+        <v>1</v>
+      </c>
+      <c r="C367" t="n">
+        <v>1</v>
+      </c>
+      <c r="D367" t="n">
+        <v>1</v>
+      </c>
+      <c r="E367" t="n">
+        <v>14.25891435863968</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
           <t>Yum</t>
         </is>
       </c>
-      <c r="B356" t="n">
-        <v>1</v>
-      </c>
-      <c r="C356" t="n">
-        <v>1</v>
-      </c>
-      <c r="D356" t="n">
-        <v>1</v>
-      </c>
-      <c r="E356" t="inlineStr"/>
+      <c r="B368" t="n">
+        <v>1</v>
+      </c>
+      <c r="C368" t="n">
+        <v>1</v>
+      </c>
+      <c r="D368" t="n">
+        <v>1</v>
+      </c>
+      <c r="E368" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9153,7 +9371,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lu</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -9228,12 +9446,12 @@
       <c r="AG10" t="inlineStr"/>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Lu</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Lu</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr"/>
@@ -10014,7 +10232,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lu</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -10085,12 +10303,12 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Lu</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Lu</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr"/>
@@ -10340,7 +10558,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lu</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -10421,12 +10639,12 @@
       <c r="AG17" t="inlineStr"/>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>Lu</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Lu</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="AJ17" t="n">
@@ -10513,7 +10731,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lu</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -10594,12 +10812,12 @@
       <c r="AG18" t="inlineStr"/>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Lu</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Lu</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="AJ18" t="n">
@@ -13133,7 +13351,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>De</t>
+          <t>Proteina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -13212,12 +13430,12 @@
       <c r="AG34" t="inlineStr"/>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>De</t>
+          <t>Proteina</t>
         </is>
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>De</t>
+          <t>Proteina</t>
         </is>
       </c>
       <c r="AJ34" t="n">
@@ -13227,7 +13445,7 @@
       <c r="AL34" t="inlineStr"/>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>de_galleta de proteina sabor chocolate chips ll</t>
+          <t>proteina_galleta de proteina sabor chocolate chips ll</t>
         </is>
       </c>
       <c r="AN34" t="inlineStr">
@@ -13242,12 +13460,12 @@
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>de_galleta de proteina sabor chocolate chips ll_0.12</t>
+          <t>proteina_galleta de proteina sabor chocolate chips ll_0.12</t>
         </is>
       </c>
       <c r="AQ34" t="inlineStr">
         <is>
-          <t>de_chips_chocolate_proteina</t>
+          <t>proteina_chips_chocolate_proteina</t>
         </is>
       </c>
       <c r="AR34" t="n">
@@ -13304,7 +13522,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>De</t>
+          <t>Chocolate</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -13383,12 +13601,12 @@
       <c r="AG35" t="inlineStr"/>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>De</t>
+          <t>Chocolate</t>
         </is>
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>De</t>
+          <t>Chocolate</t>
         </is>
       </c>
       <c r="AJ35" t="n">
@@ -13398,7 +13616,7 @@
       <c r="AL35" t="inlineStr"/>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>de_galleta de chocolate chip vegana dbl</t>
+          <t>chocolate_galleta de chocolate chip vegana dbl</t>
         </is>
       </c>
       <c r="AN35" t="inlineStr">
@@ -13413,12 +13631,12 @@
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>de_galleta de chocolate chip vegana dbl_0.07</t>
+          <t>chocolate_galleta de chocolate chip vegana dbl_0.07</t>
         </is>
       </c>
       <c r="AQ35" t="inlineStr">
         <is>
-          <t>de_chip_chocolate_vegana</t>
+          <t>chocolate_chip_chocolate_vegana</t>
         </is>
       </c>
       <c r="AR35" t="n">
@@ -13475,7 +13693,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>De</t>
+          <t>Chocolate</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -13554,12 +13772,12 @@
       <c r="AG36" t="inlineStr"/>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>De</t>
+          <t>Chocolate</t>
         </is>
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>De</t>
+          <t>Chocolate</t>
         </is>
       </c>
       <c r="AJ36" t="n">
@@ -13569,7 +13787,7 @@
       <c r="AL36" t="inlineStr"/>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>de_galleta de chocolate chip vegana dbl</t>
+          <t>chocolate_galleta de chocolate chip vegana dbl</t>
         </is>
       </c>
       <c r="AN36" t="inlineStr">
@@ -13584,12 +13802,12 @@
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>de_galleta de chocolate chip vegana dbl_0.07</t>
+          <t>chocolate_galleta de chocolate chip vegana dbl_0.07</t>
         </is>
       </c>
       <c r="AQ36" t="inlineStr">
         <is>
-          <t>de_chip_chocolate_vegana</t>
+          <t>chocolate_chip_chocolate_vegana</t>
         </is>
       </c>
       <c r="AR36" t="n">
@@ -16525,7 +16743,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>De</t>
+          <t>Mantequilla</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -16600,12 +16818,12 @@
       <c r="AG54" t="inlineStr"/>
       <c r="AH54" t="inlineStr">
         <is>
-          <t>De</t>
+          <t>Mantequilla</t>
         </is>
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>De</t>
+          <t>Mantequilla</t>
         </is>
       </c>
       <c r="AJ54" t="inlineStr"/>
@@ -16613,7 +16831,7 @@
       <c r="AL54" t="inlineStr"/>
       <c r="AM54" t="inlineStr">
         <is>
-          <t>de_galleta de mantequilla jules destrooper</t>
+          <t>mantequilla_galleta de mantequilla jules destrooper</t>
         </is>
       </c>
       <c r="AN54" t="inlineStr">
@@ -16628,12 +16846,12 @@
       </c>
       <c r="AP54" t="inlineStr">
         <is>
-          <t>de_galleta de mantequilla jules destrooper_0.1</t>
+          <t>mantequilla_galleta de mantequilla jules destrooper_0.1</t>
         </is>
       </c>
       <c r="AQ54" t="inlineStr">
         <is>
-          <t>de_destrooper_jules_mantequilla</t>
+          <t>mantequilla_destrooper_jules_mantequilla</t>
         </is>
       </c>
       <c r="AR54" t="n">
@@ -18527,7 +18745,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lu</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -18602,12 +18820,12 @@
       <c r="AG66" t="inlineStr"/>
       <c r="AH66" t="inlineStr">
         <is>
-          <t>Lu</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="AI66" t="inlineStr">
         <is>
-          <t>Lu</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="AJ66" t="inlineStr"/>
@@ -18692,7 +18910,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lu</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -18771,12 +18989,12 @@
       <c r="AG67" t="inlineStr"/>
       <c r="AH67" t="inlineStr">
         <is>
-          <t>Lu</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="AI67" t="inlineStr">
         <is>
-          <t>Lu</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="AJ67" t="n">
@@ -21068,7 +21286,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lu</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -21139,12 +21357,12 @@
       </c>
       <c r="AH81" t="inlineStr">
         <is>
-          <t>Lu</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>Lu</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="AJ81" t="inlineStr"/>
@@ -21724,7 +21942,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lu</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -21799,12 +22017,12 @@
       <c r="AG85" t="inlineStr"/>
       <c r="AH85" t="inlineStr">
         <is>
-          <t>Lu</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="AI85" t="inlineStr">
         <is>
-          <t>Lu</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="AJ85" t="inlineStr"/>
@@ -25943,7 +26161,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Lu</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -26018,12 +26236,12 @@
       <c r="AG110" t="inlineStr"/>
       <c r="AH110" t="inlineStr">
         <is>
-          <t>Lu</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="AI110" t="inlineStr">
         <is>
-          <t>Lu</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="AJ110" t="inlineStr"/>
@@ -26108,7 +26326,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Lu</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -26183,12 +26401,12 @@
       <c r="AG111" t="inlineStr"/>
       <c r="AH111" t="inlineStr">
         <is>
-          <t>Lu</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="AI111" t="inlineStr">
         <is>
-          <t>Lu</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="AJ111" t="inlineStr"/>
@@ -27579,7 +27797,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Lu</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -27654,12 +27872,12 @@
       <c r="AG120" t="inlineStr"/>
       <c r="AH120" t="inlineStr">
         <is>
-          <t>Lu</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="AI120" t="inlineStr">
         <is>
-          <t>Lu</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="AJ120" t="inlineStr"/>
@@ -28766,7 +28984,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Lu</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -28837,12 +29055,12 @@
       </c>
       <c r="AH127" t="inlineStr">
         <is>
-          <t>Lu</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="AI127" t="inlineStr">
         <is>
-          <t>Lu</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="AJ127" t="inlineStr"/>
@@ -31909,7 +32127,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Lu</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -31980,12 +32198,12 @@
       </c>
       <c r="AH146" t="inlineStr">
         <is>
-          <t>Lu</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="AI146" t="inlineStr">
         <is>
-          <t>Lu</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="AJ146" t="inlineStr"/>
@@ -33253,7 +33471,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Lu</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -33328,12 +33546,12 @@
       </c>
       <c r="AH154" t="inlineStr">
         <is>
-          <t>Lu</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="AI154" t="inlineStr">
         <is>
-          <t>Lu</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="AJ154" t="n">
@@ -41967,7 +42185,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>De</t>
+          <t>Chocolate</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -42046,12 +42264,12 @@
       <c r="AG206" t="inlineStr"/>
       <c r="AH206" t="inlineStr">
         <is>
-          <t>De</t>
+          <t>Chocolate</t>
         </is>
       </c>
       <c r="AI206" t="inlineStr">
         <is>
-          <t>De</t>
+          <t>Chocolate</t>
         </is>
       </c>
       <c r="AJ206" t="n">
@@ -42065,7 +42283,7 @@
       </c>
       <c r="AM206" t="inlineStr">
         <is>
-          <t>de_galletas de chocolate blanco y macadamia lenny y larry ll</t>
+          <t>chocolate_galletas de chocolate blanco y macadamia lenny y larry ll</t>
         </is>
       </c>
       <c r="AN206" t="inlineStr">
@@ -42080,12 +42298,12 @@
       </c>
       <c r="AP206" t="inlineStr">
         <is>
-          <t>de_galletas de chocolate blanco y macadamia lenny y larry ll_0.11</t>
+          <t>chocolate_galletas de chocolate blanco y macadamia lenny y larry ll_0.11</t>
         </is>
       </c>
       <c r="AQ206" t="inlineStr">
         <is>
-          <t>de_blanco_chocolate_larry_lenny</t>
+          <t>chocolate_blanco_chocolate_larry_lenny</t>
         </is>
       </c>
       <c r="AR206" t="n">
@@ -42663,7 +42881,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>De</t>
+          <t>Avena</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -42742,12 +42960,12 @@
       <c r="AG210" t="inlineStr"/>
       <c r="AH210" t="inlineStr">
         <is>
-          <t>De</t>
+          <t>Avena</t>
         </is>
       </c>
       <c r="AI210" t="inlineStr">
         <is>
-          <t>De</t>
+          <t>Avena</t>
         </is>
       </c>
       <c r="AJ210" t="n">
@@ -42761,7 +42979,7 @@
       </c>
       <c r="AM210" t="inlineStr">
         <is>
-          <t>de_galleta de avena choco snicker lenny y larry ll</t>
+          <t>avena_galleta de avena choco snicker lenny y larry ll</t>
         </is>
       </c>
       <c r="AN210" t="inlineStr">
@@ -42776,12 +42994,12 @@
       </c>
       <c r="AP210" t="inlineStr">
         <is>
-          <t>de_galleta de avena choco snicker lenny y larry ll_0.11</t>
+          <t>avena_galleta de avena choco snicker lenny y larry ll_0.11</t>
         </is>
       </c>
       <c r="AQ210" t="inlineStr">
         <is>
-          <t>de_avena_choco_larry_lenny</t>
+          <t>avena_avena_choco_larry_lenny</t>
         </is>
       </c>
       <c r="AR210" t="n">
@@ -43013,7 +43231,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>De</t>
+          <t>Avena</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -43092,12 +43310,12 @@
       <c r="AG212" t="inlineStr"/>
       <c r="AH212" t="inlineStr">
         <is>
-          <t>De</t>
+          <t>Avena</t>
         </is>
       </c>
       <c r="AI212" t="inlineStr">
         <is>
-          <t>De</t>
+          <t>Avena</t>
         </is>
       </c>
       <c r="AJ212" t="n">
@@ -43111,7 +43329,7 @@
       </c>
       <c r="AM212" t="inlineStr">
         <is>
-          <t>de_galleta de avena con pasas lenny y larry ll</t>
+          <t>avena_galleta de avena con pasas lenny y larry ll</t>
         </is>
       </c>
       <c r="AN212" t="inlineStr">
@@ -43126,12 +43344,12 @@
       </c>
       <c r="AP212" t="inlineStr">
         <is>
-          <t>de_galleta de avena con pasas lenny y larry ll_0.11</t>
+          <t>avena_galleta de avena con pasas lenny y larry ll_0.11</t>
         </is>
       </c>
       <c r="AQ212" t="inlineStr">
         <is>
-          <t>de_avena_larry_lenny_pasas</t>
+          <t>avena_avena_larry_lenny_pasas</t>
         </is>
       </c>
       <c r="AR212" t="n">
@@ -43349,7 +43567,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Lu</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -43426,12 +43644,12 @@
       </c>
       <c r="AH214" t="inlineStr">
         <is>
-          <t>Lu</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="AI214" t="inlineStr">
         <is>
-          <t>Lu</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="AJ214" t="n">
@@ -43697,7 +43915,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>De</t>
+          <t>Avena</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -43776,12 +43994,12 @@
       <c r="AG216" t="inlineStr"/>
       <c r="AH216" t="inlineStr">
         <is>
-          <t>De</t>
+          <t>Avena</t>
         </is>
       </c>
       <c r="AI216" t="inlineStr">
         <is>
-          <t>De</t>
+          <t>Avena</t>
         </is>
       </c>
       <c r="AJ216" t="n">
@@ -43795,7 +44013,7 @@
       </c>
       <c r="AM216" t="inlineStr">
         <is>
-          <t>de_galleta de avena choco snicker lenny y larry ll</t>
+          <t>avena_galleta de avena choco snicker lenny y larry ll</t>
         </is>
       </c>
       <c r="AN216" t="inlineStr">
@@ -43810,12 +44028,12 @@
       </c>
       <c r="AP216" t="inlineStr">
         <is>
-          <t>de_galleta de avena choco snicker lenny y larry ll_0.11</t>
+          <t>avena_galleta de avena choco snicker lenny y larry ll_0.11</t>
         </is>
       </c>
       <c r="AQ216" t="inlineStr">
         <is>
-          <t>de_avena_choco_larry_lenny</t>
+          <t>avena_avena_choco_larry_lenny</t>
         </is>
       </c>
       <c r="AR216" t="n">
@@ -43872,7 +44090,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>De</t>
+          <t>Avena</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -43951,12 +44169,12 @@
       <c r="AG217" t="inlineStr"/>
       <c r="AH217" t="inlineStr">
         <is>
-          <t>De</t>
+          <t>Avena</t>
         </is>
       </c>
       <c r="AI217" t="inlineStr">
         <is>
-          <t>De</t>
+          <t>Avena</t>
         </is>
       </c>
       <c r="AJ217" t="n">
@@ -43970,7 +44188,7 @@
       </c>
       <c r="AM217" t="inlineStr">
         <is>
-          <t>de_galleta de avena con pasas lenny y larry ll</t>
+          <t>avena_galleta de avena con pasas lenny y larry ll</t>
         </is>
       </c>
       <c r="AN217" t="inlineStr">
@@ -43985,12 +44203,12 @@
       </c>
       <c r="AP217" t="inlineStr">
         <is>
-          <t>de_galleta de avena con pasas lenny y larry ll_0.11</t>
+          <t>avena_galleta de avena con pasas lenny y larry ll_0.11</t>
         </is>
       </c>
       <c r="AQ217" t="inlineStr">
         <is>
-          <t>de_avena_larry_lenny_pasas</t>
+          <t>avena_avena_larry_lenny_pasas</t>
         </is>
       </c>
       <c r="AR217" t="n">
@@ -44047,7 +44265,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>De</t>
+          <t>Avena</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -44126,12 +44344,12 @@
       <c r="AG218" t="inlineStr"/>
       <c r="AH218" t="inlineStr">
         <is>
-          <t>De</t>
+          <t>Avena</t>
         </is>
       </c>
       <c r="AI218" t="inlineStr">
         <is>
-          <t>De</t>
+          <t>Avena</t>
         </is>
       </c>
       <c r="AJ218" t="n">
@@ -44145,7 +44363,7 @@
       </c>
       <c r="AM218" t="inlineStr">
         <is>
-          <t>de_galleta de avena con pasas lenny y larry ll</t>
+          <t>avena_galleta de avena con pasas lenny y larry ll</t>
         </is>
       </c>
       <c r="AN218" t="inlineStr">
@@ -44160,12 +44378,12 @@
       </c>
       <c r="AP218" t="inlineStr">
         <is>
-          <t>de_galleta de avena con pasas lenny y larry ll_0.11</t>
+          <t>avena_galleta de avena con pasas lenny y larry ll_0.11</t>
         </is>
       </c>
       <c r="AQ218" t="inlineStr">
         <is>
-          <t>de_avena_larry_lenny_pasas</t>
+          <t>avena_avena_larry_lenny_pasas</t>
         </is>
       </c>
       <c r="AR218" t="n">
@@ -44222,7 +44440,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>De</t>
+          <t>Chocolate</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -44301,12 +44519,12 @@
       <c r="AG219" t="inlineStr"/>
       <c r="AH219" t="inlineStr">
         <is>
-          <t>De</t>
+          <t>Chocolate</t>
         </is>
       </c>
       <c r="AI219" t="inlineStr">
         <is>
-          <t>De</t>
+          <t>Chocolate</t>
         </is>
       </c>
       <c r="AJ219" t="n">
@@ -44320,7 +44538,7 @@
       </c>
       <c r="AM219" t="inlineStr">
         <is>
-          <t>de_galletas de chocolate blanco y macadamia lenny y larry ll</t>
+          <t>chocolate_galletas de chocolate blanco y macadamia lenny y larry ll</t>
         </is>
       </c>
       <c r="AN219" t="inlineStr">
@@ -44335,12 +44553,12 @@
       </c>
       <c r="AP219" t="inlineStr">
         <is>
-          <t>de_galletas de chocolate blanco y macadamia lenny y larry ll_0.11</t>
+          <t>chocolate_galletas de chocolate blanco y macadamia lenny y larry ll_0.11</t>
         </is>
       </c>
       <c r="AQ219" t="inlineStr">
         <is>
-          <t>de_blanco_chocolate_larry_lenny</t>
+          <t>chocolate_blanco_chocolate_larry_lenny</t>
         </is>
       </c>
       <c r="AR219" t="n">
@@ -44397,7 +44615,7 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>De</t>
+          <t>Avena</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -44476,12 +44694,12 @@
       <c r="AG220" t="inlineStr"/>
       <c r="AH220" t="inlineStr">
         <is>
-          <t>De</t>
+          <t>Avena</t>
         </is>
       </c>
       <c r="AI220" t="inlineStr">
         <is>
-          <t>De</t>
+          <t>Avena</t>
         </is>
       </c>
       <c r="AJ220" t="n">
@@ -44495,7 +44713,7 @@
       </c>
       <c r="AM220" t="inlineStr">
         <is>
-          <t>de_galleta de avena choco snicker lenny y larry ll</t>
+          <t>avena_galleta de avena choco snicker lenny y larry ll</t>
         </is>
       </c>
       <c r="AN220" t="inlineStr">
@@ -44510,12 +44728,12 @@
       </c>
       <c r="AP220" t="inlineStr">
         <is>
-          <t>de_galleta de avena choco snicker lenny y larry ll_0.11</t>
+          <t>avena_galleta de avena choco snicker lenny y larry ll_0.11</t>
         </is>
       </c>
       <c r="AQ220" t="inlineStr">
         <is>
-          <t>de_avena_choco_larry_lenny</t>
+          <t>avena_avena_choco_larry_lenny</t>
         </is>
       </c>
       <c r="AR220" t="n">
@@ -44918,7 +45136,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>De</t>
+          <t>Chocolate</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -44997,12 +45215,12 @@
       <c r="AG223" t="inlineStr"/>
       <c r="AH223" t="inlineStr">
         <is>
-          <t>De</t>
+          <t>Chocolate</t>
         </is>
       </c>
       <c r="AI223" t="inlineStr">
         <is>
-          <t>De</t>
+          <t>Chocolate</t>
         </is>
       </c>
       <c r="AJ223" t="n">
@@ -45016,7 +45234,7 @@
       </c>
       <c r="AM223" t="inlineStr">
         <is>
-          <t>de_galletas de chocolate blanco y macadamia lenny y larry ll</t>
+          <t>chocolate_galletas de chocolate blanco y macadamia lenny y larry ll</t>
         </is>
       </c>
       <c r="AN223" t="inlineStr">
@@ -45031,12 +45249,12 @@
       </c>
       <c r="AP223" t="inlineStr">
         <is>
-          <t>de_galletas de chocolate blanco y macadamia lenny y larry ll_0.11</t>
+          <t>chocolate_galletas de chocolate blanco y macadamia lenny y larry ll_0.11</t>
         </is>
       </c>
       <c r="AQ223" t="inlineStr">
         <is>
-          <t>de_blanco_chocolate_larry_lenny</t>
+          <t>chocolate_blanco_chocolate_larry_lenny</t>
         </is>
       </c>
       <c r="AR223" t="n">
@@ -49477,7 +49695,7 @@
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Lu</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -49556,12 +49774,12 @@
       <c r="AG250" t="inlineStr"/>
       <c r="AH250" t="inlineStr">
         <is>
-          <t>Lu</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="AI250" t="inlineStr">
         <is>
-          <t>Lu</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="AJ250" t="n">
@@ -49813,7 +50031,7 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Lu</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -49888,12 +50106,12 @@
       <c r="AG252" t="inlineStr"/>
       <c r="AH252" t="inlineStr">
         <is>
-          <t>Lu</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="AI252" t="inlineStr">
         <is>
-          <t>Lu</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="AJ252" t="inlineStr"/>
@@ -58042,7 +58260,7 @@
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>De</t>
+          <t>Chocolate</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
@@ -58117,12 +58335,12 @@
       <c r="AG301" t="inlineStr"/>
       <c r="AH301" t="inlineStr">
         <is>
-          <t>De</t>
+          <t>Chocolate</t>
         </is>
       </c>
       <c r="AI301" t="inlineStr">
         <is>
-          <t>De</t>
+          <t>Chocolate</t>
         </is>
       </c>
       <c r="AJ301" t="inlineStr"/>
@@ -58130,7 +58348,7 @@
       <c r="AL301" t="inlineStr"/>
       <c r="AM301" t="inlineStr">
         <is>
-          <t>de_galleta de chocolate chip vegana dbl</t>
+          <t>chocolate_galleta de chocolate chip vegana dbl</t>
         </is>
       </c>
       <c r="AN301" t="inlineStr">
@@ -58145,12 +58363,12 @@
       </c>
       <c r="AP301" t="inlineStr">
         <is>
-          <t>de_galleta de chocolate chip vegana dbl_0.34</t>
+          <t>chocolate_galleta de chocolate chip vegana dbl_0.34</t>
         </is>
       </c>
       <c r="AQ301" t="inlineStr">
         <is>
-          <t>de_chip_chocolate_vegana</t>
+          <t>chocolate_chip_chocolate_vegana</t>
         </is>
       </c>
       <c r="AR301" t="n">
@@ -59064,7 +59282,7 @@
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>De</t>
+          <t>Chocolate</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
@@ -59139,12 +59357,12 @@
       <c r="AG307" t="inlineStr"/>
       <c r="AH307" t="inlineStr">
         <is>
-          <t>De</t>
+          <t>Chocolate</t>
         </is>
       </c>
       <c r="AI307" t="inlineStr">
         <is>
-          <t>De</t>
+          <t>Chocolate</t>
         </is>
       </c>
       <c r="AJ307" t="inlineStr"/>
@@ -59152,7 +59370,7 @@
       <c r="AL307" t="inlineStr"/>
       <c r="AM307" t="inlineStr">
         <is>
-          <t>de_galleta de chocolate chip vegana dbl</t>
+          <t>chocolate_galleta de chocolate chip vegana dbl</t>
         </is>
       </c>
       <c r="AN307" t="inlineStr">
@@ -59167,12 +59385,12 @@
       </c>
       <c r="AP307" t="inlineStr">
         <is>
-          <t>de_galleta de chocolate chip vegana dbl_0.34</t>
+          <t>chocolate_galleta de chocolate chip vegana dbl_0.34</t>
         </is>
       </c>
       <c r="AQ307" t="inlineStr">
         <is>
-          <t>de_chip_chocolate_vegana</t>
+          <t>chocolate_chip_chocolate_vegana</t>
         </is>
       </c>
       <c r="AR307" t="n">
@@ -64697,7 +64915,7 @@
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>Lu</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
@@ -64772,12 +64990,12 @@
       <c r="AG340" t="inlineStr"/>
       <c r="AH340" t="inlineStr">
         <is>
-          <t>Lu</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="AI340" t="inlineStr">
         <is>
-          <t>Lu</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="AJ340" t="inlineStr"/>
@@ -65198,7 +65416,7 @@
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>De</t>
+          <t>Mantequilla</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
@@ -65273,12 +65491,12 @@
       <c r="AG343" t="inlineStr"/>
       <c r="AH343" t="inlineStr">
         <is>
-          <t>De</t>
+          <t>Mantequilla</t>
         </is>
       </c>
       <c r="AI343" t="inlineStr">
         <is>
-          <t>De</t>
+          <t>Mantequilla</t>
         </is>
       </c>
       <c r="AJ343" t="inlineStr"/>
@@ -65286,7 +65504,7 @@
       <c r="AL343" t="inlineStr"/>
       <c r="AM343" t="inlineStr">
         <is>
-          <t>de_galleta de mantequilla lotus</t>
+          <t>mantequilla_galleta de mantequilla lotus</t>
         </is>
       </c>
       <c r="AN343" t="inlineStr">
@@ -65301,12 +65519,12 @@
       </c>
       <c r="AP343" t="inlineStr">
         <is>
-          <t>de_galleta de mantequilla lotus_0.25</t>
+          <t>mantequilla_galleta de mantequilla lotus_0.25</t>
         </is>
       </c>
       <c r="AQ343" t="inlineStr">
         <is>
-          <t>de_lotus_mantequilla</t>
+          <t>mantequilla_lotus_mantequilla</t>
         </is>
       </c>
       <c r="AR343" t="n">
@@ -65363,7 +65581,7 @@
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>De</t>
+          <t>Mantequilla</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
@@ -65438,12 +65656,12 @@
       <c r="AG344" t="inlineStr"/>
       <c r="AH344" t="inlineStr">
         <is>
-          <t>De</t>
+          <t>Mantequilla</t>
         </is>
       </c>
       <c r="AI344" t="inlineStr">
         <is>
-          <t>De</t>
+          <t>Mantequilla</t>
         </is>
       </c>
       <c r="AJ344" t="inlineStr"/>
@@ -65451,7 +65669,7 @@
       <c r="AL344" t="inlineStr"/>
       <c r="AM344" t="inlineStr">
         <is>
-          <t>de_galleta de mantequilla lotus</t>
+          <t>mantequilla_galleta de mantequilla lotus</t>
         </is>
       </c>
       <c r="AN344" t="inlineStr">
@@ -65466,12 +65684,12 @@
       </c>
       <c r="AP344" t="inlineStr">
         <is>
-          <t>de_galleta de mantequilla lotus_0.25</t>
+          <t>mantequilla_galleta de mantequilla lotus_0.25</t>
         </is>
       </c>
       <c r="AQ344" t="inlineStr">
         <is>
-          <t>de_lotus_mantequilla</t>
+          <t>mantequilla_lotus_mantequilla</t>
         </is>
       </c>
       <c r="AR344" t="n">
@@ -65858,7 +66076,7 @@
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>Lu</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
@@ -65933,12 +66151,12 @@
       <c r="AG347" t="inlineStr"/>
       <c r="AH347" t="inlineStr">
         <is>
-          <t>Lu</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="AI347" t="inlineStr">
         <is>
-          <t>Lu</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="AJ347" t="inlineStr"/>
@@ -67401,7 +67619,7 @@
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>De</t>
+          <t>Chocolate</t>
         </is>
       </c>
       <c r="H356" t="inlineStr">
@@ -67480,12 +67698,12 @@
       <c r="AG356" t="inlineStr"/>
       <c r="AH356" t="inlineStr">
         <is>
-          <t>De</t>
+          <t>Chocolate</t>
         </is>
       </c>
       <c r="AI356" t="inlineStr">
         <is>
-          <t>De</t>
+          <t>Chocolate</t>
         </is>
       </c>
       <c r="AJ356" t="n">
@@ -67499,7 +67717,7 @@
       </c>
       <c r="AM356" t="inlineStr">
         <is>
-          <t>de_galletas de chocolate y malvavisco mamut</t>
+          <t>chocolate_galletas de chocolate y malvavisco mamut</t>
         </is>
       </c>
       <c r="AN356" t="inlineStr">
@@ -67514,12 +67732,12 @@
       </c>
       <c r="AP356" t="inlineStr">
         <is>
-          <t>de_galletas de chocolate y malvavisco mamut_0.03</t>
+          <t>chocolate_galletas de chocolate y malvavisco mamut_0.03</t>
         </is>
       </c>
       <c r="AQ356" t="inlineStr">
         <is>
-          <t>de_chocolate_malvavisco_mamut</t>
+          <t>chocolate_chocolate_malvavisco_mamut</t>
         </is>
       </c>
       <c r="AR356" t="n">
@@ -67576,7 +67794,7 @@
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>De</t>
+          <t>Chocolate</t>
         </is>
       </c>
       <c r="H357" t="inlineStr">
@@ -67655,12 +67873,12 @@
       <c r="AG357" t="inlineStr"/>
       <c r="AH357" t="inlineStr">
         <is>
-          <t>De</t>
+          <t>Chocolate</t>
         </is>
       </c>
       <c r="AI357" t="inlineStr">
         <is>
-          <t>De</t>
+          <t>Chocolate</t>
         </is>
       </c>
       <c r="AJ357" t="n">
@@ -67674,7 +67892,7 @@
       </c>
       <c r="AM357" t="inlineStr">
         <is>
-          <t>de_galletas de chocolate y malvavisco mamut</t>
+          <t>chocolate_galletas de chocolate y malvavisco mamut</t>
         </is>
       </c>
       <c r="AN357" t="inlineStr">
@@ -67689,12 +67907,12 @@
       </c>
       <c r="AP357" t="inlineStr">
         <is>
-          <t>de_galletas de chocolate y malvavisco mamut_0.03</t>
+          <t>chocolate_galletas de chocolate y malvavisco mamut_0.03</t>
         </is>
       </c>
       <c r="AQ357" t="inlineStr">
         <is>
-          <t>de_chocolate_malvavisco_mamut</t>
+          <t>chocolate_chocolate_malvavisco_mamut</t>
         </is>
       </c>
       <c r="AR357" t="n">
@@ -67751,7 +67969,7 @@
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>De</t>
+          <t>Chocolate</t>
         </is>
       </c>
       <c r="H358" t="inlineStr">
@@ -67830,12 +68048,12 @@
       <c r="AG358" t="inlineStr"/>
       <c r="AH358" t="inlineStr">
         <is>
-          <t>De</t>
+          <t>Chocolate</t>
         </is>
       </c>
       <c r="AI358" t="inlineStr">
         <is>
-          <t>De</t>
+          <t>Chocolate</t>
         </is>
       </c>
       <c r="AJ358" t="n">
@@ -67849,7 +68067,7 @@
       </c>
       <c r="AM358" t="inlineStr">
         <is>
-          <t>de_galletas de chocolate y malvavisco mamut</t>
+          <t>chocolate_galletas de chocolate y malvavisco mamut</t>
         </is>
       </c>
       <c r="AN358" t="inlineStr">
@@ -67864,12 +68082,12 @@
       </c>
       <c r="AP358" t="inlineStr">
         <is>
-          <t>de_galletas de chocolate y malvavisco mamut_0.03</t>
+          <t>chocolate_galletas de chocolate y malvavisco mamut_0.03</t>
         </is>
       </c>
       <c r="AQ358" t="inlineStr">
         <is>
-          <t>de_chocolate_malvavisco_mamut</t>
+          <t>chocolate_chocolate_malvavisco_mamut</t>
         </is>
       </c>
       <c r="AR358" t="n">
@@ -67926,7 +68144,7 @@
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>De</t>
+          <t>Chocolate</t>
         </is>
       </c>
       <c r="H359" t="inlineStr">
@@ -68005,12 +68223,12 @@
       <c r="AG359" t="inlineStr"/>
       <c r="AH359" t="inlineStr">
         <is>
-          <t>De</t>
+          <t>Chocolate</t>
         </is>
       </c>
       <c r="AI359" t="inlineStr">
         <is>
-          <t>De</t>
+          <t>Chocolate</t>
         </is>
       </c>
       <c r="AJ359" t="n">
@@ -68024,7 +68242,7 @@
       </c>
       <c r="AM359" t="inlineStr">
         <is>
-          <t>de_galletas de chocolate y malvavisco mamut</t>
+          <t>chocolate_galletas de chocolate y malvavisco mamut</t>
         </is>
       </c>
       <c r="AN359" t="inlineStr">
@@ -68039,12 +68257,12 @@
       </c>
       <c r="AP359" t="inlineStr">
         <is>
-          <t>de_galletas de chocolate y malvavisco mamut_0.03</t>
+          <t>chocolate_galletas de chocolate y malvavisco mamut_0.03</t>
         </is>
       </c>
       <c r="AQ359" t="inlineStr">
         <is>
-          <t>de_chocolate_malvavisco_mamut</t>
+          <t>chocolate_chocolate_malvavisco_mamut</t>
         </is>
       </c>
       <c r="AR359" t="n">
@@ -68101,7 +68319,7 @@
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>De</t>
+          <t>Chocolate</t>
         </is>
       </c>
       <c r="H360" t="inlineStr">
@@ -68180,12 +68398,12 @@
       <c r="AG360" t="inlineStr"/>
       <c r="AH360" t="inlineStr">
         <is>
-          <t>De</t>
+          <t>Chocolate</t>
         </is>
       </c>
       <c r="AI360" t="inlineStr">
         <is>
-          <t>De</t>
+          <t>Chocolate</t>
         </is>
       </c>
       <c r="AJ360" t="n">
@@ -68199,7 +68417,7 @@
       </c>
       <c r="AM360" t="inlineStr">
         <is>
-          <t>de_galletas de chocolate y malvavisco mamut</t>
+          <t>chocolate_galletas de chocolate y malvavisco mamut</t>
         </is>
       </c>
       <c r="AN360" t="inlineStr">
@@ -68214,12 +68432,12 @@
       </c>
       <c r="AP360" t="inlineStr">
         <is>
-          <t>de_galletas de chocolate y malvavisco mamut_0.03</t>
+          <t>chocolate_galletas de chocolate y malvavisco mamut_0.03</t>
         </is>
       </c>
       <c r="AQ360" t="inlineStr">
         <is>
-          <t>de_chocolate_malvavisco_mamut</t>
+          <t>chocolate_chocolate_malvavisco_mamut</t>
         </is>
       </c>
       <c r="AR360" t="n">
@@ -69123,7 +69341,7 @@
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>De</t>
+          <t>Chocolate</t>
         </is>
       </c>
       <c r="H366" t="inlineStr">
@@ -69202,12 +69420,12 @@
       <c r="AG366" t="inlineStr"/>
       <c r="AH366" t="inlineStr">
         <is>
-          <t>De</t>
+          <t>Chocolate</t>
         </is>
       </c>
       <c r="AI366" t="inlineStr">
         <is>
-          <t>De</t>
+          <t>Chocolate</t>
         </is>
       </c>
       <c r="AJ366" t="n">
@@ -69221,7 +69439,7 @@
       </c>
       <c r="AM366" t="inlineStr">
         <is>
-          <t>de_galletas de chocolate y malvavisco mamut</t>
+          <t>chocolate_galletas de chocolate y malvavisco mamut</t>
         </is>
       </c>
       <c r="AN366" t="inlineStr">
@@ -69236,12 +69454,12 @@
       </c>
       <c r="AP366" t="inlineStr">
         <is>
-          <t>de_galletas de chocolate y malvavisco mamut_0.03</t>
+          <t>chocolate_galletas de chocolate y malvavisco mamut_0.03</t>
         </is>
       </c>
       <c r="AQ366" t="inlineStr">
         <is>
-          <t>de_chocolate_malvavisco_mamut</t>
+          <t>chocolate_chocolate_malvavisco_mamut</t>
         </is>
       </c>
       <c r="AR366" t="n">
@@ -69298,7 +69516,7 @@
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>De</t>
+          <t>Chocolate</t>
         </is>
       </c>
       <c r="H367" t="inlineStr">
@@ -69377,12 +69595,12 @@
       <c r="AG367" t="inlineStr"/>
       <c r="AH367" t="inlineStr">
         <is>
-          <t>De</t>
+          <t>Chocolate</t>
         </is>
       </c>
       <c r="AI367" t="inlineStr">
         <is>
-          <t>De</t>
+          <t>Chocolate</t>
         </is>
       </c>
       <c r="AJ367" t="n">
@@ -69396,7 +69614,7 @@
       </c>
       <c r="AM367" t="inlineStr">
         <is>
-          <t>de_galletas de chocolate y malvavisco mamut</t>
+          <t>chocolate_galletas de chocolate y malvavisco mamut</t>
         </is>
       </c>
       <c r="AN367" t="inlineStr">
@@ -69411,12 +69629,12 @@
       </c>
       <c r="AP367" t="inlineStr">
         <is>
-          <t>de_galletas de chocolate y malvavisco mamut_0.03</t>
+          <t>chocolate_galletas de chocolate y malvavisco mamut_0.03</t>
         </is>
       </c>
       <c r="AQ367" t="inlineStr">
         <is>
-          <t>de_chocolate_malvavisco_mamut</t>
+          <t>chocolate_chocolate_malvavisco_mamut</t>
         </is>
       </c>
       <c r="AR367" t="n">
@@ -78128,7 +78346,7 @@
       </c>
       <c r="G419" t="inlineStr">
         <is>
-          <t>De</t>
+          <t>Caramelo</t>
         </is>
       </c>
       <c r="H419" t="inlineStr">
@@ -78203,12 +78421,12 @@
       <c r="AG419" t="inlineStr"/>
       <c r="AH419" t="inlineStr">
         <is>
-          <t>De</t>
+          <t>Caramelo</t>
         </is>
       </c>
       <c r="AI419" t="inlineStr">
         <is>
-          <t>De</t>
+          <t>Caramelo</t>
         </is>
       </c>
       <c r="AJ419" t="inlineStr"/>
@@ -78216,7 +78434,7 @@
       <c r="AL419" t="inlineStr"/>
       <c r="AM419" t="inlineStr">
         <is>
-          <t>de_galleta de caramelo y mani bergen</t>
+          <t>caramelo_galleta de caramelo y mani bergen</t>
         </is>
       </c>
       <c r="AN419" t="inlineStr">
@@ -78231,12 +78449,12 @@
       </c>
       <c r="AP419" t="inlineStr">
         <is>
-          <t>de_galleta de caramelo y mani bergen_0.13</t>
+          <t>caramelo_galleta de caramelo y mani bergen_0.13</t>
         </is>
       </c>
       <c r="AQ419" t="inlineStr">
         <is>
-          <t>de_bergen_caramelo_mani</t>
+          <t>caramelo_bergen_caramelo_mani</t>
         </is>
       </c>
       <c r="AR419" t="n">
@@ -78293,7 +78511,7 @@
       </c>
       <c r="G420" t="inlineStr">
         <is>
-          <t>De</t>
+          <t>Caramelo</t>
         </is>
       </c>
       <c r="H420" t="inlineStr">
@@ -78368,12 +78586,12 @@
       <c r="AG420" t="inlineStr"/>
       <c r="AH420" t="inlineStr">
         <is>
-          <t>De</t>
+          <t>Caramelo</t>
         </is>
       </c>
       <c r="AI420" t="inlineStr">
         <is>
-          <t>De</t>
+          <t>Caramelo</t>
         </is>
       </c>
       <c r="AJ420" t="inlineStr"/>
@@ -78381,7 +78599,7 @@
       <c r="AL420" t="inlineStr"/>
       <c r="AM420" t="inlineStr">
         <is>
-          <t>de_galleta de caramelo y mani bergen</t>
+          <t>caramelo_galleta de caramelo y mani bergen</t>
         </is>
       </c>
       <c r="AN420" t="inlineStr">
@@ -78396,12 +78614,12 @@
       </c>
       <c r="AP420" t="inlineStr">
         <is>
-          <t>de_galleta de caramelo y mani bergen_0.13</t>
+          <t>caramelo_galleta de caramelo y mani bergen_0.13</t>
         </is>
       </c>
       <c r="AQ420" t="inlineStr">
         <is>
-          <t>de_bergen_caramelo_mani</t>
+          <t>caramelo_bergen_caramelo_mani</t>
         </is>
       </c>
       <c r="AR420" t="n">
@@ -78800,7 +79018,7 @@
       </c>
       <c r="G423" t="inlineStr">
         <is>
-          <t>De</t>
+          <t>Caramelo</t>
         </is>
       </c>
       <c r="H423" t="inlineStr">
@@ -78875,12 +79093,12 @@
       <c r="AG423" t="inlineStr"/>
       <c r="AH423" t="inlineStr">
         <is>
-          <t>De</t>
+          <t>Caramelo</t>
         </is>
       </c>
       <c r="AI423" t="inlineStr">
         <is>
-          <t>De</t>
+          <t>Caramelo</t>
         </is>
       </c>
       <c r="AJ423" t="inlineStr"/>
@@ -78888,7 +79106,7 @@
       <c r="AL423" t="inlineStr"/>
       <c r="AM423" t="inlineStr">
         <is>
-          <t>de_galleta de caramelo y mani bergen</t>
+          <t>caramelo_galleta de caramelo y mani bergen</t>
         </is>
       </c>
       <c r="AN423" t="inlineStr">
@@ -78903,12 +79121,12 @@
       </c>
       <c r="AP423" t="inlineStr">
         <is>
-          <t>de_galleta de caramelo y mani bergen_0.13</t>
+          <t>caramelo_galleta de caramelo y mani bergen_0.13</t>
         </is>
       </c>
       <c r="AQ423" t="inlineStr">
         <is>
-          <t>de_bergen_caramelo_mani</t>
+          <t>caramelo_bergen_caramelo_mani</t>
         </is>
       </c>
       <c r="AR423" t="n">
@@ -79476,7 +79694,7 @@
       </c>
       <c r="G427" t="inlineStr">
         <is>
-          <t>De</t>
+          <t>Chocolate</t>
         </is>
       </c>
       <c r="H427" t="inlineStr">
@@ -79555,12 +79773,12 @@
       <c r="AG427" t="inlineStr"/>
       <c r="AH427" t="inlineStr">
         <is>
-          <t>De</t>
+          <t>Chocolate</t>
         </is>
       </c>
       <c r="AI427" t="inlineStr">
         <is>
-          <t>De</t>
+          <t>Chocolate</t>
         </is>
       </c>
       <c r="AJ427" t="n">
@@ -79570,7 +79788,7 @@
       <c r="AL427" t="inlineStr"/>
       <c r="AM427" t="inlineStr">
         <is>
-          <t>de_galleta de chocolate chip mini candy cravn</t>
+          <t>chocolate_galleta de chocolate chip mini candy cravn</t>
         </is>
       </c>
       <c r="AN427" t="inlineStr">
@@ -79585,12 +79803,12 @@
       </c>
       <c r="AP427" t="inlineStr">
         <is>
-          <t>de_galleta de chocolate chip mini candy cravn_0.35</t>
+          <t>chocolate_galleta de chocolate chip mini candy cravn_0.35</t>
         </is>
       </c>
       <c r="AQ427" t="inlineStr">
         <is>
-          <t>de_candy_chip_chocolate_cravn</t>
+          <t>chocolate_candy_chip_chocolate_cravn</t>
         </is>
       </c>
       <c r="AR427" t="n">
@@ -83226,7 +83444,7 @@
       </c>
       <c r="G449" t="inlineStr">
         <is>
-          <t>Lu</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="H449" t="inlineStr">
@@ -83307,12 +83525,12 @@
       <c r="AG449" t="inlineStr"/>
       <c r="AH449" t="inlineStr">
         <is>
-          <t>Lu</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="AI449" t="inlineStr">
         <is>
-          <t>Lu</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="AJ449" t="n">

--- a/streamlit_data/regional_insights.xlsx
+++ b/streamlit_data/regional_insights.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E152"/>
+  <dimension ref="A1:E153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,7 +456,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C2" t="n">
         <v>3</v>
@@ -465,7 +465,7 @@
         <v>6</v>
       </c>
       <c r="E2" t="n">
-        <v>16.91311029719778</v>
+        <v>16.92954930121386</v>
       </c>
     </row>
     <row r="3">
@@ -1269,7 +1269,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Doritos</t>
+          <t>El Charrito</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -1281,14 +1281,12 @@
       <c r="D45" t="n">
         <v>1</v>
       </c>
-      <c r="E45" t="n">
-        <v>21.83213295019938</v>
-      </c>
+      <c r="E45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Keebler</t>
+          <t>Doritos</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -1298,16 +1296,16 @@
         <v>1</v>
       </c>
       <c r="D46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E46" t="n">
-        <v>16.53</v>
+        <v>21.83213295019938</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>El Charrito</t>
+          <t>Keebler</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -1317,9 +1315,11 @@
         <v>1</v>
       </c>
       <c r="D47" t="n">
-        <v>1</v>
-      </c>
-      <c r="E47" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="E47" t="n">
+        <v>16.53</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1343,81 +1343,81 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>La Real</t>
+          <t>Pillsbury</t>
         </is>
       </c>
       <c r="B49" t="n">
         <v>9</v>
       </c>
       <c r="C49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E49" t="n">
-        <v>12.46</v>
+        <v>7.764285714285714</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Pillsbury</t>
+          <t>La Real</t>
         </is>
       </c>
       <c r="B50" t="n">
         <v>9</v>
       </c>
       <c r="C50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>7.764285714285714</v>
+        <v>12.46</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Biskitop</t>
+          <t>Siete</t>
         </is>
       </c>
       <c r="B51" t="n">
         <v>8</v>
       </c>
       <c r="C51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D51" t="n">
         <v>2</v>
       </c>
-      <c r="E51" t="inlineStr"/>
+      <c r="E51" t="n">
+        <v>44.83675833138952</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Siete</t>
+          <t>Biskitop</t>
         </is>
       </c>
       <c r="B52" t="n">
         <v>8</v>
       </c>
       <c r="C52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D52" t="n">
         <v>2</v>
       </c>
-      <c r="E52" t="n">
-        <v>44.83675833138952</v>
-      </c>
+      <c r="E52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Festival</t>
+          <t>Golden</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -1427,16 +1427,14 @@
         <v>1</v>
       </c>
       <c r="D53" t="n">
-        <v>1</v>
-      </c>
-      <c r="E53" t="n">
-        <v>9.385016025641024</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="E53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Golden</t>
+          <t>Nature'S Own</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -1446,14 +1444,16 @@
         <v>1</v>
       </c>
       <c r="D54" t="n">
-        <v>2</v>
-      </c>
-      <c r="E54" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E54" t="n">
+        <v>7.755714285714285</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Walkers</t>
+          <t>Princesa</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -1463,16 +1463,16 @@
         <v>1</v>
       </c>
       <c r="D55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E55" t="n">
-        <v>97.43589743589745</v>
+        <v>3.535714285714286</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Princesa</t>
+          <t>Biscotto</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -1482,16 +1482,16 @@
         <v>1</v>
       </c>
       <c r="D56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E56" t="n">
-        <v>3.535714285714286</v>
+        <v>25</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Kidsmania</t>
+          <t>Walkers</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -1501,14 +1501,16 @@
         <v>1</v>
       </c>
       <c r="D57" t="n">
-        <v>1</v>
-      </c>
-      <c r="E57" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="E57" t="n">
+        <v>97.43589743589745</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Nature'S Own</t>
+          <t>Festival</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -1521,13 +1523,13 @@
         <v>1</v>
       </c>
       <c r="E58" t="n">
-        <v>7.755714285714285</v>
+        <v>9.385016025641024</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Biscotto</t>
+          <t>Kidsmania</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -1537,16 +1539,14 @@
         <v>1</v>
       </c>
       <c r="D59" t="n">
-        <v>2</v>
-      </c>
-      <c r="E59" t="n">
-        <v>25</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="E59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Sunshine</t>
+          <t>Laurieri</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -1556,16 +1556,16 @@
         <v>1</v>
       </c>
       <c r="D60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>9.488333333333333</v>
+        <v>20.65978352354142</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Kugi</t>
+          <t>Mr Bakewell</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -1582,24 +1582,26 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Mr Bakewell</t>
+          <t>Cheetos</t>
         </is>
       </c>
       <c r="B62" t="n">
         <v>6</v>
       </c>
       <c r="C62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D62" t="n">
         <v>1</v>
       </c>
-      <c r="E62" t="inlineStr"/>
+      <c r="E62" t="n">
+        <v>24.41444882993455</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Laurieri</t>
+          <t>Cadbury</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -1611,27 +1613,25 @@
       <c r="D63" t="n">
         <v>2</v>
       </c>
-      <c r="E63" t="n">
-        <v>20.65978352354142</v>
-      </c>
+      <c r="E63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Cheetos</t>
+          <t>Sunshine</t>
         </is>
       </c>
       <c r="B64" t="n">
         <v>6</v>
       </c>
       <c r="C64" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D64" t="n">
         <v>1</v>
       </c>
       <c r="E64" t="n">
-        <v>24.41444882993455</v>
+        <v>9.488333333333333</v>
       </c>
     </row>
     <row r="65">
@@ -1654,7 +1654,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Cadbury</t>
+          <t>Kugi</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -1664,14 +1664,14 @@
         <v>1</v>
       </c>
       <c r="D66" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>La Libanesa</t>
+          <t>Hosttes</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -1683,7 +1683,9 @@
       <c r="D67" t="n">
         <v>1</v>
       </c>
-      <c r="E67" t="inlineStr"/>
+      <c r="E67" t="n">
+        <v>36.83418646645511</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1707,20 +1709,20 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Bolletje</t>
+          <t>Schar</t>
         </is>
       </c>
       <c r="B69" t="n">
         <v>5</v>
       </c>
       <c r="C69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D69" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E69" t="n">
-        <v>29.40549939726599</v>
+        <v>24.18904950998269</v>
       </c>
     </row>
     <row r="70">
@@ -1743,26 +1745,26 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Schar</t>
+          <t>Bolletje</t>
         </is>
       </c>
       <c r="B71" t="n">
         <v>5</v>
       </c>
       <c r="C71" t="n">
+        <v>1</v>
+      </c>
+      <c r="D71" t="n">
         <v>2</v>
       </c>
-      <c r="D71" t="n">
-        <v>3</v>
-      </c>
       <c r="E71" t="n">
-        <v>24.18904950998269</v>
+        <v>29.40549939726599</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Tiffany</t>
+          <t>Triskits</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -1779,7 +1781,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Hosttes</t>
+          <t>La Libanesa</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -1791,14 +1793,12 @@
       <c r="D73" t="n">
         <v>1</v>
       </c>
-      <c r="E73" t="n">
-        <v>36.83418646645511</v>
-      </c>
+      <c r="E73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Triskits</t>
+          <t>Tiffany</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -1834,7 +1834,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Keeber</t>
+          <t>Otis Spunkmeyer</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -1844,35 +1844,33 @@
         <v>1</v>
       </c>
       <c r="D76" t="n">
-        <v>3</v>
-      </c>
-      <c r="E76" t="n">
-        <v>28.61772083892403</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="E76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Takis</t>
+          <t>Nestle</t>
         </is>
       </c>
       <c r="B77" t="n">
         <v>4</v>
       </c>
       <c r="C77" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D77" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E77" t="n">
-        <v>41.86</v>
+        <v>41.70528266913809</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Nestle</t>
+          <t>Ovaltine</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -1882,16 +1880,16 @@
         <v>1</v>
       </c>
       <c r="D78" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E78" t="n">
-        <v>41.70528266913809</v>
+        <v>19.9445103354795</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Otis Spunkmeyer</t>
+          <t>Herrs</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -1901,14 +1899,16 @@
         <v>1</v>
       </c>
       <c r="D79" t="n">
-        <v>2</v>
-      </c>
-      <c r="E79" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E79" t="n">
+        <v>37.30902864926393</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Ovaltine</t>
+          <t>Buenhorno</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -1920,52 +1920,50 @@
       <c r="D80" t="n">
         <v>1</v>
       </c>
-      <c r="E80" t="n">
-        <v>19.9445103354795</v>
-      </c>
+      <c r="E80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Snyder’S</t>
+          <t>Glutino</t>
         </is>
       </c>
       <c r="B81" t="n">
         <v>4</v>
       </c>
       <c r="C81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D81" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E81" t="n">
-        <v>21.8340355175269</v>
+        <v>19.41435404641845</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Glutino</t>
+          <t>Keeber</t>
         </is>
       </c>
       <c r="B82" t="n">
         <v>4</v>
       </c>
       <c r="C82" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D82" t="n">
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>19.41435404641845</v>
+        <v>28.61772083892403</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Buenhorno</t>
+          <t>Snyder’S</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -1977,31 +1975,33 @@
       <c r="D83" t="n">
         <v>1</v>
       </c>
-      <c r="E83" t="inlineStr"/>
+      <c r="E83" t="n">
+        <v>21.8340355175269</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Herrs</t>
+          <t>Takis</t>
         </is>
       </c>
       <c r="B84" t="n">
         <v>4</v>
       </c>
       <c r="C84" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D84" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>37.30902864926393</v>
+        <v>41.86</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Flourish</t>
+          <t>Dux</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -2018,24 +2018,26 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Dux</t>
+          <t>Hostess</t>
         </is>
       </c>
       <c r="B86" t="n">
         <v>3</v>
       </c>
       <c r="C86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D86" t="n">
-        <v>1</v>
-      </c>
-      <c r="E86" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="E86" t="n">
+        <v>18.15097496514973</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Waitrose</t>
+          <t>Snyders</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -2045,14 +2047,14 @@
         <v>1</v>
       </c>
       <c r="D87" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Chetos</t>
+          <t>Del-E</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -2062,7 +2064,7 @@
         <v>1</v>
       </c>
       <c r="D88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E88" t="inlineStr"/>
     </row>
@@ -2088,7 +2090,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Van Der Meulen</t>
+          <t>Flourish</t>
         </is>
       </c>
       <c r="B90" t="n">
@@ -2100,14 +2102,12 @@
       <c r="D90" t="n">
         <v>1</v>
       </c>
-      <c r="E90" t="n">
-        <v>12.12155070255629</v>
-      </c>
+      <c r="E90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Snyders</t>
+          <t>Waitrose</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -2117,33 +2117,33 @@
         <v>1</v>
       </c>
       <c r="D91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Hostess</t>
+          <t>Van Der Meulen</t>
         </is>
       </c>
       <c r="B92" t="n">
         <v>3</v>
       </c>
       <c r="C92" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D92" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E92" t="n">
-        <v>18.15097496514973</v>
+        <v>12.12155070255629</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Del-E</t>
+          <t>Chetos</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -2153,14 +2153,14 @@
         <v>1</v>
       </c>
       <c r="D93" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Voortman</t>
+          <t>Ricola</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -2173,13 +2173,13 @@
         <v>1</v>
       </c>
       <c r="E94" t="n">
-        <v>20.17345399698341</v>
+        <v>7.351955307262569</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Ricola</t>
+          <t>Wala</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -2191,14 +2191,12 @@
       <c r="D95" t="n">
         <v>1</v>
       </c>
-      <c r="E95" t="n">
-        <v>7.351955307262569</v>
-      </c>
+      <c r="E95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Vigo</t>
+          <t>Voortman</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -2211,13 +2209,13 @@
         <v>1</v>
       </c>
       <c r="E96" t="n">
-        <v>9.433248720978664</v>
+        <v>20.17345399698341</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Wala</t>
+          <t>Werther’S</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -2234,7 +2232,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Werther’S</t>
+          <t>Vigo</t>
         </is>
       </c>
       <c r="B98" t="n">
@@ -2246,12 +2244,14 @@
       <c r="D98" t="n">
         <v>1</v>
       </c>
-      <c r="E98" t="inlineStr"/>
+      <c r="E98" t="n">
+        <v>9.433248720978664</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Willie</t>
+          <t>Sara Lee</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -2263,12 +2263,14 @@
       <c r="D99" t="n">
         <v>1</v>
       </c>
-      <c r="E99" t="inlineStr"/>
+      <c r="E99" t="n">
+        <v>24.085</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Beivita</t>
+          <t>Dried</t>
         </is>
       </c>
       <c r="B100" t="n">
@@ -2278,16 +2280,14 @@
         <v>1</v>
       </c>
       <c r="D100" t="n">
-        <v>1</v>
-      </c>
-      <c r="E100" t="n">
-        <v>35.19230769230769</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="E100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Tuc</t>
+          <t>Willie</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -2299,14 +2299,12 @@
       <c r="D101" t="n">
         <v>1</v>
       </c>
-      <c r="E101" t="n">
-        <v>7.575418994413408</v>
-      </c>
+      <c r="E101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Soldanza</t>
+          <t>Beivita</t>
         </is>
       </c>
       <c r="B102" t="n">
@@ -2318,12 +2316,14 @@
       <c r="D102" t="n">
         <v>1</v>
       </c>
-      <c r="E102" t="inlineStr"/>
+      <c r="E102" t="n">
+        <v>35.19230769230769</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Cheez</t>
+          <t>Tuc</t>
         </is>
       </c>
       <c r="B103" t="n">
@@ -2335,12 +2335,14 @@
       <c r="D103" t="n">
         <v>1</v>
       </c>
-      <c r="E103" t="inlineStr"/>
+      <c r="E103" t="n">
+        <v>7.575418994413408</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Sara Lee</t>
+          <t>Soldanza</t>
         </is>
       </c>
       <c r="B104" t="n">
@@ -2352,14 +2354,12 @@
       <c r="D104" t="n">
         <v>1</v>
       </c>
-      <c r="E104" t="n">
-        <v>24.085</v>
-      </c>
+      <c r="E104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Knotts</t>
+          <t>Glad</t>
         </is>
       </c>
       <c r="B105" t="n">
@@ -2376,7 +2376,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Danisha</t>
+          <t>Cheez</t>
         </is>
       </c>
       <c r="B106" t="n">
@@ -2393,7 +2393,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Hills</t>
+          <t>Mars</t>
         </is>
       </c>
       <c r="B107" t="n">
@@ -2410,7 +2410,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Dairy</t>
+          <t>Danisha</t>
         </is>
       </c>
       <c r="B108" t="n">
@@ -2427,7 +2427,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>La Tortilla Factory</t>
+          <t>Hinged</t>
         </is>
       </c>
       <c r="B109" t="n">
@@ -2440,13 +2440,13 @@
         <v>1</v>
       </c>
       <c r="E109" t="n">
-        <v>21.71</v>
+        <v>1.907848055928269</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Hinged</t>
+          <t>Hills</t>
         </is>
       </c>
       <c r="B110" t="n">
@@ -2458,14 +2458,12 @@
       <c r="D110" t="n">
         <v>1</v>
       </c>
-      <c r="E110" t="n">
-        <v>1.907848055928269</v>
-      </c>
+      <c r="E110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Crunchmaster</t>
+          <t>La Tortilla Factory</t>
         </is>
       </c>
       <c r="B111" t="n">
@@ -2478,7 +2476,7 @@
         <v>1</v>
       </c>
       <c r="E111" t="n">
-        <v>51.37009840929231</v>
+        <v>21.71</v>
       </c>
     </row>
     <row r="112">
@@ -2503,14 +2501,14 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Mars</t>
+          <t>Nature Valley</t>
         </is>
       </c>
       <c r="B113" t="n">
         <v>2</v>
       </c>
       <c r="C113" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D113" t="n">
         <v>1</v>
@@ -2520,14 +2518,14 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Nature Valley</t>
+          <t>Dairy</t>
         </is>
       </c>
       <c r="B114" t="n">
         <v>2</v>
       </c>
       <c r="C114" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D114" t="n">
         <v>1</v>
@@ -2537,7 +2535,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Dried</t>
+          <t>Crunchmaster</t>
         </is>
       </c>
       <c r="B115" t="n">
@@ -2547,14 +2545,16 @@
         <v>1</v>
       </c>
       <c r="D115" t="n">
-        <v>2</v>
-      </c>
-      <c r="E115" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E115" t="n">
+        <v>51.37009840929231</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Glad</t>
+          <t>Knotts</t>
         </is>
       </c>
       <c r="B116" t="n">
@@ -2588,7 +2588,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Vegefarm</t>
+          <t>Badia</t>
         </is>
       </c>
       <c r="B118" t="n">
@@ -2600,14 +2600,12 @@
       <c r="D118" t="n">
         <v>1</v>
       </c>
-      <c r="E118" t="n">
-        <v>27.42714334124026</v>
-      </c>
+      <c r="E118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Kimberley's Bakeshoppe</t>
+          <t>King's Hawaiian</t>
         </is>
       </c>
       <c r="B119" t="n">
@@ -2624,7 +2622,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Highland</t>
+          <t>Holiday</t>
         </is>
       </c>
       <c r="B120" t="n">
@@ -2641,7 +2639,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Hershey</t>
+          <t>Kimberley's Bakeshoppe</t>
         </is>
       </c>
       <c r="B121" t="n">
@@ -2653,14 +2651,12 @@
       <c r="D121" t="n">
         <v>1</v>
       </c>
-      <c r="E121" t="n">
-        <v>19.07848055928269</v>
-      </c>
+      <c r="E121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Goldfish</t>
+          <t>Twizzlers</t>
         </is>
       </c>
       <c r="B122" t="n">
@@ -2672,14 +2668,12 @@
       <c r="D122" t="n">
         <v>1</v>
       </c>
-      <c r="E122" t="n">
-        <v>15.39664804469274</v>
-      </c>
+      <c r="E122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Haagen Daz</t>
+          <t>Hollandia</t>
         </is>
       </c>
       <c r="B123" t="n">
@@ -2691,12 +2685,14 @@
       <c r="D123" t="n">
         <v>1</v>
       </c>
-      <c r="E123" t="inlineStr"/>
+      <c r="E123" t="n">
+        <v>52.34878150009826</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Twizzlers</t>
+          <t>Jumbo</t>
         </is>
       </c>
       <c r="B124" t="n">
@@ -2708,12 +2704,14 @@
       <c r="D124" t="n">
         <v>1</v>
       </c>
-      <c r="E124" t="inlineStr"/>
+      <c r="E124" t="n">
+        <v>11.48504273504274</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Haribo</t>
+          <t>Cusano´s</t>
         </is>
       </c>
       <c r="B125" t="n">
@@ -2730,7 +2728,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Holiday</t>
+          <t>Triscuit</t>
         </is>
       </c>
       <c r="B126" t="n">
@@ -2742,12 +2740,14 @@
       <c r="D126" t="n">
         <v>1</v>
       </c>
-      <c r="E126" t="inlineStr"/>
+      <c r="E126" t="n">
+        <v>21.76632743949854</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Give &amp; Go</t>
+          <t>Ducales</t>
         </is>
       </c>
       <c r="B127" t="n">
@@ -2759,12 +2759,14 @@
       <c r="D127" t="n">
         <v>1</v>
       </c>
-      <c r="E127" t="inlineStr"/>
+      <c r="E127" t="n">
+        <v>21.76632743949854</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Ducales</t>
+          <t>Give &amp; Go</t>
         </is>
       </c>
       <c r="B128" t="n">
@@ -2776,14 +2778,12 @@
       <c r="D128" t="n">
         <v>1</v>
       </c>
-      <c r="E128" t="n">
-        <v>21.76632743949854</v>
-      </c>
+      <c r="E128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Triscuit</t>
+          <t>Lewis Bake Shop</t>
         </is>
       </c>
       <c r="B129" t="n">
@@ -2796,13 +2796,13 @@
         <v>1</v>
       </c>
       <c r="E129" t="n">
-        <v>21.76632743949854</v>
+        <v>3.284356678113635</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Hollandia</t>
+          <t>Vegefarm</t>
         </is>
       </c>
       <c r="B130" t="n">
@@ -2815,13 +2815,13 @@
         <v>1</v>
       </c>
       <c r="E130" t="n">
-        <v>52.34878150009826</v>
+        <v>27.42714334124026</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Jumbo</t>
+          <t>Chester</t>
         </is>
       </c>
       <c r="B131" t="n">
@@ -2833,14 +2833,12 @@
       <c r="D131" t="n">
         <v>1</v>
       </c>
-      <c r="E131" t="n">
-        <v>11.48504273504274</v>
-      </c>
+      <c r="E131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Double Duty</t>
+          <t>Marie</t>
         </is>
       </c>
       <c r="B132" t="n">
@@ -2857,7 +2855,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Cho Cho</t>
+          <t>Ortega</t>
         </is>
       </c>
       <c r="B133" t="n">
@@ -2869,12 +2867,14 @@
       <c r="D133" t="n">
         <v>1</v>
       </c>
-      <c r="E133" t="inlineStr"/>
+      <c r="E133" t="n">
+        <v>10.91045974485786</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>King's Hawaiian</t>
+          <t>Oscar Mayer</t>
         </is>
       </c>
       <c r="B134" t="n">
@@ -2886,12 +2886,14 @@
       <c r="D134" t="n">
         <v>1</v>
       </c>
-      <c r="E134" t="inlineStr"/>
+      <c r="E134" t="n">
+        <v>21.70707121411719</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Members Selection</t>
+          <t>Hershey</t>
         </is>
       </c>
       <c r="B135" t="n">
@@ -2903,12 +2905,14 @@
       <c r="D135" t="n">
         <v>1</v>
       </c>
-      <c r="E135" t="inlineStr"/>
+      <c r="E135" t="n">
+        <v>19.07848055928269</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Ortega</t>
+          <t>Cho Cho</t>
         </is>
       </c>
       <c r="B136" t="n">
@@ -2920,14 +2924,12 @@
       <c r="D136" t="n">
         <v>1</v>
       </c>
-      <c r="E136" t="n">
-        <v>10.91045974485786</v>
-      </c>
+      <c r="E136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Oscar Mayer</t>
+          <t>Nerds</t>
         </is>
       </c>
       <c r="B137" t="n">
@@ -2939,14 +2941,12 @@
       <c r="D137" t="n">
         <v>1</v>
       </c>
-      <c r="E137" t="n">
-        <v>21.70707121411719</v>
-      </c>
+      <c r="E137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Nerds</t>
+          <t>Highland</t>
         </is>
       </c>
       <c r="B138" t="n">
@@ -2963,7 +2963,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Choppers</t>
+          <t>Haribo</t>
         </is>
       </c>
       <c r="B139" t="n">
@@ -2980,7 +2980,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Ferrero</t>
+          <t>Haagen Daz</t>
         </is>
       </c>
       <c r="B140" t="n">
@@ -2997,7 +2997,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Chowmein</t>
+          <t>Post</t>
         </is>
       </c>
       <c r="B141" t="n">
@@ -3009,12 +3009,14 @@
       <c r="D141" t="n">
         <v>1</v>
       </c>
-      <c r="E141" t="inlineStr"/>
+      <c r="E141" t="n">
+        <v>7.51</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Cloverhill</t>
+          <t>Double Duty</t>
         </is>
       </c>
       <c r="B142" t="n">
@@ -3031,7 +3033,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Mcvitie'S</t>
+          <t>Reynolds</t>
         </is>
       </c>
       <c r="B143" t="n">
@@ -3043,14 +3045,12 @@
       <c r="D143" t="n">
         <v>1</v>
       </c>
-      <c r="E143" t="n">
-        <v>37.62485187066193</v>
-      </c>
+      <c r="E143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Badia</t>
+          <t>Choppers</t>
         </is>
       </c>
       <c r="B144" t="n">
@@ -3067,7 +3067,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Reynolds</t>
+          <t>Ferrero</t>
         </is>
       </c>
       <c r="B145" t="n">
@@ -3084,7 +3084,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Marie</t>
+          <t>Ruffles</t>
         </is>
       </c>
       <c r="B146" t="n">
@@ -3096,12 +3096,14 @@
       <c r="D146" t="n">
         <v>1</v>
       </c>
-      <c r="E146" t="inlineStr"/>
+      <c r="E146" t="n">
+        <v>20.12215858124287</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Ruffles</t>
+          <t>Chowmein</t>
         </is>
       </c>
       <c r="B147" t="n">
@@ -3113,14 +3115,12 @@
       <c r="D147" t="n">
         <v>1</v>
       </c>
-      <c r="E147" t="n">
-        <v>20.12215858124287</v>
-      </c>
+      <c r="E147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Lewis Bake Shop</t>
+          <t>Goldfish</t>
         </is>
       </c>
       <c r="B148" t="n">
@@ -3133,13 +3133,13 @@
         <v>1</v>
       </c>
       <c r="E148" t="n">
-        <v>3.284356678113635</v>
+        <v>15.39664804469274</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Cusano´s</t>
+          <t>Cloverhill</t>
         </is>
       </c>
       <c r="B149" t="n">
@@ -3175,7 +3175,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Chester</t>
+          <t>Members Selection</t>
         </is>
       </c>
       <c r="B151" t="n">
@@ -3192,19 +3192,38 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
+          <t>Mcvitie'S</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>1</v>
+      </c>
+      <c r="C152" t="n">
+        <v>1</v>
+      </c>
+      <c r="D152" t="n">
+        <v>1</v>
+      </c>
+      <c r="E152" t="n">
+        <v>37.62485187066193</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
           <t>Fernandes</t>
         </is>
       </c>
-      <c r="B152" t="n">
-        <v>1</v>
-      </c>
-      <c r="C152" t="n">
-        <v>1</v>
-      </c>
-      <c r="D152" t="n">
-        <v>1</v>
-      </c>
-      <c r="E152" t="inlineStr"/>
+      <c r="B153" t="n">
+        <v>1</v>
+      </c>
+      <c r="C153" t="n">
+        <v>1</v>
+      </c>
+      <c r="D153" t="n">
+        <v>1</v>
+      </c>
+      <c r="E153" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/streamlit_data/regional_insights.xlsx
+++ b/streamlit_data/regional_insights.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E162"/>
+  <dimension ref="A1:E166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,7 +456,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>785</v>
+        <v>747</v>
       </c>
       <c r="C2" t="n">
         <v>3</v>
@@ -465,7 +465,7 @@
         <v>6</v>
       </c>
       <c r="E2" t="n">
-        <v>16.83975842641787</v>
+        <v>16.94884964459087</v>
       </c>
     </row>
     <row r="3">
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C9" t="n">
         <v>2</v>
@@ -598,7 +598,7 @@
         <v>5</v>
       </c>
       <c r="E9" t="n">
-        <v>18.17607494328508</v>
+        <v>17.99949631927472</v>
       </c>
     </row>
     <row r="10">
@@ -832,7 +832,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Pringles</t>
+          <t>Ritz</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -842,16 +842,16 @@
         <v>2</v>
       </c>
       <c r="D22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>30.43700668692141</v>
+        <v>12.2312637036403</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Ritz</t>
+          <t>Pringles</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -861,10 +861,10 @@
         <v>2</v>
       </c>
       <c r="D23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E23" t="n">
-        <v>12.2312637036403</v>
+        <v>30.43700668692141</v>
       </c>
     </row>
     <row r="24">
@@ -908,96 +908,96 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Colombina</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E26" t="n">
-        <v>12.20950617283951</v>
+        <v>16.75291666666667</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Old El Paso</t>
+          <t>Colombina</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C27" t="n">
         <v>2</v>
       </c>
       <c r="D27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E27" t="n">
-        <v>13.455</v>
+        <v>12.20950617283951</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Mi Trigo</t>
+          <t>Old El Paso</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>23</v>
       </c>
       <c r="C28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>7.637391304347826</v>
+        <v>13.455</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Duetto</t>
+          <t>Mi Trigo</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C29" t="n">
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E29" t="n">
-        <v>4.406190476190476</v>
+        <v>7.637391304347826</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Bauducco</t>
+          <t>Duetto</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v>14.2729343508003</v>
+        <v>4.406190476190476</v>
       </c>
     </row>
     <row r="31">
@@ -1041,64 +1041,64 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Lider</t>
+          <t>Bauducco</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D33" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>7.467272727272728</v>
+        <v>14.2729343508003</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Tostitos</t>
+          <t>Lider</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>16.30891918387187</v>
+        <v>7.467272727272728</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Charles</t>
+          <t>Tostitos</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D35" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>19.27125506072875</v>
+        <v>16.30891918387187</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Pepperidge</t>
+          <t>Charles</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -1108,20 +1108,20 @@
         <v>1</v>
       </c>
       <c r="D36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E36" t="n">
-        <v>29.39239164449742</v>
+        <v>19.27125506072875</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Devon</t>
+          <t>Pepperidge</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C37" t="n">
         <v>1</v>
@@ -1130,32 +1130,32 @@
         <v>2</v>
       </c>
       <c r="E37" t="n">
-        <v>9.404842870544091</v>
+        <v>29.39239164449742</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Noel</t>
+          <t>Devon</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C38" t="n">
+        <v>1</v>
+      </c>
+      <c r="D38" t="n">
         <v>2</v>
       </c>
-      <c r="D38" t="n">
-        <v>3</v>
-      </c>
       <c r="E38" t="n">
-        <v>19.31337392062075</v>
+        <v>9.404842870544091</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Wow</t>
+          <t>Wasa</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -1165,39 +1165,39 @@
         <v>1</v>
       </c>
       <c r="D39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>9.45857142857143</v>
+        <v>20.93163482244135</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Wasa</t>
+          <t>Noel</t>
         </is>
       </c>
       <c r="B40" t="n">
         <v>13</v>
       </c>
       <c r="C40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>20.93163482244135</v>
+        <v>19.31337392062075</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Wibisco</t>
+          <t>Wow</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C41" t="n">
         <v>1</v>
@@ -1206,51 +1206,51 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>7.709999008179106</v>
+        <v>9.45857142857143</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Motto</t>
+          <t>Wibisco</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D42" t="n">
         <v>1</v>
       </c>
       <c r="E42" t="n">
-        <v>15.4472192513369</v>
+        <v>7.709999008179106</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Doritos</t>
+          <t>Motto</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E43" t="n">
-        <v>20.25820736467665</v>
+        <v>15.4472192513369</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>El Charrito</t>
+          <t>Keebler</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -1260,14 +1260,16 @@
         <v>1</v>
       </c>
       <c r="D44" t="n">
-        <v>1</v>
-      </c>
-      <c r="E44" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="E44" t="n">
+        <v>16.53</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Keebler</t>
+          <t>El Charrito</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -1277,29 +1279,27 @@
         <v>1</v>
       </c>
       <c r="D45" t="n">
-        <v>2</v>
-      </c>
-      <c r="E45" t="n">
-        <v>16.53</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="E45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Pillsbury</t>
+          <t>Doritos</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D46" t="n">
         <v>2</v>
       </c>
       <c r="E46" t="n">
-        <v>7.764285714285714</v>
+        <v>20.25820736467665</v>
       </c>
     </row>
     <row r="47">
@@ -1324,7 +1324,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Siete</t>
+          <t>Chips Ahoy</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -1334,10 +1334,10 @@
         <v>2</v>
       </c>
       <c r="D48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E48" t="n">
-        <v>35.46555757535778</v>
+        <v>12.99941707258641</v>
       </c>
     </row>
     <row r="49">
@@ -1381,7 +1381,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Chips Ahoy</t>
+          <t>Pillsbury</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -1391,35 +1391,35 @@
         <v>2</v>
       </c>
       <c r="D51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>12.99941707258641</v>
+        <v>7.764285714285714</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Member's Selection</t>
+          <t>Siete</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D52" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E52" t="n">
-        <v>13.74</v>
+        <v>35.46555757535778</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Biskitop</t>
+          <t>Member's Selection</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -1429,18 +1429,20 @@
         <v>1</v>
       </c>
       <c r="D53" t="n">
-        <v>2</v>
-      </c>
-      <c r="E53" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E53" t="n">
+        <v>13.74</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Biscotto</t>
+          <t>Biskitop</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C54" t="n">
         <v>1</v>
@@ -1448,31 +1450,31 @@
       <c r="D54" t="n">
         <v>2</v>
       </c>
-      <c r="E54" t="n">
-        <v>25</v>
-      </c>
+      <c r="E54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Kidsmania</t>
+          <t>Bisco</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C55" t="n">
         <v>1</v>
       </c>
       <c r="D55" t="n">
-        <v>1</v>
-      </c>
-      <c r="E55" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="E55" t="n">
+        <v>9.168749999999999</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Festival</t>
+          <t>Princesa</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -1485,13 +1487,13 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>9.385016025641024</v>
+        <v>3.535714285714286</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Nature'S Own</t>
+          <t>Golden</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -1501,16 +1503,14 @@
         <v>1</v>
       </c>
       <c r="D57" t="n">
-        <v>1</v>
-      </c>
-      <c r="E57" t="n">
-        <v>7.755714285714285</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="E57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Golden</t>
+          <t>Biscotto</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -1522,7 +1522,9 @@
       <c r="D58" t="n">
         <v>2</v>
       </c>
-      <c r="E58" t="inlineStr"/>
+      <c r="E58" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1546,7 +1548,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Princesa</t>
+          <t>Festival</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -1559,49 +1561,49 @@
         <v>1</v>
       </c>
       <c r="E60" t="n">
-        <v>3.535714285714286</v>
+        <v>9.385016025641024</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Cadbury</t>
+          <t>Nature'S Own</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C61" t="n">
         <v>1</v>
       </c>
       <c r="D61" t="n">
-        <v>2</v>
-      </c>
-      <c r="E61" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E61" t="n">
+        <v>7.755714285714285</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Schar</t>
+          <t>Kidsmania</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C62" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D62" t="n">
-        <v>3</v>
-      </c>
-      <c r="E62" t="n">
-        <v>24.18904950998269</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="E62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Laurieri</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -1611,33 +1613,33 @@
         <v>1</v>
       </c>
       <c r="D63" t="n">
-        <v>2</v>
-      </c>
-      <c r="E63" t="n">
-        <v>20.65978352354142</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="E63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Mr Bakewell</t>
+          <t>Schar</t>
         </is>
       </c>
       <c r="B64" t="n">
         <v>6</v>
       </c>
       <c r="C64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D64" t="n">
-        <v>1</v>
-      </c>
-      <c r="E64" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E64" t="n">
+        <v>24.18904950998269</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Sunshine</t>
+          <t>Laurieri</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -1647,16 +1649,16 @@
         <v>1</v>
       </c>
       <c r="D65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E65" t="n">
-        <v>9.488333333333333</v>
+        <v>20.65978352354142</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Mr Bakewell</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -1673,7 +1675,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Kugi</t>
+          <t>Cadbury</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -1683,18 +1685,18 @@
         <v>1</v>
       </c>
       <c r="D67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Stiratini</t>
+          <t>Sunshine</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C68" t="n">
         <v>1</v>
@@ -1703,17 +1705,17 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>17.42078051958985</v>
+        <v>9.488333333333333</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Merba</t>
+          <t>Kugi</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C69" t="n">
         <v>1</v>
@@ -1726,26 +1728,24 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Kiss</t>
+          <t>Tiffany</t>
         </is>
       </c>
       <c r="B70" t="n">
         <v>5</v>
       </c>
       <c r="C70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D70" t="n">
-        <v>3</v>
-      </c>
-      <c r="E70" t="n">
-        <v>20.05506545869531</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="E70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Tiffany</t>
+          <t>Stiratini</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -1757,12 +1757,14 @@
       <c r="D71" t="n">
         <v>1</v>
       </c>
-      <c r="E71" t="inlineStr"/>
+      <c r="E71" t="n">
+        <v>17.42078051958985</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Triskits</t>
+          <t>Merba</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -1815,45 +1817,45 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Badia</t>
+          <t>Bagel Bites</t>
         </is>
       </c>
       <c r="B75" t="n">
         <v>5</v>
       </c>
       <c r="C75" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D75" t="n">
         <v>1</v>
       </c>
       <c r="E75" t="n">
-        <v>28.56294367711628</v>
+        <v>14.76764878866199</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Bagel Bites</t>
+          <t>Badia</t>
         </is>
       </c>
       <c r="B76" t="n">
         <v>5</v>
       </c>
       <c r="C76" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D76" t="n">
         <v>1</v>
       </c>
       <c r="E76" t="n">
-        <v>14.76764878866199</v>
+        <v>28.56294367711628</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Cheetos</t>
+          <t>Kiss</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -1863,10 +1865,10 @@
         <v>2</v>
       </c>
       <c r="D77" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E77" t="n">
-        <v>23.77550530709329</v>
+        <v>20.05506545869531</v>
       </c>
     </row>
     <row r="78">
@@ -1891,30 +1893,30 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Hosttes</t>
+          <t>Cheetos</t>
         </is>
       </c>
       <c r="B79" t="n">
         <v>5</v>
       </c>
       <c r="C79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D79" t="n">
         <v>1</v>
       </c>
       <c r="E79" t="n">
-        <v>36.83418646645511</v>
+        <v>23.77550530709329</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Snyder’S</t>
+          <t>Triskits</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C80" t="n">
         <v>1</v>
@@ -1922,44 +1924,44 @@
       <c r="D80" t="n">
         <v>1</v>
       </c>
-      <c r="E80" t="n">
-        <v>21.8340355175269</v>
-      </c>
+      <c r="E80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Otis Spunkmeyer</t>
+          <t>Hosttes</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C81" t="n">
         <v>1</v>
       </c>
       <c r="D81" t="n">
-        <v>2</v>
-      </c>
-      <c r="E81" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E81" t="n">
+        <v>36.83418646645511</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Glutino</t>
+          <t>Herrs</t>
         </is>
       </c>
       <c r="B82" t="n">
         <v>4</v>
       </c>
       <c r="C82" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D82" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E82" t="n">
-        <v>19.41435404641845</v>
+        <v>37.30902864926393</v>
       </c>
     </row>
     <row r="83">
@@ -1984,7 +1986,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Nestle</t>
+          <t>Stonefire</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -1994,35 +1996,33 @@
         <v>1</v>
       </c>
       <c r="D84" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E84" t="n">
-        <v>41.70528266913809</v>
+        <v>16.92</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Takis</t>
+          <t>Otis Spunkmeyer</t>
         </is>
       </c>
       <c r="B85" t="n">
         <v>4</v>
       </c>
       <c r="C85" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D85" t="n">
         <v>2</v>
       </c>
-      <c r="E85" t="n">
-        <v>41.86</v>
-      </c>
+      <c r="E85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Ovaltine</t>
+          <t>Buenhorno</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -2034,14 +2034,12 @@
       <c r="D86" t="n">
         <v>1</v>
       </c>
-      <c r="E86" t="n">
-        <v>19.9445103354795</v>
-      </c>
+      <c r="E86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Buenhorno</t>
+          <t>Snyder’S</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -2053,12 +2051,14 @@
       <c r="D87" t="n">
         <v>1</v>
       </c>
-      <c r="E87" t="inlineStr"/>
+      <c r="E87" t="n">
+        <v>21.8340355175269</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Herrs</t>
+          <t>Nestle</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -2068,56 +2068,58 @@
         <v>1</v>
       </c>
       <c r="D88" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>37.30902864926393</v>
+        <v>41.70528266913809</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Stonefire</t>
+          <t>Glutino</t>
         </is>
       </c>
       <c r="B89" t="n">
         <v>4</v>
       </c>
       <c r="C89" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D89" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E89" t="n">
-        <v>16.92</v>
+        <v>19.41435404641845</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Dux</t>
+          <t>Takis</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C90" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D90" t="n">
-        <v>1</v>
-      </c>
-      <c r="E90" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="E90" t="n">
+        <v>41.86</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Snyders</t>
+          <t>Ovaltine</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C91" t="n">
         <v>1</v>
@@ -2125,31 +2127,33 @@
       <c r="D91" t="n">
         <v>1</v>
       </c>
-      <c r="E91" t="inlineStr"/>
+      <c r="E91" t="n">
+        <v>19.9445103354795</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Van Der Meulen</t>
+          <t>Milka</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C92" t="n">
         <v>1</v>
       </c>
       <c r="D92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E92" t="n">
-        <v>12.12155070255629</v>
+        <v>29.0725</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Confetti</t>
+          <t>Dux</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -2166,7 +2170,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Verkade</t>
+          <t>Pizkas</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -2179,13 +2183,13 @@
         <v>1</v>
       </c>
       <c r="E94" t="n">
-        <v>13.51789778605421</v>
+        <v>4.146666666666667</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Pizkas</t>
+          <t>Waitrose</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -2195,16 +2199,14 @@
         <v>1</v>
       </c>
       <c r="D95" t="n">
-        <v>1</v>
-      </c>
-      <c r="E95" t="n">
-        <v>4.146666666666667</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="E95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Waitrose</t>
+          <t>Confetti</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -2214,14 +2216,14 @@
         <v>1</v>
       </c>
       <c r="D96" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Flourish</t>
+          <t>Verkade</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -2233,12 +2235,14 @@
       <c r="D97" t="n">
         <v>1</v>
       </c>
-      <c r="E97" t="inlineStr"/>
+      <c r="E97" t="n">
+        <v>13.51789778605421</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Crix</t>
+          <t>Van Der Meulen</t>
         </is>
       </c>
       <c r="B98" t="n">
@@ -2251,13 +2255,13 @@
         <v>1</v>
       </c>
       <c r="E98" t="n">
-        <v>7.160318629656713</v>
+        <v>12.12155070255629</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Chetos</t>
+          <t>Flourish</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -2274,7 +2278,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Del-E</t>
+          <t>Crix</t>
         </is>
       </c>
       <c r="B100" t="n">
@@ -2284,18 +2288,20 @@
         <v>1</v>
       </c>
       <c r="D100" t="n">
-        <v>2</v>
-      </c>
-      <c r="E100" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E100" t="n">
+        <v>7.160318629656713</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Kinder</t>
+          <t>Snyders</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C101" t="n">
         <v>1</v>
@@ -2308,11 +2314,11 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Crunchmaster</t>
+          <t>Chetos</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C102" t="n">
         <v>1</v>
@@ -2320,18 +2326,16 @@
       <c r="D102" t="n">
         <v>1</v>
       </c>
-      <c r="E102" t="n">
-        <v>51.37009840929231</v>
-      </c>
+      <c r="E102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Dried</t>
+          <t>Del-E</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C103" t="n">
         <v>1</v>
@@ -2344,7 +2348,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Ricola</t>
+          <t>Willie</t>
         </is>
       </c>
       <c r="B104" t="n">
@@ -2356,14 +2360,12 @@
       <c r="D104" t="n">
         <v>1</v>
       </c>
-      <c r="E104" t="n">
-        <v>7.351955307262569</v>
-      </c>
+      <c r="E104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Cole´s</t>
+          <t>Werther’S</t>
         </is>
       </c>
       <c r="B105" t="n">
@@ -2375,14 +2377,12 @@
       <c r="D105" t="n">
         <v>1</v>
       </c>
-      <c r="E105" t="n">
-        <v>21.94025264317509</v>
-      </c>
+      <c r="E105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Sara Lee</t>
+          <t>Vigo</t>
         </is>
       </c>
       <c r="B106" t="n">
@@ -2395,13 +2395,13 @@
         <v>1</v>
       </c>
       <c r="E106" t="n">
-        <v>24.085</v>
+        <v>9.433248720978664</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Danisha</t>
+          <t>Wala</t>
         </is>
       </c>
       <c r="B107" t="n">
@@ -2418,7 +2418,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Dairy</t>
+          <t>Ricola</t>
         </is>
       </c>
       <c r="B108" t="n">
@@ -2430,12 +2430,14 @@
       <c r="D108" t="n">
         <v>1</v>
       </c>
-      <c r="E108" t="inlineStr"/>
+      <c r="E108" t="n">
+        <v>7.351955307262569</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Soldanza</t>
+          <t>Sara Lee</t>
         </is>
       </c>
       <c r="B109" t="n">
@@ -2447,12 +2449,14 @@
       <c r="D109" t="n">
         <v>1</v>
       </c>
-      <c r="E109" t="inlineStr"/>
+      <c r="E109" t="n">
+        <v>24.085</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Beivita</t>
+          <t>Voortman</t>
         </is>
       </c>
       <c r="B110" t="n">
@@ -2465,13 +2469,13 @@
         <v>1</v>
       </c>
       <c r="E110" t="n">
-        <v>35.19230769230769</v>
+        <v>20.17345399698341</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Lewis Bake Shop</t>
+          <t>Beivita</t>
         </is>
       </c>
       <c r="B111" t="n">
@@ -2484,13 +2488,13 @@
         <v>1</v>
       </c>
       <c r="E111" t="n">
-        <v>5.189283551419543</v>
+        <v>35.19230769230769</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Wala</t>
+          <t>Soldanza</t>
         </is>
       </c>
       <c r="B112" t="n">
@@ -2507,7 +2511,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Mars</t>
+          <t>Tuc</t>
         </is>
       </c>
       <c r="B113" t="n">
@@ -2519,12 +2523,14 @@
       <c r="D113" t="n">
         <v>1</v>
       </c>
-      <c r="E113" t="inlineStr"/>
+      <c r="E113" t="n">
+        <v>7.575418994413408</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Knotts</t>
+          <t>Can Can</t>
         </is>
       </c>
       <c r="B114" t="n">
@@ -2536,12 +2542,14 @@
       <c r="D114" t="n">
         <v>1</v>
       </c>
-      <c r="E114" t="inlineStr"/>
+      <c r="E114" t="n">
+        <v>3.915</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Willie</t>
+          <t>Dried</t>
         </is>
       </c>
       <c r="B115" t="n">
@@ -2551,14 +2559,14 @@
         <v>1</v>
       </c>
       <c r="D115" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Werther’S</t>
+          <t>Hinged</t>
         </is>
       </c>
       <c r="B116" t="n">
@@ -2570,12 +2578,14 @@
       <c r="D116" t="n">
         <v>1</v>
       </c>
-      <c r="E116" t="inlineStr"/>
+      <c r="E116" t="n">
+        <v>1.907848055928269</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>La Tortilla Factory</t>
+          <t>Cole´s</t>
         </is>
       </c>
       <c r="B117" t="n">
@@ -2588,13 +2598,13 @@
         <v>1</v>
       </c>
       <c r="E117" t="n">
-        <v>21.71</v>
+        <v>21.94025264317509</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Cheez</t>
+          <t>La Tortilla Factory</t>
         </is>
       </c>
       <c r="B118" t="n">
@@ -2606,12 +2616,14 @@
       <c r="D118" t="n">
         <v>1</v>
       </c>
-      <c r="E118" t="inlineStr"/>
+      <c r="E118" t="n">
+        <v>21.71</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Hinged</t>
+          <t>Knotts</t>
         </is>
       </c>
       <c r="B119" t="n">
@@ -2623,14 +2635,12 @@
       <c r="D119" t="n">
         <v>1</v>
       </c>
-      <c r="E119" t="n">
-        <v>1.907848055928269</v>
-      </c>
+      <c r="E119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Hills</t>
+          <t>Mars</t>
         </is>
       </c>
       <c r="B120" t="n">
@@ -2647,7 +2657,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Tuc</t>
+          <t>Dairy</t>
         </is>
       </c>
       <c r="B121" t="n">
@@ -2659,14 +2669,12 @@
       <c r="D121" t="n">
         <v>1</v>
       </c>
-      <c r="E121" t="n">
-        <v>7.575418994413408</v>
-      </c>
+      <c r="E121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Voortman</t>
+          <t>Kinder</t>
         </is>
       </c>
       <c r="B122" t="n">
@@ -2678,14 +2686,12 @@
       <c r="D122" t="n">
         <v>1</v>
       </c>
-      <c r="E122" t="n">
-        <v>20.17345399698341</v>
-      </c>
+      <c r="E122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Vigo</t>
+          <t>Glad</t>
         </is>
       </c>
       <c r="B123" t="n">
@@ -2697,21 +2703,19 @@
       <c r="D123" t="n">
         <v>1</v>
       </c>
-      <c r="E123" t="n">
-        <v>9.433248720978664</v>
-      </c>
+      <c r="E123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Nature Valley</t>
+          <t>Danisha</t>
         </is>
       </c>
       <c r="B124" t="n">
         <v>2</v>
       </c>
       <c r="C124" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D124" t="n">
         <v>1</v>
@@ -2721,14 +2725,14 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Glad</t>
+          <t>Nature Valley</t>
         </is>
       </c>
       <c r="B125" t="n">
         <v>2</v>
       </c>
       <c r="C125" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D125" t="n">
         <v>1</v>
@@ -2738,11 +2742,11 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Cloverhill</t>
+          <t>Crunchmaster</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C126" t="n">
         <v>1</v>
@@ -2750,16 +2754,18 @@
       <c r="D126" t="n">
         <v>1</v>
       </c>
-      <c r="E126" t="inlineStr"/>
+      <c r="E126" t="n">
+        <v>51.37009840929231</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Vegefarm</t>
+          <t>Hills</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C127" t="n">
         <v>1</v>
@@ -2767,18 +2773,16 @@
       <c r="D127" t="n">
         <v>1</v>
       </c>
-      <c r="E127" t="n">
-        <v>27.42714334124026</v>
-      </c>
+      <c r="E127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Cho Cho</t>
+          <t>Cheez</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C128" t="n">
         <v>1</v>
@@ -2791,11 +2795,11 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Choppers</t>
+          <t>Lewis Bake Shop</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C129" t="n">
         <v>1</v>
@@ -2803,12 +2807,14 @@
       <c r="D129" t="n">
         <v>1</v>
       </c>
-      <c r="E129" t="inlineStr"/>
+      <c r="E129" t="n">
+        <v>5.189283551419543</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Cusano´s</t>
+          <t>Highland</t>
         </is>
       </c>
       <c r="B130" t="n">
@@ -2825,7 +2831,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Twizzlers</t>
+          <t>Triscuit</t>
         </is>
       </c>
       <c r="B131" t="n">
@@ -2837,12 +2843,14 @@
       <c r="D131" t="n">
         <v>1</v>
       </c>
-      <c r="E131" t="inlineStr"/>
+      <c r="E131" t="n">
+        <v>21.76632743949854</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Chester</t>
+          <t>Hershey</t>
         </is>
       </c>
       <c r="B132" t="n">
@@ -2854,12 +2862,14 @@
       <c r="D132" t="n">
         <v>1</v>
       </c>
-      <c r="E132" t="inlineStr"/>
+      <c r="E132" t="n">
+        <v>19.07848055928269</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Chowmein</t>
+          <t>Twizzlers</t>
         </is>
       </c>
       <c r="B133" t="n">
@@ -2876,7 +2886,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Triscuit</t>
+          <t>Ortega</t>
         </is>
       </c>
       <c r="B134" t="n">
@@ -2889,13 +2899,13 @@
         <v>1</v>
       </c>
       <c r="E134" t="n">
-        <v>21.76632743949854</v>
+        <v>10.91045974485786</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>King's Hawaiian</t>
+          <t>Haribo</t>
         </is>
       </c>
       <c r="B135" t="n">
@@ -2912,7 +2922,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Snickers</t>
+          <t>Haagen Daz</t>
         </is>
       </c>
       <c r="B136" t="n">
@@ -2924,14 +2934,12 @@
       <c r="D136" t="n">
         <v>1</v>
       </c>
-      <c r="E136" t="n">
-        <v>40.99</v>
-      </c>
+      <c r="E136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Haagen Daz</t>
+          <t>Holiday</t>
         </is>
       </c>
       <c r="B137" t="n">
@@ -2948,7 +2956,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Kimberley's Bakeshoppe</t>
+          <t>HOL Foods</t>
         </is>
       </c>
       <c r="B138" t="n">
@@ -2960,12 +2968,14 @@
       <c r="D138" t="n">
         <v>1</v>
       </c>
-      <c r="E138" t="inlineStr"/>
+      <c r="E138" t="n">
+        <v>14.42307692307692</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Jumbo</t>
+          <t>Cusano´s</t>
         </is>
       </c>
       <c r="B139" t="n">
@@ -2977,14 +2987,12 @@
       <c r="D139" t="n">
         <v>1</v>
       </c>
-      <c r="E139" t="n">
-        <v>11.48504273504274</v>
-      </c>
+      <c r="E139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Hostess</t>
+          <t>Goldfish</t>
         </is>
       </c>
       <c r="B140" t="n">
@@ -2997,13 +3005,13 @@
         <v>1</v>
       </c>
       <c r="E140" t="n">
-        <v>20.82</v>
+        <v>15.39664804469274</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Hollandia</t>
+          <t>Give &amp; Go</t>
         </is>
       </c>
       <c r="B141" t="n">
@@ -3015,14 +3023,12 @@
       <c r="D141" t="n">
         <v>1</v>
       </c>
-      <c r="E141" t="n">
-        <v>52.34878150009826</v>
-      </c>
+      <c r="E141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Holiday</t>
+          <t>Ferrero</t>
         </is>
       </c>
       <c r="B142" t="n">
@@ -3039,7 +3045,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Marie</t>
+          <t>Fernandes</t>
         </is>
       </c>
       <c r="B143" t="n">
@@ -3056,7 +3062,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Mcvitie'S</t>
+          <t>Double Duty</t>
         </is>
       </c>
       <c r="B144" t="n">
@@ -3068,14 +3074,12 @@
       <c r="D144" t="n">
         <v>1</v>
       </c>
-      <c r="E144" t="n">
-        <v>37.62485187066193</v>
-      </c>
+      <c r="E144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Highland</t>
+          <t>Vegefarm</t>
         </is>
       </c>
       <c r="B145" t="n">
@@ -3087,12 +3091,14 @@
       <c r="D145" t="n">
         <v>1</v>
       </c>
-      <c r="E145" t="inlineStr"/>
+      <c r="E145" t="n">
+        <v>27.42714334124026</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Members Selection</t>
+          <t>Kimberley's Bakeshoppe</t>
         </is>
       </c>
       <c r="B146" t="n">
@@ -3109,7 +3115,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Hershey</t>
+          <t>Hollandia</t>
         </is>
       </c>
       <c r="B147" t="n">
@@ -3122,13 +3128,13 @@
         <v>1</v>
       </c>
       <c r="E147" t="n">
-        <v>19.07848055928269</v>
+        <v>52.34878150009826</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Haribo</t>
+          <t>Hostess</t>
         </is>
       </c>
       <c r="B148" t="n">
@@ -3140,12 +3146,14 @@
       <c r="D148" t="n">
         <v>1</v>
       </c>
-      <c r="E148" t="inlineStr"/>
+      <c r="E148" t="n">
+        <v>20.82</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>HOL Foods</t>
+          <t>Chester</t>
         </is>
       </c>
       <c r="B149" t="n">
@@ -3157,14 +3165,12 @@
       <c r="D149" t="n">
         <v>1</v>
       </c>
-      <c r="E149" t="n">
-        <v>14.42307692307692</v>
-      </c>
+      <c r="E149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Double Duty</t>
+          <t>Nerds</t>
         </is>
       </c>
       <c r="B150" t="n">
@@ -3181,7 +3187,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Goldfish</t>
+          <t>Ducales</t>
         </is>
       </c>
       <c r="B151" t="n">
@@ -3194,13 +3200,13 @@
         <v>1</v>
       </c>
       <c r="E151" t="n">
-        <v>15.39664804469274</v>
+        <v>21.76632743949854</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Nerds</t>
+          <t>Choppers</t>
         </is>
       </c>
       <c r="B152" t="n">
@@ -3217,7 +3223,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Give &amp; Go</t>
+          <t>Pirucream</t>
         </is>
       </c>
       <c r="B153" t="n">
@@ -3229,12 +3235,14 @@
       <c r="D153" t="n">
         <v>1</v>
       </c>
-      <c r="E153" t="inlineStr"/>
+      <c r="E153" t="n">
+        <v>20.53625219611713</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Ortega</t>
+          <t>Pirulin</t>
         </is>
       </c>
       <c r="B154" t="n">
@@ -3246,14 +3254,12 @@
       <c r="D154" t="n">
         <v>1</v>
       </c>
-      <c r="E154" t="n">
-        <v>10.91045974485786</v>
-      </c>
+      <c r="E154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Oscar Mayer</t>
+          <t>Members Selection</t>
         </is>
       </c>
       <c r="B155" t="n">
@@ -3265,14 +3271,12 @@
       <c r="D155" t="n">
         <v>1</v>
       </c>
-      <c r="E155" t="n">
-        <v>21.70707121411719</v>
-      </c>
+      <c r="E155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Ferrero</t>
+          <t>Post</t>
         </is>
       </c>
       <c r="B156" t="n">
@@ -3284,12 +3288,14 @@
       <c r="D156" t="n">
         <v>1</v>
       </c>
-      <c r="E156" t="inlineStr"/>
+      <c r="E156" t="n">
+        <v>7.51</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Fernandes</t>
+          <t>Mcvitie'S</t>
         </is>
       </c>
       <c r="B157" t="n">
@@ -3301,12 +3307,14 @@
       <c r="D157" t="n">
         <v>1</v>
       </c>
-      <c r="E157" t="inlineStr"/>
+      <c r="E157" t="n">
+        <v>37.62485187066193</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Pirulin</t>
+          <t>Reynolds</t>
         </is>
       </c>
       <c r="B158" t="n">
@@ -3323,7 +3331,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Post</t>
+          <t>Marie</t>
         </is>
       </c>
       <c r="B159" t="n">
@@ -3335,14 +3343,12 @@
       <c r="D159" t="n">
         <v>1</v>
       </c>
-      <c r="E159" t="n">
-        <v>7.51</v>
-      </c>
+      <c r="E159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Ducales</t>
+          <t>Chowmein</t>
         </is>
       </c>
       <c r="B160" t="n">
@@ -3354,14 +3360,12 @@
       <c r="D160" t="n">
         <v>1</v>
       </c>
-      <c r="E160" t="n">
-        <v>21.76632743949854</v>
-      </c>
+      <c r="E160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Reynolds</t>
+          <t>Cloverhill</t>
         </is>
       </c>
       <c r="B161" t="n">
@@ -3378,7 +3382,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Pirucream</t>
+          <t>Snickers</t>
         </is>
       </c>
       <c r="B162" t="n">
@@ -3391,8 +3395,80 @@
         <v>1</v>
       </c>
       <c r="E162" t="n">
-        <v>20.53625219611713</v>
-      </c>
+        <v>40.99</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>King's Hawaiian</t>
+        </is>
+      </c>
+      <c r="B163" t="n">
+        <v>1</v>
+      </c>
+      <c r="C163" t="n">
+        <v>1</v>
+      </c>
+      <c r="D163" t="n">
+        <v>1</v>
+      </c>
+      <c r="E163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Oscar Mayer</t>
+        </is>
+      </c>
+      <c r="B164" t="n">
+        <v>1</v>
+      </c>
+      <c r="C164" t="n">
+        <v>1</v>
+      </c>
+      <c r="D164" t="n">
+        <v>1</v>
+      </c>
+      <c r="E164" t="n">
+        <v>21.70707121411719</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Jumbo</t>
+        </is>
+      </c>
+      <c r="B165" t="n">
+        <v>1</v>
+      </c>
+      <c r="C165" t="n">
+        <v>1</v>
+      </c>
+      <c r="D165" t="n">
+        <v>1</v>
+      </c>
+      <c r="E165" t="n">
+        <v>11.48504273504274</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Cho Cho</t>
+        </is>
+      </c>
+      <c r="B166" t="n">
+        <v>1</v>
+      </c>
+      <c r="C166" t="n">
+        <v>1</v>
+      </c>
+      <c r="D166" t="n">
+        <v>1</v>
+      </c>
+      <c r="E166" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9323,7 +9399,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -9402,12 +9478,12 @@
       <c r="AG32" t="inlineStr"/>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="AJ32" t="n">
@@ -9421,7 +9497,7 @@
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>unknown_galleta maiz con chocolate x carrefour bio</t>
+          <t>carrefour_galleta maiz con chocolate x carrefour bio</t>
         </is>
       </c>
       <c r="AN32" t="inlineStr">
@@ -9436,12 +9512,12 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>unknown_galleta maiz con chocolate x carrefour bio_0.09</t>
+          <t>carrefour_galleta maiz con chocolate x carrefour bio_0.09</t>
         </is>
       </c>
       <c r="AQ32" t="inlineStr">
         <is>
-          <t>unknown_carrefour_chocolate_maiz</t>
+          <t>carrefour_carrefour_chocolate_maiz</t>
         </is>
       </c>
       <c r="AR32" t="n">
@@ -21807,7 +21883,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Milka</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -21886,12 +21962,12 @@
       <c r="AG106" t="inlineStr"/>
       <c r="AH106" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Milka</t>
         </is>
       </c>
       <c r="AI106" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Milka</t>
         </is>
       </c>
       <c r="AJ106" t="n">
@@ -21905,7 +21981,7 @@
       </c>
       <c r="AM106" t="inlineStr">
         <is>
-          <t>unknown_galleta milka choco brownie</t>
+          <t>milka_galleta milka choco brownie</t>
         </is>
       </c>
       <c r="AN106" t="inlineStr">
@@ -21920,12 +21996,12 @@
       </c>
       <c r="AP106" t="inlineStr">
         <is>
-          <t>unknown_galleta milka choco brownie_0.15</t>
+          <t>milka_galleta milka choco brownie_0.15</t>
         </is>
       </c>
       <c r="AQ106" t="inlineStr">
         <is>
-          <t>unknown_brownie_choco_milka</t>
+          <t>milka_brownie_choco_milka</t>
         </is>
       </c>
       <c r="AR106" t="n">
@@ -22157,7 +22233,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -22236,12 +22312,12 @@
       <c r="AG108" t="inlineStr"/>
       <c r="AH108" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="AI108" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="AJ108" t="n">
@@ -22251,7 +22327,7 @@
       <c r="AL108" t="inlineStr"/>
       <c r="AM108" t="inlineStr">
         <is>
-          <t>unknown_levadura para panes y brioches carrefour original</t>
+          <t>carrefour_levadura para panes y brioches carrefour original</t>
         </is>
       </c>
       <c r="AN108" t="inlineStr">
@@ -22266,12 +22342,12 @@
       </c>
       <c r="AP108" t="inlineStr">
         <is>
-          <t>unknown_levadura para panes y brioches carrefour original_0.03</t>
+          <t>carrefour_levadura para panes y brioches carrefour original_0.03</t>
         </is>
       </c>
       <c r="AQ108" t="inlineStr">
         <is>
-          <t>unknown_brioches_carrefour_levadura_panes</t>
+          <t>carrefour_brioches_carrefour_levadura_panes</t>
         </is>
       </c>
       <c r="AR108" t="n">
@@ -28692,7 +28768,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -28767,12 +28843,12 @@
       <c r="AG147" t="inlineStr"/>
       <c r="AH147" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="AI147" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="AJ147" t="inlineStr"/>
@@ -28780,7 +28856,7 @@
       <c r="AL147" t="inlineStr"/>
       <c r="AM147" t="inlineStr">
         <is>
-          <t>lu_galleta carrefour cocoa sin</t>
+          <t>carrefour_galleta carrefour cocoa sin</t>
         </is>
       </c>
       <c r="AN147" t="inlineStr">
@@ -28795,12 +28871,12 @@
       </c>
       <c r="AP147" t="inlineStr">
         <is>
-          <t>lu_galleta carrefour cocoa sin_0.12</t>
+          <t>carrefour_galleta carrefour cocoa sin_0.12</t>
         </is>
       </c>
       <c r="AQ147" t="inlineStr">
         <is>
-          <t>lu_carrefour_cocoa</t>
+          <t>carrefour_carrefour_cocoa</t>
         </is>
       </c>
       <c r="AR147" t="n">
@@ -33287,7 +33363,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -33362,12 +33438,12 @@
       <c r="AG174" t="inlineStr"/>
       <c r="AH174" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="AI174" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="AJ174" t="inlineStr"/>
@@ -33375,7 +33451,7 @@
       <c r="AL174" t="inlineStr"/>
       <c r="AM174" t="inlineStr">
         <is>
-          <t>unknown_galleta carrefour de pepitas de limon verde</t>
+          <t>carrefour_galleta carrefour de pepitas de limon verde</t>
         </is>
       </c>
       <c r="AN174" t="inlineStr">
@@ -33390,12 +33466,12 @@
       </c>
       <c r="AP174" t="inlineStr">
         <is>
-          <t>unknown_galleta carrefour de pepitas de limon verde_0.1</t>
+          <t>carrefour_galleta carrefour de pepitas de limon verde_0.1</t>
         </is>
       </c>
       <c r="AQ174" t="inlineStr">
         <is>
-          <t>unknown_carrefour_limon_pepitas_verde</t>
+          <t>carrefour_carrefour_limon_pepitas_verde</t>
         </is>
       </c>
       <c r="AR174" t="n">
@@ -34673,7 +34749,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Milka</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -34752,12 +34828,12 @@
       <c r="AG182" t="inlineStr"/>
       <c r="AH182" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Milka</t>
         </is>
       </c>
       <c r="AI182" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Milka</t>
         </is>
       </c>
       <c r="AJ182" t="n">
@@ -34771,7 +34847,7 @@
       </c>
       <c r="AM182" t="inlineStr">
         <is>
-          <t>unknown_choco wafer galletas de barquillo cubiertas de chocolate milka</t>
+          <t>milka_choco wafer galletas de barquillo cubiertas de chocolate milka</t>
         </is>
       </c>
       <c r="AN182" t="inlineStr">
@@ -34786,12 +34862,12 @@
       </c>
       <c r="AP182" t="inlineStr">
         <is>
-          <t>unknown_choco wafer galletas de barquillo cubiertas de chocolate milka_0.18</t>
+          <t>milka_choco wafer galletas de barquillo cubiertas de chocolate milka_0.18</t>
         </is>
       </c>
       <c r="AQ182" t="inlineStr">
         <is>
-          <t>unknown_barquillo_choco_chocolate_cubiertas</t>
+          <t>milka_barquillo_choco_chocolate_cubiertas</t>
         </is>
       </c>
       <c r="AR182" t="n">
@@ -37500,7 +37576,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Milka</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -37579,12 +37655,12 @@
       <c r="AG199" t="inlineStr"/>
       <c r="AH199" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Milka</t>
         </is>
       </c>
       <c r="AI199" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Milka</t>
         </is>
       </c>
       <c r="AJ199" t="n">
@@ -37598,7 +37674,7 @@
       </c>
       <c r="AM199" t="inlineStr">
         <is>
-          <t>unknown_chocolate milka nutty wafer</t>
+          <t>milka_chocolate milka nutty wafer</t>
         </is>
       </c>
       <c r="AN199" t="inlineStr">
@@ -37613,12 +37689,12 @@
       </c>
       <c r="AP199" t="inlineStr">
         <is>
-          <t>unknown_chocolate milka nutty wafer_0.27</t>
+          <t>milka_chocolate milka nutty wafer_0.27</t>
         </is>
       </c>
       <c r="AQ199" t="inlineStr">
         <is>
-          <t>unknown_chocolate_milka_nutty_wafer</t>
+          <t>milka_chocolate_milka_nutty_wafer</t>
         </is>
       </c>
       <c r="AR199" t="n">
@@ -42322,7 +42398,7 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Milka</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -42401,12 +42477,12 @@
       <c r="AG227" t="inlineStr"/>
       <c r="AH227" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Milka</t>
         </is>
       </c>
       <c r="AI227" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Milka</t>
         </is>
       </c>
       <c r="AJ227" t="n">
@@ -42420,7 +42496,7 @@
       </c>
       <c r="AM227" t="inlineStr">
         <is>
-          <t>unknown_choco wafer galletas de barquillo cubiertas de chocolate milka</t>
+          <t>milka_choco wafer galletas de barquillo cubiertas de chocolate milka</t>
         </is>
       </c>
       <c r="AN227" t="inlineStr">
@@ -42435,12 +42511,12 @@
       </c>
       <c r="AP227" t="inlineStr">
         <is>
-          <t>unknown_choco wafer galletas de barquillo cubiertas de chocolate milka_0.18</t>
+          <t>milka_choco wafer galletas de barquillo cubiertas de chocolate milka_0.18</t>
         </is>
       </c>
       <c r="AQ227" t="inlineStr">
         <is>
-          <t>unknown_barquillo_choco_chocolate_cubiertas</t>
+          <t>milka_barquillo_choco_chocolate_cubiertas</t>
         </is>
       </c>
       <c r="AR227" t="n">
@@ -47818,7 +47894,7 @@
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -47897,12 +47973,12 @@
       <c r="AG259" t="inlineStr"/>
       <c r="AH259" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="AI259" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="AJ259" t="n">
@@ -47916,7 +47992,7 @@
       </c>
       <c r="AM259" t="inlineStr">
         <is>
-          <t>unknown_galleta carrefour chocolate caramelo</t>
+          <t>carrefour_galleta carrefour chocolate caramelo</t>
         </is>
       </c>
       <c r="AN259" t="inlineStr">
@@ -47931,12 +48007,12 @@
       </c>
       <c r="AP259" t="inlineStr">
         <is>
-          <t>unknown_galleta carrefour chocolate caramelo_0.12</t>
+          <t>carrefour_galleta carrefour chocolate caramelo_0.12</t>
         </is>
       </c>
       <c r="AQ259" t="inlineStr">
         <is>
-          <t>unknown_caramelo_carrefour_chocolate</t>
+          <t>carrefour_caramelo_carrefour_chocolate</t>
         </is>
       </c>
       <c r="AR259" t="n">
@@ -48333,7 +48409,7 @@
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
@@ -48412,12 +48488,12 @@
       <c r="AG262" t="inlineStr"/>
       <c r="AH262" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="AI262" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="AJ262" t="n">
@@ -48431,7 +48507,7 @@
       </c>
       <c r="AM262" t="inlineStr">
         <is>
-          <t>unknown_surtido de galletas carrefour extra</t>
+          <t>carrefour_surtido de galletas carrefour extra</t>
         </is>
       </c>
       <c r="AN262" t="inlineStr">
@@ -48446,12 +48522,12 @@
       </c>
       <c r="AP262" t="inlineStr">
         <is>
-          <t>unknown_surtido de galletas carrefour extra_0.2</t>
+          <t>carrefour_surtido de galletas carrefour extra_0.2</t>
         </is>
       </c>
       <c r="AQ262" t="inlineStr">
         <is>
-          <t>unknown_carrefour_extra_surtido</t>
+          <t>carrefour_carrefour_extra_surtido</t>
         </is>
       </c>
       <c r="AR262" t="n">
@@ -52075,7 +52151,7 @@
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -52154,12 +52230,12 @@
       <c r="AG284" t="inlineStr"/>
       <c r="AH284" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="AI284" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="AJ284" t="n">
@@ -52173,7 +52249,7 @@
       </c>
       <c r="AM284" t="inlineStr">
         <is>
-          <t>unknown_galleta carrefour proteinas</t>
+          <t>carrefour_galleta carrefour proteinas</t>
         </is>
       </c>
       <c r="AN284" t="inlineStr">
@@ -52188,12 +52264,12 @@
       </c>
       <c r="AP284" t="inlineStr">
         <is>
-          <t>unknown_galleta carrefour proteinas_0.15</t>
+          <t>carrefour_galleta carrefour proteinas_0.15</t>
         </is>
       </c>
       <c r="AQ284" t="inlineStr">
         <is>
-          <t>unknown_carrefour_proteinas</t>
+          <t>carrefour_carrefour_proteinas</t>
         </is>
       </c>
       <c r="AR284" t="n">
@@ -54823,7 +54899,7 @@
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Bisco</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
@@ -54902,12 +54978,12 @@
       <c r="AG300" t="inlineStr"/>
       <c r="AH300" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Bisco</t>
         </is>
       </c>
       <c r="AI300" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Bisco</t>
         </is>
       </c>
       <c r="AJ300" t="n">
@@ -54917,7 +54993,7 @@
       <c r="AL300" t="inlineStr"/>
       <c r="AM300" t="inlineStr">
         <is>
-          <t>unknown_galletas biscuit mood rellenas de chocolate biscolata</t>
+          <t>bisco_galletas biscuit mood rellenas de chocolate biscolata</t>
         </is>
       </c>
       <c r="AN300" t="inlineStr">
@@ -54932,12 +55008,12 @@
       </c>
       <c r="AP300" t="inlineStr">
         <is>
-          <t>unknown_galletas biscuit mood rellenas de chocolate biscolata_0.12</t>
+          <t>bisco_galletas biscuit mood rellenas de chocolate biscolata_0.12</t>
         </is>
       </c>
       <c r="AQ300" t="inlineStr">
         <is>
-          <t>unknown_biscolata_biscuit_chocolate_mood</t>
+          <t>bisco_biscolata_biscuit_chocolate_mood</t>
         </is>
       </c>
       <c r="AR300" t="n">
@@ -55169,7 +55245,7 @@
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Bisco</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
@@ -55248,12 +55324,12 @@
       <c r="AG302" t="inlineStr"/>
       <c r="AH302" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Bisco</t>
         </is>
       </c>
       <c r="AI302" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Bisco</t>
         </is>
       </c>
       <c r="AJ302" t="n">
@@ -55263,7 +55339,7 @@
       <c r="AL302" t="inlineStr"/>
       <c r="AM302" t="inlineStr">
         <is>
-          <t>unknown_galletas biscuit mood rellenas de chocolate biscolata</t>
+          <t>bisco_galletas biscuit mood rellenas de chocolate biscolata</t>
         </is>
       </c>
       <c r="AN302" t="inlineStr">
@@ -55278,12 +55354,12 @@
       </c>
       <c r="AP302" t="inlineStr">
         <is>
-          <t>unknown_galletas biscuit mood rellenas de chocolate biscolata_0.12</t>
+          <t>bisco_galletas biscuit mood rellenas de chocolate biscolata_0.12</t>
         </is>
       </c>
       <c r="AQ302" t="inlineStr">
         <is>
-          <t>unknown_biscolata_biscuit_chocolate_mood</t>
+          <t>bisco_biscolata_biscuit_chocolate_mood</t>
         </is>
       </c>
       <c r="AR302" t="n">
@@ -68553,7 +68629,7 @@
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="H380" t="inlineStr">
@@ -68632,12 +68708,12 @@
       <c r="AG380" t="inlineStr"/>
       <c r="AH380" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="AI380" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="AJ380" t="n">
@@ -68651,7 +68727,7 @@
       </c>
       <c r="AM380" t="inlineStr">
         <is>
-          <t>unknown_galleta carrefour chocolate avellas</t>
+          <t>carrefour_galleta carrefour chocolate avellas</t>
         </is>
       </c>
       <c r="AN380" t="inlineStr">
@@ -68666,12 +68742,12 @@
       </c>
       <c r="AP380" t="inlineStr">
         <is>
-          <t>unknown_galleta carrefour chocolate avellas_0.24</t>
+          <t>carrefour_galleta carrefour chocolate avellas_0.24</t>
         </is>
       </c>
       <c r="AQ380" t="inlineStr">
         <is>
-          <t>unknown_avellas_carrefour_chocolate</t>
+          <t>carrefour_avellas_carrefour_chocolate</t>
         </is>
       </c>
       <c r="AR380" t="n">
@@ -72502,7 +72578,7 @@
       </c>
       <c r="G403" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="H403" t="inlineStr">
@@ -72581,12 +72657,12 @@
       <c r="AG403" t="inlineStr"/>
       <c r="AH403" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="AI403" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="AJ403" t="n">
@@ -72600,7 +72676,7 @@
       </c>
       <c r="AM403" t="inlineStr">
         <is>
-          <t>unknown_galleta carrefour praline de avellanas</t>
+          <t>carrefour_galleta carrefour praline de avellanas</t>
         </is>
       </c>
       <c r="AN403" t="inlineStr">
@@ -72615,12 +72691,12 @@
       </c>
       <c r="AP403" t="inlineStr">
         <is>
-          <t>unknown_galleta carrefour praline de avellanas_0.11</t>
+          <t>carrefour_galleta carrefour praline de avellanas_0.11</t>
         </is>
       </c>
       <c r="AQ403" t="inlineStr">
         <is>
-          <t>unknown_avellanas_carrefour_praline</t>
+          <t>carrefour_avellanas_carrefour_praline</t>
         </is>
       </c>
       <c r="AR403" t="n">
@@ -72677,7 +72753,7 @@
       </c>
       <c r="G404" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="H404" t="inlineStr">
@@ -72756,12 +72832,12 @@
       <c r="AG404" t="inlineStr"/>
       <c r="AH404" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="AI404" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="AJ404" t="n">
@@ -72775,7 +72851,7 @@
       </c>
       <c r="AM404" t="inlineStr">
         <is>
-          <t>unknown_galletas de aperitivo carrefour classic galletas de emmental</t>
+          <t>carrefour_galletas de aperitivo carrefour classic galletas de emmental</t>
         </is>
       </c>
       <c r="AN404" t="inlineStr">
@@ -72790,12 +72866,12 @@
       </c>
       <c r="AP404" t="inlineStr">
         <is>
-          <t>unknown_galletas de aperitivo carrefour classic galletas de emmental_0.1</t>
+          <t>carrefour_galletas de aperitivo carrefour classic galletas de emmental_0.1</t>
         </is>
       </c>
       <c r="AQ404" t="inlineStr">
         <is>
-          <t>unknown_aperitivo_carrefour_emmental</t>
+          <t>carrefour_aperitivo_carrefour_emmental</t>
         </is>
       </c>
       <c r="AR404" t="n">
@@ -74926,7 +75002,7 @@
       </c>
       <c r="G417" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="H417" t="inlineStr">
@@ -75005,12 +75081,12 @@
       <c r="AG417" t="inlineStr"/>
       <c r="AH417" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="AI417" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="AJ417" t="n">
@@ -75024,7 +75100,7 @@
       </c>
       <c r="AM417" t="inlineStr">
         <is>
-          <t>unknown_galleta carrefour chocolate con leche</t>
+          <t>carrefour_galleta carrefour chocolate con leche</t>
         </is>
       </c>
       <c r="AN417" t="inlineStr">
@@ -75039,12 +75115,12 @@
       </c>
       <c r="AP417" t="inlineStr">
         <is>
-          <t>unknown_galleta carrefour chocolate con leche_0.15</t>
+          <t>carrefour_galleta carrefour chocolate con leche_0.15</t>
         </is>
       </c>
       <c r="AQ417" t="inlineStr">
         <is>
-          <t>unknown_carrefour_chocolate_leche</t>
+          <t>carrefour_carrefour_chocolate_leche</t>
         </is>
       </c>
       <c r="AR417" t="n">
@@ -76487,7 +76563,7 @@
       </c>
       <c r="G426" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="H426" t="inlineStr">
@@ -76566,12 +76642,12 @@
       <c r="AG426" t="inlineStr"/>
       <c r="AH426" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="AI426" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="AJ426" t="n">
@@ -76585,7 +76661,7 @@
       </c>
       <c r="AM426" t="inlineStr">
         <is>
-          <t>unknown_galleta carrefour chocograni chocolat noir</t>
+          <t>carrefour_galleta carrefour chocograni chocolat noir</t>
         </is>
       </c>
       <c r="AN426" t="inlineStr">
@@ -76600,12 +76676,12 @@
       </c>
       <c r="AP426" t="inlineStr">
         <is>
-          <t>unknown_galleta carrefour chocograni chocolat noir_0.2</t>
+          <t>carrefour_galleta carrefour chocograni chocolat noir_0.2</t>
         </is>
       </c>
       <c r="AQ426" t="inlineStr">
         <is>
-          <t>unknown_carrefour_chocograni_chocolat_noir</t>
+          <t>carrefour_carrefour_chocograni_chocolat_noir</t>
         </is>
       </c>
       <c r="AR426" t="n">
@@ -79406,7 +79482,7 @@
       </c>
       <c r="G443" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="H443" t="inlineStr">
@@ -79485,12 +79561,12 @@
       <c r="AG443" t="inlineStr"/>
       <c r="AH443" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="AI443" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="AJ443" t="n">
@@ -79504,7 +79580,7 @@
       </c>
       <c r="AM443" t="inlineStr">
         <is>
-          <t>unknown_galletas carrefour finas de gofre pura mantequilla</t>
+          <t>carrefour_galletas carrefour finas de gofre pura mantequilla</t>
         </is>
       </c>
       <c r="AN443" t="inlineStr">
@@ -79519,12 +79595,12 @@
       </c>
       <c r="AP443" t="inlineStr">
         <is>
-          <t>unknown_galletas carrefour finas de gofre pura mantequilla_0.3</t>
+          <t>carrefour_galletas carrefour finas de gofre pura mantequilla_0.3</t>
         </is>
       </c>
       <c r="AQ443" t="inlineStr">
         <is>
-          <t>unknown_carrefour_finas_gofre_mantequilla</t>
+          <t>carrefour_carrefour_finas_gofre_mantequilla</t>
         </is>
       </c>
       <c r="AR443" t="n">

--- a/streamlit_data/regional_insights.xlsx
+++ b/streamlit_data/regional_insights.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E194"/>
+  <dimension ref="A1:E206"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,7 +456,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>502</v>
+        <v>413</v>
       </c>
       <c r="C2" t="n">
         <v>3</v>
@@ -465,7 +465,7 @@
         <v>6</v>
       </c>
       <c r="E2" t="n">
-        <v>18.10395836360415</v>
+        <v>19.04487809045697</v>
       </c>
     </row>
     <row r="3">
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>308</v>
+        <v>292</v>
       </c>
       <c r="C3" t="n">
         <v>2</v>
@@ -604,20 +604,20 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>Gamesa</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>16.1440042129727</v>
+        <v>14.41709677419355</v>
       </c>
     </row>
     <row r="11">
@@ -642,11 +642,11 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Gamesa</t>
+          <t>Hatuey</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="C12" t="n">
         <v>1</v>
@@ -655,7 +655,7 @@
         <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>14.41709677419355</v>
+        <v>4.617555555555556</v>
       </c>
     </row>
     <row r="13">
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C13" t="n">
         <v>2</v>
@@ -680,11 +680,11 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Hatuey</t>
+          <t>Aviva</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C14" t="n">
         <v>1</v>
@@ -693,64 +693,64 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>4.617555555555556</v>
+        <v>4.98566037735849</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Aviva</t>
+          <t>Molino Del Sol</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>4.98566037735849</v>
+        <v>6.051923076923076</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Molino Del Sol</t>
+          <t>La Panera</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>6.051923076923076</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>La Panera</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>49</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E17" t="n">
-        <v>8.199999999999999</v>
+        <v>20.04552732589859</v>
       </c>
     </row>
     <row r="18">
@@ -813,26 +813,26 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Betty Crocker</t>
+          <t>Fritolay</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>35</v>
       </c>
       <c r="C21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D21" t="n">
         <v>3</v>
       </c>
       <c r="E21" t="n">
-        <v>11.50905500557616</v>
+        <v>24.18856987356913</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Fritolay</t>
+          <t>Sunshine Snacks</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -842,29 +842,29 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E22" t="n">
-        <v>24.18856987356913</v>
+        <v>20.92956623821305</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sunshine Snacks</t>
+          <t>Betty Crocker</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>35</v>
       </c>
       <c r="C23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E23" t="n">
-        <v>20.92956623821305</v>
+        <v>11.50905500557616</v>
       </c>
     </row>
     <row r="24">
@@ -889,26 +889,26 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Pringles</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E25" t="n">
-        <v>30.43700668692141</v>
+        <v>18.21875</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Ritz</t>
+          <t>Pringles</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -918,181 +918,181 @@
         <v>2</v>
       </c>
       <c r="D26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E26" t="n">
-        <v>12.2312637036403</v>
+        <v>30.43700668692141</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Bermudez</t>
+          <t>Ritz</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D27" t="n">
         <v>3</v>
       </c>
       <c r="E27" t="n">
-        <v>9.901427320955712</v>
+        <v>12.2312637036403</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Club Social</t>
+          <t>Bermudez</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>28</v>
       </c>
       <c r="C28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>6.351099247772932</v>
+        <v>9.901427320955712</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Carrefour</t>
+          <t>Club Social</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D29" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>16.75291666666667</v>
+        <v>6.351099247772932</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Colombina</t>
+          <t>Buenhorno</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D30" t="n">
         <v>3</v>
       </c>
       <c r="E30" t="n">
-        <v>12.20950617283951</v>
+        <v>9.6225</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Mi Trigo</t>
+          <t>Colombina</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>7.637391304347826</v>
+        <v>12.20950617283951</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Old El Paso</t>
+          <t>Mi Trigo</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>23</v>
       </c>
       <c r="C32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" t="n">
         <v>2</v>
       </c>
-      <c r="D32" t="n">
-        <v>1</v>
-      </c>
       <c r="E32" t="n">
-        <v>13.455</v>
+        <v>7.637391304347826</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Duetto</t>
+          <t>Old El Paso</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D33" t="n">
         <v>1</v>
       </c>
       <c r="E33" t="n">
-        <v>4.406190476190476</v>
+        <v>13.455</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Bauducco</t>
+          <t>Bolin</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E34" t="n">
-        <v>14.2729343508003</v>
+        <v>3.895714285714285</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Pepperidge Farm</t>
+          <t>Duetto</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C35" t="n">
         <v>1</v>
       </c>
       <c r="D35" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>19.8023205237686</v>
+        <v>4.406190476190476</v>
       </c>
     </row>
     <row r="36">
@@ -1117,68 +1117,68 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Lider</t>
+          <t>Bauducco</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D37" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E37" t="n">
-        <v>7.467272727272728</v>
+        <v>14.2729343508003</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Lenny &amp; Larry's</t>
+          <t>Pepperidge Farm</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C38" t="n">
         <v>1</v>
       </c>
       <c r="D38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E38" t="n">
-        <v>26.45875</v>
+        <v>19.8023205237686</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Tostitos</t>
+          <t>Pepin</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" t="n">
         <v>2</v>
       </c>
-      <c r="D39" t="n">
-        <v>1</v>
-      </c>
       <c r="E39" t="n">
-        <v>16.30891918387187</v>
+        <v>3.923333333333334</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Charles</t>
+          <t>Lider</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C40" t="n">
         <v>1</v>
@@ -1187,17 +1187,17 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>19.27125506072875</v>
+        <v>7.467272727272728</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Pepperidge</t>
+          <t>Lenny &amp; Larry's</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C41" t="n">
         <v>1</v>
@@ -1206,36 +1206,36 @@
         <v>2</v>
       </c>
       <c r="E41" t="n">
-        <v>29.39239164449742</v>
+        <v>26.45875</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Crav'N</t>
+          <t>Tostitos</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C42" t="n">
         <v>2</v>
       </c>
       <c r="D42" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E42" t="n">
-        <v>20.64511696006157</v>
+        <v>16.30891918387187</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Devon</t>
+          <t>Pepperidge</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C43" t="n">
         <v>1</v>
@@ -1244,70 +1244,70 @@
         <v>2</v>
       </c>
       <c r="E43" t="n">
-        <v>9.404842870544091</v>
+        <v>29.39239164449742</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Wasa</t>
+          <t>Charles</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C44" t="n">
         <v>1</v>
       </c>
       <c r="D44" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E44" t="n">
-        <v>20.93163482244135</v>
+        <v>19.27125506072875</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Noel</t>
+          <t>Crav'N</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C45" t="n">
         <v>2</v>
       </c>
       <c r="D45" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E45" t="n">
-        <v>19.31337392062075</v>
+        <v>20.64511696006157</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Wow</t>
+          <t>Devon</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C46" t="n">
         <v>1</v>
       </c>
       <c r="D46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E46" t="n">
-        <v>9.45857142857143</v>
+        <v>9.404842870544091</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Wow</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -1317,96 +1317,96 @@
         <v>1</v>
       </c>
       <c r="D47" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>3.208571428571429</v>
+        <v>9.45857142857143</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Bergen</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C48" t="n">
         <v>1</v>
       </c>
       <c r="D48" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E48" t="n">
-        <v>11.83083333333333</v>
+        <v>3.208571428571429</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Wibisco</t>
+          <t>Wasa</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C49" t="n">
         <v>1</v>
       </c>
       <c r="D49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E49" t="n">
-        <v>7.709999008179106</v>
+        <v>20.93163482244135</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Motto</t>
+          <t>Wibisco</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D50" t="n">
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>15.4472192513369</v>
+        <v>7.709999008179106</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Shoon</t>
+          <t>Bergen</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C51" t="n">
         <v>1</v>
       </c>
       <c r="D51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E51" t="n">
-        <v>23.68495475113122</v>
+        <v>11.83083333333333</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Doritos</t>
+          <t>Shoon</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C52" t="n">
         <v>1</v>
@@ -1415,49 +1415,51 @@
         <v>2</v>
       </c>
       <c r="E52" t="n">
-        <v>20.25820736467665</v>
+        <v>23.68495475113122</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Keebler</t>
+          <t>Motto</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>16.53</v>
+        <v>15.4472192513369</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Qiin</t>
+          <t>Noel</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D54" t="n">
-        <v>1</v>
-      </c>
-      <c r="E54" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E54" t="n">
+        <v>19.31337392062075</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>El Charrito</t>
+          <t>Qiin</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -1474,64 +1476,62 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Cuetara</t>
+          <t>Keebler</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C56" t="n">
         <v>1</v>
       </c>
       <c r="D56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E56" t="n">
-        <v>10.41222222222222</v>
+        <v>16.53</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Pillsbury</t>
+          <t>El Charrito</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C57" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D57" t="n">
-        <v>2</v>
-      </c>
-      <c r="E57" t="n">
-        <v>7.764285714285714</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="E57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Chips Ahoy</t>
+          <t>Doritos</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C58" t="n">
+        <v>1</v>
+      </c>
+      <c r="D58" t="n">
         <v>2</v>
       </c>
-      <c r="D58" t="n">
-        <v>1</v>
-      </c>
       <c r="E58" t="n">
-        <v>12.99941707258641</v>
+        <v>20.25820736467665</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Siete</t>
+          <t>Pillsbury</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -1544,13 +1544,13 @@
         <v>2</v>
       </c>
       <c r="E59" t="n">
-        <v>35.46555757535778</v>
+        <v>7.764285714285714</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>La Real</t>
+          <t>Festival</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -1563,127 +1563,131 @@
         <v>1</v>
       </c>
       <c r="E60" t="n">
-        <v>12.46</v>
+        <v>9.385016025641024</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Member's Selection</t>
+          <t>Siete</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D61" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E61" t="n">
-        <v>13.74</v>
+        <v>35.46555757535778</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Eggo</t>
+          <t>Chips Ahoy</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D62" t="n">
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>14.6121807037156</v>
+        <v>12.99941707258641</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Bisco</t>
+          <t>Cuetara</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C63" t="n">
         <v>1</v>
       </c>
       <c r="D63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E63" t="n">
-        <v>9.168749999999999</v>
+        <v>10.41222222222222</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Biskitop</t>
+          <t>La Real</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C64" t="n">
         <v>1</v>
       </c>
       <c r="D64" t="n">
-        <v>2</v>
-      </c>
-      <c r="E64" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E64" t="n">
+        <v>12.46</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Kidsmania</t>
+          <t>Bisco</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C65" t="n">
         <v>1</v>
       </c>
       <c r="D65" t="n">
-        <v>1</v>
-      </c>
-      <c r="E65" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="E65" t="n">
+        <v>9.168749999999999</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Walkers</t>
+          <t>Member's Selection</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C66" t="n">
         <v>1</v>
       </c>
       <c r="D66" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E66" t="n">
-        <v>97.43589743589745</v>
+        <v>13.74</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Biscotto</t>
+          <t>Biskitop</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C67" t="n">
         <v>1</v>
@@ -1691,31 +1695,31 @@
       <c r="D67" t="n">
         <v>2</v>
       </c>
-      <c r="E67" t="n">
-        <v>25</v>
-      </c>
+      <c r="E67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Golden</t>
+          <t>Eggo</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C68" t="n">
         <v>1</v>
       </c>
       <c r="D68" t="n">
-        <v>2</v>
-      </c>
-      <c r="E68" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E68" t="n">
+        <v>14.6121807037156</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Festival</t>
+          <t>Kidsmania</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -1727,14 +1731,12 @@
       <c r="D69" t="n">
         <v>1</v>
       </c>
-      <c r="E69" t="n">
-        <v>9.385016025641024</v>
-      </c>
+      <c r="E69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Princesa</t>
+          <t>Golden</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -1744,11 +1746,9 @@
         <v>1</v>
       </c>
       <c r="D70" t="n">
-        <v>1</v>
-      </c>
-      <c r="E70" t="n">
-        <v>3.535714285714286</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="E70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -1772,49 +1772,49 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Schar</t>
+          <t>Holsum</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C72" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D72" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E72" t="n">
-        <v>24.18904950998269</v>
+        <v>7.78</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Laurieri</t>
+          <t>Princesa</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C73" t="n">
         <v>1</v>
       </c>
       <c r="D73" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E73" t="n">
-        <v>20.65978352354142</v>
+        <v>3.535714285714286</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Cadbury</t>
+          <t>Walkers</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C74" t="n">
         <v>1</v>
@@ -1822,46 +1822,52 @@
       <c r="D74" t="n">
         <v>2</v>
       </c>
-      <c r="E74" t="inlineStr"/>
+      <c r="E74" t="n">
+        <v>97.43589743589745</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Mr Bakewell</t>
+          <t>Crich</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C75" t="n">
         <v>1</v>
       </c>
       <c r="D75" t="n">
-        <v>1</v>
-      </c>
-      <c r="E75" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="E75" t="n">
+        <v>13.94857142857143</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Kugi</t>
+          <t>Biscotto</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C76" t="n">
         <v>1</v>
       </c>
       <c r="D76" t="n">
-        <v>1</v>
-      </c>
-      <c r="E76" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="E76" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Sunshine</t>
+          <t>Cadbury</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -1871,20 +1877,18 @@
         <v>1</v>
       </c>
       <c r="D77" t="n">
-        <v>1</v>
-      </c>
-      <c r="E77" t="n">
-        <v>9.488333333333333</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="E77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Hosttes</t>
+          <t>Sunshine</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C78" t="n">
         <v>1</v>
@@ -1893,17 +1897,17 @@
         <v>1</v>
       </c>
       <c r="E78" t="n">
-        <v>36.83418646645511</v>
+        <v>9.488333333333333</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Merba</t>
+          <t>Costa</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C79" t="n">
         <v>1</v>
@@ -1911,35 +1915,35 @@
       <c r="D79" t="n">
         <v>1</v>
       </c>
-      <c r="E79" t="inlineStr"/>
+      <c r="E79" t="n">
+        <v>14.64666666666667</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Badia</t>
+          <t>Otis Spunkmeyer</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C80" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D80" t="n">
-        <v>1</v>
-      </c>
-      <c r="E80" t="n">
-        <v>28.56294367711628</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="E80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Kiss</t>
+          <t>Schar</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C81" t="n">
         <v>2</v>
@@ -1948,17 +1952,17 @@
         <v>3</v>
       </c>
       <c r="E81" t="n">
-        <v>20.05506545869531</v>
+        <v>24.18904950998269</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>La Libanesa</t>
+          <t>Kugi</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C82" t="n">
         <v>1</v>
@@ -1971,83 +1975,81 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Bagel Bites</t>
+          <t>Laurieri</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C83" t="n">
+        <v>1</v>
+      </c>
+      <c r="D83" t="n">
         <v>2</v>
       </c>
-      <c r="D83" t="n">
-        <v>1</v>
-      </c>
       <c r="E83" t="n">
-        <v>14.76764878866199</v>
+        <v>20.65978352354142</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Nutella</t>
+          <t>Mr Bakewell</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C84" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D84" t="n">
         <v>1</v>
       </c>
-      <c r="E84" t="n">
-        <v>15.46996215078755</v>
-      </c>
+      <c r="E84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Stiratini</t>
+          <t>Badia</t>
         </is>
       </c>
       <c r="B85" t="n">
         <v>5</v>
       </c>
       <c r="C85" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D85" t="n">
         <v>1</v>
       </c>
       <c r="E85" t="n">
-        <v>17.42078051958985</v>
+        <v>28.56294367711628</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>La Dulcerita</t>
+          <t>Bagel Bites</t>
         </is>
       </c>
       <c r="B86" t="n">
         <v>5</v>
       </c>
       <c r="C86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D86" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>14.22407288526729</v>
+        <v>14.76764878866199</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Tiffany</t>
+          <t>Hosttes</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -2059,24 +2061,28 @@
       <c r="D87" t="n">
         <v>1</v>
       </c>
-      <c r="E87" t="inlineStr"/>
+      <c r="E87" t="n">
+        <v>36.83418646645511</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Buenhorno</t>
+          <t>Kiss</t>
         </is>
       </c>
       <c r="B88" t="n">
         <v>5</v>
       </c>
       <c r="C88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D88" t="n">
-        <v>1</v>
-      </c>
-      <c r="E88" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E88" t="n">
+        <v>20.05506545869531</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -2100,7 +2106,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Bolletje</t>
+          <t>La Libanesa</t>
         </is>
       </c>
       <c r="B90" t="n">
@@ -2110,16 +2116,14 @@
         <v>1</v>
       </c>
       <c r="D90" t="n">
-        <v>2</v>
-      </c>
-      <c r="E90" t="n">
-        <v>29.40549939726599</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="E90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Triskits</t>
+          <t>Merba</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -2136,47 +2140,49 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Takis</t>
+          <t>La Dulcerita</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C92" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D92" t="n">
         <v>2</v>
       </c>
       <c r="E92" t="n">
-        <v>41.86</v>
+        <v>14.22407288526729</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Otis Spunkmeyer</t>
+          <t>Nutella</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C93" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D93" t="n">
-        <v>2</v>
-      </c>
-      <c r="E93" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E93" t="n">
+        <v>15.46996215078755</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Dulcesol</t>
+          <t>Tiffany</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C94" t="n">
         <v>1</v>
@@ -2184,18 +2190,16 @@
       <c r="D94" t="n">
         <v>1</v>
       </c>
-      <c r="E94" t="n">
-        <v>6.916666666666667</v>
-      </c>
+      <c r="E94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Stonefire</t>
+          <t>Stiratini</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C95" t="n">
         <v>1</v>
@@ -2204,89 +2208,87 @@
         <v>1</v>
       </c>
       <c r="E95" t="n">
-        <v>16.92</v>
+        <v>17.42078051958985</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Milka</t>
+          <t>Triskits</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C96" t="n">
         <v>1</v>
       </c>
       <c r="D96" t="n">
-        <v>2</v>
-      </c>
-      <c r="E96" t="n">
-        <v>29.0725</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="E96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Nestle</t>
+          <t>Bolletje</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C97" t="n">
         <v>1</v>
       </c>
       <c r="D97" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E97" t="n">
-        <v>41.70528266913809</v>
+        <v>29.40549939726599</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Glutino</t>
+          <t>Milka</t>
         </is>
       </c>
       <c r="B98" t="n">
         <v>4</v>
       </c>
       <c r="C98" t="n">
+        <v>1</v>
+      </c>
+      <c r="D98" t="n">
         <v>2</v>
       </c>
-      <c r="D98" t="n">
-        <v>3</v>
-      </c>
       <c r="E98" t="n">
-        <v>19.41435404641845</v>
+        <v>29.0725</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Snyder’S</t>
+          <t>Kinder</t>
         </is>
       </c>
       <c r="B99" t="n">
         <v>4</v>
       </c>
       <c r="C99" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D99" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E99" t="n">
-        <v>21.8340355175269</v>
+        <v>9.291503578576814</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Herrs</t>
+          <t>Ovaltine</t>
         </is>
       </c>
       <c r="B100" t="n">
@@ -2299,13 +2301,13 @@
         <v>1</v>
       </c>
       <c r="E100" t="n">
-        <v>37.30902864926393</v>
+        <v>19.9445103354795</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Ovaltine</t>
+          <t>Stonefire</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -2318,32 +2320,32 @@
         <v>1</v>
       </c>
       <c r="E101" t="n">
-        <v>19.9445103354795</v>
+        <v>16.92</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Kinder</t>
+          <t>Nestle</t>
         </is>
       </c>
       <c r="B102" t="n">
         <v>4</v>
       </c>
       <c r="C102" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D102" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E102" t="n">
-        <v>9.291503578576814</v>
+        <v>41.70528266913809</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Keeber</t>
+          <t>Herrs</t>
         </is>
       </c>
       <c r="B103" t="n">
@@ -2353,20 +2355,20 @@
         <v>1</v>
       </c>
       <c r="D103" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E103" t="n">
-        <v>28.61772083892403</v>
+        <v>37.30902864926393</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Dux</t>
+          <t>Snyder’S</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C104" t="n">
         <v>1</v>
@@ -2374,71 +2376,75 @@
       <c r="D104" t="n">
         <v>1</v>
       </c>
-      <c r="E104" t="inlineStr"/>
+      <c r="E104" t="n">
+        <v>21.8340355175269</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Crix</t>
+          <t>Glutino</t>
         </is>
       </c>
       <c r="B105" t="n">
+        <v>4</v>
+      </c>
+      <c r="C105" t="n">
+        <v>2</v>
+      </c>
+      <c r="D105" t="n">
         <v>3</v>
       </c>
-      <c r="C105" t="n">
-        <v>1</v>
-      </c>
-      <c r="D105" t="n">
-        <v>1</v>
-      </c>
       <c r="E105" t="n">
-        <v>7.160318629656713</v>
+        <v>19.41435404641845</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Waitrose</t>
+          <t>Takis</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C106" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D106" t="n">
         <v>2</v>
       </c>
-      <c r="E106" t="inlineStr"/>
+      <c r="E106" t="n">
+        <v>41.86</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Chobani</t>
+          <t>Keeber</t>
         </is>
       </c>
       <c r="B107" t="n">
+        <v>4</v>
+      </c>
+      <c r="C107" t="n">
+        <v>1</v>
+      </c>
+      <c r="D107" t="n">
         <v>3</v>
       </c>
-      <c r="C107" t="n">
-        <v>1</v>
-      </c>
-      <c r="D107" t="n">
-        <v>1</v>
-      </c>
       <c r="E107" t="n">
-        <v>25.58923192551497</v>
+        <v>28.61772083892403</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Snyders</t>
+          <t>Dulcesol</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C108" t="n">
         <v>1</v>
@@ -2446,12 +2452,14 @@
       <c r="D108" t="n">
         <v>1</v>
       </c>
-      <c r="E108" t="inlineStr"/>
+      <c r="E108" t="n">
+        <v>6.916666666666667</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Chetos</t>
+          <t>Totino's</t>
         </is>
       </c>
       <c r="B109" t="n">
@@ -2463,12 +2471,14 @@
       <c r="D109" t="n">
         <v>1</v>
       </c>
-      <c r="E109" t="inlineStr"/>
+      <c r="E109" t="n">
+        <v>10.85144743680014</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Del-E</t>
+          <t>Chetos</t>
         </is>
       </c>
       <c r="B110" t="n">
@@ -2478,14 +2488,14 @@
         <v>1</v>
       </c>
       <c r="D110" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Pizkas</t>
+          <t>Chobani</t>
         </is>
       </c>
       <c r="B111" t="n">
@@ -2498,13 +2508,13 @@
         <v>1</v>
       </c>
       <c r="E111" t="n">
-        <v>4.146666666666667</v>
+        <v>25.58923192551497</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Roomboter</t>
+          <t>Waitrose</t>
         </is>
       </c>
       <c r="B112" t="n">
@@ -2516,14 +2526,12 @@
       <c r="D112" t="n">
         <v>2</v>
       </c>
-      <c r="E112" t="n">
-        <v>16.70555144365191</v>
-      </c>
+      <c r="E112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Confetti</t>
+          <t>Verkade</t>
         </is>
       </c>
       <c r="B113" t="n">
@@ -2535,12 +2543,14 @@
       <c r="D113" t="n">
         <v>1</v>
       </c>
-      <c r="E113" t="inlineStr"/>
+      <c r="E113" t="n">
+        <v>13.51789778605421</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Verkade</t>
+          <t>Van Der Meulen</t>
         </is>
       </c>
       <c r="B114" t="n">
@@ -2553,13 +2563,13 @@
         <v>1</v>
       </c>
       <c r="E114" t="n">
-        <v>13.51789778605421</v>
+        <v>12.12155070255629</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Elina</t>
+          <t>Confetti</t>
         </is>
       </c>
       <c r="B115" t="n">
@@ -2571,14 +2581,12 @@
       <c r="D115" t="n">
         <v>1</v>
       </c>
-      <c r="E115" t="n">
-        <v>35.07692932225363</v>
-      </c>
+      <c r="E115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Van Der Meulen</t>
+          <t>Crix</t>
         </is>
       </c>
       <c r="B116" t="n">
@@ -2591,13 +2599,13 @@
         <v>1</v>
       </c>
       <c r="E116" t="n">
-        <v>12.12155070255629</v>
+        <v>7.160318629656713</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Flourish</t>
+          <t>Del-E</t>
         </is>
       </c>
       <c r="B117" t="n">
@@ -2607,35 +2615,37 @@
         <v>1</v>
       </c>
       <c r="D117" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Mars</t>
+          <t>Town House</t>
         </is>
       </c>
       <c r="B118" t="n">
+        <v>3</v>
+      </c>
+      <c r="C118" t="n">
         <v>2</v>
       </c>
-      <c r="C118" t="n">
-        <v>1</v>
-      </c>
       <c r="D118" t="n">
-        <v>1</v>
-      </c>
-      <c r="E118" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="E118" t="n">
+        <v>24.31600957701516</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Werther’S</t>
+          <t>Dux</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C119" t="n">
         <v>1</v>
@@ -2648,11 +2658,11 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Tuc</t>
+          <t>Flourish</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C120" t="n">
         <v>1</v>
@@ -2660,18 +2670,16 @@
       <c r="D120" t="n">
         <v>1</v>
       </c>
-      <c r="E120" t="n">
-        <v>7.575418994413408</v>
-      </c>
+      <c r="E120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Cole´s</t>
+          <t>Snyders</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C121" t="n">
         <v>1</v>
@@ -2679,18 +2687,16 @@
       <c r="D121" t="n">
         <v>1</v>
       </c>
-      <c r="E121" t="n">
-        <v>21.94025264317509</v>
-      </c>
+      <c r="E121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Wala</t>
+          <t>Pizkas</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C122" t="n">
         <v>1</v>
@@ -2698,16 +2704,18 @@
       <c r="D122" t="n">
         <v>1</v>
       </c>
-      <c r="E122" t="inlineStr"/>
+      <c r="E122" t="n">
+        <v>4.146666666666667</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Knotts</t>
+          <t>Elina</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C123" t="n">
         <v>1</v>
@@ -2715,29 +2723,33 @@
       <c r="D123" t="n">
         <v>1</v>
       </c>
-      <c r="E123" t="inlineStr"/>
+      <c r="E123" t="n">
+        <v>35.07692932225363</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Willie</t>
+          <t>Roomboter</t>
         </is>
       </c>
       <c r="B124" t="n">
+        <v>3</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1</v>
+      </c>
+      <c r="D124" t="n">
         <v>2</v>
       </c>
-      <c r="C124" t="n">
-        <v>1</v>
-      </c>
-      <c r="D124" t="n">
-        <v>1</v>
-      </c>
-      <c r="E124" t="inlineStr"/>
+      <c r="E124" t="n">
+        <v>16.70555144365191</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Sara Lee</t>
+          <t>Ricola</t>
         </is>
       </c>
       <c r="B125" t="n">
@@ -2750,13 +2762,13 @@
         <v>1</v>
       </c>
       <c r="E125" t="n">
-        <v>24.085</v>
+        <v>7.351955307262569</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Wheat Thins</t>
+          <t>Willie</t>
         </is>
       </c>
       <c r="B126" t="n">
@@ -2768,14 +2780,12 @@
       <c r="D126" t="n">
         <v>1</v>
       </c>
-      <c r="E126" t="n">
-        <v>8.979888962508067</v>
-      </c>
+      <c r="E126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Soldanza</t>
+          <t>Wheat Thins</t>
         </is>
       </c>
       <c r="B127" t="n">
@@ -2787,12 +2797,14 @@
       <c r="D127" t="n">
         <v>1</v>
       </c>
-      <c r="E127" t="inlineStr"/>
+      <c r="E127" t="n">
+        <v>8.979888962508067</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Cheez</t>
+          <t>Werther’S</t>
         </is>
       </c>
       <c r="B128" t="n">
@@ -2809,7 +2821,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Hills</t>
+          <t>Wala</t>
         </is>
       </c>
       <c r="B129" t="n">
@@ -2826,7 +2838,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Can Can</t>
+          <t>Voortman</t>
         </is>
       </c>
       <c r="B130" t="n">
@@ -2839,13 +2851,13 @@
         <v>1</v>
       </c>
       <c r="E130" t="n">
-        <v>3.915</v>
+        <v>20.17345399698341</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Hinged</t>
+          <t>Vigo</t>
         </is>
       </c>
       <c r="B131" t="n">
@@ -2858,13 +2870,13 @@
         <v>1</v>
       </c>
       <c r="E131" t="n">
-        <v>1.907848055928269</v>
+        <v>9.433248720978664</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Twix</t>
+          <t>Sara Lee</t>
         </is>
       </c>
       <c r="B132" t="n">
@@ -2877,13 +2889,13 @@
         <v>1</v>
       </c>
       <c r="E132" t="n">
-        <v>25.28014847471393</v>
+        <v>24.085</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Crunchmaster</t>
+          <t>Soldanza</t>
         </is>
       </c>
       <c r="B133" t="n">
@@ -2895,14 +2907,12 @@
       <c r="D133" t="n">
         <v>1</v>
       </c>
-      <c r="E133" t="n">
-        <v>51.37009840929231</v>
-      </c>
+      <c r="E133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Glad</t>
+          <t>Twix</t>
         </is>
       </c>
       <c r="B134" t="n">
@@ -2914,12 +2924,14 @@
       <c r="D134" t="n">
         <v>1</v>
       </c>
-      <c r="E134" t="inlineStr"/>
+      <c r="E134" t="n">
+        <v>25.28014847471393</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Lewis Bake Shop</t>
+          <t>Tuc</t>
         </is>
       </c>
       <c r="B135" t="n">
@@ -2932,13 +2944,13 @@
         <v>1</v>
       </c>
       <c r="E135" t="n">
-        <v>5.189283551419543</v>
+        <v>7.575418994413408</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Beivita</t>
+          <t>Pico Bello</t>
         </is>
       </c>
       <c r="B136" t="n">
@@ -2951,13 +2963,13 @@
         <v>1</v>
       </c>
       <c r="E136" t="n">
-        <v>35.19230769230769</v>
+        <v>21.08728168019017</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Dried</t>
+          <t>Knotts</t>
         </is>
       </c>
       <c r="B137" t="n">
@@ -2967,14 +2979,14 @@
         <v>1</v>
       </c>
       <c r="D137" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Dove</t>
+          <t>Glad</t>
         </is>
       </c>
       <c r="B138" t="n">
@@ -2986,14 +2998,12 @@
       <c r="D138" t="n">
         <v>1</v>
       </c>
-      <c r="E138" t="n">
-        <v>10.95146340976004</v>
-      </c>
+      <c r="E138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Vigo</t>
+          <t>Lewis Bake Shop</t>
         </is>
       </c>
       <c r="B139" t="n">
@@ -3006,20 +3016,20 @@
         <v>1</v>
       </c>
       <c r="E139" t="n">
-        <v>9.433248720978664</v>
+        <v>5.189283551419543</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Nature Valley</t>
+          <t>Dairy</t>
         </is>
       </c>
       <c r="B140" t="n">
         <v>2</v>
       </c>
       <c r="C140" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D140" t="n">
         <v>1</v>
@@ -3029,7 +3039,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Voortman</t>
+          <t>Crunchmaster</t>
         </is>
       </c>
       <c r="B141" t="n">
@@ -3042,13 +3052,13 @@
         <v>1</v>
       </c>
       <c r="E141" t="n">
-        <v>20.17345399698341</v>
+        <v>51.37009840929231</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>La Tortilla Factory</t>
+          <t>Cole´s</t>
         </is>
       </c>
       <c r="B142" t="n">
@@ -3061,7 +3071,7 @@
         <v>1</v>
       </c>
       <c r="E142" t="n">
-        <v>21.71</v>
+        <v>21.94025264317509</v>
       </c>
     </row>
     <row r="143">
@@ -3084,7 +3094,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Dairy</t>
+          <t>Dove</t>
         </is>
       </c>
       <c r="B144" t="n">
@@ -3096,12 +3106,14 @@
       <c r="D144" t="n">
         <v>1</v>
       </c>
-      <c r="E144" t="inlineStr"/>
+      <c r="E144" t="n">
+        <v>10.95146340976004</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Ricola</t>
+          <t>Dried</t>
         </is>
       </c>
       <c r="B145" t="n">
@@ -3111,20 +3123,18 @@
         <v>1</v>
       </c>
       <c r="D145" t="n">
-        <v>1</v>
-      </c>
-      <c r="E145" t="n">
-        <v>7.351955307262569</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="E145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Twizzlers</t>
+          <t>Hinged</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C146" t="n">
         <v>1</v>
@@ -3132,16 +3142,18 @@
       <c r="D146" t="n">
         <v>1</v>
       </c>
-      <c r="E146" t="inlineStr"/>
+      <c r="E146" t="n">
+        <v>1.907848055928269</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Snickers</t>
+          <t>La Tortilla Factory</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C147" t="n">
         <v>1</v>
@@ -3150,17 +3162,17 @@
         <v>1</v>
       </c>
       <c r="E147" t="n">
-        <v>40.99</v>
+        <v>21.71</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Stouffer's</t>
+          <t>Cheez</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C148" t="n">
         <v>1</v>
@@ -3168,18 +3180,16 @@
       <c r="D148" t="n">
         <v>1</v>
       </c>
-      <c r="E148" t="n">
-        <v>27.47380304721075</v>
-      </c>
+      <c r="E148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Triscuit</t>
+          <t>Mars</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C149" t="n">
         <v>1</v>
@@ -3187,18 +3197,16 @@
       <c r="D149" t="n">
         <v>1</v>
       </c>
-      <c r="E149" t="n">
-        <v>21.76632743949854</v>
-      </c>
+      <c r="E149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Toblerone</t>
+          <t>Can Can</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C150" t="n">
         <v>1</v>
@@ -3207,17 +3215,17 @@
         <v>1</v>
       </c>
       <c r="E150" t="n">
-        <v>14.42655274400263</v>
+        <v>3.915</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Santitas</t>
+          <t>Beivita</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C151" t="n">
         <v>1</v>
@@ -3226,55 +3234,53 @@
         <v>1</v>
       </c>
       <c r="E151" t="n">
-        <v>23.62766194234949</v>
+        <v>35.19230769230769</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Vegefarm</t>
+          <t>Ferrero</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C152" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D152" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E152" t="n">
-        <v>27.42714334124026</v>
+        <v>48.37</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Kraft</t>
+          <t>Nature Valley</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C153" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D153" t="n">
         <v>1</v>
       </c>
-      <c r="E153" t="n">
-        <v>9.264432029795158</v>
-      </c>
+      <c r="E153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Reynolds</t>
+          <t>Hills</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C154" t="n">
         <v>1</v>
@@ -3287,7 +3293,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Haagen Daz</t>
+          <t>Ducales</t>
         </is>
       </c>
       <c r="B155" t="n">
@@ -3299,12 +3305,14 @@
       <c r="D155" t="n">
         <v>1</v>
       </c>
-      <c r="E155" t="inlineStr"/>
+      <c r="E155" t="n">
+        <v>21.76632743949854</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Goldfish</t>
+          <t>Toblerone</t>
         </is>
       </c>
       <c r="B156" t="n">
@@ -3317,13 +3325,13 @@
         <v>1</v>
       </c>
       <c r="E156" t="n">
-        <v>15.39664804469274</v>
+        <v>14.42655274400263</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Give &amp; Go</t>
+          <t>Double Duty</t>
         </is>
       </c>
       <c r="B157" t="n">
@@ -3340,7 +3348,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Frito-Lay</t>
+          <t>DiGiorno</t>
         </is>
       </c>
       <c r="B158" t="n">
@@ -3352,12 +3360,14 @@
       <c r="D158" t="n">
         <v>1</v>
       </c>
-      <c r="E158" t="inlineStr"/>
+      <c r="E158" t="n">
+        <v>14.25891435863968</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Ferrero</t>
+          <t>Triscuit</t>
         </is>
       </c>
       <c r="B159" t="n">
@@ -3369,7 +3379,9 @@
       <c r="D159" t="n">
         <v>1</v>
       </c>
-      <c r="E159" t="inlineStr"/>
+      <c r="E159" t="n">
+        <v>21.76632743949854</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -3391,7 +3403,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Ducales</t>
+          <t>Vegefarm</t>
         </is>
       </c>
       <c r="B161" t="n">
@@ -3404,13 +3416,13 @@
         <v>1</v>
       </c>
       <c r="E161" t="n">
-        <v>21.76632743949854</v>
+        <v>27.42714334124026</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Double Duty</t>
+          <t>Cusano´s</t>
         </is>
       </c>
       <c r="B162" t="n">
@@ -3427,7 +3439,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>DiGiorno</t>
+          <t>Twizzlers</t>
         </is>
       </c>
       <c r="B163" t="n">
@@ -3439,14 +3451,12 @@
       <c r="D163" t="n">
         <v>1</v>
       </c>
-      <c r="E163" t="n">
-        <v>14.25891435863968</v>
-      </c>
+      <c r="E163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Cusano´s</t>
+          <t>Sultana</t>
         </is>
       </c>
       <c r="B164" t="n">
@@ -3458,7 +3468,9 @@
       <c r="D164" t="n">
         <v>1</v>
       </c>
-      <c r="E164" t="inlineStr"/>
+      <c r="E164" t="n">
+        <v>18.58472998137803</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -3514,7 +3526,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Cho Cho</t>
+          <t>Chokis</t>
         </is>
       </c>
       <c r="B168" t="n">
@@ -3526,12 +3538,14 @@
       <c r="D168" t="n">
         <v>1</v>
       </c>
-      <c r="E168" t="inlineStr"/>
+      <c r="E168" t="n">
+        <v>11.44</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Chiefeez</t>
+          <t>Cho Cho</t>
         </is>
       </c>
       <c r="B169" t="n">
@@ -3548,7 +3562,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Chester</t>
+          <t>Chiefeez</t>
         </is>
       </c>
       <c r="B170" t="n">
@@ -3565,7 +3579,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Bigelow</t>
+          <t>Chester</t>
         </is>
       </c>
       <c r="B171" t="n">
@@ -3582,7 +3596,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Becky's</t>
+          <t>Bigelow</t>
         </is>
       </c>
       <c r="B172" t="n">
@@ -3594,14 +3608,12 @@
       <c r="D172" t="n">
         <v>1</v>
       </c>
-      <c r="E172" t="n">
-        <v>19.37665392531608</v>
-      </c>
+      <c r="E172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>HOL Foods</t>
+          <t>Becky's</t>
         </is>
       </c>
       <c r="B173" t="n">
@@ -3614,13 +3626,13 @@
         <v>1</v>
       </c>
       <c r="E173" t="n">
-        <v>14.42307692307692</v>
+        <v>19.37665392531608</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Haribo</t>
+          <t>Fit Crunch</t>
         </is>
       </c>
       <c r="B174" t="n">
@@ -3632,12 +3644,14 @@
       <c r="D174" t="n">
         <v>1</v>
       </c>
-      <c r="E174" t="inlineStr"/>
+      <c r="E174" t="n">
+        <v>61.6</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Post</t>
+          <t>Nerds</t>
         </is>
       </c>
       <c r="B175" t="n">
@@ -3649,14 +3663,12 @@
       <c r="D175" t="n">
         <v>1</v>
       </c>
-      <c r="E175" t="n">
-        <v>7.51</v>
-      </c>
+      <c r="E175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Hershey</t>
+          <t>Stouffer's</t>
         </is>
       </c>
       <c r="B176" t="n">
@@ -3669,13 +3681,13 @@
         <v>1</v>
       </c>
       <c r="E176" t="n">
-        <v>19.07848055928269</v>
+        <v>27.47380304721075</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Pirulin</t>
+          <t>Hostess</t>
         </is>
       </c>
       <c r="B177" t="n">
@@ -3687,12 +3699,14 @@
       <c r="D177" t="n">
         <v>1</v>
       </c>
-      <c r="E177" t="inlineStr"/>
+      <c r="E177" t="n">
+        <v>20.82</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Pirucream</t>
+          <t>Members Selection</t>
         </is>
       </c>
       <c r="B178" t="n">
@@ -3704,14 +3718,12 @@
       <c r="D178" t="n">
         <v>1</v>
       </c>
-      <c r="E178" t="n">
-        <v>20.53625219611713</v>
-      </c>
+      <c r="E178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Oscar Mayer</t>
+          <t>Mcvitie'S</t>
         </is>
       </c>
       <c r="B179" t="n">
@@ -3724,7 +3736,7 @@
         <v>1</v>
       </c>
       <c r="E179" t="n">
-        <v>21.70707121411719</v>
+        <v>37.62485187066193</v>
       </c>
     </row>
     <row r="180">
@@ -3749,7 +3761,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Odorex</t>
+          <t>Oscar Mayer</t>
         </is>
       </c>
       <c r="B181" t="n">
@@ -3761,12 +3773,14 @@
       <c r="D181" t="n">
         <v>1</v>
       </c>
-      <c r="E181" t="inlineStr"/>
+      <c r="E181" t="n">
+        <v>21.70707121411719</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Nerds</t>
+          <t>Marie</t>
         </is>
       </c>
       <c r="B182" t="n">
@@ -3783,7 +3797,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Members Selection</t>
+          <t>Liga</t>
         </is>
       </c>
       <c r="B183" t="n">
@@ -3795,12 +3809,14 @@
       <c r="D183" t="n">
         <v>1</v>
       </c>
-      <c r="E183" t="inlineStr"/>
+      <c r="E183" t="n">
+        <v>10.58305138091117</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Mcvitie'S</t>
+          <t>Kraft</t>
         </is>
       </c>
       <c r="B184" t="n">
@@ -3813,13 +3829,13 @@
         <v>1</v>
       </c>
       <c r="E184" t="n">
-        <v>37.62485187066193</v>
+        <v>9.264432029795158</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Marie</t>
+          <t>King's Hawaiian</t>
         </is>
       </c>
       <c r="B185" t="n">
@@ -3836,7 +3852,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Liga</t>
+          <t>Kimberley's Bakeshoppe</t>
         </is>
       </c>
       <c r="B186" t="n">
@@ -3848,14 +3864,12 @@
       <c r="D186" t="n">
         <v>1</v>
       </c>
-      <c r="E186" t="n">
-        <v>10.58305138091117</v>
-      </c>
+      <c r="E186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>King's Hawaiian</t>
+          <t>Pirucream</t>
         </is>
       </c>
       <c r="B187" t="n">
@@ -3867,12 +3881,14 @@
       <c r="D187" t="n">
         <v>1</v>
       </c>
-      <c r="E187" t="inlineStr"/>
+      <c r="E187" t="n">
+        <v>20.53625219611713</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Kimberley's Bakeshoppe</t>
+          <t>Pirulin</t>
         </is>
       </c>
       <c r="B188" t="n">
@@ -3889,7 +3905,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Hostess</t>
+          <t>Jos Poell</t>
         </is>
       </c>
       <c r="B189" t="n">
@@ -3902,13 +3918,13 @@
         <v>1</v>
       </c>
       <c r="E189" t="n">
-        <v>20.82</v>
+        <v>25.38795779019243</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Hollandia</t>
+          <t>Post</t>
         </is>
       </c>
       <c r="B190" t="n">
@@ -3921,13 +3937,13 @@
         <v>1</v>
       </c>
       <c r="E190" t="n">
-        <v>52.34878150009826</v>
+        <v>7.51</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Holiday</t>
+          <t>Hollandia</t>
         </is>
       </c>
       <c r="B191" t="n">
@@ -3939,12 +3955,14 @@
       <c r="D191" t="n">
         <v>1</v>
       </c>
-      <c r="E191" t="inlineStr"/>
+      <c r="E191" t="n">
+        <v>52.34878150009826</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Highland</t>
+          <t>Frito-Lay</t>
         </is>
       </c>
       <c r="B192" t="n">
@@ -3961,7 +3979,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>HiPro</t>
+          <t>Holiday</t>
         </is>
       </c>
       <c r="B193" t="n">
@@ -3978,19 +3996,233 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
+          <t>Reynolds</t>
+        </is>
+      </c>
+      <c r="B194" t="n">
+        <v>1</v>
+      </c>
+      <c r="C194" t="n">
+        <v>1</v>
+      </c>
+      <c r="D194" t="n">
+        <v>1</v>
+      </c>
+      <c r="E194" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Highland</t>
+        </is>
+      </c>
+      <c r="B195" t="n">
+        <v>1</v>
+      </c>
+      <c r="C195" t="n">
+        <v>1</v>
+      </c>
+      <c r="D195" t="n">
+        <v>1</v>
+      </c>
+      <c r="E195" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Santitas</t>
+        </is>
+      </c>
+      <c r="B196" t="n">
+        <v>1</v>
+      </c>
+      <c r="C196" t="n">
+        <v>1</v>
+      </c>
+      <c r="D196" t="n">
+        <v>1</v>
+      </c>
+      <c r="E196" t="n">
+        <v>23.62766194234949</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>HiPro</t>
+        </is>
+      </c>
+      <c r="B197" t="n">
+        <v>1</v>
+      </c>
+      <c r="C197" t="n">
+        <v>1</v>
+      </c>
+      <c r="D197" t="n">
+        <v>1</v>
+      </c>
+      <c r="E197" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Hershey</t>
+        </is>
+      </c>
+      <c r="B198" t="n">
+        <v>1</v>
+      </c>
+      <c r="C198" t="n">
+        <v>1</v>
+      </c>
+      <c r="D198" t="n">
+        <v>1</v>
+      </c>
+      <c r="E198" t="n">
+        <v>19.07848055928269</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Haribo</t>
+        </is>
+      </c>
+      <c r="B199" t="n">
+        <v>1</v>
+      </c>
+      <c r="C199" t="n">
+        <v>1</v>
+      </c>
+      <c r="D199" t="n">
+        <v>1</v>
+      </c>
+      <c r="E199" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Haagen Daz</t>
+        </is>
+      </c>
+      <c r="B200" t="n">
+        <v>1</v>
+      </c>
+      <c r="C200" t="n">
+        <v>1</v>
+      </c>
+      <c r="D200" t="n">
+        <v>1</v>
+      </c>
+      <c r="E200" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Snickers</t>
+        </is>
+      </c>
+      <c r="B201" t="n">
+        <v>1</v>
+      </c>
+      <c r="C201" t="n">
+        <v>1</v>
+      </c>
+      <c r="D201" t="n">
+        <v>1</v>
+      </c>
+      <c r="E201" t="n">
+        <v>40.99</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>HOL Foods</t>
+        </is>
+      </c>
+      <c r="B202" t="n">
+        <v>1</v>
+      </c>
+      <c r="C202" t="n">
+        <v>1</v>
+      </c>
+      <c r="D202" t="n">
+        <v>1</v>
+      </c>
+      <c r="E202" t="n">
+        <v>14.42307692307692</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Goldfish</t>
+        </is>
+      </c>
+      <c r="B203" t="n">
+        <v>1</v>
+      </c>
+      <c r="C203" t="n">
+        <v>1</v>
+      </c>
+      <c r="D203" t="n">
+        <v>1</v>
+      </c>
+      <c r="E203" t="n">
+        <v>15.39664804469274</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Odorex</t>
+        </is>
+      </c>
+      <c r="B204" t="n">
+        <v>1</v>
+      </c>
+      <c r="C204" t="n">
+        <v>1</v>
+      </c>
+      <c r="D204" t="n">
+        <v>1</v>
+      </c>
+      <c r="E204" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Give &amp; Go</t>
+        </is>
+      </c>
+      <c r="B205" t="n">
+        <v>1</v>
+      </c>
+      <c r="C205" t="n">
+        <v>1</v>
+      </c>
+      <c r="D205" t="n">
+        <v>1</v>
+      </c>
+      <c r="E205" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
           <t>Yasso</t>
         </is>
       </c>
-      <c r="B194" t="n">
-        <v>1</v>
-      </c>
-      <c r="C194" t="n">
-        <v>1</v>
-      </c>
-      <c r="D194" t="n">
-        <v>1</v>
-      </c>
-      <c r="E194" t="inlineStr"/>
+      <c r="B206" t="n">
+        <v>1</v>
+      </c>
+      <c r="C206" t="n">
+        <v>1</v>
+      </c>
+      <c r="D206" t="n">
+        <v>1</v>
+      </c>
+      <c r="E206" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4098,7 +4330,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>325</v>
+        <v>308</v>
       </c>
       <c r="D4" t="n">
         <v>22.60982128245165</v>
@@ -4170,7 +4402,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D7" t="n">
         <v>17.25766323803849</v>
@@ -6698,7 +6930,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -6777,17 +7009,17 @@
       <c r="AG13" t="inlineStr"/>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>unknown_10 brioche comte truf crf</t>
+          <t>carrefour_10 brioche comte truf crf</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -6802,7 +7034,7 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>unknown_10 brioche comte truf crf_0.11</t>
+          <t>carrefour_10 brioche comte truf crf_0.11</t>
         </is>
       </c>
       <c r="AN13" t="n">
@@ -6816,7 +7048,7 @@
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>unknown_brioche_comte_truf</t>
+          <t>carrefour_brioche_comte_truf</t>
         </is>
       </c>
       <c r="AR13" t="n">
@@ -7223,7 +7455,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Fit Crunch</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -7302,17 +7534,17 @@
       <c r="AG16" t="inlineStr"/>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Fit Crunch</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Fit Crunch</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>unknown_barra proteina fit crunch wafer mantequilla mani</t>
+          <t>fit crunch_barra proteina fit crunch wafer mantequilla mani</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
@@ -7327,7 +7559,7 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>unknown_barra proteina fit crunch wafer mantequilla mani_0.04</t>
+          <t>fit crunch_barra proteina fit crunch wafer mantequilla mani_0.04</t>
         </is>
       </c>
       <c r="AN16" t="n">
@@ -7341,7 +7573,7 @@
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>unknown_barra_crunch_mani_mantequilla</t>
+          <t>fit crunch_barra_crunch_mani_mantequilla</t>
         </is>
       </c>
       <c r="AR16" t="n">
@@ -12078,7 +12310,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Ferrero</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -12157,17 +12389,17 @@
       <c r="AG45" t="inlineStr"/>
       <c r="AH45" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Ferrero</t>
         </is>
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Ferrero</t>
         </is>
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>unknown_barra de chocolate con wafer y crema de avellana ferrero tronky</t>
+          <t>ferrero_barra de chocolate con wafer y crema de avellana ferrero tronky</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -12182,7 +12414,7 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>unknown_barra de chocolate con wafer y crema de avellana ferrero tronky_0.02</t>
+          <t>ferrero_barra de chocolate con wafer y crema de avellana ferrero tronky_0.02</t>
         </is>
       </c>
       <c r="AN45" t="n">
@@ -12196,7 +12428,7 @@
       </c>
       <c r="AQ45" t="inlineStr">
         <is>
-          <t>unknown_avellana_barra_chocolate_ferrero</t>
+          <t>ferrero_avellana_barra_chocolate_ferrero</t>
         </is>
       </c>
       <c r="AR45" t="n">
@@ -27946,7 +28178,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Crich</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -28025,17 +28257,17 @@
       <c r="AG139" t="inlineStr"/>
       <c r="AH139" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Crich</t>
         </is>
       </c>
       <c r="AI139" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Crich</t>
         </is>
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>unknown_galletas bio snack cakes with leguminous crich</t>
+          <t>crich_galletas bio snack cakes with leguminous crich</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -28050,7 +28282,7 @@
       </c>
       <c r="AM139" t="inlineStr">
         <is>
-          <t>unknown_galletas bio snack cakes with leguminous crich_0.07</t>
+          <t>crich_galletas bio snack cakes with leguminous crich_0.07</t>
         </is>
       </c>
       <c r="AN139" t="n">
@@ -28064,7 +28296,7 @@
       </c>
       <c r="AQ139" t="inlineStr">
         <is>
-          <t>unknown_cakes_crich_leguminous_snack</t>
+          <t>crich_cakes_crich_leguminous_snack</t>
         </is>
       </c>
       <c r="AR139" t="n">
@@ -29455,7 +29687,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -29534,17 +29766,17 @@
       <c r="AG148" t="inlineStr"/>
       <c r="AH148" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="AI148" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>unknown_wafer cho negro crf sel</t>
+          <t>carrefour_wafer cho negro crf sel</t>
         </is>
       </c>
       <c r="AK148" t="inlineStr">
@@ -29559,7 +29791,7 @@
       </c>
       <c r="AM148" t="inlineStr">
         <is>
-          <t>unknown_wafer cho negro crf sel_0.1</t>
+          <t>carrefour_wafer cho negro crf sel_0.1</t>
         </is>
       </c>
       <c r="AN148" t="n">
@@ -29573,7 +29805,7 @@
       </c>
       <c r="AQ148" t="inlineStr">
         <is>
-          <t>unknown_negro_wafer</t>
+          <t>carrefour_negro_wafer</t>
         </is>
       </c>
       <c r="AR148" t="n">
@@ -48070,7 +48302,7 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -48149,17 +48381,17 @@
       <c r="AG257" t="inlineStr"/>
       <c r="AH257" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="AI257" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="AJ257" t="inlineStr">
         <is>
-          <t>unknown_galleta avena choco crf</t>
+          <t>carrefour_galleta avena choco crf</t>
         </is>
       </c>
       <c r="AK257" t="inlineStr">
@@ -48174,7 +48406,7 @@
       </c>
       <c r="AM257" t="inlineStr">
         <is>
-          <t>unknown_galleta avena choco crf_0.15</t>
+          <t>carrefour_galleta avena choco crf_0.15</t>
         </is>
       </c>
       <c r="AN257" t="n">
@@ -48188,7 +48420,7 @@
       </c>
       <c r="AQ257" t="inlineStr">
         <is>
-          <t>unknown_avena_choco</t>
+          <t>carrefour_avena_choco</t>
         </is>
       </c>
       <c r="AR257" t="n">
@@ -49106,7 +49338,7 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Costa</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -49185,17 +49417,17 @@
       <c r="AG263" t="inlineStr"/>
       <c r="AH263" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Costa</t>
         </is>
       </c>
       <c r="AI263" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Costa</t>
         </is>
       </c>
       <c r="AJ263" t="inlineStr">
         <is>
-          <t>unknown_galleta costa choco rolls crispy</t>
+          <t>costa_galleta costa choco rolls crispy</t>
         </is>
       </c>
       <c r="AK263" t="inlineStr">
@@ -49210,7 +49442,7 @@
       </c>
       <c r="AM263" t="inlineStr">
         <is>
-          <t>unknown_galleta costa choco rolls crispy_0.13</t>
+          <t>costa_galleta costa choco rolls crispy_0.13</t>
         </is>
       </c>
       <c r="AN263" t="n">
@@ -49224,7 +49456,7 @@
       </c>
       <c r="AQ263" t="inlineStr">
         <is>
-          <t>unknown_choco_costa_crispy_rolls</t>
+          <t>costa_choco_costa_crispy_rolls</t>
         </is>
       </c>
       <c r="AR263" t="n">
@@ -61607,7 +61839,7 @@
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Town House</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
@@ -61686,17 +61918,17 @@
       <c r="AG336" t="inlineStr"/>
       <c r="AH336" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Town House</t>
         </is>
       </c>
       <c r="AI336" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Town House</t>
         </is>
       </c>
       <c r="AJ336" t="inlineStr">
         <is>
-          <t>unknown_galleta pita town house con sal marina</t>
+          <t>town house_galleta pita town house con sal marina</t>
         </is>
       </c>
       <c r="AK336" t="inlineStr">
@@ -61711,7 +61943,7 @@
       </c>
       <c r="AM336" t="inlineStr">
         <is>
-          <t>unknown_galleta pita town house con sal marina_0.27</t>
+          <t>town house_galleta pita town house con sal marina_0.27</t>
         </is>
       </c>
       <c r="AN336" t="n">
@@ -61721,7 +61953,7 @@
       <c r="AP336" t="inlineStr"/>
       <c r="AQ336" t="inlineStr">
         <is>
-          <t>unknown_house_marina_pita_town</t>
+          <t>town house_house_marina_pita_town</t>
         </is>
       </c>
       <c r="AR336" t="n">
@@ -62468,7 +62700,7 @@
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
@@ -62547,17 +62779,17 @@
       <c r="AG341" t="inlineStr"/>
       <c r="AH341" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="AI341" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="AJ341" t="inlineStr">
         <is>
-          <t>unknown_wafer fres crf</t>
+          <t>carrefour_wafer fres crf</t>
         </is>
       </c>
       <c r="AK341" t="inlineStr">
@@ -62572,7 +62804,7 @@
       </c>
       <c r="AM341" t="inlineStr">
         <is>
-          <t>unknown_wafer fres crf_0.16</t>
+          <t>carrefour_wafer fres crf_0.16</t>
         </is>
       </c>
       <c r="AN341" t="n">
@@ -62586,7 +62818,7 @@
       </c>
       <c r="AQ341" t="inlineStr">
         <is>
-          <t>unknown_fres_wafer</t>
+          <t>carrefour_fres_wafer</t>
         </is>
       </c>
       <c r="AR341" t="n">
@@ -64484,7 +64716,7 @@
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Costa</t>
         </is>
       </c>
       <c r="H353" t="inlineStr">
@@ -64563,17 +64795,17 @@
       <c r="AG353" t="inlineStr"/>
       <c r="AH353" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Costa</t>
         </is>
       </c>
       <c r="AI353" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Costa</t>
         </is>
       </c>
       <c r="AJ353" t="inlineStr">
         <is>
-          <t>unknown_galleta costa donut blanca</t>
+          <t>costa_galleta costa donut blanca</t>
         </is>
       </c>
       <c r="AK353" t="inlineStr">
@@ -64588,7 +64820,7 @@
       </c>
       <c r="AM353" t="inlineStr">
         <is>
-          <t>unknown_galleta costa donut blanca_0.1</t>
+          <t>costa_galleta costa donut blanca_0.1</t>
         </is>
       </c>
       <c r="AN353" t="n">
@@ -64602,7 +64834,7 @@
       </c>
       <c r="AQ353" t="inlineStr">
         <is>
-          <t>unknown_blanca_costa_donut</t>
+          <t>costa_blanca_costa_donut</t>
         </is>
       </c>
       <c r="AR353" t="n">
@@ -77777,7 +78009,7 @@
       </c>
       <c r="G430" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Crich</t>
         </is>
       </c>
       <c r="H430" t="inlineStr">
@@ -77852,17 +78084,17 @@
       <c r="AG430" t="inlineStr"/>
       <c r="AH430" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Crich</t>
         </is>
       </c>
       <c r="AI430" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Crich</t>
         </is>
       </c>
       <c r="AJ430" t="inlineStr">
         <is>
-          <t>unknown_galleta crich wafers crema cappuccino</t>
+          <t>crich_galleta crich wafers crema cappuccino</t>
         </is>
       </c>
       <c r="AK430" t="inlineStr">
@@ -77877,7 +78109,7 @@
       </c>
       <c r="AM430" t="inlineStr">
         <is>
-          <t>unknown_galleta crich wafers crema cappuccino_0.25</t>
+          <t>crich_galleta crich wafers crema cappuccino_0.25</t>
         </is>
       </c>
       <c r="AN430" t="inlineStr"/>
@@ -77885,7 +78117,7 @@
       <c r="AP430" t="inlineStr"/>
       <c r="AQ430" t="inlineStr">
         <is>
-          <t>unknown_cappuccino_crich_wafers</t>
+          <t>crich_cappuccino_crich_wafers</t>
         </is>
       </c>
       <c r="AR430" t="n">
@@ -79839,7 +80071,7 @@
       </c>
       <c r="G442" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Crich</t>
         </is>
       </c>
       <c r="H442" t="inlineStr">
@@ -79914,17 +80146,17 @@
       <c r="AG442" t="inlineStr"/>
       <c r="AH442" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Crich</t>
         </is>
       </c>
       <c r="AI442" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Crich</t>
         </is>
       </c>
       <c r="AJ442" t="inlineStr">
         <is>
-          <t>unknown_galletas crich chocolate wafers</t>
+          <t>crich_galletas crich chocolate wafers</t>
         </is>
       </c>
       <c r="AK442" t="inlineStr">
@@ -79939,7 +80171,7 @@
       </c>
       <c r="AM442" t="inlineStr">
         <is>
-          <t>unknown_galletas crich chocolate wafers_0.25</t>
+          <t>crich_galletas crich chocolate wafers_0.25</t>
         </is>
       </c>
       <c r="AN442" t="inlineStr"/>
@@ -79947,7 +80179,7 @@
       <c r="AP442" t="inlineStr"/>
       <c r="AQ442" t="inlineStr">
         <is>
-          <t>unknown_chocolate_crich_wafers</t>
+          <t>crich_chocolate_crich_wafers</t>
         </is>
       </c>
       <c r="AR442" t="n">
@@ -80525,7 +80757,7 @@
       </c>
       <c r="G446" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Costa</t>
         </is>
       </c>
       <c r="H446" t="inlineStr">
@@ -80604,17 +80836,17 @@
       <c r="AG446" t="inlineStr"/>
       <c r="AH446" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Costa</t>
         </is>
       </c>
       <c r="AI446" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Costa</t>
         </is>
       </c>
       <c r="AJ446" t="inlineStr">
         <is>
-          <t>unknown_galleta costa chocolate</t>
+          <t>costa_galleta costa chocolate</t>
         </is>
       </c>
       <c r="AK446" t="inlineStr">
@@ -80629,7 +80861,7 @@
       </c>
       <c r="AM446" t="inlineStr">
         <is>
-          <t>unknown_galleta costa chocolate_0.14</t>
+          <t>costa_galleta costa chocolate_0.14</t>
         </is>
       </c>
       <c r="AN446" t="n">
@@ -80643,7 +80875,7 @@
       </c>
       <c r="AQ446" t="inlineStr">
         <is>
-          <t>unknown_chocolate_costa</t>
+          <t>costa_chocolate_costa</t>
         </is>
       </c>
       <c r="AR446" t="n">
@@ -80700,7 +80932,7 @@
       </c>
       <c r="G447" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Costa</t>
         </is>
       </c>
       <c r="H447" t="inlineStr">
@@ -80779,17 +81011,17 @@
       <c r="AG447" t="inlineStr"/>
       <c r="AH447" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Costa</t>
         </is>
       </c>
       <c r="AI447" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Costa</t>
         </is>
       </c>
       <c r="AJ447" t="inlineStr">
         <is>
-          <t>unknown_galleta costa limon</t>
+          <t>costa_galleta costa limon</t>
         </is>
       </c>
       <c r="AK447" t="inlineStr">
@@ -80804,7 +81036,7 @@
       </c>
       <c r="AM447" t="inlineStr">
         <is>
-          <t>unknown_galleta costa limon_0.14</t>
+          <t>costa_galleta costa limon_0.14</t>
         </is>
       </c>
       <c r="AN447" t="n">
@@ -80818,7 +81050,7 @@
       </c>
       <c r="AQ447" t="inlineStr">
         <is>
-          <t>unknown_costa_limon</t>
+          <t>costa_costa_limon</t>
         </is>
       </c>
       <c r="AR447" t="n">
@@ -82050,7 +82282,7 @@
       </c>
       <c r="G455" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Buenhorno</t>
         </is>
       </c>
       <c r="H455" t="inlineStr">
@@ -82129,17 +82361,17 @@
       <c r="AG455" t="inlineStr"/>
       <c r="AH455" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Buenhorno</t>
         </is>
       </c>
       <c r="AI455" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Buenhorno</t>
         </is>
       </c>
       <c r="AJ455" t="inlineStr">
         <is>
-          <t>unknown_pan brioche trenzado rell canela buenhorno</t>
+          <t>buenhorno_pan brioche trenzado rell canela buenhorno</t>
         </is>
       </c>
       <c r="AK455" t="inlineStr">
@@ -82154,7 +82386,7 @@
       </c>
       <c r="AM455" t="inlineStr">
         <is>
-          <t>unknown_pan brioche trenzado rell canela buenhorno_0.4</t>
+          <t>buenhorno_pan brioche trenzado rell canela buenhorno_0.4</t>
         </is>
       </c>
       <c r="AN455" t="n">
@@ -82164,7 +82396,7 @@
       <c r="AP455" t="inlineStr"/>
       <c r="AQ455" t="inlineStr">
         <is>
-          <t>unknown_brioche_buenhorno_canela_rell</t>
+          <t>buenhorno_brioche_buenhorno_canela_rell</t>
         </is>
       </c>
       <c r="AR455" t="n">
@@ -82396,7 +82628,7 @@
       </c>
       <c r="G457" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Buenhorno</t>
         </is>
       </c>
       <c r="H457" t="inlineStr">
@@ -82475,17 +82707,17 @@
       <c r="AG457" t="inlineStr"/>
       <c r="AH457" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Buenhorno</t>
         </is>
       </c>
       <c r="AI457" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Buenhorno</t>
         </is>
       </c>
       <c r="AJ457" t="inlineStr">
         <is>
-          <t>unknown_pan brioche artesal buenhorno con almendras</t>
+          <t>buenhorno_pan brioche artesal buenhorno con almendras</t>
         </is>
       </c>
       <c r="AK457" t="inlineStr">
@@ -82500,7 +82732,7 @@
       </c>
       <c r="AM457" t="inlineStr">
         <is>
-          <t>unknown_pan brioche artesal buenhorno con almendras_0.45</t>
+          <t>buenhorno_pan brioche artesal buenhorno con almendras_0.45</t>
         </is>
       </c>
       <c r="AN457" t="n">
@@ -82510,7 +82742,7 @@
       <c r="AP457" t="inlineStr"/>
       <c r="AQ457" t="inlineStr">
         <is>
-          <t>unknown_almendras_artesal_brioche_buenhorno</t>
+          <t>buenhorno_almendras_artesal_brioche_buenhorno</t>
         </is>
       </c>
       <c r="AR457" t="n">
@@ -85122,7 +85354,7 @@
       </c>
       <c r="G473" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Holsum</t>
         </is>
       </c>
       <c r="H473" t="inlineStr">
@@ -85201,17 +85433,17 @@
       <c r="AG473" t="inlineStr"/>
       <c r="AH473" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Holsum</t>
         </is>
       </c>
       <c r="AI473" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Holsum</t>
         </is>
       </c>
       <c r="AJ473" t="inlineStr">
         <is>
-          <t>unknown_pan viga de papa holsum</t>
+          <t>holsum_pan viga de papa holsum</t>
         </is>
       </c>
       <c r="AK473" t="inlineStr">
@@ -85226,7 +85458,7 @@
       </c>
       <c r="AM473" t="inlineStr">
         <is>
-          <t>unknown_pan viga de papa holsum_0.56</t>
+          <t>holsum_pan viga de papa holsum_0.56</t>
         </is>
       </c>
       <c r="AN473" t="n">
@@ -85236,7 +85468,7 @@
       <c r="AP473" t="inlineStr"/>
       <c r="AQ473" t="inlineStr">
         <is>
-          <t>unknown_holsum_papa_viga</t>
+          <t>holsum_holsum_papa_viga</t>
         </is>
       </c>
       <c r="AR473" t="n">
@@ -85293,7 +85525,7 @@
       </c>
       <c r="G474" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Holsum</t>
         </is>
       </c>
       <c r="H474" t="inlineStr">
@@ -85372,17 +85604,17 @@
       <c r="AG474" t="inlineStr"/>
       <c r="AH474" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Holsum</t>
         </is>
       </c>
       <c r="AI474" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Holsum</t>
         </is>
       </c>
       <c r="AJ474" t="inlineStr">
         <is>
-          <t>unknown_pan viga de mantequilla holsum</t>
+          <t>holsum_pan viga de mantequilla holsum</t>
         </is>
       </c>
       <c r="AK474" t="inlineStr">
@@ -85397,7 +85629,7 @@
       </c>
       <c r="AM474" t="inlineStr">
         <is>
-          <t>unknown_pan viga de mantequilla holsum_0.56</t>
+          <t>holsum_pan viga de mantequilla holsum_0.56</t>
         </is>
       </c>
       <c r="AN474" t="n">
@@ -85407,7 +85639,7 @@
       <c r="AP474" t="inlineStr"/>
       <c r="AQ474" t="inlineStr">
         <is>
-          <t>unknown_holsum_mantequilla_viga</t>
+          <t>holsum_holsum_mantequilla_viga</t>
         </is>
       </c>
       <c r="AR474" t="n">
@@ -86397,7 +86629,7 @@
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>324</v>
+        <v>307</v>
       </c>
       <c r="E12" t="n">
         <v>22.60982128245165</v>
@@ -86437,7 +86669,7 @@
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E14" t="n">
         <v>17.25766323803849</v>
@@ -86597,7 +86829,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86775,7 +87007,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>noel_festival_noel_strawberry</t>
+          <t>bauducco_bauducco_chocolate_wafer</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -86785,147 +87017,147 @@
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Noel</t>
+          <t>Bauducco</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Noel Festival Strawberry Cookies</t>
+          <t>Galletas Wafer Con Relleno Sabor Chocolate Bauducco</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.4807692307692308</v>
+        <v>1.5</v>
       </c>
       <c r="H4" t="n">
-        <v>2.731843575418994</v>
+        <v>7.64804469273743</v>
       </c>
       <c r="I4" t="n">
-        <v>1.606306403094112</v>
+        <v>3.959962756052141</v>
       </c>
       <c r="J4" t="n">
-        <v>12.1415270018622</v>
+        <v>10.6</v>
       </c>
       <c r="K4" t="n">
-        <v>12.1415270018622</v>
+        <v>25.49348230912477</v>
       </c>
       <c r="L4" t="n">
-        <v>12.1415270018622</v>
+        <v>19.31607697082557</v>
       </c>
       <c r="M4" t="n">
-        <v>2.251074344649763</v>
+        <v>6.14804469273743</v>
       </c>
       <c r="N4" t="n">
-        <v>468.2234636871507</v>
+        <v>409.8696461824953</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>bauducco_bauducco_chocolate_wafer</t>
+          <t>ritz_ritz</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>2</v>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bauducco</t>
+          <t>Ritz</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Galletas Wafer Con Relleno Sabor Chocolate Bauducco</t>
+          <t>Galleta Ritz</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1.5</v>
+        <v>0.76</v>
       </c>
       <c r="H5" t="n">
-        <v>7.64804469273743</v>
+        <v>3.849162011173184</v>
       </c>
       <c r="I5" t="n">
-        <v>3.959962756052141</v>
+        <v>1.395832402234637</v>
       </c>
       <c r="J5" t="n">
-        <v>10.6</v>
+        <v>11.35</v>
       </c>
       <c r="K5" t="n">
-        <v>25.49348230912477</v>
+        <v>15.39664804469274</v>
       </c>
       <c r="L5" t="n">
-        <v>19.31607697082557</v>
+        <v>12.39532960893855</v>
       </c>
       <c r="M5" t="n">
-        <v>6.14804469273743</v>
+        <v>3.089162011173184</v>
       </c>
       <c r="N5" t="n">
-        <v>409.8696461824953</v>
+        <v>406.4686856806821</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ritz_ritz</t>
+          <t>nabisco_nabisco_oreo</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>2</v>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ritz</t>
+          <t>Nabisco</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Galleta Ritz</t>
+          <t>Nabisco Galletas Oreo 2 Unidades</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0.76</v>
+        <v>1.201923076923077</v>
       </c>
       <c r="H6" t="n">
-        <v>3.849162011173184</v>
+        <v>6.02</v>
       </c>
       <c r="I6" t="n">
-        <v>1.395832402234637</v>
+        <v>3.610961538461538</v>
       </c>
       <c r="J6" t="n">
-        <v>11.35</v>
+        <v>13.97</v>
       </c>
       <c r="K6" t="n">
-        <v>15.39664804469274</v>
+        <v>13.97</v>
       </c>
       <c r="L6" t="n">
-        <v>12.39532960893855</v>
+        <v>13.97</v>
       </c>
       <c r="M6" t="n">
-        <v>3.089162011173184</v>
+        <v>4.818076923076923</v>
       </c>
       <c r="N6" t="n">
-        <v>406.4686856806821</v>
+        <v>400.8639999999999</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>nabisco_nabisco_oreo</t>
+          <t>chips ahoy_ahoy_chips</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -86939,43 +87171,43 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Nabisco</t>
+          <t>Chips Ahoy</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nabisco Galletas Oreo 2 Unidades</t>
+          <t>Galletas Chips Ahoy</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1.201923076923077</v>
+        <v>2.094972067039106</v>
       </c>
       <c r="H7" t="n">
-        <v>6.02</v>
+        <v>5.78</v>
       </c>
       <c r="I7" t="n">
-        <v>3.610961538461538</v>
+        <v>3.937486033519553</v>
       </c>
       <c r="J7" t="n">
-        <v>13.97</v>
+        <v>5.684463481350521</v>
       </c>
       <c r="K7" t="n">
-        <v>13.97</v>
+        <v>15.69</v>
       </c>
       <c r="L7" t="n">
-        <v>13.97</v>
+        <v>10.68723174067526</v>
       </c>
       <c r="M7" t="n">
-        <v>4.818076923076923</v>
+        <v>3.685027932960894</v>
       </c>
       <c r="N7" t="n">
-        <v>400.8639999999999</v>
+        <v>175.8986666666667</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>chips ahoy_ahoy_chips</t>
+          <t>pringles_cream_onion_pringles_sour</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -86985,147 +87217,147 @@
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Chips Ahoy</t>
+          <t>Pringles</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Galletas Chips Ahoy</t>
+          <t>Pringles Sour Cream &amp; Onion</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>2.094972067039106</v>
+        <v>1.514423076923077</v>
       </c>
       <c r="H8" t="n">
-        <v>5.78</v>
+        <v>4.134615384615385</v>
       </c>
       <c r="I8" t="n">
-        <v>3.937486033519553</v>
+        <v>2.722315481306403</v>
       </c>
       <c r="J8" t="n">
-        <v>5.684463481350521</v>
+        <v>23.61153873683875</v>
       </c>
       <c r="K8" t="n">
-        <v>15.69</v>
+        <v>42.29240830124789</v>
       </c>
       <c r="L8" t="n">
-        <v>10.68723174067526</v>
+        <v>30.80703596541372</v>
       </c>
       <c r="M8" t="n">
-        <v>3.685027932960894</v>
+        <v>2.620192307692308</v>
       </c>
       <c r="N8" t="n">
-        <v>175.8986666666667</v>
+        <v>173.015873015873</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>pringles_cream_onion_pringles_sour</t>
+          <t>toufayan_croissant_toufayan</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>2</v>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Pringles</t>
+          <t>Toufayan</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Pringles Sour Cream &amp; Onion</t>
+          <t>Croissant Mini Toufayan</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1.514423076923077</v>
+        <v>3.95</v>
       </c>
       <c r="H9" t="n">
-        <v>4.134615384615385</v>
+        <v>9.326923076923077</v>
       </c>
       <c r="I9" t="n">
-        <v>2.722315481306403</v>
+        <v>4.851153846153847</v>
       </c>
       <c r="J9" t="n">
-        <v>23.61153873683875</v>
+        <v>11.32</v>
       </c>
       <c r="K9" t="n">
-        <v>42.29240830124789</v>
+        <v>11.36</v>
       </c>
       <c r="L9" t="n">
-        <v>30.80703596541372</v>
+        <v>11.344</v>
       </c>
       <c r="M9" t="n">
-        <v>2.620192307692308</v>
+        <v>5.376923076923076</v>
       </c>
       <c r="N9" t="n">
-        <v>173.015873015873</v>
+        <v>136.124634858812</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>toufayan_croissant_toufayan</t>
+          <t>pringles_pizza_pringles</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Toufayan</t>
+          <t>Pringles</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Croissant Mini Toufayan</t>
+          <t>PRINGLES PIZZA</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>3.95</v>
+        <v>2.340782122905028</v>
       </c>
       <c r="H10" t="n">
-        <v>9.326923076923077</v>
+        <v>4.254807692307693</v>
       </c>
       <c r="I10" t="n">
-        <v>4.851153846153847</v>
+        <v>3.031863271737574</v>
       </c>
       <c r="J10" t="n">
-        <v>11.32</v>
+        <v>35.89944647294644</v>
       </c>
       <c r="K10" t="n">
-        <v>11.36</v>
+        <v>35.89944647294644</v>
       </c>
       <c r="L10" t="n">
-        <v>11.344</v>
+        <v>35.89944647294644</v>
       </c>
       <c r="M10" t="n">
-        <v>5.376923076923076</v>
+        <v>1.914025569402666</v>
       </c>
       <c r="N10" t="n">
-        <v>136.124634858812</v>
+        <v>81.7686341105196</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>pringles_pizza_pringles</t>
+          <t>pringles_cheddar_cheese_pringles</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -87144,38 +87376,38 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>PRINGLES PIZZA</t>
+          <t>Pringles Cheddar Cheese</t>
         </is>
       </c>
       <c r="G11" t="n">
+        <v>1.442307692307692</v>
+      </c>
+      <c r="H11" t="n">
         <v>2.340782122905028</v>
       </c>
-      <c r="H11" t="n">
-        <v>4.254807692307693</v>
-      </c>
       <c r="I11" t="n">
-        <v>3.031863271737574</v>
+        <v>1.780583011029939</v>
       </c>
       <c r="J11" t="n">
-        <v>35.89944647294644</v>
+        <v>33.02749075511072</v>
       </c>
       <c r="K11" t="n">
-        <v>35.89944647294644</v>
+        <v>38.99300056143422</v>
       </c>
       <c r="L11" t="n">
-        <v>35.89944647294644</v>
+        <v>36.01024565827247</v>
       </c>
       <c r="M11" t="n">
-        <v>1.914025569402666</v>
+        <v>0.8984744305973358</v>
       </c>
       <c r="N11" t="n">
-        <v>81.7686341105196</v>
+        <v>62.29422718808196</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>pringles_cheddar_cheese_pringles</t>
+          <t>oreo_oreo</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -87185,90 +87417,40 @@
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Pringles</t>
+          <t>Oreo</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Pringles Cheddar Cheese</t>
+          <t>Galletas Oreo Original</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>1.442307692307692</v>
+        <v>2.731843575418994</v>
       </c>
       <c r="H12" t="n">
-        <v>2.340782122905028</v>
+        <v>3.64</v>
       </c>
       <c r="I12" t="n">
-        <v>1.780583011029939</v>
+        <v>3.126480446927374</v>
       </c>
       <c r="J12" t="n">
-        <v>33.02749075511072</v>
+        <v>13.65921787709497</v>
       </c>
       <c r="K12" t="n">
-        <v>38.99300056143422</v>
+        <v>101.21</v>
       </c>
       <c r="L12" t="n">
-        <v>36.01024565827247</v>
+        <v>47.582104283054</v>
       </c>
       <c r="M12" t="n">
-        <v>0.8984744305973358</v>
+        <v>0.9081564245810063</v>
       </c>
       <c r="N12" t="n">
-        <v>62.29422718808196</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>oreo_oreo</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>2</v>
-      </c>
-      <c r="C13" t="n">
-        <v>2</v>
-      </c>
-      <c r="D13" t="n">
-        <v>4</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Oreo</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Galletas Oreo Original</t>
-        </is>
-      </c>
-      <c r="G13" t="n">
-        <v>2.731843575418994</v>
-      </c>
-      <c r="H13" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="I13" t="n">
-        <v>3.126480446927374</v>
-      </c>
-      <c r="J13" t="n">
-        <v>13.65921787709497</v>
-      </c>
-      <c r="K13" t="n">
-        <v>101.21</v>
-      </c>
-      <c r="L13" t="n">
-        <v>47.582104283054</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0.9081564245810063</v>
-      </c>
-      <c r="N13" t="n">
         <v>33.24335378323111</v>
       </c>
     </row>

--- a/streamlit_data/regional_insights.xlsx
+++ b/streamlit_data/regional_insights.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E206"/>
+  <dimension ref="A1:E209"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,7 +456,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>413</v>
+        <v>387</v>
       </c>
       <c r="C2" t="n">
         <v>3</v>
@@ -465,7 +465,7 @@
         <v>6</v>
       </c>
       <c r="E2" t="n">
-        <v>19.04487809045697</v>
+        <v>19.8804201585068</v>
       </c>
     </row>
     <row r="3">
@@ -604,39 +604,39 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Gamesa</t>
+          <t>Jumbo</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>62</v>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E10" t="n">
-        <v>14.41709677419355</v>
+        <v>17.84871204831632</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Jumbo</t>
+          <t>Gamesa</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>62</v>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>17.84871204831632</v>
+        <v>14.41709677419355</v>
       </c>
     </row>
     <row r="12">
@@ -737,58 +737,58 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>Líder</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E17" t="n">
-        <v>20.04552732589859</v>
+        <v>14.10285714285714</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Líder</t>
+          <t>Food Club</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
         <v>4</v>
       </c>
       <c r="E18" t="n">
-        <v>14.10285714285714</v>
+        <v>12.65465098064463</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Food Club</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C19" t="n">
         <v>2</v>
       </c>
       <c r="D19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E19" t="n">
-        <v>12.65465098064463</v>
+        <v>22.50885642478337</v>
       </c>
     </row>
     <row r="20">
@@ -832,39 +832,39 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sunshine Snacks</t>
+          <t>Betty Crocker</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>35</v>
       </c>
       <c r="C22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>20.92956623821305</v>
+        <v>11.50905500557616</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Betty Crocker</t>
+          <t>Sunshine Snacks</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>35</v>
       </c>
       <c r="C23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E23" t="n">
-        <v>11.50905500557616</v>
+        <v>20.92956623821305</v>
       </c>
     </row>
     <row r="24">
@@ -908,7 +908,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Pringles</t>
+          <t>Ritz</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -918,16 +918,16 @@
         <v>2</v>
       </c>
       <c r="D26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E26" t="n">
-        <v>30.43700668692141</v>
+        <v>12.2312637036403</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Ritz</t>
+          <t>Pringles</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -937,48 +937,48 @@
         <v>2</v>
       </c>
       <c r="D27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>12.2312637036403</v>
+        <v>30.43700668692141</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Bermudez</t>
+          <t>Club Social</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>28</v>
       </c>
       <c r="C28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>9.901427320955712</v>
+        <v>6.351099247772932</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Club Social</t>
+          <t>Bermudez</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>28</v>
       </c>
       <c r="C29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E29" t="n">
-        <v>6.351099247772932</v>
+        <v>9.901427320955712</v>
       </c>
     </row>
     <row r="30">
@@ -1022,39 +1022,39 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Mi Trigo</t>
+          <t>Old El Paso</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>23</v>
       </c>
       <c r="C32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>7.637391304347826</v>
+        <v>13.455</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Old El Paso</t>
+          <t>Mi Trigo</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>23</v>
       </c>
       <c r="C33" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" t="n">
         <v>2</v>
       </c>
-      <c r="D33" t="n">
-        <v>1</v>
-      </c>
       <c r="E33" t="n">
-        <v>13.455</v>
+        <v>7.637391304347826</v>
       </c>
     </row>
     <row r="34">
@@ -1098,7 +1098,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Oh Snacks</t>
+          <t>Pepin</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -1108,29 +1108,29 @@
         <v>1</v>
       </c>
       <c r="D36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>38.08068575758553</v>
+        <v>3.923333333333334</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Bauducco</t>
+          <t>Princesa</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>18</v>
       </c>
       <c r="C37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E37" t="n">
-        <v>14.2729343508003</v>
+        <v>3.588888888888889</v>
       </c>
     </row>
     <row r="38">
@@ -1155,102 +1155,102 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Pepin</t>
+          <t>Bauducco</t>
         </is>
       </c>
       <c r="B39" t="n">
         <v>18</v>
       </c>
       <c r="C39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D39" t="n">
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>3.923333333333334</v>
+        <v>14.2729343508003</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Lider</t>
+          <t>Oh Snacks</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C40" t="n">
         <v>1</v>
       </c>
       <c r="D40" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E40" t="n">
-        <v>7.467272727272728</v>
+        <v>38.08068575758553</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Lenny &amp; Larry's</t>
+          <t>Lider</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C41" t="n">
         <v>1</v>
       </c>
       <c r="D41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E41" t="n">
-        <v>26.45875</v>
+        <v>7.467272727272728</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Tostitos</t>
+          <t>Lenny &amp; Larry's</t>
         </is>
       </c>
       <c r="B42" t="n">
         <v>16</v>
       </c>
       <c r="C42" t="n">
+        <v>1</v>
+      </c>
+      <c r="D42" t="n">
         <v>2</v>
       </c>
-      <c r="D42" t="n">
-        <v>1</v>
-      </c>
       <c r="E42" t="n">
-        <v>16.30891918387187</v>
+        <v>26.45875</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Pepperidge</t>
+          <t>Tostitos</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E43" t="n">
-        <v>29.39239164449742</v>
+        <v>16.30891918387187</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Charles</t>
+          <t>La Libanesa</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -1260,92 +1260,90 @@
         <v>1</v>
       </c>
       <c r="D44" t="n">
-        <v>3</v>
-      </c>
-      <c r="E44" t="n">
-        <v>19.27125506072875</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="E44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Crav'N</t>
+          <t>Pepperidge</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C45" t="n">
+        <v>1</v>
+      </c>
+      <c r="D45" t="n">
         <v>2</v>
       </c>
-      <c r="D45" t="n">
-        <v>4</v>
-      </c>
       <c r="E45" t="n">
-        <v>20.64511696006157</v>
+        <v>29.39239164449742</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Devon</t>
+          <t>Charles</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C46" t="n">
         <v>1</v>
       </c>
       <c r="D46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>9.404842870544091</v>
+        <v>19.27125506072875</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Wow</t>
+          <t>Devon</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C47" t="n">
         <v>1</v>
       </c>
       <c r="D47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E47" t="n">
-        <v>9.45857142857143</v>
+        <v>9.404842870544091</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Crav'N</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D48" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E48" t="n">
-        <v>3.208571428571429</v>
+        <v>20.64511696006157</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Wasa</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -1355,20 +1353,20 @@
         <v>1</v>
       </c>
       <c r="D49" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>20.93163482244135</v>
+        <v>3.208571428571429</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Wibisco</t>
+          <t>Wow</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C50" t="n">
         <v>1</v>
@@ -1377,70 +1375,70 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>7.709999008179106</v>
+        <v>9.45857142857143</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Bergen</t>
+          <t>Wasa</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C51" t="n">
         <v>1</v>
       </c>
       <c r="D51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>11.83083333333333</v>
+        <v>20.93163482244135</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Shoon</t>
+          <t>Wibisco</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C52" t="n">
         <v>1</v>
       </c>
       <c r="D52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E52" t="n">
-        <v>23.68495475113122</v>
+        <v>7.709999008179106</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Motto</t>
+          <t>Bergen</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D53" t="n">
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>15.4472192513369</v>
+        <v>11.83083333333333</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Noel</t>
+          <t>Motto</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -1450,37 +1448,39 @@
         <v>2</v>
       </c>
       <c r="D54" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E54" t="n">
-        <v>19.31337392062075</v>
+        <v>15.4472192513369</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Qiin</t>
+          <t>Noel</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D55" t="n">
-        <v>1</v>
-      </c>
-      <c r="E55" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E55" t="n">
+        <v>19.31337392062075</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Keebler</t>
+          <t>Shoon</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C56" t="n">
         <v>1</v>
@@ -1489,13 +1489,13 @@
         <v>2</v>
       </c>
       <c r="E56" t="n">
-        <v>16.53</v>
+        <v>23.68495475113122</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>El Charrito</t>
+          <t>Qiin</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -1531,30 +1531,30 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Pillsbury</t>
+          <t>Keebler</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C59" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D59" t="n">
         <v>2</v>
       </c>
       <c r="E59" t="n">
-        <v>7.764285714285714</v>
+        <v>16.53</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Festival</t>
+          <t>El Charrito</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C60" t="n">
         <v>1</v>
@@ -1562,128 +1562,126 @@
       <c r="D60" t="n">
         <v>1</v>
       </c>
-      <c r="E60" t="n">
-        <v>9.385016025641024</v>
-      </c>
+      <c r="E60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Siete</t>
+          <t>La Real</t>
         </is>
       </c>
       <c r="B61" t="n">
         <v>9</v>
       </c>
       <c r="C61" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D61" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E61" t="n">
-        <v>35.46555757535778</v>
+        <v>12.46</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Chips Ahoy</t>
+          <t>Festival</t>
         </is>
       </c>
       <c r="B62" t="n">
         <v>9</v>
       </c>
       <c r="C62" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D62" t="n">
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>12.99941707258641</v>
+        <v>9.385016025641024</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Cuetara</t>
+          <t>Siete</t>
         </is>
       </c>
       <c r="B63" t="n">
         <v>9</v>
       </c>
       <c r="C63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>10.41222222222222</v>
+        <v>35.46555757535778</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>La Real</t>
+          <t>Pillsbury</t>
         </is>
       </c>
       <c r="B64" t="n">
         <v>9</v>
       </c>
       <c r="C64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E64" t="n">
-        <v>12.46</v>
+        <v>7.764285714285714</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Bisco</t>
+          <t>Chips Ahoy</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D65" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>9.168749999999999</v>
+        <v>12.99941707258641</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Member's Selection</t>
+          <t>Cuetara</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C66" t="n">
         <v>1</v>
       </c>
       <c r="D66" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E66" t="n">
-        <v>13.74</v>
+        <v>10.41222222222222</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Biskitop</t>
+          <t>Bisco</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -1695,12 +1693,14 @@
       <c r="D67" t="n">
         <v>2</v>
       </c>
-      <c r="E67" t="inlineStr"/>
+      <c r="E67" t="n">
+        <v>9.168749999999999</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Eggo</t>
+          <t>Biskitop</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -1710,50 +1710,52 @@
         <v>1</v>
       </c>
       <c r="D68" t="n">
-        <v>1</v>
-      </c>
-      <c r="E68" t="n">
-        <v>14.6121807037156</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="E68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Kidsmania</t>
+          <t>Member's Selection</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C69" t="n">
         <v>1</v>
       </c>
       <c r="D69" t="n">
-        <v>1</v>
-      </c>
-      <c r="E69" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E69" t="n">
+        <v>13.74</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Golden</t>
+          <t>Eggo</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C70" t="n">
         <v>1</v>
       </c>
       <c r="D70" t="n">
-        <v>2</v>
-      </c>
-      <c r="E70" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E70" t="n">
+        <v>14.6121807037156</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Nature'S Own</t>
+          <t>Lavigne</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -1766,13 +1768,13 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>7.755714285714285</v>
+        <v>9.161428571428571</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Holsum</t>
+          <t>Biscotto</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -1782,16 +1784,16 @@
         <v>1</v>
       </c>
       <c r="D72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>7.78</v>
+        <v>25</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Princesa</t>
+          <t>Kidsmania</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -1803,14 +1805,12 @@
       <c r="D73" t="n">
         <v>1</v>
       </c>
-      <c r="E73" t="n">
-        <v>3.535714285714286</v>
-      </c>
+      <c r="E73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Walkers</t>
+          <t>Golden</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -1822,9 +1822,7 @@
       <c r="D74" t="n">
         <v>2</v>
       </c>
-      <c r="E74" t="n">
-        <v>97.43589743589745</v>
-      </c>
+      <c r="E74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -1848,7 +1846,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Biscotto</t>
+          <t>Nature'S Own</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -1858,52 +1856,54 @@
         <v>1</v>
       </c>
       <c r="D76" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E76" t="n">
-        <v>25</v>
+        <v>7.755714285714285</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Cadbury</t>
+          <t>Holsum</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C77" t="n">
         <v>1</v>
       </c>
       <c r="D77" t="n">
-        <v>2</v>
-      </c>
-      <c r="E77" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E77" t="n">
+        <v>7.78</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Sunshine</t>
+          <t>Walkers</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C78" t="n">
         <v>1</v>
       </c>
       <c r="D78" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>9.488333333333333</v>
+        <v>97.43589743589745</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Costa</t>
+          <t>Cadbury</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -1913,16 +1913,14 @@
         <v>1</v>
       </c>
       <c r="D79" t="n">
-        <v>1</v>
-      </c>
-      <c r="E79" t="n">
-        <v>14.64666666666667</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="E79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Otis Spunkmeyer</t>
+          <t>Kugi</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -1932,50 +1930,50 @@
         <v>1</v>
       </c>
       <c r="D80" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Schar</t>
+          <t>Otis Spunkmeyer</t>
         </is>
       </c>
       <c r="B81" t="n">
         <v>6</v>
       </c>
       <c r="C81" t="n">
+        <v>1</v>
+      </c>
+      <c r="D81" t="n">
         <v>2</v>
       </c>
-      <c r="D81" t="n">
-        <v>3</v>
-      </c>
-      <c r="E81" t="n">
-        <v>24.18904950998269</v>
-      </c>
+      <c r="E81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Kugi</t>
+          <t>Schar</t>
         </is>
       </c>
       <c r="B82" t="n">
         <v>6</v>
       </c>
       <c r="C82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D82" t="n">
-        <v>1</v>
-      </c>
-      <c r="E82" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E82" t="n">
+        <v>24.18904950998269</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Laurieri</t>
+          <t>Sunshine</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -1985,10 +1983,10 @@
         <v>1</v>
       </c>
       <c r="D83" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>20.65978352354142</v>
+        <v>9.488333333333333</v>
       </c>
     </row>
     <row r="84">
@@ -2011,64 +2009,64 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Badia</t>
+          <t>Costa</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C85" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D85" t="n">
         <v>1</v>
       </c>
       <c r="E85" t="n">
-        <v>28.56294367711628</v>
+        <v>14.64666666666667</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Bagel Bites</t>
+          <t>Laurieri</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C86" t="n">
+        <v>1</v>
+      </c>
+      <c r="D86" t="n">
         <v>2</v>
       </c>
-      <c r="D86" t="n">
-        <v>1</v>
-      </c>
       <c r="E86" t="n">
-        <v>14.76764878866199</v>
+        <v>20.65978352354142</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Hosttes</t>
+          <t>Nutella</t>
         </is>
       </c>
       <c r="B87" t="n">
         <v>5</v>
       </c>
       <c r="C87" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D87" t="n">
         <v>1</v>
       </c>
       <c r="E87" t="n">
-        <v>36.83418646645511</v>
+        <v>15.46996215078755</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Kiss</t>
+          <t>Bagel Bites</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -2078,52 +2076,54 @@
         <v>2</v>
       </c>
       <c r="D88" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E88" t="n">
-        <v>20.05506545869531</v>
+        <v>14.76764878866199</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Cheetos</t>
+          <t>Hosttes</t>
         </is>
       </c>
       <c r="B89" t="n">
         <v>5</v>
       </c>
       <c r="C89" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D89" t="n">
         <v>1</v>
       </c>
       <c r="E89" t="n">
-        <v>23.77550530709329</v>
+        <v>36.83418646645511</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>La Libanesa</t>
+          <t>Badia</t>
         </is>
       </c>
       <c r="B90" t="n">
         <v>5</v>
       </c>
       <c r="C90" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D90" t="n">
         <v>1</v>
       </c>
-      <c r="E90" t="inlineStr"/>
+      <c r="E90" t="n">
+        <v>28.56294367711628</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Merba</t>
+          <t>Triskits</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -2159,43 +2159,45 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Nutella</t>
+          <t>Bolletje</t>
         </is>
       </c>
       <c r="B93" t="n">
         <v>5</v>
       </c>
       <c r="C93" t="n">
+        <v>1</v>
+      </c>
+      <c r="D93" t="n">
         <v>2</v>
       </c>
-      <c r="D93" t="n">
-        <v>1</v>
-      </c>
       <c r="E93" t="n">
-        <v>15.46996215078755</v>
+        <v>29.40549939726599</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Tiffany</t>
+          <t>Cheetos</t>
         </is>
       </c>
       <c r="B94" t="n">
         <v>5</v>
       </c>
       <c r="C94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D94" t="n">
         <v>1</v>
       </c>
-      <c r="E94" t="inlineStr"/>
+      <c r="E94" t="n">
+        <v>23.77550530709329</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Stiratini</t>
+          <t>Merba</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -2207,14 +2209,12 @@
       <c r="D95" t="n">
         <v>1</v>
       </c>
-      <c r="E95" t="n">
-        <v>17.42078051958985</v>
-      </c>
+      <c r="E95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Triskits</t>
+          <t>Tiffany</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -2231,64 +2231,64 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Bolletje</t>
+          <t>Kiss</t>
         </is>
       </c>
       <c r="B97" t="n">
         <v>5</v>
       </c>
       <c r="C97" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D97" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E97" t="n">
-        <v>29.40549939726599</v>
+        <v>20.05506545869531</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Milka</t>
+          <t>Stiratini</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C98" t="n">
         <v>1</v>
       </c>
       <c r="D98" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E98" t="n">
-        <v>29.0725</v>
+        <v>17.42078051958985</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Kinder</t>
+          <t>Ovaltine</t>
         </is>
       </c>
       <c r="B99" t="n">
         <v>4</v>
       </c>
       <c r="C99" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D99" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E99" t="n">
-        <v>9.291503578576814</v>
+        <v>19.9445103354795</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Ovaltine</t>
+          <t>Milka</t>
         </is>
       </c>
       <c r="B100" t="n">
@@ -2298,10 +2298,10 @@
         <v>1</v>
       </c>
       <c r="D100" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E100" t="n">
-        <v>19.9445103354795</v>
+        <v>29.0725</v>
       </c>
     </row>
     <row r="101">
@@ -2345,26 +2345,26 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Herrs</t>
+          <t>Takis</t>
         </is>
       </c>
       <c r="B103" t="n">
         <v>4</v>
       </c>
       <c r="C103" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D103" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E103" t="n">
-        <v>37.30902864926393</v>
+        <v>41.86</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Snyder’S</t>
+          <t>Keeber</t>
         </is>
       </c>
       <c r="B104" t="n">
@@ -2374,96 +2374,96 @@
         <v>1</v>
       </c>
       <c r="D104" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E104" t="n">
-        <v>21.8340355175269</v>
+        <v>28.61772083892403</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Glutino</t>
+          <t>Herrs</t>
         </is>
       </c>
       <c r="B105" t="n">
         <v>4</v>
       </c>
       <c r="C105" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D105" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E105" t="n">
-        <v>19.41435404641845</v>
+        <v>37.30902864926393</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Takis</t>
+          <t>Snyder’S</t>
         </is>
       </c>
       <c r="B106" t="n">
         <v>4</v>
       </c>
       <c r="C106" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D106" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E106" t="n">
-        <v>41.86</v>
+        <v>21.8340355175269</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Keeber</t>
+          <t>Glutino</t>
         </is>
       </c>
       <c r="B107" t="n">
         <v>4</v>
       </c>
       <c r="C107" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D107" t="n">
         <v>3</v>
       </c>
       <c r="E107" t="n">
-        <v>28.61772083892403</v>
+        <v>19.41435404641845</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Dulcesol</t>
+          <t>Kinder</t>
         </is>
       </c>
       <c r="B108" t="n">
         <v>4</v>
       </c>
       <c r="C108" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D108" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E108" t="n">
-        <v>6.916666666666667</v>
+        <v>9.291503578576814</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Totino's</t>
+          <t>Dulcesol</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C109" t="n">
         <v>1</v>
@@ -2472,13 +2472,13 @@
         <v>1</v>
       </c>
       <c r="E109" t="n">
-        <v>10.85144743680014</v>
+        <v>6.916666666666667</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Chetos</t>
+          <t>Dux</t>
         </is>
       </c>
       <c r="B110" t="n">
@@ -2495,7 +2495,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Chobani</t>
+          <t>Verkade</t>
         </is>
       </c>
       <c r="B111" t="n">
@@ -2508,13 +2508,13 @@
         <v>1</v>
       </c>
       <c r="E111" t="n">
-        <v>25.58923192551497</v>
+        <v>13.51789778605421</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Waitrose</t>
+          <t>Van Der Meulen</t>
         </is>
       </c>
       <c r="B112" t="n">
@@ -2524,14 +2524,16 @@
         <v>1</v>
       </c>
       <c r="D112" t="n">
-        <v>2</v>
-      </c>
-      <c r="E112" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E112" t="n">
+        <v>12.12155070255629</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Verkade</t>
+          <t>Confetti</t>
         </is>
       </c>
       <c r="B113" t="n">
@@ -2543,14 +2545,12 @@
       <c r="D113" t="n">
         <v>1</v>
       </c>
-      <c r="E113" t="n">
-        <v>13.51789778605421</v>
-      </c>
+      <c r="E113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Van Der Meulen</t>
+          <t>Crix</t>
         </is>
       </c>
       <c r="B114" t="n">
@@ -2563,13 +2563,13 @@
         <v>1</v>
       </c>
       <c r="E114" t="n">
-        <v>12.12155070255629</v>
+        <v>7.160318629656713</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Confetti</t>
+          <t>Chetos</t>
         </is>
       </c>
       <c r="B115" t="n">
@@ -2586,7 +2586,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Crix</t>
+          <t>Del-E</t>
         </is>
       </c>
       <c r="B116" t="n">
@@ -2596,16 +2596,14 @@
         <v>1</v>
       </c>
       <c r="D116" t="n">
-        <v>1</v>
-      </c>
-      <c r="E116" t="n">
-        <v>7.160318629656713</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="E116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Del-E</t>
+          <t>Totino's</t>
         </is>
       </c>
       <c r="B117" t="n">
@@ -2615,9 +2613,11 @@
         <v>1</v>
       </c>
       <c r="D117" t="n">
-        <v>2</v>
-      </c>
-      <c r="E117" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E117" t="n">
+        <v>10.85144743680014</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -2641,7 +2641,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Dux</t>
+          <t>Elina</t>
         </is>
       </c>
       <c r="B119" t="n">
@@ -2653,12 +2653,14 @@
       <c r="D119" t="n">
         <v>1</v>
       </c>
-      <c r="E119" t="inlineStr"/>
+      <c r="E119" t="n">
+        <v>35.07692932225363</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Flourish</t>
+          <t>Waitrose</t>
         </is>
       </c>
       <c r="B120" t="n">
@@ -2668,14 +2670,14 @@
         <v>1</v>
       </c>
       <c r="D120" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Snyders</t>
+          <t>Flourish</t>
         </is>
       </c>
       <c r="B121" t="n">
@@ -2692,7 +2694,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Pizkas</t>
+          <t>Snyders</t>
         </is>
       </c>
       <c r="B122" t="n">
@@ -2704,14 +2706,12 @@
       <c r="D122" t="n">
         <v>1</v>
       </c>
-      <c r="E122" t="n">
-        <v>4.146666666666667</v>
-      </c>
+      <c r="E122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Elina</t>
+          <t>Roomboter</t>
         </is>
       </c>
       <c r="B123" t="n">
@@ -2721,16 +2721,16 @@
         <v>1</v>
       </c>
       <c r="D123" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E123" t="n">
-        <v>35.07692932225363</v>
+        <v>16.70555144365191</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Roomboter</t>
+          <t>Pizkas</t>
         </is>
       </c>
       <c r="B124" t="n">
@@ -2740,20 +2740,20 @@
         <v>1</v>
       </c>
       <c r="D124" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E124" t="n">
-        <v>16.70555144365191</v>
+        <v>4.146666666666667</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Ricola</t>
+          <t>Chobani</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C125" t="n">
         <v>1</v>
@@ -2762,13 +2762,13 @@
         <v>1</v>
       </c>
       <c r="E125" t="n">
-        <v>7.351955307262569</v>
+        <v>25.58923192551497</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Willie</t>
+          <t>Werther’S</t>
         </is>
       </c>
       <c r="B126" t="n">
@@ -2785,7 +2785,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Wheat Thins</t>
+          <t>Wala</t>
         </is>
       </c>
       <c r="B127" t="n">
@@ -2797,14 +2797,12 @@
       <c r="D127" t="n">
         <v>1</v>
       </c>
-      <c r="E127" t="n">
-        <v>8.979888962508067</v>
-      </c>
+      <c r="E127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Werther’S</t>
+          <t>Wheat Thins</t>
         </is>
       </c>
       <c r="B128" t="n">
@@ -2816,12 +2814,14 @@
       <c r="D128" t="n">
         <v>1</v>
       </c>
-      <c r="E128" t="inlineStr"/>
+      <c r="E128" t="n">
+        <v>8.979888962508067</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Wala</t>
+          <t>Willie</t>
         </is>
       </c>
       <c r="B129" t="n">
@@ -2838,7 +2838,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Voortman</t>
+          <t>Pico Bello</t>
         </is>
       </c>
       <c r="B130" t="n">
@@ -2851,13 +2851,13 @@
         <v>1</v>
       </c>
       <c r="E130" t="n">
-        <v>20.17345399698341</v>
+        <v>21.08728168019017</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Vigo</t>
+          <t>Voortman</t>
         </is>
       </c>
       <c r="B131" t="n">
@@ -2870,13 +2870,13 @@
         <v>1</v>
       </c>
       <c r="E131" t="n">
-        <v>9.433248720978664</v>
+        <v>20.17345399698341</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Sara Lee</t>
+          <t>Vigo</t>
         </is>
       </c>
       <c r="B132" t="n">
@@ -2889,13 +2889,13 @@
         <v>1</v>
       </c>
       <c r="E132" t="n">
-        <v>24.085</v>
+        <v>9.433248720978664</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Soldanza</t>
+          <t>Twix</t>
         </is>
       </c>
       <c r="B133" t="n">
@@ -2907,12 +2907,14 @@
       <c r="D133" t="n">
         <v>1</v>
       </c>
-      <c r="E133" t="inlineStr"/>
+      <c r="E133" t="n">
+        <v>25.28014847471393</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Twix</t>
+          <t>Tuc</t>
         </is>
       </c>
       <c r="B134" t="n">
@@ -2925,13 +2927,13 @@
         <v>1</v>
       </c>
       <c r="E134" t="n">
-        <v>25.28014847471393</v>
+        <v>7.575418994413408</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Tuc</t>
+          <t>Soldanza</t>
         </is>
       </c>
       <c r="B135" t="n">
@@ -2943,14 +2945,12 @@
       <c r="D135" t="n">
         <v>1</v>
       </c>
-      <c r="E135" t="n">
-        <v>7.575418994413408</v>
-      </c>
+      <c r="E135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Pico Bello</t>
+          <t>Sara Lee</t>
         </is>
       </c>
       <c r="B136" t="n">
@@ -2963,13 +2963,13 @@
         <v>1</v>
       </c>
       <c r="E136" t="n">
-        <v>21.08728168019017</v>
+        <v>24.085</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Knotts</t>
+          <t>Ricola</t>
         </is>
       </c>
       <c r="B137" t="n">
@@ -2981,12 +2981,14 @@
       <c r="D137" t="n">
         <v>1</v>
       </c>
-      <c r="E137" t="inlineStr"/>
+      <c r="E137" t="n">
+        <v>7.351955307262569</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Glad</t>
+          <t>Agua Vivo</t>
         </is>
       </c>
       <c r="B138" t="n">
@@ -2998,12 +3000,14 @@
       <c r="D138" t="n">
         <v>1</v>
       </c>
-      <c r="E138" t="inlineStr"/>
+      <c r="E138" t="n">
+        <v>12.445</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Lewis Bake Shop</t>
+          <t>dollys</t>
         </is>
       </c>
       <c r="B139" t="n">
@@ -3016,30 +3020,32 @@
         <v>1</v>
       </c>
       <c r="E139" t="n">
-        <v>5.189283551419543</v>
+        <v>3.96</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Dairy</t>
+          <t>Ferrero</t>
         </is>
       </c>
       <c r="B140" t="n">
         <v>2</v>
       </c>
       <c r="C140" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D140" t="n">
-        <v>1</v>
-      </c>
-      <c r="E140" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="E140" t="n">
+        <v>48.37</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Crunchmaster</t>
+          <t>La Tortilla Factory</t>
         </is>
       </c>
       <c r="B141" t="n">
@@ -3052,13 +3058,13 @@
         <v>1</v>
       </c>
       <c r="E141" t="n">
-        <v>51.37009840929231</v>
+        <v>21.71</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Cole´s</t>
+          <t>Hinged</t>
         </is>
       </c>
       <c r="B142" t="n">
@@ -3071,13 +3077,13 @@
         <v>1</v>
       </c>
       <c r="E142" t="n">
-        <v>21.94025264317509</v>
+        <v>1.907848055928269</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Danisha</t>
+          <t>Crunchmaster</t>
         </is>
       </c>
       <c r="B143" t="n">
@@ -3089,12 +3095,14 @@
       <c r="D143" t="n">
         <v>1</v>
       </c>
-      <c r="E143" t="inlineStr"/>
+      <c r="E143" t="n">
+        <v>51.37009840929231</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Dove</t>
+          <t>Cole´s</t>
         </is>
       </c>
       <c r="B144" t="n">
@@ -3107,13 +3115,13 @@
         <v>1</v>
       </c>
       <c r="E144" t="n">
-        <v>10.95146340976004</v>
+        <v>21.94025264317509</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Dried</t>
+          <t>Dairy</t>
         </is>
       </c>
       <c r="B145" t="n">
@@ -3123,14 +3131,14 @@
         <v>1</v>
       </c>
       <c r="D145" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Hinged</t>
+          <t>Danisha</t>
         </is>
       </c>
       <c r="B146" t="n">
@@ -3142,14 +3150,12 @@
       <c r="D146" t="n">
         <v>1</v>
       </c>
-      <c r="E146" t="n">
-        <v>1.907848055928269</v>
-      </c>
+      <c r="E146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>La Tortilla Factory</t>
+          <t>Dove</t>
         </is>
       </c>
       <c r="B147" t="n">
@@ -3162,13 +3168,13 @@
         <v>1</v>
       </c>
       <c r="E147" t="n">
-        <v>21.71</v>
+        <v>10.95146340976004</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Cheez</t>
+          <t>Dried</t>
         </is>
       </c>
       <c r="B148" t="n">
@@ -3178,14 +3184,14 @@
         <v>1</v>
       </c>
       <c r="D148" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Mars</t>
+          <t>Glad</t>
         </is>
       </c>
       <c r="B149" t="n">
@@ -3202,7 +3208,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Can Can</t>
+          <t>Knotts</t>
         </is>
       </c>
       <c r="B150" t="n">
@@ -3214,14 +3220,12 @@
       <c r="D150" t="n">
         <v>1</v>
       </c>
-      <c r="E150" t="n">
-        <v>3.915</v>
-      </c>
+      <c r="E150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Beivita</t>
+          <t>Lewis Bake Shop</t>
         </is>
       </c>
       <c r="B151" t="n">
@@ -3234,49 +3238,49 @@
         <v>1</v>
       </c>
       <c r="E151" t="n">
-        <v>35.19230769230769</v>
+        <v>5.189283551419543</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Ferrero</t>
+          <t>Cheez</t>
         </is>
       </c>
       <c r="B152" t="n">
         <v>2</v>
       </c>
       <c r="C152" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D152" t="n">
-        <v>2</v>
-      </c>
-      <c r="E152" t="n">
-        <v>48.37</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="E152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Nature Valley</t>
+          <t>Can Can</t>
         </is>
       </c>
       <c r="B153" t="n">
         <v>2</v>
       </c>
       <c r="C153" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D153" t="n">
         <v>1</v>
       </c>
-      <c r="E153" t="inlineStr"/>
+      <c r="E153" t="n">
+        <v>3.915</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Hills</t>
+          <t>Mars</t>
         </is>
       </c>
       <c r="B154" t="n">
@@ -3293,11 +3297,11 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Ducales</t>
+          <t>Beivita</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C155" t="n">
         <v>1</v>
@@ -3306,36 +3310,34 @@
         <v>1</v>
       </c>
       <c r="E155" t="n">
-        <v>21.76632743949854</v>
+        <v>35.19230769230769</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Toblerone</t>
+          <t>Nature Valley</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C156" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D156" t="n">
         <v>1</v>
       </c>
-      <c r="E156" t="n">
-        <v>14.42655274400263</v>
-      </c>
+      <c r="E156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Double Duty</t>
+          <t>Hills</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C157" t="n">
         <v>1</v>
@@ -3348,7 +3350,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>DiGiorno</t>
+          <t>Cusano´s</t>
         </is>
       </c>
       <c r="B158" t="n">
@@ -3360,14 +3362,12 @@
       <c r="D158" t="n">
         <v>1</v>
       </c>
-      <c r="E158" t="n">
-        <v>14.25891435863968</v>
-      </c>
+      <c r="E158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Triscuit</t>
+          <t>Double Duty</t>
         </is>
       </c>
       <c r="B159" t="n">
@@ -3379,14 +3379,12 @@
       <c r="D159" t="n">
         <v>1</v>
       </c>
-      <c r="E159" t="n">
-        <v>21.76632743949854</v>
-      </c>
+      <c r="E159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Fernandes</t>
+          <t>DiGiorno</t>
         </is>
       </c>
       <c r="B160" t="n">
@@ -3398,12 +3396,14 @@
       <c r="D160" t="n">
         <v>1</v>
       </c>
-      <c r="E160" t="inlineStr"/>
+      <c r="E160" t="n">
+        <v>14.25891435863968</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Vegefarm</t>
+          <t>Triscuit</t>
         </is>
       </c>
       <c r="B161" t="n">
@@ -3416,13 +3416,13 @@
         <v>1</v>
       </c>
       <c r="E161" t="n">
-        <v>27.42714334124026</v>
+        <v>21.76632743949854</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Cusano´s</t>
+          <t>Toblerone</t>
         </is>
       </c>
       <c r="B162" t="n">
@@ -3434,12 +3434,14 @@
       <c r="D162" t="n">
         <v>1</v>
       </c>
-      <c r="E162" t="inlineStr"/>
+      <c r="E162" t="n">
+        <v>14.42655274400263</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Twizzlers</t>
+          <t>Ducales</t>
         </is>
       </c>
       <c r="B163" t="n">
@@ -3451,12 +3453,14 @@
       <c r="D163" t="n">
         <v>1</v>
       </c>
-      <c r="E163" t="inlineStr"/>
+      <c r="E163" t="n">
+        <v>21.76632743949854</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Sultana</t>
+          <t>Fernandes</t>
         </is>
       </c>
       <c r="B164" t="n">
@@ -3468,14 +3472,12 @@
       <c r="D164" t="n">
         <v>1</v>
       </c>
-      <c r="E164" t="n">
-        <v>18.58472998137803</v>
-      </c>
+      <c r="E164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Cloverhill</t>
+          <t>Nerds</t>
         </is>
       </c>
       <c r="B165" t="n">
@@ -3492,7 +3494,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Chowmein</t>
+          <t>Twizzlers</t>
         </is>
       </c>
       <c r="B166" t="n">
@@ -3509,7 +3511,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Choppers</t>
+          <t>Vegefarm</t>
         </is>
       </c>
       <c r="B167" t="n">
@@ -3521,12 +3523,14 @@
       <c r="D167" t="n">
         <v>1</v>
       </c>
-      <c r="E167" t="inlineStr"/>
+      <c r="E167" t="n">
+        <v>27.42714334124026</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Chokis</t>
+          <t>Fit Crunch</t>
         </is>
       </c>
       <c r="B168" t="n">
@@ -3539,13 +3543,13 @@
         <v>1</v>
       </c>
       <c r="E168" t="n">
-        <v>11.44</v>
+        <v>61.6</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Cho Cho</t>
+          <t>Chowmein</t>
         </is>
       </c>
       <c r="B169" t="n">
@@ -3562,7 +3566,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Chiefeez</t>
+          <t>Choppers</t>
         </is>
       </c>
       <c r="B170" t="n">
@@ -3579,7 +3583,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Chester</t>
+          <t>Chokis</t>
         </is>
       </c>
       <c r="B171" t="n">
@@ -3591,12 +3595,14 @@
       <c r="D171" t="n">
         <v>1</v>
       </c>
-      <c r="E171" t="inlineStr"/>
+      <c r="E171" t="n">
+        <v>11.44</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Bigelow</t>
+          <t>Cho Cho</t>
         </is>
       </c>
       <c r="B172" t="n">
@@ -3613,7 +3619,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Becky's</t>
+          <t>Chiefeez</t>
         </is>
       </c>
       <c r="B173" t="n">
@@ -3625,14 +3631,12 @@
       <c r="D173" t="n">
         <v>1</v>
       </c>
-      <c r="E173" t="n">
-        <v>19.37665392531608</v>
-      </c>
+      <c r="E173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Fit Crunch</t>
+          <t>Chester</t>
         </is>
       </c>
       <c r="B174" t="n">
@@ -3644,14 +3648,12 @@
       <c r="D174" t="n">
         <v>1</v>
       </c>
-      <c r="E174" t="n">
-        <v>61.6</v>
-      </c>
+      <c r="E174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Nerds</t>
+          <t>Bigelow</t>
         </is>
       </c>
       <c r="B175" t="n">
@@ -3668,7 +3670,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Stouffer's</t>
+          <t>Becky's</t>
         </is>
       </c>
       <c r="B176" t="n">
@@ -3681,13 +3683,13 @@
         <v>1</v>
       </c>
       <c r="E176" t="n">
-        <v>27.47380304721075</v>
+        <v>19.37665392531608</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Hostess</t>
+          <t>Yasso</t>
         </is>
       </c>
       <c r="B177" t="n">
@@ -3699,14 +3701,12 @@
       <c r="D177" t="n">
         <v>1</v>
       </c>
-      <c r="E177" t="n">
-        <v>20.82</v>
-      </c>
+      <c r="E177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Members Selection</t>
+          <t>Cloverhill</t>
         </is>
       </c>
       <c r="B178" t="n">
@@ -3723,7 +3723,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Mcvitie'S</t>
+          <t>Give &amp; Go</t>
         </is>
       </c>
       <c r="B179" t="n">
@@ -3735,14 +3735,12 @@
       <c r="D179" t="n">
         <v>1</v>
       </c>
-      <c r="E179" t="n">
-        <v>37.62485187066193</v>
-      </c>
+      <c r="E179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Ortega</t>
+          <t>Sultana</t>
         </is>
       </c>
       <c r="B180" t="n">
@@ -3755,13 +3753,13 @@
         <v>1</v>
       </c>
       <c r="E180" t="n">
-        <v>10.91045974485786</v>
+        <v>18.58472998137803</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Oscar Mayer</t>
+          <t>Stouffer's</t>
         </is>
       </c>
       <c r="B181" t="n">
@@ -3774,13 +3772,13 @@
         <v>1</v>
       </c>
       <c r="E181" t="n">
-        <v>21.70707121411719</v>
+        <v>27.47380304721075</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Marie</t>
+          <t>Members Selection</t>
         </is>
       </c>
       <c r="B182" t="n">
@@ -3797,7 +3795,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Liga</t>
+          <t>Mcvitie'S</t>
         </is>
       </c>
       <c r="B183" t="n">
@@ -3810,13 +3808,13 @@
         <v>1</v>
       </c>
       <c r="E183" t="n">
-        <v>10.58305138091117</v>
+        <v>37.62485187066193</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Kraft</t>
+          <t>Ortega</t>
         </is>
       </c>
       <c r="B184" t="n">
@@ -3829,13 +3827,13 @@
         <v>1</v>
       </c>
       <c r="E184" t="n">
-        <v>9.264432029795158</v>
+        <v>10.91045974485786</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>King's Hawaiian</t>
+          <t>Oscar Mayer</t>
         </is>
       </c>
       <c r="B185" t="n">
@@ -3847,12 +3845,14 @@
       <c r="D185" t="n">
         <v>1</v>
       </c>
-      <c r="E185" t="inlineStr"/>
+      <c r="E185" t="n">
+        <v>21.70707121411719</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Kimberley's Bakeshoppe</t>
+          <t>Marie</t>
         </is>
       </c>
       <c r="B186" t="n">
@@ -3869,7 +3869,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Pirucream</t>
+          <t>Liga</t>
         </is>
       </c>
       <c r="B187" t="n">
@@ -3882,13 +3882,13 @@
         <v>1</v>
       </c>
       <c r="E187" t="n">
-        <v>20.53625219611713</v>
+        <v>10.58305138091117</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Pirulin</t>
+          <t>King's Hawaiian</t>
         </is>
       </c>
       <c r="B188" t="n">
@@ -3905,7 +3905,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Jos Poell</t>
+          <t>Kimberley's Bakeshoppe</t>
         </is>
       </c>
       <c r="B189" t="n">
@@ -3917,14 +3917,12 @@
       <c r="D189" t="n">
         <v>1</v>
       </c>
-      <c r="E189" t="n">
-        <v>25.38795779019243</v>
-      </c>
+      <c r="E189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Post</t>
+          <t>Pirucream</t>
         </is>
       </c>
       <c r="B190" t="n">
@@ -3937,13 +3935,13 @@
         <v>1</v>
       </c>
       <c r="E190" t="n">
-        <v>7.51</v>
+        <v>20.53625219611713</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Hollandia</t>
+          <t>Pirulin</t>
         </is>
       </c>
       <c r="B191" t="n">
@@ -3955,14 +3953,12 @@
       <c r="D191" t="n">
         <v>1</v>
       </c>
-      <c r="E191" t="n">
-        <v>52.34878150009826</v>
-      </c>
+      <c r="E191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Frito-Lay</t>
+          <t>Jos Poell</t>
         </is>
       </c>
       <c r="B192" t="n">
@@ -3974,12 +3970,14 @@
       <c r="D192" t="n">
         <v>1</v>
       </c>
-      <c r="E192" t="inlineStr"/>
+      <c r="E192" t="n">
+        <v>25.38795779019243</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Holiday</t>
+          <t>Post</t>
         </is>
       </c>
       <c r="B193" t="n">
@@ -3991,12 +3989,14 @@
       <c r="D193" t="n">
         <v>1</v>
       </c>
-      <c r="E193" t="inlineStr"/>
+      <c r="E193" t="n">
+        <v>7.51</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Reynolds</t>
+          <t>Hostess</t>
         </is>
       </c>
       <c r="B194" t="n">
@@ -4008,12 +4008,14 @@
       <c r="D194" t="n">
         <v>1</v>
       </c>
-      <c r="E194" t="inlineStr"/>
+      <c r="E194" t="n">
+        <v>20.82</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Highland</t>
+          <t>Hollandia</t>
         </is>
       </c>
       <c r="B195" t="n">
@@ -4025,12 +4027,14 @@
       <c r="D195" t="n">
         <v>1</v>
       </c>
-      <c r="E195" t="inlineStr"/>
+      <c r="E195" t="n">
+        <v>52.34878150009826</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Santitas</t>
+          <t>Holiday</t>
         </is>
       </c>
       <c r="B196" t="n">
@@ -4042,14 +4046,12 @@
       <c r="D196" t="n">
         <v>1</v>
       </c>
-      <c r="E196" t="n">
-        <v>23.62766194234949</v>
-      </c>
+      <c r="E196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>HiPro</t>
+          <t>Reynolds</t>
         </is>
       </c>
       <c r="B197" t="n">
@@ -4066,7 +4068,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Hershey</t>
+          <t>Highland</t>
         </is>
       </c>
       <c r="B198" t="n">
@@ -4078,14 +4080,12 @@
       <c r="D198" t="n">
         <v>1</v>
       </c>
-      <c r="E198" t="n">
-        <v>19.07848055928269</v>
-      </c>
+      <c r="E198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Haribo</t>
+          <t>Santitas</t>
         </is>
       </c>
       <c r="B199" t="n">
@@ -4097,12 +4097,14 @@
       <c r="D199" t="n">
         <v>1</v>
       </c>
-      <c r="E199" t="inlineStr"/>
+      <c r="E199" t="n">
+        <v>23.62766194234949</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Haagen Daz</t>
+          <t>HiPro</t>
         </is>
       </c>
       <c r="B200" t="n">
@@ -4119,7 +4121,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Snickers</t>
+          <t>Hershey</t>
         </is>
       </c>
       <c r="B201" t="n">
@@ -4132,13 +4134,13 @@
         <v>1</v>
       </c>
       <c r="E201" t="n">
-        <v>40.99</v>
+        <v>19.07848055928269</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>HOL Foods</t>
+          <t>Haribo</t>
         </is>
       </c>
       <c r="B202" t="n">
@@ -4150,14 +4152,12 @@
       <c r="D202" t="n">
         <v>1</v>
       </c>
-      <c r="E202" t="n">
-        <v>14.42307692307692</v>
-      </c>
+      <c r="E202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Goldfish</t>
+          <t>Haagen Daz</t>
         </is>
       </c>
       <c r="B203" t="n">
@@ -4169,14 +4169,12 @@
       <c r="D203" t="n">
         <v>1</v>
       </c>
-      <c r="E203" t="n">
-        <v>15.39664804469274</v>
-      </c>
+      <c r="E203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Odorex</t>
+          <t>Snickers</t>
         </is>
       </c>
       <c r="B204" t="n">
@@ -4188,12 +4186,14 @@
       <c r="D204" t="n">
         <v>1</v>
       </c>
-      <c r="E204" t="inlineStr"/>
+      <c r="E204" t="n">
+        <v>40.99</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Give &amp; Go</t>
+          <t>HOL Foods</t>
         </is>
       </c>
       <c r="B205" t="n">
@@ -4205,12 +4205,14 @@
       <c r="D205" t="n">
         <v>1</v>
       </c>
-      <c r="E205" t="inlineStr"/>
+      <c r="E205" t="n">
+        <v>14.42307692307692</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Yasso</t>
+          <t>Goldfish</t>
         </is>
       </c>
       <c r="B206" t="n">
@@ -4222,7 +4224,62 @@
       <c r="D206" t="n">
         <v>1</v>
       </c>
-      <c r="E206" t="inlineStr"/>
+      <c r="E206" t="n">
+        <v>15.39664804469274</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Odorex</t>
+        </is>
+      </c>
+      <c r="B207" t="n">
+        <v>1</v>
+      </c>
+      <c r="C207" t="n">
+        <v>1</v>
+      </c>
+      <c r="D207" t="n">
+        <v>1</v>
+      </c>
+      <c r="E207" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Frito-Lay</t>
+        </is>
+      </c>
+      <c r="B208" t="n">
+        <v>1</v>
+      </c>
+      <c r="C208" t="n">
+        <v>1</v>
+      </c>
+      <c r="D208" t="n">
+        <v>1</v>
+      </c>
+      <c r="E208" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Kraft</t>
+        </is>
+      </c>
+      <c r="B209" t="n">
+        <v>1</v>
+      </c>
+      <c r="C209" t="n">
+        <v>1</v>
+      </c>
+      <c r="D209" t="n">
+        <v>1</v>
+      </c>
+      <c r="E209" t="n">
+        <v>9.264432029795158</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -78695,7 +78752,7 @@
       </c>
       <c r="G434" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Agua Vivo</t>
         </is>
       </c>
       <c r="H434" t="inlineStr">
@@ -78774,17 +78831,17 @@
       <c r="AG434" t="inlineStr"/>
       <c r="AH434" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Agua Vivo</t>
         </is>
       </c>
       <c r="AI434" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Agua Vivo</t>
         </is>
       </c>
       <c r="AJ434" t="inlineStr">
         <is>
-          <t>unknown_galleta de agua vivo</t>
+          <t>agua vivo_galleta de agua vivo</t>
         </is>
       </c>
       <c r="AK434" t="inlineStr">
@@ -78799,7 +78856,7 @@
       </c>
       <c r="AM434" t="inlineStr">
         <is>
-          <t>unknown_galleta de agua vivo_0.14</t>
+          <t>agua vivo_galleta de agua vivo_0.14</t>
         </is>
       </c>
       <c r="AN434" t="n">
@@ -78813,7 +78870,7 @@
       </c>
       <c r="AQ434" t="inlineStr">
         <is>
-          <t>unknown_agua_vivo</t>
+          <t>agua vivo_agua_vivo</t>
         </is>
       </c>
       <c r="AR434" t="n">

--- a/streamlit_data/regional_insights.xlsx
+++ b/streamlit_data/regional_insights.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E209"/>
+  <dimension ref="A1:E213"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,7 +456,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>387</v>
+        <v>346</v>
       </c>
       <c r="C2" t="n">
         <v>3</v>
@@ -465,7 +465,7 @@
         <v>6</v>
       </c>
       <c r="E2" t="n">
-        <v>19.8804201585068</v>
+        <v>20.23741564522681</v>
       </c>
     </row>
     <row r="3">
@@ -642,39 +642,39 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Hatuey</t>
+          <t>Instorebakery</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>56</v>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E12" t="n">
-        <v>4.617555555555556</v>
+        <v>20.54408949352927</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Instorebakery</t>
+          <t>Hatuey</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>56</v>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>20.54408949352927</v>
+        <v>4.617555555555556</v>
       </c>
     </row>
     <row r="14">
@@ -832,39 +832,39 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Betty Crocker</t>
+          <t>Sunshine Snacks</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>35</v>
       </c>
       <c r="C22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E22" t="n">
-        <v>11.50905500557616</v>
+        <v>20.92956623821305</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sunshine Snacks</t>
+          <t>Betty Crocker</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>35</v>
       </c>
       <c r="C23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E23" t="n">
-        <v>20.92956623821305</v>
+        <v>11.50905500557616</v>
       </c>
     </row>
     <row r="24">
@@ -946,39 +946,39 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Club Social</t>
+          <t>Bermudez</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>28</v>
       </c>
       <c r="C28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>6.351099247772932</v>
+        <v>9.901427320955712</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Bermudez</t>
+          <t>Club Social</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>28</v>
       </c>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D29" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>9.901427320955712</v>
+        <v>6.351099247772932</v>
       </c>
     </row>
     <row r="30">
@@ -1098,7 +1098,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Pepin</t>
+          <t>La Real</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -1108,10 +1108,10 @@
         <v>1</v>
       </c>
       <c r="D36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E36" t="n">
-        <v>3.923333333333334</v>
+        <v>10.1025</v>
       </c>
     </row>
     <row r="37">
@@ -1193,39 +1193,39 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Lider</t>
+          <t>Pepin</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C41" t="n">
         <v>1</v>
       </c>
       <c r="D41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E41" t="n">
-        <v>7.467272727272728</v>
+        <v>3.923333333333334</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Lenny &amp; Larry's</t>
+          <t>Lider</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C42" t="n">
         <v>1</v>
       </c>
       <c r="D42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E42" t="n">
-        <v>26.45875</v>
+        <v>7.467272727272728</v>
       </c>
     </row>
     <row r="43">
@@ -1250,43 +1250,45 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>La Libanesa</t>
+          <t>Lenny &amp; Larry's</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C44" t="n">
         <v>1</v>
       </c>
       <c r="D44" t="n">
-        <v>1</v>
-      </c>
-      <c r="E44" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="E44" t="n">
+        <v>26.45875</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Pepperidge</t>
+          <t>El Charrito</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C45" t="n">
         <v>1</v>
       </c>
       <c r="D45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E45" t="n">
-        <v>29.39239164449742</v>
+        <v>4.845</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Charles</t>
+          <t>Pepperidge</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -1296,92 +1298,90 @@
         <v>1</v>
       </c>
       <c r="D46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E46" t="n">
-        <v>19.27125506072875</v>
+        <v>29.39239164449742</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Devon</t>
+          <t>Charles</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C47" t="n">
         <v>1</v>
       </c>
       <c r="D47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E47" t="n">
-        <v>9.404842870544091</v>
+        <v>19.27125506072875</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Crav'N</t>
+          <t>La Libanesa</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D48" t="n">
-        <v>4</v>
-      </c>
-      <c r="E48" t="n">
-        <v>20.64511696006157</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="E48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Devon</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C49" t="n">
         <v>1</v>
       </c>
       <c r="D49" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E49" t="n">
-        <v>3.208571428571429</v>
+        <v>9.404842870544091</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Wow</t>
+          <t>Crav'N</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D50" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E50" t="n">
-        <v>9.45857142857143</v>
+        <v>20.64511696006157</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Wasa</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -1391,115 +1391,115 @@
         <v>1</v>
       </c>
       <c r="D51" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E51" t="n">
-        <v>20.93163482244135</v>
+        <v>3.208571428571429</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Wibisco</t>
+          <t>Wala</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C52" t="n">
         <v>1</v>
       </c>
       <c r="D52" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E52" t="n">
-        <v>7.709999008179106</v>
+        <v>5.640000000000001</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Bergen</t>
+          <t>Wasa</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C53" t="n">
         <v>1</v>
       </c>
       <c r="D53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E53" t="n">
-        <v>11.83083333333333</v>
+        <v>20.93163482244135</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Motto</t>
+          <t>Wow</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D54" t="n">
         <v>1</v>
       </c>
       <c r="E54" t="n">
-        <v>15.4472192513369</v>
+        <v>9.45857142857143</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Noel</t>
+          <t>Bergen</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D55" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E55" t="n">
-        <v>19.31337392062075</v>
+        <v>11.83083333333333</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Shoon</t>
+          <t>Quadratini</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C56" t="n">
         <v>1</v>
       </c>
       <c r="D56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>23.68495475113122</v>
+        <v>25.69083333333333</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Qiin</t>
+          <t>Wibisco</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C57" t="n">
         <v>1</v>
@@ -1507,16 +1507,18 @@
       <c r="D57" t="n">
         <v>1</v>
       </c>
-      <c r="E57" t="inlineStr"/>
+      <c r="E57" t="n">
+        <v>7.709999008179106</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Doritos</t>
+          <t>Shoon</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C58" t="n">
         <v>1</v>
@@ -1525,72 +1527,74 @@
         <v>2</v>
       </c>
       <c r="E58" t="n">
-        <v>20.25820736467665</v>
+        <v>23.68495475113122</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Keebler</t>
+          <t>Noel</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D59" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E59" t="n">
-        <v>16.53</v>
+        <v>19.31337392062075</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>El Charrito</t>
+          <t>Motto</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D60" t="n">
         <v>1</v>
       </c>
-      <c r="E60" t="inlineStr"/>
+      <c r="E60" t="n">
+        <v>15.4472192513369</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>La Real</t>
+          <t>Doritos</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C61" t="n">
         <v>1</v>
       </c>
       <c r="D61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E61" t="n">
-        <v>12.46</v>
+        <v>20.25820736467665</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Festival</t>
+          <t>Qiin</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C62" t="n">
         <v>1</v>
@@ -1598,27 +1602,25 @@
       <c r="D62" t="n">
         <v>1</v>
       </c>
-      <c r="E62" t="n">
-        <v>9.385016025641024</v>
-      </c>
+      <c r="E62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Siete</t>
+          <t>Keebler</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D63" t="n">
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>35.46555757535778</v>
+        <v>16.53</v>
       </c>
     </row>
     <row r="64">
@@ -1643,7 +1645,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Chips Ahoy</t>
+          <t>Siete</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -1653,10 +1655,10 @@
         <v>2</v>
       </c>
       <c r="D65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E65" t="n">
-        <v>12.99941707258641</v>
+        <v>35.46555757535778</v>
       </c>
     </row>
     <row r="66">
@@ -1681,43 +1683,45 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Bisco</t>
+          <t>Chips Ahoy</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E67" t="n">
-        <v>9.168749999999999</v>
+        <v>12.99941707258641</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Biskitop</t>
+          <t>Festival</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C68" t="n">
         <v>1</v>
       </c>
       <c r="D68" t="n">
-        <v>2</v>
-      </c>
-      <c r="E68" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E68" t="n">
+        <v>9.385016025641024</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Member's Selection</t>
+          <t>Eggo</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -1727,16 +1731,16 @@
         <v>1</v>
       </c>
       <c r="D69" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E69" t="n">
-        <v>13.74</v>
+        <v>14.6121807037156</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Eggo</t>
+          <t>Biskitop</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -1746,35 +1750,33 @@
         <v>1</v>
       </c>
       <c r="D70" t="n">
-        <v>1</v>
-      </c>
-      <c r="E70" t="n">
-        <v>14.6121807037156</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="E70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Lavigne</t>
+          <t>Member's Selection</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C71" t="n">
         <v>1</v>
       </c>
       <c r="D71" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E71" t="n">
-        <v>9.161428571428571</v>
+        <v>13.74</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Biscotto</t>
+          <t>Lavigne</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -1784,10 +1786,10 @@
         <v>1</v>
       </c>
       <c r="D72" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E72" t="n">
-        <v>25</v>
+        <v>9.161428571428571</v>
       </c>
     </row>
     <row r="73">
@@ -1810,7 +1812,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Golden</t>
+          <t>Walkers</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -1822,12 +1824,14 @@
       <c r="D74" t="n">
         <v>2</v>
       </c>
-      <c r="E74" t="inlineStr"/>
+      <c r="E74" t="n">
+        <v>97.43589743589745</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Crich</t>
+          <t>Nature'S Own</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -1837,16 +1841,16 @@
         <v>1</v>
       </c>
       <c r="D75" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E75" t="n">
-        <v>13.94857142857143</v>
+        <v>7.755714285714285</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Nature'S Own</t>
+          <t>Holsum</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -1859,13 +1863,13 @@
         <v>1</v>
       </c>
       <c r="E76" t="n">
-        <v>7.755714285714285</v>
+        <v>7.78</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Holsum</t>
+          <t>Golden</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -1875,16 +1879,14 @@
         <v>1</v>
       </c>
       <c r="D77" t="n">
-        <v>1</v>
-      </c>
-      <c r="E77" t="n">
-        <v>7.78</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="E77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Walkers</t>
+          <t>Crich</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -1897,17 +1899,17 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>97.43589743589745</v>
+        <v>13.94857142857143</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Cadbury</t>
+          <t>Biscotto</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C79" t="n">
         <v>1</v>
@@ -1915,7 +1917,9 @@
       <c r="D79" t="n">
         <v>2</v>
       </c>
-      <c r="E79" t="inlineStr"/>
+      <c r="E79" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -1937,7 +1941,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Otis Spunkmeyer</t>
+          <t>Mr Bakewell</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -1947,33 +1951,33 @@
         <v>1</v>
       </c>
       <c r="D81" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Schar</t>
+          <t>Costa</t>
         </is>
       </c>
       <c r="B82" t="n">
         <v>6</v>
       </c>
       <c r="C82" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D82" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E82" t="n">
-        <v>24.18904950998269</v>
+        <v>14.64666666666667</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Sunshine</t>
+          <t>Cadbury</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -1983,16 +1987,14 @@
         <v>1</v>
       </c>
       <c r="D83" t="n">
-        <v>1</v>
-      </c>
-      <c r="E83" t="n">
-        <v>9.488333333333333</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="E83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Mr Bakewell</t>
+          <t>Laurieri</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -2002,33 +2004,35 @@
         <v>1</v>
       </c>
       <c r="D84" t="n">
-        <v>1</v>
-      </c>
-      <c r="E84" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="E84" t="n">
+        <v>20.65978352354142</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Costa</t>
+          <t>Schar</t>
         </is>
       </c>
       <c r="B85" t="n">
         <v>6</v>
       </c>
       <c r="C85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D85" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>14.64666666666667</v>
+        <v>24.18904950998269</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Laurieri</t>
+          <t>Otis Spunkmeyer</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -2040,52 +2044,50 @@
       <c r="D86" t="n">
         <v>2</v>
       </c>
-      <c r="E86" t="n">
-        <v>20.65978352354142</v>
-      </c>
+      <c r="E86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Nutella</t>
+          <t>Bisco Pan</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C87" t="n">
+        <v>1</v>
+      </c>
+      <c r="D87" t="n">
         <v>2</v>
       </c>
-      <c r="D87" t="n">
-        <v>1</v>
-      </c>
       <c r="E87" t="n">
-        <v>15.46996215078755</v>
+        <v>5.82</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Bagel Bites</t>
+          <t>Sunshine</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C88" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D88" t="n">
         <v>1</v>
       </c>
       <c r="E88" t="n">
-        <v>14.76764878866199</v>
+        <v>9.488333333333333</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Hosttes</t>
+          <t>Triskits</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -2097,88 +2099,88 @@
       <c r="D89" t="n">
         <v>1</v>
       </c>
-      <c r="E89" t="n">
-        <v>36.83418646645511</v>
-      </c>
+      <c r="E89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Badia</t>
+          <t>Hosttes</t>
         </is>
       </c>
       <c r="B90" t="n">
         <v>5</v>
       </c>
       <c r="C90" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D90" t="n">
         <v>1</v>
       </c>
       <c r="E90" t="n">
-        <v>28.56294367711628</v>
+        <v>36.83418646645511</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Triskits</t>
+          <t>Cheetos</t>
         </is>
       </c>
       <c r="B91" t="n">
         <v>5</v>
       </c>
       <c r="C91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D91" t="n">
         <v>1</v>
       </c>
-      <c r="E91" t="inlineStr"/>
+      <c r="E91" t="n">
+        <v>23.77550530709329</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>La Dulcerita</t>
+          <t>Kiss</t>
         </is>
       </c>
       <c r="B92" t="n">
         <v>5</v>
       </c>
       <c r="C92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D92" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E92" t="n">
-        <v>14.22407288526729</v>
+        <v>20.05506545869531</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Bolletje</t>
+          <t>Badia</t>
         </is>
       </c>
       <c r="B93" t="n">
         <v>5</v>
       </c>
       <c r="C93" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D93" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E93" t="n">
-        <v>29.40549939726599</v>
+        <v>28.56294367711628</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Cheetos</t>
+          <t>Bagel Bites</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -2191,13 +2193,13 @@
         <v>1</v>
       </c>
       <c r="E94" t="n">
-        <v>23.77550530709329</v>
+        <v>14.76764878866199</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Merba</t>
+          <t>Tiffany</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -2214,38 +2216,38 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Tiffany</t>
+          <t>Nutella</t>
         </is>
       </c>
       <c r="B96" t="n">
         <v>5</v>
       </c>
       <c r="C96" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D96" t="n">
         <v>1</v>
       </c>
-      <c r="E96" t="inlineStr"/>
+      <c r="E96" t="n">
+        <v>15.46996215078755</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Kiss</t>
+          <t>Merba</t>
         </is>
       </c>
       <c r="B97" t="n">
         <v>5</v>
       </c>
       <c r="C97" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D97" t="n">
-        <v>3</v>
-      </c>
-      <c r="E97" t="n">
-        <v>20.05506545869531</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="E97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -2269,30 +2271,30 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Ovaltine</t>
+          <t>La Dulcerita</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C99" t="n">
         <v>1</v>
       </c>
       <c r="D99" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E99" t="n">
-        <v>19.9445103354795</v>
+        <v>14.22407288526729</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Milka</t>
+          <t>Bolletje</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C100" t="n">
         <v>1</v>
@@ -2301,13 +2303,13 @@
         <v>2</v>
       </c>
       <c r="E100" t="n">
-        <v>29.0725</v>
+        <v>29.40549939726599</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Stonefire</t>
+          <t>Ovaltine</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -2320,13 +2322,13 @@
         <v>1</v>
       </c>
       <c r="E101" t="n">
-        <v>16.92</v>
+        <v>19.9445103354795</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Nestle</t>
+          <t>Milka</t>
         </is>
       </c>
       <c r="B102" t="n">
@@ -2336,16 +2338,16 @@
         <v>1</v>
       </c>
       <c r="D102" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E102" t="n">
-        <v>41.70528266913809</v>
+        <v>29.0725</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Takis</t>
+          <t>Kinder</t>
         </is>
       </c>
       <c r="B103" t="n">
@@ -2358,13 +2360,13 @@
         <v>2</v>
       </c>
       <c r="E103" t="n">
-        <v>41.86</v>
+        <v>9.291503578576814</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Keeber</t>
+          <t>Nestle</t>
         </is>
       </c>
       <c r="B104" t="n">
@@ -2377,13 +2379,13 @@
         <v>3</v>
       </c>
       <c r="E104" t="n">
-        <v>28.61772083892403</v>
+        <v>41.70528266913809</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Herrs</t>
+          <t>Stonefire</t>
         </is>
       </c>
       <c r="B105" t="n">
@@ -2396,13 +2398,13 @@
         <v>1</v>
       </c>
       <c r="E105" t="n">
-        <v>37.30902864926393</v>
+        <v>16.92</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Snyder’S</t>
+          <t>Herrs</t>
         </is>
       </c>
       <c r="B106" t="n">
@@ -2415,7 +2417,7 @@
         <v>1</v>
       </c>
       <c r="E106" t="n">
-        <v>21.8340355175269</v>
+        <v>37.30902864926393</v>
       </c>
     </row>
     <row r="107">
@@ -2440,26 +2442,26 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Kinder</t>
+          <t>Snyder’S</t>
         </is>
       </c>
       <c r="B108" t="n">
         <v>4</v>
       </c>
       <c r="C108" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D108" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E108" t="n">
-        <v>9.291503578576814</v>
+        <v>21.8340355175269</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Dulcesol</t>
+          <t>Keeber</t>
         </is>
       </c>
       <c r="B109" t="n">
@@ -2469,37 +2471,39 @@
         <v>1</v>
       </c>
       <c r="D109" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E109" t="n">
-        <v>6.916666666666667</v>
+        <v>28.61772083892403</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Dux</t>
+          <t>Takis</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C110" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D110" t="n">
-        <v>1</v>
-      </c>
-      <c r="E110" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="E110" t="n">
+        <v>41.86</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Verkade</t>
+          <t>Dulcesol</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C111" t="n">
         <v>1</v>
@@ -2508,13 +2512,13 @@
         <v>1</v>
       </c>
       <c r="E111" t="n">
-        <v>13.51789778605421</v>
+        <v>6.916666666666667</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Van Der Meulen</t>
+          <t>Dux</t>
         </is>
       </c>
       <c r="B112" t="n">
@@ -2526,14 +2530,12 @@
       <c r="D112" t="n">
         <v>1</v>
       </c>
-      <c r="E112" t="n">
-        <v>12.12155070255629</v>
-      </c>
+      <c r="E112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Confetti</t>
+          <t>Van Der Meulen</t>
         </is>
       </c>
       <c r="B113" t="n">
@@ -2545,12 +2547,14 @@
       <c r="D113" t="n">
         <v>1</v>
       </c>
-      <c r="E113" t="inlineStr"/>
+      <c r="E113" t="n">
+        <v>12.12155070255629</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Crix</t>
+          <t>Confetti</t>
         </is>
       </c>
       <c r="B114" t="n">
@@ -2562,14 +2566,12 @@
       <c r="D114" t="n">
         <v>1</v>
       </c>
-      <c r="E114" t="n">
-        <v>7.160318629656713</v>
-      </c>
+      <c r="E114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Chetos</t>
+          <t>Crix</t>
         </is>
       </c>
       <c r="B115" t="n">
@@ -2581,12 +2583,14 @@
       <c r="D115" t="n">
         <v>1</v>
       </c>
-      <c r="E115" t="inlineStr"/>
+      <c r="E115" t="n">
+        <v>7.160318629656713</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Del-E</t>
+          <t>Chobani</t>
         </is>
       </c>
       <c r="B116" t="n">
@@ -2596,14 +2600,16 @@
         <v>1</v>
       </c>
       <c r="D116" t="n">
-        <v>2</v>
-      </c>
-      <c r="E116" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E116" t="n">
+        <v>25.58923192551497</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Totino's</t>
+          <t>Waitrose</t>
         </is>
       </c>
       <c r="B117" t="n">
@@ -2613,11 +2619,9 @@
         <v>1</v>
       </c>
       <c r="D117" t="n">
-        <v>1</v>
-      </c>
-      <c r="E117" t="n">
-        <v>10.85144743680014</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="E117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -2641,7 +2645,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Elina</t>
+          <t>Del-E</t>
         </is>
       </c>
       <c r="B119" t="n">
@@ -2651,16 +2655,14 @@
         <v>1</v>
       </c>
       <c r="D119" t="n">
-        <v>1</v>
-      </c>
-      <c r="E119" t="n">
-        <v>35.07692932225363</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="E119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Waitrose</t>
+          <t>Totino's</t>
         </is>
       </c>
       <c r="B120" t="n">
@@ -2670,14 +2672,16 @@
         <v>1</v>
       </c>
       <c r="D120" t="n">
-        <v>2</v>
-      </c>
-      <c r="E120" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E120" t="n">
+        <v>10.85144743680014</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Flourish</t>
+          <t>Elina</t>
         </is>
       </c>
       <c r="B121" t="n">
@@ -2689,12 +2693,14 @@
       <c r="D121" t="n">
         <v>1</v>
       </c>
-      <c r="E121" t="inlineStr"/>
+      <c r="E121" t="n">
+        <v>35.07692932225363</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Snyders</t>
+          <t>Flourish</t>
         </is>
       </c>
       <c r="B122" t="n">
@@ -2711,7 +2717,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Roomboter</t>
+          <t>Chetos</t>
         </is>
       </c>
       <c r="B123" t="n">
@@ -2721,16 +2727,14 @@
         <v>1</v>
       </c>
       <c r="D123" t="n">
-        <v>2</v>
-      </c>
-      <c r="E123" t="n">
-        <v>16.70555144365191</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="E123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Pizkas</t>
+          <t>Snyders</t>
         </is>
       </c>
       <c r="B124" t="n">
@@ -2742,14 +2746,12 @@
       <c r="D124" t="n">
         <v>1</v>
       </c>
-      <c r="E124" t="n">
-        <v>4.146666666666667</v>
-      </c>
+      <c r="E124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Chobani</t>
+          <t>Roomboter</t>
         </is>
       </c>
       <c r="B125" t="n">
@@ -2759,20 +2761,20 @@
         <v>1</v>
       </c>
       <c r="D125" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E125" t="n">
-        <v>25.58923192551497</v>
+        <v>16.70555144365191</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Werther’S</t>
+          <t>Pizkas</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C126" t="n">
         <v>1</v>
@@ -2780,16 +2782,18 @@
       <c r="D126" t="n">
         <v>1</v>
       </c>
-      <c r="E126" t="inlineStr"/>
+      <c r="E126" t="n">
+        <v>4.146666666666667</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Wala</t>
+          <t>Verkade</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C127" t="n">
         <v>1</v>
@@ -2797,12 +2801,14 @@
       <c r="D127" t="n">
         <v>1</v>
       </c>
-      <c r="E127" t="inlineStr"/>
+      <c r="E127" t="n">
+        <v>13.51789778605421</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Wheat Thins</t>
+          <t>Voortman</t>
         </is>
       </c>
       <c r="B128" t="n">
@@ -2815,13 +2821,13 @@
         <v>1</v>
       </c>
       <c r="E128" t="n">
-        <v>8.979888962508067</v>
+        <v>20.17345399698341</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Willie</t>
+          <t>Werther’S</t>
         </is>
       </c>
       <c r="B129" t="n">
@@ -2838,7 +2844,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Pico Bello</t>
+          <t>Wheat Thins</t>
         </is>
       </c>
       <c r="B130" t="n">
@@ -2851,13 +2857,13 @@
         <v>1</v>
       </c>
       <c r="E130" t="n">
-        <v>21.08728168019017</v>
+        <v>8.979888962508067</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Voortman</t>
+          <t>Willie</t>
         </is>
       </c>
       <c r="B131" t="n">
@@ -2869,14 +2875,12 @@
       <c r="D131" t="n">
         <v>1</v>
       </c>
-      <c r="E131" t="n">
-        <v>20.17345399698341</v>
-      </c>
+      <c r="E131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Vigo</t>
+          <t>Pico Bello</t>
         </is>
       </c>
       <c r="B132" t="n">
@@ -2889,13 +2893,13 @@
         <v>1</v>
       </c>
       <c r="E132" t="n">
-        <v>9.433248720978664</v>
+        <v>21.08728168019017</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Twix</t>
+          <t>Vigo</t>
         </is>
       </c>
       <c r="B133" t="n">
@@ -2908,13 +2912,13 @@
         <v>1</v>
       </c>
       <c r="E133" t="n">
-        <v>25.28014847471393</v>
+        <v>9.433248720978664</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Tuc</t>
+          <t>Twix</t>
         </is>
       </c>
       <c r="B134" t="n">
@@ -2927,13 +2931,13 @@
         <v>1</v>
       </c>
       <c r="E134" t="n">
-        <v>7.575418994413408</v>
+        <v>25.28014847471393</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Soldanza</t>
+          <t>Tuc</t>
         </is>
       </c>
       <c r="B135" t="n">
@@ -2945,12 +2949,14 @@
       <c r="D135" t="n">
         <v>1</v>
       </c>
-      <c r="E135" t="inlineStr"/>
+      <c r="E135" t="n">
+        <v>7.575418994413408</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Sara Lee</t>
+          <t>Soldanza</t>
         </is>
       </c>
       <c r="B136" t="n">
@@ -2962,14 +2968,12 @@
       <c r="D136" t="n">
         <v>1</v>
       </c>
-      <c r="E136" t="n">
-        <v>24.085</v>
-      </c>
+      <c r="E136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Ricola</t>
+          <t>Sara Lee</t>
         </is>
       </c>
       <c r="B137" t="n">
@@ -2982,13 +2986,13 @@
         <v>1</v>
       </c>
       <c r="E137" t="n">
-        <v>7.351955307262569</v>
+        <v>24.085</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Agua Vivo</t>
+          <t>Royal Dansk</t>
         </is>
       </c>
       <c r="B138" t="n">
@@ -3001,13 +3005,13 @@
         <v>1</v>
       </c>
       <c r="E138" t="n">
-        <v>12.445</v>
+        <v>20.48</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>dollys</t>
+          <t>Ricola</t>
         </is>
       </c>
       <c r="B139" t="n">
@@ -3020,32 +3024,32 @@
         <v>1</v>
       </c>
       <c r="E139" t="n">
-        <v>3.96</v>
+        <v>7.351955307262569</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Ferrero</t>
+          <t>Agua Vivo</t>
         </is>
       </c>
       <c r="B140" t="n">
         <v>2</v>
       </c>
       <c r="C140" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D140" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E140" t="n">
-        <v>48.37</v>
+        <v>12.445</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>La Tortilla Factory</t>
+          <t>dollys</t>
         </is>
       </c>
       <c r="B141" t="n">
@@ -3058,13 +3062,13 @@
         <v>1</v>
       </c>
       <c r="E141" t="n">
-        <v>21.71</v>
+        <v>3.96</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Hinged</t>
+          <t>Cheez</t>
         </is>
       </c>
       <c r="B142" t="n">
@@ -3076,14 +3080,12 @@
       <c r="D142" t="n">
         <v>1</v>
       </c>
-      <c r="E142" t="n">
-        <v>1.907848055928269</v>
-      </c>
+      <c r="E142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Crunchmaster</t>
+          <t>La Tortilla Factory</t>
         </is>
       </c>
       <c r="B143" t="n">
@@ -3096,13 +3098,13 @@
         <v>1</v>
       </c>
       <c r="E143" t="n">
-        <v>51.37009840929231</v>
+        <v>21.71</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Cole´s</t>
+          <t>Dairy</t>
         </is>
       </c>
       <c r="B144" t="n">
@@ -3114,14 +3116,12 @@
       <c r="D144" t="n">
         <v>1</v>
       </c>
-      <c r="E144" t="n">
-        <v>21.94025264317509</v>
-      </c>
+      <c r="E144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Dairy</t>
+          <t>Hinged</t>
         </is>
       </c>
       <c r="B145" t="n">
@@ -3133,12 +3133,14 @@
       <c r="D145" t="n">
         <v>1</v>
       </c>
-      <c r="E145" t="inlineStr"/>
+      <c r="E145" t="n">
+        <v>1.907848055928269</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Danisha</t>
+          <t>Dove</t>
         </is>
       </c>
       <c r="B146" t="n">
@@ -3150,12 +3152,14 @@
       <c r="D146" t="n">
         <v>1</v>
       </c>
-      <c r="E146" t="inlineStr"/>
+      <c r="E146" t="n">
+        <v>10.95146340976004</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Dove</t>
+          <t>Glad</t>
         </is>
       </c>
       <c r="B147" t="n">
@@ -3167,14 +3171,12 @@
       <c r="D147" t="n">
         <v>1</v>
       </c>
-      <c r="E147" t="n">
-        <v>10.95146340976004</v>
-      </c>
+      <c r="E147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Dried</t>
+          <t>Cole´s</t>
         </is>
       </c>
       <c r="B148" t="n">
@@ -3184,14 +3186,16 @@
         <v>1</v>
       </c>
       <c r="D148" t="n">
-        <v>2</v>
-      </c>
-      <c r="E148" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E148" t="n">
+        <v>21.94025264317509</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Glad</t>
+          <t>Crunchmaster</t>
         </is>
       </c>
       <c r="B149" t="n">
@@ -3203,7 +3207,9 @@
       <c r="D149" t="n">
         <v>1</v>
       </c>
-      <c r="E149" t="inlineStr"/>
+      <c r="E149" t="n">
+        <v>51.37009840929231</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -3244,7 +3250,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Cheez</t>
+          <t>Can Can</t>
         </is>
       </c>
       <c r="B152" t="n">
@@ -3256,12 +3262,14 @@
       <c r="D152" t="n">
         <v>1</v>
       </c>
-      <c r="E152" t="inlineStr"/>
+      <c r="E152" t="n">
+        <v>3.915</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Can Can</t>
+          <t>Bisco</t>
         </is>
       </c>
       <c r="B153" t="n">
@@ -3274,7 +3282,7 @@
         <v>1</v>
       </c>
       <c r="E153" t="n">
-        <v>3.915</v>
+        <v>19.215</v>
       </c>
     </row>
     <row r="154">
@@ -3297,7 +3305,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Beivita</t>
+          <t>Dried</t>
         </is>
       </c>
       <c r="B155" t="n">
@@ -3307,28 +3315,28 @@
         <v>1</v>
       </c>
       <c r="D155" t="n">
-        <v>1</v>
-      </c>
-      <c r="E155" t="n">
-        <v>35.19230769230769</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="E155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Nature Valley</t>
+          <t>Beivita</t>
         </is>
       </c>
       <c r="B156" t="n">
         <v>2</v>
       </c>
       <c r="C156" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D156" t="n">
         <v>1</v>
       </c>
-      <c r="E156" t="inlineStr"/>
+      <c r="E156" t="n">
+        <v>35.19230769230769</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -3350,31 +3358,33 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Cusano´s</t>
+          <t>Ferrero</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C158" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D158" t="n">
-        <v>1</v>
-      </c>
-      <c r="E158" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="E158" t="n">
+        <v>48.37</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Double Duty</t>
+          <t>Nature Valley</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C159" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D159" t="n">
         <v>1</v>
@@ -3384,11 +3394,11 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>DiGiorno</t>
+          <t>Danisha</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C160" t="n">
         <v>1</v>
@@ -3396,9 +3406,7 @@
       <c r="D160" t="n">
         <v>1</v>
       </c>
-      <c r="E160" t="n">
-        <v>14.25891435863968</v>
-      </c>
+      <c r="E160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -3422,7 +3430,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Toblerone</t>
+          <t>Nerds</t>
         </is>
       </c>
       <c r="B162" t="n">
@@ -3434,14 +3442,12 @@
       <c r="D162" t="n">
         <v>1</v>
       </c>
-      <c r="E162" t="n">
-        <v>14.42655274400263</v>
-      </c>
+      <c r="E162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Ducales</t>
+          <t>DiGiorno</t>
         </is>
       </c>
       <c r="B163" t="n">
@@ -3454,13 +3460,13 @@
         <v>1</v>
       </c>
       <c r="E163" t="n">
-        <v>21.76632743949854</v>
+        <v>14.25891435863968</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Fernandes</t>
+          <t>Double Duty</t>
         </is>
       </c>
       <c r="B164" t="n">
@@ -3477,7 +3483,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Nerds</t>
+          <t>Toblerone</t>
         </is>
       </c>
       <c r="B165" t="n">
@@ -3489,12 +3495,14 @@
       <c r="D165" t="n">
         <v>1</v>
       </c>
-      <c r="E165" t="inlineStr"/>
+      <c r="E165" t="n">
+        <v>14.42655274400263</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Twizzlers</t>
+          <t>Ducales</t>
         </is>
       </c>
       <c r="B166" t="n">
@@ -3506,12 +3514,14 @@
       <c r="D166" t="n">
         <v>1</v>
       </c>
-      <c r="E166" t="inlineStr"/>
+      <c r="E166" t="n">
+        <v>21.76632743949854</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Vegefarm</t>
+          <t>Cusano´s</t>
         </is>
       </c>
       <c r="B167" t="n">
@@ -3523,14 +3533,12 @@
       <c r="D167" t="n">
         <v>1</v>
       </c>
-      <c r="E167" t="n">
-        <v>27.42714334124026</v>
-      </c>
+      <c r="E167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Fit Crunch</t>
+          <t>Vegefarm</t>
         </is>
       </c>
       <c r="B168" t="n">
@@ -3543,13 +3551,13 @@
         <v>1</v>
       </c>
       <c r="E168" t="n">
-        <v>61.6</v>
+        <v>27.42714334124026</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Chowmein</t>
+          <t>Twizzlers</t>
         </is>
       </c>
       <c r="B169" t="n">
@@ -3566,7 +3574,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Choppers</t>
+          <t>Cloverhill</t>
         </is>
       </c>
       <c r="B170" t="n">
@@ -3583,7 +3591,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Chokis</t>
+          <t>Fernandes</t>
         </is>
       </c>
       <c r="B171" t="n">
@@ -3595,14 +3603,12 @@
       <c r="D171" t="n">
         <v>1</v>
       </c>
-      <c r="E171" t="n">
-        <v>11.44</v>
-      </c>
+      <c r="E171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Cho Cho</t>
+          <t>Chowmein</t>
         </is>
       </c>
       <c r="B172" t="n">
@@ -3619,7 +3625,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Chiefeez</t>
+          <t>Choppers</t>
         </is>
       </c>
       <c r="B173" t="n">
@@ -3636,7 +3642,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Chester</t>
+          <t>Chokis</t>
         </is>
       </c>
       <c r="B174" t="n">
@@ -3648,12 +3654,14 @@
       <c r="D174" t="n">
         <v>1</v>
       </c>
-      <c r="E174" t="inlineStr"/>
+      <c r="E174" t="n">
+        <v>11.44</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Bigelow</t>
+          <t>Cho Cho</t>
         </is>
       </c>
       <c r="B175" t="n">
@@ -3670,7 +3678,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Becky's</t>
+          <t>Chiefeez</t>
         </is>
       </c>
       <c r="B176" t="n">
@@ -3682,14 +3690,12 @@
       <c r="D176" t="n">
         <v>1</v>
       </c>
-      <c r="E176" t="n">
-        <v>19.37665392531608</v>
-      </c>
+      <c r="E176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Yasso</t>
+          <t>Chester</t>
         </is>
       </c>
       <c r="B177" t="n">
@@ -3706,7 +3712,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Cloverhill</t>
+          <t>Bigelow</t>
         </is>
       </c>
       <c r="B178" t="n">
@@ -3723,7 +3729,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Give &amp; Go</t>
+          <t>Becky's</t>
         </is>
       </c>
       <c r="B179" t="n">
@@ -3735,12 +3741,14 @@
       <c r="D179" t="n">
         <v>1</v>
       </c>
-      <c r="E179" t="inlineStr"/>
+      <c r="E179" t="n">
+        <v>19.37665392531608</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Sultana</t>
+          <t>Yasso</t>
         </is>
       </c>
       <c r="B180" t="n">
@@ -3752,14 +3760,12 @@
       <c r="D180" t="n">
         <v>1</v>
       </c>
-      <c r="E180" t="n">
-        <v>18.58472998137803</v>
-      </c>
+      <c r="E180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Stouffer's</t>
+          <t>El Corte Inglés</t>
         </is>
       </c>
       <c r="B181" t="n">
@@ -3772,13 +3778,13 @@
         <v>1</v>
       </c>
       <c r="E181" t="n">
-        <v>27.47380304721075</v>
+        <v>8.85</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Members Selection</t>
+          <t>Frito-Lay</t>
         </is>
       </c>
       <c r="B182" t="n">
@@ -3795,7 +3801,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Mcvitie'S</t>
+          <t>Sultana</t>
         </is>
       </c>
       <c r="B183" t="n">
@@ -3808,13 +3814,13 @@
         <v>1</v>
       </c>
       <c r="E183" t="n">
-        <v>37.62485187066193</v>
+        <v>18.58472998137803</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Ortega</t>
+          <t>Hollandia</t>
         </is>
       </c>
       <c r="B184" t="n">
@@ -3827,13 +3833,13 @@
         <v>1</v>
       </c>
       <c r="E184" t="n">
-        <v>10.91045974485786</v>
+        <v>52.34878150009826</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Oscar Mayer</t>
+          <t>Members Selection</t>
         </is>
       </c>
       <c r="B185" t="n">
@@ -3845,14 +3851,12 @@
       <c r="D185" t="n">
         <v>1</v>
       </c>
-      <c r="E185" t="n">
-        <v>21.70707121411719</v>
-      </c>
+      <c r="E185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Marie</t>
+          <t>Mcvitie'S</t>
         </is>
       </c>
       <c r="B186" t="n">
@@ -3864,12 +3868,14 @@
       <c r="D186" t="n">
         <v>1</v>
       </c>
-      <c r="E186" t="inlineStr"/>
+      <c r="E186" t="n">
+        <v>37.62485187066193</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Liga</t>
+          <t>Ortega</t>
         </is>
       </c>
       <c r="B187" t="n">
@@ -3882,13 +3888,13 @@
         <v>1</v>
       </c>
       <c r="E187" t="n">
-        <v>10.58305138091117</v>
+        <v>10.91045974485786</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>King's Hawaiian</t>
+          <t>Oscar Mayer</t>
         </is>
       </c>
       <c r="B188" t="n">
@@ -3900,12 +3906,14 @@
       <c r="D188" t="n">
         <v>1</v>
       </c>
-      <c r="E188" t="inlineStr"/>
+      <c r="E188" t="n">
+        <v>21.70707121411719</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Kimberley's Bakeshoppe</t>
+          <t>Marie</t>
         </is>
       </c>
       <c r="B189" t="n">
@@ -3922,7 +3930,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Pirucream</t>
+          <t>Liga</t>
         </is>
       </c>
       <c r="B190" t="n">
@@ -3935,13 +3943,13 @@
         <v>1</v>
       </c>
       <c r="E190" t="n">
-        <v>20.53625219611713</v>
+        <v>10.58305138091117</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Pirulin</t>
+          <t>King's Hawaiian</t>
         </is>
       </c>
       <c r="B191" t="n">
@@ -3958,7 +3966,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Jos Poell</t>
+          <t>Kimberley's Bakeshoppe</t>
         </is>
       </c>
       <c r="B192" t="n">
@@ -3970,14 +3978,12 @@
       <c r="D192" t="n">
         <v>1</v>
       </c>
-      <c r="E192" t="n">
-        <v>25.38795779019243</v>
-      </c>
+      <c r="E192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Post</t>
+          <t>Pirucream</t>
         </is>
       </c>
       <c r="B193" t="n">
@@ -3990,13 +3996,13 @@
         <v>1</v>
       </c>
       <c r="E193" t="n">
-        <v>7.51</v>
+        <v>20.53625219611713</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Hostess</t>
+          <t>Pirulin</t>
         </is>
       </c>
       <c r="B194" t="n">
@@ -4008,14 +4014,12 @@
       <c r="D194" t="n">
         <v>1</v>
       </c>
-      <c r="E194" t="n">
-        <v>20.82</v>
-      </c>
+      <c r="E194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Hollandia</t>
+          <t>Jos Poell</t>
         </is>
       </c>
       <c r="B195" t="n">
@@ -4028,13 +4032,13 @@
         <v>1</v>
       </c>
       <c r="E195" t="n">
-        <v>52.34878150009826</v>
+        <v>25.38795779019243</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Holiday</t>
+          <t>Post</t>
         </is>
       </c>
       <c r="B196" t="n">
@@ -4046,12 +4050,14 @@
       <c r="D196" t="n">
         <v>1</v>
       </c>
-      <c r="E196" t="inlineStr"/>
+      <c r="E196" t="n">
+        <v>7.51</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Reynolds</t>
+          <t>Hostess</t>
         </is>
       </c>
       <c r="B197" t="n">
@@ -4063,12 +4069,14 @@
       <c r="D197" t="n">
         <v>1</v>
       </c>
-      <c r="E197" t="inlineStr"/>
+      <c r="E197" t="n">
+        <v>20.82</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Highland</t>
+          <t>Holiday</t>
         </is>
       </c>
       <c r="B198" t="n">
@@ -4085,7 +4093,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Santitas</t>
+          <t>Stouffer's</t>
         </is>
       </c>
       <c r="B199" t="n">
@@ -4098,13 +4106,13 @@
         <v>1</v>
       </c>
       <c r="E199" t="n">
-        <v>23.62766194234949</v>
+        <v>27.47380304721075</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>HiPro</t>
+          <t>Reynolds</t>
         </is>
       </c>
       <c r="B200" t="n">
@@ -4121,7 +4129,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Hershey</t>
+          <t>Highland</t>
         </is>
       </c>
       <c r="B201" t="n">
@@ -4133,14 +4141,12 @@
       <c r="D201" t="n">
         <v>1</v>
       </c>
-      <c r="E201" t="n">
-        <v>19.07848055928269</v>
-      </c>
+      <c r="E201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Haribo</t>
+          <t>HiPro</t>
         </is>
       </c>
       <c r="B202" t="n">
@@ -4157,7 +4163,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Haagen Daz</t>
+          <t>Hershey</t>
         </is>
       </c>
       <c r="B203" t="n">
@@ -4169,12 +4175,14 @@
       <c r="D203" t="n">
         <v>1</v>
       </c>
-      <c r="E203" t="inlineStr"/>
+      <c r="E203" t="n">
+        <v>19.07848055928269</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Snickers</t>
+          <t>Santitas</t>
         </is>
       </c>
       <c r="B204" t="n">
@@ -4187,13 +4195,13 @@
         <v>1</v>
       </c>
       <c r="E204" t="n">
-        <v>40.99</v>
+        <v>23.62766194234949</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>HOL Foods</t>
+          <t>Haribo</t>
         </is>
       </c>
       <c r="B205" t="n">
@@ -4205,14 +4213,12 @@
       <c r="D205" t="n">
         <v>1</v>
       </c>
-      <c r="E205" t="n">
-        <v>14.42307692307692</v>
-      </c>
+      <c r="E205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Goldfish</t>
+          <t>Haagen Daz</t>
         </is>
       </c>
       <c r="B206" t="n">
@@ -4224,14 +4230,12 @@
       <c r="D206" t="n">
         <v>1</v>
       </c>
-      <c r="E206" t="n">
-        <v>15.39664804469274</v>
-      </c>
+      <c r="E206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Odorex</t>
+          <t>HOL Foods</t>
         </is>
       </c>
       <c r="B207" t="n">
@@ -4243,12 +4247,14 @@
       <c r="D207" t="n">
         <v>1</v>
       </c>
-      <c r="E207" t="inlineStr"/>
+      <c r="E207" t="n">
+        <v>14.42307692307692</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Frito-Lay</t>
+          <t>Goldfish</t>
         </is>
       </c>
       <c r="B208" t="n">
@@ -4260,24 +4266,98 @@
       <c r="D208" t="n">
         <v>1</v>
       </c>
-      <c r="E208" t="inlineStr"/>
+      <c r="E208" t="n">
+        <v>15.39664804469274</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
+          <t>Snickers</t>
+        </is>
+      </c>
+      <c r="B209" t="n">
+        <v>1</v>
+      </c>
+      <c r="C209" t="n">
+        <v>1</v>
+      </c>
+      <c r="D209" t="n">
+        <v>1</v>
+      </c>
+      <c r="E209" t="n">
+        <v>40.99</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Give &amp; Go</t>
+        </is>
+      </c>
+      <c r="B210" t="n">
+        <v>1</v>
+      </c>
+      <c r="C210" t="n">
+        <v>1</v>
+      </c>
+      <c r="D210" t="n">
+        <v>1</v>
+      </c>
+      <c r="E210" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Odorex</t>
+        </is>
+      </c>
+      <c r="B211" t="n">
+        <v>1</v>
+      </c>
+      <c r="C211" t="n">
+        <v>1</v>
+      </c>
+      <c r="D211" t="n">
+        <v>1</v>
+      </c>
+      <c r="E211" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Fit Crunch</t>
+        </is>
+      </c>
+      <c r="B212" t="n">
+        <v>1</v>
+      </c>
+      <c r="C212" t="n">
+        <v>1</v>
+      </c>
+      <c r="D212" t="n">
+        <v>1</v>
+      </c>
+      <c r="E212" t="n">
+        <v>61.6</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
           <t>Kraft</t>
         </is>
       </c>
-      <c r="B209" t="n">
-        <v>1</v>
-      </c>
-      <c r="C209" t="n">
-        <v>1</v>
-      </c>
-      <c r="D209" t="n">
-        <v>1</v>
-      </c>
-      <c r="E209" t="n">
+      <c r="B213" t="n">
+        <v>1</v>
+      </c>
+      <c r="C213" t="n">
+        <v>1</v>
+      </c>
+      <c r="D213" t="n">
+        <v>1</v>
+      </c>
+      <c r="E213" t="n">
         <v>9.264432029795158</v>
       </c>
     </row>
@@ -33124,7 +33204,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Quadratini</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -33203,17 +33283,17 @@
       <c r="AG168" t="inlineStr"/>
       <c r="AH168" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Quadratini</t>
         </is>
       </c>
       <c r="AI168" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Quadratini</t>
         </is>
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>unknown_galletas quadratini tiramisu loacker</t>
+          <t>quadratini_galletas quadratini tiramisu loacker</t>
         </is>
       </c>
       <c r="AK168" t="inlineStr">
@@ -33228,7 +33308,7 @@
       </c>
       <c r="AM168" t="inlineStr">
         <is>
-          <t>unknown_galletas quadratini tiramisu loacker_0.11</t>
+          <t>quadratini_galletas quadratini tiramisu loacker_0.11</t>
         </is>
       </c>
       <c r="AN168" t="n">
@@ -33242,7 +33322,7 @@
       </c>
       <c r="AQ168" t="inlineStr">
         <is>
-          <t>unknown_loacker_quadratini_tiramisu</t>
+          <t>quadratini_loacker_quadratini_tiramisu</t>
         </is>
       </c>
       <c r="AR168" t="n">
@@ -33299,7 +33379,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Quadratini</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -33378,17 +33458,17 @@
       <c r="AG169" t="inlineStr"/>
       <c r="AH169" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Quadratini</t>
         </is>
       </c>
       <c r="AI169" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Quadratini</t>
         </is>
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>unknown_galletas quadratini tiramisu loacker</t>
+          <t>quadratini_galletas quadratini tiramisu loacker</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
@@ -33403,7 +33483,7 @@
       </c>
       <c r="AM169" t="inlineStr">
         <is>
-          <t>unknown_galletas quadratini tiramisu loacker_0.11</t>
+          <t>quadratini_galletas quadratini tiramisu loacker_0.11</t>
         </is>
       </c>
       <c r="AN169" t="n">
@@ -33417,7 +33497,7 @@
       </c>
       <c r="AQ169" t="inlineStr">
         <is>
-          <t>unknown_loacker_quadratini_tiramisu</t>
+          <t>quadratini_loacker_quadratini_tiramisu</t>
         </is>
       </c>
       <c r="AR169" t="n">
@@ -44927,7 +45007,7 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Quadratini</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -45006,17 +45086,17 @@
       <c r="AG237" t="inlineStr"/>
       <c r="AH237" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Quadratini</t>
         </is>
       </c>
       <c r="AI237" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Quadratini</t>
         </is>
       </c>
       <c r="AJ237" t="inlineStr">
         <is>
-          <t>unknown_galletas quadratini cacao loacker</t>
+          <t>quadratini_galletas quadratini cacao loacker</t>
         </is>
       </c>
       <c r="AK237" t="inlineStr">
@@ -45031,7 +45111,7 @@
       </c>
       <c r="AM237" t="inlineStr">
         <is>
-          <t>unknown_galletas quadratini cacao loacker_0.12</t>
+          <t>quadratini_galletas quadratini cacao loacker_0.12</t>
         </is>
       </c>
       <c r="AN237" t="n">
@@ -45045,7 +45125,7 @@
       </c>
       <c r="AQ237" t="inlineStr">
         <is>
-          <t>unknown_cacao_loacker_quadratini</t>
+          <t>quadratini_cacao_loacker_quadratini</t>
         </is>
       </c>
       <c r="AR237" t="n">
@@ -45102,7 +45182,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Quadratini</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -45181,17 +45261,17 @@
       <c r="AG238" t="inlineStr"/>
       <c r="AH238" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Quadratini</t>
         </is>
       </c>
       <c r="AI238" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Quadratini</t>
         </is>
       </c>
       <c r="AJ238" t="inlineStr">
         <is>
-          <t>unknown_galletas quadratini cocoa milk loacker</t>
+          <t>quadratini_galletas quadratini cocoa milk loacker</t>
         </is>
       </c>
       <c r="AK238" t="inlineStr">
@@ -45206,7 +45286,7 @@
       </c>
       <c r="AM238" t="inlineStr">
         <is>
-          <t>unknown_galletas quadratini cocoa milk loacker_0.12</t>
+          <t>quadratini_galletas quadratini cocoa milk loacker_0.12</t>
         </is>
       </c>
       <c r="AN238" t="n">
@@ -45220,7 +45300,7 @@
       </c>
       <c r="AQ238" t="inlineStr">
         <is>
-          <t>unknown_cocoa_loacker_milk_quadratini</t>
+          <t>quadratini_cocoa_loacker_milk_quadratini</t>
         </is>
       </c>
       <c r="AR238" t="n">
@@ -45277,7 +45357,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Quadratini</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -45352,17 +45432,17 @@
       <c r="AG239" t="inlineStr"/>
       <c r="AH239" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Quadratini</t>
         </is>
       </c>
       <c r="AI239" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Quadratini</t>
         </is>
       </c>
       <c r="AJ239" t="inlineStr">
         <is>
-          <t>unknown_galletas quadratini coconut loacker</t>
+          <t>quadratini_galletas quadratini coconut loacker</t>
         </is>
       </c>
       <c r="AK239" t="inlineStr">
@@ -45377,7 +45457,7 @@
       </c>
       <c r="AM239" t="inlineStr">
         <is>
-          <t>unknown_galletas quadratini coconut loacker_0.12</t>
+          <t>quadratini_galletas quadratini coconut loacker_0.12</t>
         </is>
       </c>
       <c r="AN239" t="inlineStr"/>
@@ -45385,7 +45465,7 @@
       <c r="AP239" t="inlineStr"/>
       <c r="AQ239" t="inlineStr">
         <is>
-          <t>unknown_coconut_loacker_quadratini</t>
+          <t>quadratini_coconut_loacker_quadratini</t>
         </is>
       </c>
       <c r="AR239" t="n">
@@ -45442,7 +45522,7 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Quadratini</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -45521,17 +45601,17 @@
       <c r="AG240" t="inlineStr"/>
       <c r="AH240" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Quadratini</t>
         </is>
       </c>
       <c r="AI240" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Quadratini</t>
         </is>
       </c>
       <c r="AJ240" t="inlineStr">
         <is>
-          <t>unknown_galletas wafer quadratini napolitaner loacker</t>
+          <t>quadratini_galletas wafer quadratini napolitaner loacker</t>
         </is>
       </c>
       <c r="AK240" t="inlineStr">
@@ -45546,7 +45626,7 @@
       </c>
       <c r="AM240" t="inlineStr">
         <is>
-          <t>unknown_galletas wafer quadratini napolitaner loacker_0.12</t>
+          <t>quadratini_galletas wafer quadratini napolitaner loacker_0.12</t>
         </is>
       </c>
       <c r="AN240" t="n">
@@ -45560,7 +45640,7 @@
       </c>
       <c r="AQ240" t="inlineStr">
         <is>
-          <t>unknown_loacker_napolitaner_quadratini_wafer</t>
+          <t>quadratini_loacker_napolitaner_quadratini_wafer</t>
         </is>
       </c>
       <c r="AR240" t="n">
@@ -45617,7 +45697,7 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Quadratini</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -45696,17 +45776,17 @@
       <c r="AG241" t="inlineStr"/>
       <c r="AH241" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Quadratini</t>
         </is>
       </c>
       <c r="AI241" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Quadratini</t>
         </is>
       </c>
       <c r="AJ241" t="inlineStr">
         <is>
-          <t>unknown_galletas quadratini cocoa milk loacker</t>
+          <t>quadratini_galletas quadratini cocoa milk loacker</t>
         </is>
       </c>
       <c r="AK241" t="inlineStr">
@@ -45721,7 +45801,7 @@
       </c>
       <c r="AM241" t="inlineStr">
         <is>
-          <t>unknown_galletas quadratini cocoa milk loacker_0.12</t>
+          <t>quadratini_galletas quadratini cocoa milk loacker_0.12</t>
         </is>
       </c>
       <c r="AN241" t="n">
@@ -45735,7 +45815,7 @@
       </c>
       <c r="AQ241" t="inlineStr">
         <is>
-          <t>unknown_cocoa_loacker_milk_quadratini</t>
+          <t>quadratini_cocoa_loacker_milk_quadratini</t>
         </is>
       </c>
       <c r="AR241" t="n">
@@ -45792,7 +45872,7 @@
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Quadratini</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -45871,17 +45951,17 @@
       <c r="AG242" t="inlineStr"/>
       <c r="AH242" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Quadratini</t>
         </is>
       </c>
       <c r="AI242" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Quadratini</t>
         </is>
       </c>
       <c r="AJ242" t="inlineStr">
         <is>
-          <t>unknown_galletas quadratini cacao loacker</t>
+          <t>quadratini_galletas quadratini cacao loacker</t>
         </is>
       </c>
       <c r="AK242" t="inlineStr">
@@ -45896,7 +45976,7 @@
       </c>
       <c r="AM242" t="inlineStr">
         <is>
-          <t>unknown_galletas quadratini cacao loacker_0.12</t>
+          <t>quadratini_galletas quadratini cacao loacker_0.12</t>
         </is>
       </c>
       <c r="AN242" t="n">
@@ -45910,7 +45990,7 @@
       </c>
       <c r="AQ242" t="inlineStr">
         <is>
-          <t>unknown_cacao_loacker_quadratini</t>
+          <t>quadratini_cacao_loacker_quadratini</t>
         </is>
       </c>
       <c r="AR242" t="n">
@@ -45967,7 +46047,7 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Quadratini</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -46046,17 +46126,17 @@
       <c r="AG243" t="inlineStr"/>
       <c r="AH243" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Quadratini</t>
         </is>
       </c>
       <c r="AI243" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Quadratini</t>
         </is>
       </c>
       <c r="AJ243" t="inlineStr">
         <is>
-          <t>unknown_galletas wafer quadratini napolitaner loacker</t>
+          <t>quadratini_galletas wafer quadratini napolitaner loacker</t>
         </is>
       </c>
       <c r="AK243" t="inlineStr">
@@ -46071,7 +46151,7 @@
       </c>
       <c r="AM243" t="inlineStr">
         <is>
-          <t>unknown_galletas wafer quadratini napolitaner loacker_0.12</t>
+          <t>quadratini_galletas wafer quadratini napolitaner loacker_0.12</t>
         </is>
       </c>
       <c r="AN243" t="n">
@@ -46085,7 +46165,7 @@
       </c>
       <c r="AQ243" t="inlineStr">
         <is>
-          <t>unknown_loacker_napolitaner_quadratini_wafer</t>
+          <t>quadratini_loacker_napolitaner_quadratini_wafer</t>
         </is>
       </c>
       <c r="AR243" t="n">
@@ -46142,7 +46222,7 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Quadratini</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -46221,17 +46301,17 @@
       <c r="AG244" t="inlineStr"/>
       <c r="AH244" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Quadratini</t>
         </is>
       </c>
       <c r="AI244" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Quadratini</t>
         </is>
       </c>
       <c r="AJ244" t="inlineStr">
         <is>
-          <t>unknown_galletas wafer quadratini sabor a vainilla loacker</t>
+          <t>quadratini_galletas wafer quadratini sabor a vainilla loacker</t>
         </is>
       </c>
       <c r="AK244" t="inlineStr">
@@ -46246,7 +46326,7 @@
       </c>
       <c r="AM244" t="inlineStr">
         <is>
-          <t>unknown_galletas wafer quadratini sabor a vainilla loacker_0.12</t>
+          <t>quadratini_galletas wafer quadratini sabor a vainilla loacker_0.12</t>
         </is>
       </c>
       <c r="AN244" t="n">
@@ -46260,7 +46340,7 @@
       </c>
       <c r="AQ244" t="inlineStr">
         <is>
-          <t>unknown_loacker_quadratini_vainilla_wafer</t>
+          <t>quadratini_loacker_quadratini_vainilla_wafer</t>
         </is>
       </c>
       <c r="AR244" t="n">
@@ -46317,7 +46397,7 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Quadratini</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -46396,17 +46476,17 @@
       <c r="AG245" t="inlineStr"/>
       <c r="AH245" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Quadratini</t>
         </is>
       </c>
       <c r="AI245" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Quadratini</t>
         </is>
       </c>
       <c r="AJ245" t="inlineStr">
         <is>
-          <t>unknown_galletas wafer quadratini sabor a vainilla loacker</t>
+          <t>quadratini_galletas wafer quadratini sabor a vainilla loacker</t>
         </is>
       </c>
       <c r="AK245" t="inlineStr">
@@ -46421,7 +46501,7 @@
       </c>
       <c r="AM245" t="inlineStr">
         <is>
-          <t>unknown_galletas wafer quadratini sabor a vainilla loacker_0.12</t>
+          <t>quadratini_galletas wafer quadratini sabor a vainilla loacker_0.12</t>
         </is>
       </c>
       <c r="AN245" t="n">
@@ -46435,7 +46515,7 @@
       </c>
       <c r="AQ245" t="inlineStr">
         <is>
-          <t>unknown_loacker_quadratini_vainilla_wafer</t>
+          <t>quadratini_loacker_quadratini_vainilla_wafer</t>
         </is>
       </c>
       <c r="AR245" t="n">
@@ -48880,7 +48960,7 @@
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Quadratini</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -48955,17 +49035,17 @@
       <c r="AG260" t="inlineStr"/>
       <c r="AH260" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Quadratini</t>
         </is>
       </c>
       <c r="AI260" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Quadratini</t>
         </is>
       </c>
       <c r="AJ260" t="inlineStr">
         <is>
-          <t>unknown_galletas quadratini coconut loacker</t>
+          <t>quadratini_galletas quadratini coconut loacker</t>
         </is>
       </c>
       <c r="AK260" t="inlineStr">
@@ -48980,7 +49060,7 @@
       </c>
       <c r="AM260" t="inlineStr">
         <is>
-          <t>unknown_galletas quadratini coconut loacker_0.12</t>
+          <t>quadratini_galletas quadratini coconut loacker_0.12</t>
         </is>
       </c>
       <c r="AN260" t="inlineStr"/>
@@ -48988,7 +49068,7 @@
       <c r="AP260" t="inlineStr"/>
       <c r="AQ260" t="inlineStr">
         <is>
-          <t>unknown_coconut_loacker_quadratini</t>
+          <t>quadratini_coconut_loacker_quadratini</t>
         </is>
       </c>
       <c r="AR260" t="n">
@@ -53302,7 +53382,7 @@
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Royal Dansk</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
@@ -53381,17 +53461,17 @@
       <c r="AG286" t="inlineStr"/>
       <c r="AH286" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Royal Dansk</t>
         </is>
       </c>
       <c r="AI286" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Royal Dansk</t>
         </is>
       </c>
       <c r="AJ286" t="inlineStr">
         <is>
-          <t>unknown_galletas danesa royal dansk</t>
+          <t>royal dansk_galletas danesa royal dansk</t>
         </is>
       </c>
       <c r="AK286" t="inlineStr">
@@ -53406,7 +53486,7 @@
       </c>
       <c r="AM286" t="inlineStr">
         <is>
-          <t>unknown_galletas danesa royal dansk_0.34</t>
+          <t>royal dansk_galletas danesa royal dansk_0.34</t>
         </is>
       </c>
       <c r="AN286" t="n">
@@ -53420,7 +53500,7 @@
       </c>
       <c r="AQ286" t="inlineStr">
         <is>
-          <t>unknown_danesa_dansk_royal</t>
+          <t>royal dansk_danesa_dansk_royal</t>
         </is>
       </c>
       <c r="AR286" t="n">
@@ -53477,7 +53557,7 @@
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Royal Dansk</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
@@ -53556,17 +53636,17 @@
       <c r="AG287" t="inlineStr"/>
       <c r="AH287" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Royal Dansk</t>
         </is>
       </c>
       <c r="AI287" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Royal Dansk</t>
         </is>
       </c>
       <c r="AJ287" t="inlineStr">
         <is>
-          <t>unknown_galletas danesa royal dansk</t>
+          <t>royal dansk_galletas danesa royal dansk</t>
         </is>
       </c>
       <c r="AK287" t="inlineStr">
@@ -53581,7 +53661,7 @@
       </c>
       <c r="AM287" t="inlineStr">
         <is>
-          <t>unknown_galletas danesa royal dansk_0.34</t>
+          <t>royal dansk_galletas danesa royal dansk_0.34</t>
         </is>
       </c>
       <c r="AN287" t="n">
@@ -53595,7 +53675,7 @@
       </c>
       <c r="AQ287" t="inlineStr">
         <is>
-          <t>unknown_danesa_dansk_royal</t>
+          <t>royal dansk_danesa_dansk_royal</t>
         </is>
       </c>
       <c r="AR287" t="n">

--- a/streamlit_data/regional_insights.xlsx
+++ b/streamlit_data/regional_insights.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E213"/>
+  <dimension ref="A1:E226"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,39 +452,39 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>346</v>
+        <v>292</v>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E2" t="n">
-        <v>20.23741564522681</v>
+        <v>17.83393510147484</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E3" t="n">
-        <v>17.83393510147484</v>
+        <v>20.06214984603233</v>
       </c>
     </row>
     <row r="4">
@@ -604,39 +604,39 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Jumbo</t>
+          <t>Gamesa</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>62</v>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>17.84871204831632</v>
+        <v>14.41709677419355</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Gamesa</t>
+          <t>Jumbo</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>62</v>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E11" t="n">
-        <v>14.41709677419355</v>
+        <v>17.84871204831632</v>
       </c>
     </row>
     <row r="12">
@@ -775,45 +775,45 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>Dino</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>22.50885642478337</v>
+        <v>6.937857142857142</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Dino</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E20" t="n">
-        <v>6.937857142857142</v>
+        <v>22.29926448546671</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Fritolay</t>
+          <t>Sunshine Snacks</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -823,48 +823,48 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>24.18856987356913</v>
+        <v>20.92956623821305</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sunshine Snacks</t>
+          <t>Betty Crocker</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>35</v>
       </c>
       <c r="C22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>20.92956623821305</v>
+        <v>11.50905500557616</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Betty Crocker</t>
+          <t>Fritolay</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>35</v>
       </c>
       <c r="C23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D23" t="n">
         <v>3</v>
       </c>
       <c r="E23" t="n">
-        <v>11.50905500557616</v>
+        <v>24.18856987356913</v>
       </c>
     </row>
     <row r="24">
@@ -908,7 +908,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Ritz</t>
+          <t>Pringles</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -918,16 +918,16 @@
         <v>2</v>
       </c>
       <c r="D26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E26" t="n">
-        <v>12.2312637036403</v>
+        <v>30.43700668692141</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Pringles</t>
+          <t>Ritz</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -937,10 +937,10 @@
         <v>2</v>
       </c>
       <c r="D27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E27" t="n">
-        <v>30.43700668692141</v>
+        <v>12.2312637036403</v>
       </c>
     </row>
     <row r="28">
@@ -1022,39 +1022,39 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Old El Paso</t>
+          <t>Mi Trigo</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>23</v>
       </c>
       <c r="C32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" t="n">
         <v>2</v>
       </c>
-      <c r="D32" t="n">
-        <v>1</v>
-      </c>
       <c r="E32" t="n">
-        <v>13.455</v>
+        <v>7.637391304347826</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Mi Trigo</t>
+          <t>Old El Paso</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>23</v>
       </c>
       <c r="C33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E33" t="n">
-        <v>7.637391304347826</v>
+        <v>13.455</v>
       </c>
     </row>
     <row r="34">
@@ -1098,7 +1098,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>La Real</t>
+          <t>Princesa</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="E36" t="n">
-        <v>10.1025</v>
+        <v>3.588888888888889</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Princesa</t>
+          <t>La Real</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1130,13 +1130,13 @@
         <v>1</v>
       </c>
       <c r="E37" t="n">
-        <v>3.588888888888889</v>
+        <v>10.1025</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Pepperidge Farm</t>
+          <t>Pepin</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -1146,10 +1146,10 @@
         <v>1</v>
       </c>
       <c r="D38" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E38" t="n">
-        <v>19.8023205237686</v>
+        <v>3.923333333333334</v>
       </c>
     </row>
     <row r="39">
@@ -1193,7 +1193,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Pepin</t>
+          <t>Pepperidge Farm</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -1203,10 +1203,10 @@
         <v>1</v>
       </c>
       <c r="D41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E41" t="n">
-        <v>3.923333333333334</v>
+        <v>19.8023205237686</v>
       </c>
     </row>
     <row r="42">
@@ -1250,7 +1250,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Lenny &amp; Larry's</t>
+          <t>El Charrito</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -1260,16 +1260,16 @@
         <v>1</v>
       </c>
       <c r="D44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>26.45875</v>
+        <v>4.845</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>El Charrito</t>
+          <t>Lenny &amp; Larry's</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -1279,16 +1279,16 @@
         <v>1</v>
       </c>
       <c r="D45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>4.845</v>
+        <v>26.45875</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Pepperidge</t>
+          <t>La Libanesa</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -1298,11 +1298,9 @@
         <v>1</v>
       </c>
       <c r="D46" t="n">
-        <v>2</v>
-      </c>
-      <c r="E46" t="n">
-        <v>29.39239164449742</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="E46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1326,7 +1324,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>La Libanesa</t>
+          <t>Pepperidge</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -1336,52 +1334,54 @@
         <v>1</v>
       </c>
       <c r="D48" t="n">
-        <v>1</v>
-      </c>
-      <c r="E48" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="E48" t="n">
+        <v>29.39239164449742</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Devon</t>
+          <t>Crav'N</t>
         </is>
       </c>
       <c r="B49" t="n">
         <v>14</v>
       </c>
       <c r="C49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D49" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E49" t="n">
-        <v>9.404842870544091</v>
+        <v>20.64511696006157</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Crav'N</t>
+          <t>Devon</t>
         </is>
       </c>
       <c r="B50" t="n">
         <v>14</v>
       </c>
       <c r="C50" t="n">
+        <v>1</v>
+      </c>
+      <c r="D50" t="n">
         <v>2</v>
       </c>
-      <c r="D50" t="n">
-        <v>4</v>
-      </c>
       <c r="E50" t="n">
-        <v>20.64511696006157</v>
+        <v>9.404842870544091</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Wow</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -1391,16 +1391,16 @@
         <v>1</v>
       </c>
       <c r="D51" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E51" t="n">
-        <v>3.208571428571429</v>
+        <v>9.45857142857143</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Wala</t>
+          <t>Wasa</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -1410,16 +1410,16 @@
         <v>1</v>
       </c>
       <c r="D52" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E52" t="n">
-        <v>5.640000000000001</v>
+        <v>20.93163482244135</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Wasa</t>
+          <t>Wala</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -1429,16 +1429,16 @@
         <v>1</v>
       </c>
       <c r="D53" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E53" t="n">
-        <v>20.93163482244135</v>
+        <v>5.640000000000001</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Wow</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -1448,10 +1448,10 @@
         <v>1</v>
       </c>
       <c r="D54" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E54" t="n">
-        <v>9.45857142857143</v>
+        <v>3.208571428571429</v>
       </c>
     </row>
     <row r="55">
@@ -1476,7 +1476,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Quadratini</t>
+          <t>Sweet Ps</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -1489,7 +1489,7 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>25.69083333333333</v>
+        <v>15.17</v>
       </c>
     </row>
     <row r="57">
@@ -1514,39 +1514,39 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Shoon</t>
+          <t>Quadratini</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C58" t="n">
         <v>1</v>
       </c>
       <c r="D58" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E58" t="n">
-        <v>23.68495475113122</v>
+        <v>25.69083333333333</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Noel</t>
+          <t>Shoon</t>
         </is>
       </c>
       <c r="B59" t="n">
         <v>11</v>
       </c>
       <c r="C59" t="n">
+        <v>1</v>
+      </c>
+      <c r="D59" t="n">
         <v>2</v>
       </c>
-      <c r="D59" t="n">
-        <v>3</v>
-      </c>
       <c r="E59" t="n">
-        <v>19.31337392062075</v>
+        <v>23.68495475113122</v>
       </c>
     </row>
     <row r="60">
@@ -1571,20 +1571,20 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Doritos</t>
+          <t>Noel</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D61" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>20.25820736467665</v>
+        <v>19.31337392062075</v>
       </c>
     </row>
     <row r="62">
@@ -1626,26 +1626,26 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Pillsbury</t>
+          <t>Doritos</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C64" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D64" t="n">
         <v>2</v>
       </c>
       <c r="E64" t="n">
-        <v>7.764285714285714</v>
+        <v>20.25820736467665</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Siete</t>
+          <t>Pillsbury</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -1658,13 +1658,13 @@
         <v>2</v>
       </c>
       <c r="E65" t="n">
-        <v>35.46555757535778</v>
+        <v>7.764285714285714</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Cuetara</t>
+          <t>Festival</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -1677,13 +1677,13 @@
         <v>1</v>
       </c>
       <c r="E66" t="n">
-        <v>10.41222222222222</v>
+        <v>9.385016025641024</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Chips Ahoy</t>
+          <t>Siete</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -1693,39 +1693,39 @@
         <v>2</v>
       </c>
       <c r="D67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E67" t="n">
-        <v>12.99941707258641</v>
+        <v>35.46555757535778</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Festival</t>
+          <t>Chips Ahoy</t>
         </is>
       </c>
       <c r="B68" t="n">
         <v>9</v>
       </c>
       <c r="C68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D68" t="n">
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>9.385016025641024</v>
+        <v>12.99941707258641</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Eggo</t>
+          <t>Cuetara</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C69" t="n">
         <v>1</v>
@@ -1734,7 +1734,7 @@
         <v>1</v>
       </c>
       <c r="E69" t="n">
-        <v>14.6121807037156</v>
+        <v>10.41222222222222</v>
       </c>
     </row>
     <row r="70">
@@ -1757,7 +1757,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Member's Selection</t>
+          <t>Eggo</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -1767,35 +1767,35 @@
         <v>1</v>
       </c>
       <c r="D71" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>13.74</v>
+        <v>14.6121807037156</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Lavigne</t>
+          <t>Member's Selection</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C72" t="n">
         <v>1</v>
       </c>
       <c r="D72" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E72" t="n">
-        <v>9.161428571428571</v>
+        <v>13.74</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Kidsmania</t>
+          <t>Lavigne</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -1807,7 +1807,9 @@
       <c r="D73" t="n">
         <v>1</v>
       </c>
-      <c r="E73" t="inlineStr"/>
+      <c r="E73" t="n">
+        <v>9.161428571428571</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -1831,7 +1833,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Nature'S Own</t>
+          <t>Holsum</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -1844,13 +1846,13 @@
         <v>1</v>
       </c>
       <c r="E75" t="n">
-        <v>7.755714285714285</v>
+        <v>7.78</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Holsum</t>
+          <t>Biscotto</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -1860,16 +1862,16 @@
         <v>1</v>
       </c>
       <c r="D76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E76" t="n">
-        <v>7.78</v>
+        <v>25</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Golden</t>
+          <t>Nature'S Own</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -1879,14 +1881,16 @@
         <v>1</v>
       </c>
       <c r="D77" t="n">
-        <v>2</v>
-      </c>
-      <c r="E77" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E77" t="n">
+        <v>7.755714285714285</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Crich</t>
+          <t>Golden</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -1898,14 +1902,12 @@
       <c r="D78" t="n">
         <v>2</v>
       </c>
-      <c r="E78" t="n">
-        <v>13.94857142857143</v>
-      </c>
+      <c r="E78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Biscotto</t>
+          <t>Kidsmania</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -1915,37 +1917,37 @@
         <v>1</v>
       </c>
       <c r="D79" t="n">
-        <v>2</v>
-      </c>
-      <c r="E79" t="n">
-        <v>25</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="E79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Kugi</t>
+          <t>Crich</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C80" t="n">
         <v>1</v>
       </c>
       <c r="D80" t="n">
-        <v>1</v>
-      </c>
-      <c r="E80" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="E80" t="n">
+        <v>13.94857142857143</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Mr Bakewell</t>
+          <t>Ecovida</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C81" t="n">
         <v>1</v>
@@ -1953,12 +1955,14 @@
       <c r="D81" t="n">
         <v>1</v>
       </c>
-      <c r="E81" t="inlineStr"/>
+      <c r="E81" t="n">
+        <v>21.75714285714286</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Costa</t>
+          <t>Laurieri</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -1968,10 +1972,10 @@
         <v>1</v>
       </c>
       <c r="D82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E82" t="n">
-        <v>14.64666666666667</v>
+        <v>20.65978352354142</v>
       </c>
     </row>
     <row r="83">
@@ -1994,7 +1998,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Laurieri</t>
+          <t>Sunshine</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -2004,35 +2008,35 @@
         <v>1</v>
       </c>
       <c r="D84" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E84" t="n">
-        <v>20.65978352354142</v>
+        <v>9.488333333333333</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Schar</t>
+          <t>Costa</t>
         </is>
       </c>
       <c r="B85" t="n">
         <v>6</v>
       </c>
       <c r="C85" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D85" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E85" t="n">
-        <v>24.18904950998269</v>
+        <v>14.64666666666667</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Otis Spunkmeyer</t>
+          <t>Spongy</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -2042,33 +2046,35 @@
         <v>1</v>
       </c>
       <c r="D86" t="n">
-        <v>2</v>
-      </c>
-      <c r="E86" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E86" t="n">
+        <v>7.990000000000001</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Bisco Pan</t>
+          <t>Schar</t>
         </is>
       </c>
       <c r="B87" t="n">
         <v>6</v>
       </c>
       <c r="C87" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D87" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E87" t="n">
-        <v>5.82</v>
+        <v>24.18904950998269</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Sunshine</t>
+          <t>Kugi</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -2080,35 +2086,35 @@
       <c r="D88" t="n">
         <v>1</v>
       </c>
-      <c r="E88" t="n">
-        <v>9.488333333333333</v>
-      </c>
+      <c r="E88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Triskits</t>
+          <t>Bisco Pan</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C89" t="n">
         <v>1</v>
       </c>
       <c r="D89" t="n">
-        <v>1</v>
-      </c>
-      <c r="E89" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="E89" t="n">
+        <v>5.82</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Hosttes</t>
+          <t>Sheila G's</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C90" t="n">
         <v>1</v>
@@ -2117,89 +2123,83 @@
         <v>1</v>
       </c>
       <c r="E90" t="n">
-        <v>36.83418646645511</v>
+        <v>34.93</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Cheetos</t>
+          <t>Mr Bakewell</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C91" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D91" t="n">
         <v>1</v>
       </c>
-      <c r="E91" t="n">
-        <v>23.77550530709329</v>
-      </c>
+      <c r="E91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Kiss</t>
+          <t>Mandul</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C92" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D92" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E92" t="n">
-        <v>20.05506545869531</v>
+        <v>18.36833333333334</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Badia</t>
+          <t>Otis Spunkmeyer</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C93" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D93" t="n">
-        <v>1</v>
-      </c>
-      <c r="E93" t="n">
-        <v>28.56294367711628</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="E93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Bagel Bites</t>
+          <t>Merba</t>
         </is>
       </c>
       <c r="B94" t="n">
         <v>5</v>
       </c>
       <c r="C94" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D94" t="n">
         <v>1</v>
       </c>
-      <c r="E94" t="n">
-        <v>14.76764878866199</v>
-      </c>
+      <c r="E94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Tiffany</t>
+          <t>Stiratini</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -2211,67 +2211,69 @@
       <c r="D95" t="n">
         <v>1</v>
       </c>
-      <c r="E95" t="inlineStr"/>
+      <c r="E95" t="n">
+        <v>17.42078051958985</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Nutella</t>
+          <t>Tiffany</t>
         </is>
       </c>
       <c r="B96" t="n">
         <v>5</v>
       </c>
       <c r="C96" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D96" t="n">
         <v>1</v>
       </c>
-      <c r="E96" t="n">
-        <v>15.46996215078755</v>
-      </c>
+      <c r="E96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Merba</t>
+          <t>Bagel Bites</t>
         </is>
       </c>
       <c r="B97" t="n">
         <v>5</v>
       </c>
       <c r="C97" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D97" t="n">
         <v>1</v>
       </c>
-      <c r="E97" t="inlineStr"/>
+      <c r="E97" t="n">
+        <v>14.76764878866199</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Stiratini</t>
+          <t>Cheetos</t>
         </is>
       </c>
       <c r="B98" t="n">
         <v>5</v>
       </c>
       <c r="C98" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D98" t="n">
         <v>1</v>
       </c>
       <c r="E98" t="n">
-        <v>17.42078051958985</v>
+        <v>23.77550530709329</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>La Dulcerita</t>
+          <t>Triskits</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -2281,16 +2283,14 @@
         <v>1</v>
       </c>
       <c r="D99" t="n">
-        <v>2</v>
-      </c>
-      <c r="E99" t="n">
-        <v>14.22407288526729</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="E99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Bolletje</t>
+          <t>Hosttes</t>
         </is>
       </c>
       <c r="B100" t="n">
@@ -2300,168 +2300,166 @@
         <v>1</v>
       </c>
       <c r="D100" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E100" t="n">
-        <v>29.40549939726599</v>
+        <v>36.83418646645511</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Ovaltine</t>
+          <t>Bolletje</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C101" t="n">
         <v>1</v>
       </c>
       <c r="D101" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E101" t="n">
-        <v>19.9445103354795</v>
+        <v>29.40549939726599</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Milka</t>
+          <t>Over The Top</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C102" t="n">
         <v>1</v>
       </c>
       <c r="D102" t="n">
-        <v>2</v>
-      </c>
-      <c r="E102" t="n">
-        <v>29.0725</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="E102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Kinder</t>
+          <t>Nutella</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C103" t="n">
         <v>2</v>
       </c>
       <c r="D103" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E103" t="n">
-        <v>9.291503578576814</v>
+        <v>15.46996215078755</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Nestle</t>
+          <t>La Dulcerita</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C104" t="n">
         <v>1</v>
       </c>
       <c r="D104" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E104" t="n">
-        <v>41.70528266913809</v>
+        <v>14.22407288526729</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Stonefire</t>
+          <t>Kiss</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C105" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D105" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E105" t="n">
-        <v>16.92</v>
+        <v>20.05506545869531</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Herrs</t>
+          <t>Badia</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C106" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D106" t="n">
         <v>1</v>
       </c>
       <c r="E106" t="n">
-        <v>37.30902864926393</v>
+        <v>28.56294367711628</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Glutino</t>
+          <t>DBL</t>
         </is>
       </c>
       <c r="B107" t="n">
         <v>4</v>
       </c>
       <c r="C107" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D107" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E107" t="n">
-        <v>19.41435404641845</v>
+        <v>33.695</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Snyder’S</t>
+          <t>Kinder</t>
         </is>
       </c>
       <c r="B108" t="n">
         <v>4</v>
       </c>
       <c r="C108" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D108" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E108" t="n">
-        <v>21.8340355175269</v>
+        <v>9.291503578576814</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Keeber</t>
+          <t>Repeat</t>
         </is>
       </c>
       <c r="B109" t="n">
@@ -2471,35 +2469,35 @@
         <v>1</v>
       </c>
       <c r="D109" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E109" t="n">
-        <v>28.61772083892403</v>
+        <v>49.2325</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Takis</t>
+          <t>Dulcesol</t>
         </is>
       </c>
       <c r="B110" t="n">
         <v>4</v>
       </c>
       <c r="C110" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D110" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E110" t="n">
-        <v>41.86</v>
+        <v>6.916666666666667</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Dulcesol</t>
+          <t>Mestemacher</t>
         </is>
       </c>
       <c r="B111" t="n">
@@ -2512,34 +2510,36 @@
         <v>1</v>
       </c>
       <c r="E111" t="n">
-        <v>6.916666666666667</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Dux</t>
+          <t>Keeber</t>
         </is>
       </c>
       <c r="B112" t="n">
+        <v>4</v>
+      </c>
+      <c r="C112" t="n">
+        <v>1</v>
+      </c>
+      <c r="D112" t="n">
         <v>3</v>
       </c>
-      <c r="C112" t="n">
-        <v>1</v>
-      </c>
-      <c r="D112" t="n">
-        <v>1</v>
-      </c>
-      <c r="E112" t="inlineStr"/>
+      <c r="E112" t="n">
+        <v>28.61772083892403</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Van Der Meulen</t>
+          <t>Ovaltine</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C113" t="n">
         <v>1</v>
@@ -2548,17 +2548,17 @@
         <v>1</v>
       </c>
       <c r="E113" t="n">
-        <v>12.12155070255629</v>
+        <v>19.9445103354795</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Confetti</t>
+          <t>Herrs</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C114" t="n">
         <v>1</v>
@@ -2566,107 +2566,111 @@
       <c r="D114" t="n">
         <v>1</v>
       </c>
-      <c r="E114" t="inlineStr"/>
+      <c r="E114" t="n">
+        <v>37.30902864926393</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Crix</t>
+          <t>Takis</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C115" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D115" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E115" t="n">
-        <v>7.160318629656713</v>
+        <v>41.86</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Chobani</t>
+          <t>Milka</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C116" t="n">
         <v>1</v>
       </c>
       <c r="D116" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E116" t="n">
-        <v>25.58923192551497</v>
+        <v>29.0725</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Waitrose</t>
+          <t>BGourmet</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C117" t="n">
         <v>1</v>
       </c>
       <c r="D117" t="n">
-        <v>2</v>
-      </c>
-      <c r="E117" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E117" t="n">
+        <v>14.2425</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Stonefire</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C118" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D118" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E118" t="n">
-        <v>24.31600957701516</v>
+        <v>16.92</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Del-E</t>
+          <t>Green Is My Thing</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C119" t="n">
         <v>1</v>
       </c>
       <c r="D119" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Totino's</t>
+          <t>Snyder’S</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C120" t="n">
         <v>1</v>
@@ -2675,49 +2679,51 @@
         <v>1</v>
       </c>
       <c r="E120" t="n">
-        <v>10.85144743680014</v>
+        <v>21.8340355175269</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Elina</t>
+          <t>Glutino</t>
         </is>
       </c>
       <c r="B121" t="n">
+        <v>4</v>
+      </c>
+      <c r="C121" t="n">
+        <v>2</v>
+      </c>
+      <c r="D121" t="n">
         <v>3</v>
       </c>
-      <c r="C121" t="n">
-        <v>1</v>
-      </c>
-      <c r="D121" t="n">
-        <v>1</v>
-      </c>
       <c r="E121" t="n">
-        <v>35.07692932225363</v>
+        <v>19.41435404641845</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Flourish</t>
+          <t>Nestle</t>
         </is>
       </c>
       <c r="B122" t="n">
+        <v>4</v>
+      </c>
+      <c r="C122" t="n">
+        <v>1</v>
+      </c>
+      <c r="D122" t="n">
         <v>3</v>
       </c>
-      <c r="C122" t="n">
-        <v>1</v>
-      </c>
-      <c r="D122" t="n">
-        <v>1</v>
-      </c>
-      <c r="E122" t="inlineStr"/>
+      <c r="E122" t="n">
+        <v>41.70528266913809</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Chetos</t>
+          <t>Chobani</t>
         </is>
       </c>
       <c r="B123" t="n">
@@ -2729,12 +2735,14 @@
       <c r="D123" t="n">
         <v>1</v>
       </c>
-      <c r="E123" t="inlineStr"/>
+      <c r="E123" t="n">
+        <v>25.58923192551497</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Snyders</t>
+          <t>Verkade</t>
         </is>
       </c>
       <c r="B124" t="n">
@@ -2746,12 +2754,14 @@
       <c r="D124" t="n">
         <v>1</v>
       </c>
-      <c r="E124" t="inlineStr"/>
+      <c r="E124" t="n">
+        <v>13.51789778605421</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Roomboter</t>
+          <t>Van Der Meulen</t>
         </is>
       </c>
       <c r="B125" t="n">
@@ -2761,16 +2771,16 @@
         <v>1</v>
       </c>
       <c r="D125" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E125" t="n">
-        <v>16.70555144365191</v>
+        <v>12.12155070255629</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Pizkas</t>
+          <t>Waitrose</t>
         </is>
       </c>
       <c r="B126" t="n">
@@ -2780,16 +2790,14 @@
         <v>1</v>
       </c>
       <c r="D126" t="n">
-        <v>1</v>
-      </c>
-      <c r="E126" t="n">
-        <v>4.146666666666667</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="E126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Verkade</t>
+          <t>Elina</t>
         </is>
       </c>
       <c r="B127" t="n">
@@ -2802,36 +2810,34 @@
         <v>1</v>
       </c>
       <c r="E127" t="n">
-        <v>13.51789778605421</v>
+        <v>35.07692932225363</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Voortman</t>
+          <t>Del-E</t>
         </is>
       </c>
       <c r="B128" t="n">
+        <v>3</v>
+      </c>
+      <c r="C128" t="n">
+        <v>1</v>
+      </c>
+      <c r="D128" t="n">
         <v>2</v>
       </c>
-      <c r="C128" t="n">
-        <v>1</v>
-      </c>
-      <c r="D128" t="n">
-        <v>1</v>
-      </c>
-      <c r="E128" t="n">
-        <v>20.17345399698341</v>
-      </c>
+      <c r="E128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Werther’S</t>
+          <t>Confetti</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C129" t="n">
         <v>1</v>
@@ -2844,11 +2850,11 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Wheat Thins</t>
+          <t>Crix</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C130" t="n">
         <v>1</v>
@@ -2857,17 +2863,17 @@
         <v>1</v>
       </c>
       <c r="E130" t="n">
-        <v>8.979888962508067</v>
+        <v>7.160318629656713</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Willie</t>
+          <t>Pizkas</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C131" t="n">
         <v>1</v>
@@ -2875,35 +2881,37 @@
       <c r="D131" t="n">
         <v>1</v>
       </c>
-      <c r="E131" t="inlineStr"/>
+      <c r="E131" t="n">
+        <v>4.146666666666667</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Pico Bello</t>
+          <t>Town House</t>
         </is>
       </c>
       <c r="B132" t="n">
+        <v>3</v>
+      </c>
+      <c r="C132" t="n">
         <v>2</v>
       </c>
-      <c r="C132" t="n">
-        <v>1</v>
-      </c>
       <c r="D132" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E132" t="n">
-        <v>21.08728168019017</v>
+        <v>24.31600957701516</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Vigo</t>
+          <t>Chetos</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C133" t="n">
         <v>1</v>
@@ -2911,18 +2919,16 @@
       <c r="D133" t="n">
         <v>1</v>
       </c>
-      <c r="E133" t="n">
-        <v>9.433248720978664</v>
-      </c>
+      <c r="E133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Twix</t>
+          <t>Totino's</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C134" t="n">
         <v>1</v>
@@ -2931,36 +2937,36 @@
         <v>1</v>
       </c>
       <c r="E134" t="n">
-        <v>25.28014847471393</v>
+        <v>10.85144743680014</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Tuc</t>
+          <t>Roomboter</t>
         </is>
       </c>
       <c r="B135" t="n">
+        <v>3</v>
+      </c>
+      <c r="C135" t="n">
+        <v>1</v>
+      </c>
+      <c r="D135" t="n">
         <v>2</v>
       </c>
-      <c r="C135" t="n">
-        <v>1</v>
-      </c>
-      <c r="D135" t="n">
-        <v>1</v>
-      </c>
       <c r="E135" t="n">
-        <v>7.575418994413408</v>
+        <v>16.70555144365191</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Soldanza</t>
+          <t>Snyders</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C136" t="n">
         <v>1</v>
@@ -2973,11 +2979,11 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Sara Lee</t>
+          <t>Dux</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C137" t="n">
         <v>1</v>
@@ -2985,18 +2991,16 @@
       <c r="D137" t="n">
         <v>1</v>
       </c>
-      <c r="E137" t="n">
-        <v>24.085</v>
-      </c>
+      <c r="E137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Royal Dansk</t>
+          <t>Flourish</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C138" t="n">
         <v>1</v>
@@ -3004,14 +3008,12 @@
       <c r="D138" t="n">
         <v>1</v>
       </c>
-      <c r="E138" t="n">
-        <v>20.48</v>
-      </c>
+      <c r="E138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Ricola</t>
+          <t>Voortman</t>
         </is>
       </c>
       <c r="B139" t="n">
@@ -3024,13 +3026,13 @@
         <v>1</v>
       </c>
       <c r="E139" t="n">
-        <v>7.351955307262569</v>
+        <v>20.17345399698341</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Agua Vivo</t>
+          <t>Sara Lee</t>
         </is>
       </c>
       <c r="B140" t="n">
@@ -3043,13 +3045,13 @@
         <v>1</v>
       </c>
       <c r="E140" t="n">
-        <v>12.445</v>
+        <v>24.085</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>dollys</t>
+          <t>Willie</t>
         </is>
       </c>
       <c r="B141" t="n">
@@ -3061,14 +3063,12 @@
       <c r="D141" t="n">
         <v>1</v>
       </c>
-      <c r="E141" t="n">
-        <v>3.96</v>
-      </c>
+      <c r="E141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Cheez</t>
+          <t>Pico Bello</t>
         </is>
       </c>
       <c r="B142" t="n">
@@ -3080,12 +3080,14 @@
       <c r="D142" t="n">
         <v>1</v>
       </c>
-      <c r="E142" t="inlineStr"/>
+      <c r="E142" t="n">
+        <v>21.08728168019017</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>La Tortilla Factory</t>
+          <t>Wheat Thins</t>
         </is>
       </c>
       <c r="B143" t="n">
@@ -3098,13 +3100,13 @@
         <v>1</v>
       </c>
       <c r="E143" t="n">
-        <v>21.71</v>
+        <v>8.979888962508067</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Dairy</t>
+          <t>Ricola</t>
         </is>
       </c>
       <c r="B144" t="n">
@@ -3116,12 +3118,14 @@
       <c r="D144" t="n">
         <v>1</v>
       </c>
-      <c r="E144" t="inlineStr"/>
+      <c r="E144" t="n">
+        <v>7.351955307262569</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Hinged</t>
+          <t>Royal Dansk</t>
         </is>
       </c>
       <c r="B145" t="n">
@@ -3134,13 +3138,13 @@
         <v>1</v>
       </c>
       <c r="E145" t="n">
-        <v>1.907848055928269</v>
+        <v>20.48</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Dove</t>
+          <t>Vigo</t>
         </is>
       </c>
       <c r="B146" t="n">
@@ -3153,13 +3157,13 @@
         <v>1</v>
       </c>
       <c r="E146" t="n">
-        <v>10.95146340976004</v>
+        <v>9.433248720978664</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Glad</t>
+          <t>Werther’S</t>
         </is>
       </c>
       <c r="B147" t="n">
@@ -3176,7 +3180,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Cole´s</t>
+          <t>Soldanza</t>
         </is>
       </c>
       <c r="B148" t="n">
@@ -3188,14 +3192,12 @@
       <c r="D148" t="n">
         <v>1</v>
       </c>
-      <c r="E148" t="n">
-        <v>21.94025264317509</v>
-      </c>
+      <c r="E148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Crunchmaster</t>
+          <t>Tuc</t>
         </is>
       </c>
       <c r="B149" t="n">
@@ -3208,13 +3210,13 @@
         <v>1</v>
       </c>
       <c r="E149" t="n">
-        <v>51.37009840929231</v>
+        <v>7.575418994413408</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Knotts</t>
+          <t>Twix</t>
         </is>
       </c>
       <c r="B150" t="n">
@@ -3226,12 +3228,14 @@
       <c r="D150" t="n">
         <v>1</v>
       </c>
-      <c r="E150" t="inlineStr"/>
+      <c r="E150" t="n">
+        <v>25.28014847471393</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Lewis Bake Shop</t>
+          <t>Agua Vivo</t>
         </is>
       </c>
       <c r="B151" t="n">
@@ -3244,13 +3248,13 @@
         <v>1</v>
       </c>
       <c r="E151" t="n">
-        <v>5.189283551419543</v>
+        <v>12.445</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Can Can</t>
+          <t>dollys</t>
         </is>
       </c>
       <c r="B152" t="n">
@@ -3263,13 +3267,13 @@
         <v>1</v>
       </c>
       <c r="E152" t="n">
-        <v>3.915</v>
+        <v>3.96</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Bisco</t>
+          <t>Crunchmaster</t>
         </is>
       </c>
       <c r="B153" t="n">
@@ -3282,13 +3286,13 @@
         <v>1</v>
       </c>
       <c r="E153" t="n">
-        <v>19.215</v>
+        <v>51.37009840929231</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Mars</t>
+          <t>Danisha</t>
         </is>
       </c>
       <c r="B154" t="n">
@@ -3305,7 +3309,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Dried</t>
+          <t>Cole´s</t>
         </is>
       </c>
       <c r="B155" t="n">
@@ -3315,14 +3319,16 @@
         <v>1</v>
       </c>
       <c r="D155" t="n">
-        <v>2</v>
-      </c>
-      <c r="E155" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E155" t="n">
+        <v>21.94025264317509</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Beivita</t>
+          <t>Ita Abu</t>
         </is>
       </c>
       <c r="B156" t="n">
@@ -3334,14 +3340,12 @@
       <c r="D156" t="n">
         <v>1</v>
       </c>
-      <c r="E156" t="n">
-        <v>35.19230769230769</v>
-      </c>
+      <c r="E156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Hills</t>
+          <t>Hinged</t>
         </is>
       </c>
       <c r="B157" t="n">
@@ -3353,48 +3357,50 @@
       <c r="D157" t="n">
         <v>1</v>
       </c>
-      <c r="E157" t="inlineStr"/>
+      <c r="E157" t="n">
+        <v>1.907848055928269</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Ferrero</t>
+          <t>Gri Gri</t>
         </is>
       </c>
       <c r="B158" t="n">
         <v>2</v>
       </c>
       <c r="C158" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D158" t="n">
-        <v>2</v>
-      </c>
-      <c r="E158" t="n">
-        <v>48.37</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="E158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Nature Valley</t>
+          <t>Dove</t>
         </is>
       </c>
       <c r="B159" t="n">
         <v>2</v>
       </c>
       <c r="C159" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D159" t="n">
         <v>1</v>
       </c>
-      <c r="E159" t="inlineStr"/>
+      <c r="E159" t="n">
+        <v>10.95146340976004</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Danisha</t>
+          <t>Glad</t>
         </is>
       </c>
       <c r="B160" t="n">
@@ -3411,11 +3417,11 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Triscuit</t>
+          <t>Dairy</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C161" t="n">
         <v>1</v>
@@ -3423,18 +3429,16 @@
       <c r="D161" t="n">
         <v>1</v>
       </c>
-      <c r="E161" t="n">
-        <v>21.76632743949854</v>
-      </c>
+      <c r="E161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Nerds</t>
+          <t>Cheez</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C162" t="n">
         <v>1</v>
@@ -3447,11 +3451,11 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>DiGiorno</t>
+          <t>Knotts</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C163" t="n">
         <v>1</v>
@@ -3459,18 +3463,16 @@
       <c r="D163" t="n">
         <v>1</v>
       </c>
-      <c r="E163" t="n">
-        <v>14.25891435863968</v>
-      </c>
+      <c r="E163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Double Duty</t>
+          <t>La Tortilla Factory</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C164" t="n">
         <v>1</v>
@@ -3478,16 +3480,18 @@
       <c r="D164" t="n">
         <v>1</v>
       </c>
-      <c r="E164" t="inlineStr"/>
+      <c r="E164" t="n">
+        <v>21.71</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Toblerone</t>
+          <t>Lewis Bake Shop</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C165" t="n">
         <v>1</v>
@@ -3496,17 +3500,17 @@
         <v>1</v>
       </c>
       <c r="E165" t="n">
-        <v>14.42655274400263</v>
+        <v>5.189283551419543</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Ducales</t>
+          <t>Can Can</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C166" t="n">
         <v>1</v>
@@ -3515,17 +3519,17 @@
         <v>1</v>
       </c>
       <c r="E166" t="n">
-        <v>21.76632743949854</v>
+        <v>3.915</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Cusano´s</t>
+          <t>Bisco</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C167" t="n">
         <v>1</v>
@@ -3533,16 +3537,18 @@
       <c r="D167" t="n">
         <v>1</v>
       </c>
-      <c r="E167" t="inlineStr"/>
+      <c r="E167" t="n">
+        <v>19.215</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Vegefarm</t>
+          <t>Mars</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C168" t="n">
         <v>1</v>
@@ -3550,35 +3556,33 @@
       <c r="D168" t="n">
         <v>1</v>
       </c>
-      <c r="E168" t="n">
-        <v>27.42714334124026</v>
-      </c>
+      <c r="E168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Twizzlers</t>
+          <t>Dried</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C169" t="n">
         <v>1</v>
       </c>
       <c r="D169" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Cloverhill</t>
+          <t>Beivita</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C170" t="n">
         <v>1</v>
@@ -3586,19 +3590,21 @@
       <c r="D170" t="n">
         <v>1</v>
       </c>
-      <c r="E170" t="inlineStr"/>
+      <c r="E170" t="n">
+        <v>35.19230769230769</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Fernandes</t>
+          <t>Nature Valley</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C171" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D171" t="n">
         <v>1</v>
@@ -3608,11 +3614,11 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Chowmein</t>
+          <t>Hills</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C172" t="n">
         <v>1</v>
@@ -3625,24 +3631,26 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Choppers</t>
+          <t>Ferrero</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C173" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D173" t="n">
-        <v>1</v>
-      </c>
-      <c r="E173" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="E173" t="n">
+        <v>48.37</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Chokis</t>
+          <t>Triscuit</t>
         </is>
       </c>
       <c r="B174" t="n">
@@ -3655,13 +3663,13 @@
         <v>1</v>
       </c>
       <c r="E174" t="n">
-        <v>11.44</v>
+        <v>21.76632743949854</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Cho Cho</t>
+          <t>Odorex</t>
         </is>
       </c>
       <c r="B175" t="n">
@@ -3678,7 +3686,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Chiefeez</t>
+          <t>DiGiorno</t>
         </is>
       </c>
       <c r="B176" t="n">
@@ -3690,12 +3698,14 @@
       <c r="D176" t="n">
         <v>1</v>
       </c>
-      <c r="E176" t="inlineStr"/>
+      <c r="E176" t="n">
+        <v>14.25891435863968</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Chester</t>
+          <t>Double Duty</t>
         </is>
       </c>
       <c r="B177" t="n">
@@ -3712,7 +3722,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Bigelow</t>
+          <t>Ducales</t>
         </is>
       </c>
       <c r="B178" t="n">
@@ -3724,12 +3734,14 @@
       <c r="D178" t="n">
         <v>1</v>
       </c>
-      <c r="E178" t="inlineStr"/>
+      <c r="E178" t="n">
+        <v>21.76632743949854</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Becky's</t>
+          <t>El Corte Inglés</t>
         </is>
       </c>
       <c r="B179" t="n">
@@ -3742,13 +3754,13 @@
         <v>1</v>
       </c>
       <c r="E179" t="n">
-        <v>19.37665392531608</v>
+        <v>8.85</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Yasso</t>
+          <t>Toblerone</t>
         </is>
       </c>
       <c r="B180" t="n">
@@ -3760,12 +3772,14 @@
       <c r="D180" t="n">
         <v>1</v>
       </c>
-      <c r="E180" t="inlineStr"/>
+      <c r="E180" t="n">
+        <v>14.42655274400263</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>El Corte Inglés</t>
+          <t>Vegefarm</t>
         </is>
       </c>
       <c r="B181" t="n">
@@ -3778,13 +3792,13 @@
         <v>1</v>
       </c>
       <c r="E181" t="n">
-        <v>8.85</v>
+        <v>27.42714334124026</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Frito-Lay</t>
+          <t>Cusano´s</t>
         </is>
       </c>
       <c r="B182" t="n">
@@ -3801,7 +3815,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Sultana</t>
+          <t>Twizzlers</t>
         </is>
       </c>
       <c r="B183" t="n">
@@ -3813,14 +3827,12 @@
       <c r="D183" t="n">
         <v>1</v>
       </c>
-      <c r="E183" t="n">
-        <v>18.58472998137803</v>
-      </c>
+      <c r="E183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Hollandia</t>
+          <t>Cloverhill</t>
         </is>
       </c>
       <c r="B184" t="n">
@@ -3832,14 +3844,12 @@
       <c r="D184" t="n">
         <v>1</v>
       </c>
-      <c r="E184" t="n">
-        <v>52.34878150009826</v>
-      </c>
+      <c r="E184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Members Selection</t>
+          <t>Chowmein</t>
         </is>
       </c>
       <c r="B185" t="n">
@@ -3856,7 +3866,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Mcvitie'S</t>
+          <t>Choppers</t>
         </is>
       </c>
       <c r="B186" t="n">
@@ -3868,14 +3878,12 @@
       <c r="D186" t="n">
         <v>1</v>
       </c>
-      <c r="E186" t="n">
-        <v>37.62485187066193</v>
-      </c>
+      <c r="E186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Ortega</t>
+          <t>Chokis</t>
         </is>
       </c>
       <c r="B187" t="n">
@@ -3888,13 +3896,13 @@
         <v>1</v>
       </c>
       <c r="E187" t="n">
-        <v>10.91045974485786</v>
+        <v>11.44</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Oscar Mayer</t>
+          <t>Cho Cho</t>
         </is>
       </c>
       <c r="B188" t="n">
@@ -3906,14 +3914,12 @@
       <c r="D188" t="n">
         <v>1</v>
       </c>
-      <c r="E188" t="n">
-        <v>21.70707121411719</v>
-      </c>
+      <c r="E188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Marie</t>
+          <t>Chiefeez</t>
         </is>
       </c>
       <c r="B189" t="n">
@@ -3930,7 +3936,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Liga</t>
+          <t>Chester</t>
         </is>
       </c>
       <c r="B190" t="n">
@@ -3942,14 +3948,12 @@
       <c r="D190" t="n">
         <v>1</v>
       </c>
-      <c r="E190" t="n">
-        <v>10.58305138091117</v>
-      </c>
+      <c r="E190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>King's Hawaiian</t>
+          <t>Bigelow</t>
         </is>
       </c>
       <c r="B191" t="n">
@@ -3966,7 +3970,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Kimberley's Bakeshoppe</t>
+          <t>Becky's</t>
         </is>
       </c>
       <c r="B192" t="n">
@@ -3978,12 +3982,14 @@
       <c r="D192" t="n">
         <v>1</v>
       </c>
-      <c r="E192" t="inlineStr"/>
+      <c r="E192" t="n">
+        <v>19.37665392531608</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Pirucream</t>
+          <t>Yasso</t>
         </is>
       </c>
       <c r="B193" t="n">
@@ -3995,14 +4001,12 @@
       <c r="D193" t="n">
         <v>1</v>
       </c>
-      <c r="E193" t="n">
-        <v>20.53625219611713</v>
-      </c>
+      <c r="E193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Pirulin</t>
+          <t>Fernandes</t>
         </is>
       </c>
       <c r="B194" t="n">
@@ -4019,7 +4023,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Jos Poell</t>
+          <t>Give &amp; Go</t>
         </is>
       </c>
       <c r="B195" t="n">
@@ -4031,14 +4035,12 @@
       <c r="D195" t="n">
         <v>1</v>
       </c>
-      <c r="E195" t="n">
-        <v>25.38795779019243</v>
-      </c>
+      <c r="E195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Post</t>
+          <t>Sultana</t>
         </is>
       </c>
       <c r="B196" t="n">
@@ -4051,13 +4053,13 @@
         <v>1</v>
       </c>
       <c r="E196" t="n">
-        <v>7.51</v>
+        <v>18.58472998137803</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Hostess</t>
+          <t>Hollandia</t>
         </is>
       </c>
       <c r="B197" t="n">
@@ -4070,13 +4072,13 @@
         <v>1</v>
       </c>
       <c r="E197" t="n">
-        <v>20.82</v>
+        <v>52.34878150009826</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Holiday</t>
+          <t>Ortega</t>
         </is>
       </c>
       <c r="B198" t="n">
@@ -4088,12 +4090,14 @@
       <c r="D198" t="n">
         <v>1</v>
       </c>
-      <c r="E198" t="inlineStr"/>
+      <c r="E198" t="n">
+        <v>10.91045974485786</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Stouffer's</t>
+          <t>Oscar Mayer</t>
         </is>
       </c>
       <c r="B199" t="n">
@@ -4106,13 +4110,13 @@
         <v>1</v>
       </c>
       <c r="E199" t="n">
-        <v>27.47380304721075</v>
+        <v>21.70707121411719</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Reynolds</t>
+          <t>Members Selection</t>
         </is>
       </c>
       <c r="B200" t="n">
@@ -4129,7 +4133,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Highland</t>
+          <t>Mcvitie'S</t>
         </is>
       </c>
       <c r="B201" t="n">
@@ -4141,12 +4145,14 @@
       <c r="D201" t="n">
         <v>1</v>
       </c>
-      <c r="E201" t="inlineStr"/>
+      <c r="E201" t="n">
+        <v>37.62485187066193</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>HiPro</t>
+          <t>Marie</t>
         </is>
       </c>
       <c r="B202" t="n">
@@ -4163,7 +4169,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Hershey</t>
+          <t>Liga</t>
         </is>
       </c>
       <c r="B203" t="n">
@@ -4176,13 +4182,13 @@
         <v>1</v>
       </c>
       <c r="E203" t="n">
-        <v>19.07848055928269</v>
+        <v>10.58305138091117</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Santitas</t>
+          <t>Pirucream</t>
         </is>
       </c>
       <c r="B204" t="n">
@@ -4195,13 +4201,13 @@
         <v>1</v>
       </c>
       <c r="E204" t="n">
-        <v>23.62766194234949</v>
+        <v>20.53625219611713</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Haribo</t>
+          <t>Pirulin</t>
         </is>
       </c>
       <c r="B205" t="n">
@@ -4218,7 +4224,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Haagen Daz</t>
+          <t>King's Hawaiian</t>
         </is>
       </c>
       <c r="B206" t="n">
@@ -4235,7 +4241,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>HOL Foods</t>
+          <t>Post</t>
         </is>
       </c>
       <c r="B207" t="n">
@@ -4248,13 +4254,13 @@
         <v>1</v>
       </c>
       <c r="E207" t="n">
-        <v>14.42307692307692</v>
+        <v>7.51</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Goldfish</t>
+          <t>Kimberley's Bakeshoppe</t>
         </is>
       </c>
       <c r="B208" t="n">
@@ -4266,14 +4272,12 @@
       <c r="D208" t="n">
         <v>1</v>
       </c>
-      <c r="E208" t="n">
-        <v>15.39664804469274</v>
-      </c>
+      <c r="E208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Snickers</t>
+          <t>Jos Poell</t>
         </is>
       </c>
       <c r="B209" t="n">
@@ -4286,13 +4290,13 @@
         <v>1</v>
       </c>
       <c r="E209" t="n">
-        <v>40.99</v>
+        <v>25.38795779019243</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Give &amp; Go</t>
+          <t>Hostess</t>
         </is>
       </c>
       <c r="B210" t="n">
@@ -4304,12 +4308,14 @@
       <c r="D210" t="n">
         <v>1</v>
       </c>
-      <c r="E210" t="inlineStr"/>
+      <c r="E210" t="n">
+        <v>20.82</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Odorex</t>
+          <t>Reynolds</t>
         </is>
       </c>
       <c r="B211" t="n">
@@ -4326,7 +4332,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Fit Crunch</t>
+          <t>Stouffer's</t>
         </is>
       </c>
       <c r="B212" t="n">
@@ -4339,25 +4345,258 @@
         <v>1</v>
       </c>
       <c r="E212" t="n">
-        <v>61.6</v>
+        <v>27.47380304721075</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
+          <t>Holiday</t>
+        </is>
+      </c>
+      <c r="B213" t="n">
+        <v>1</v>
+      </c>
+      <c r="C213" t="n">
+        <v>1</v>
+      </c>
+      <c r="D213" t="n">
+        <v>1</v>
+      </c>
+      <c r="E213" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Highland</t>
+        </is>
+      </c>
+      <c r="B214" t="n">
+        <v>1</v>
+      </c>
+      <c r="C214" t="n">
+        <v>1</v>
+      </c>
+      <c r="D214" t="n">
+        <v>1</v>
+      </c>
+      <c r="E214" t="inlineStr"/>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Santitas</t>
+        </is>
+      </c>
+      <c r="B215" t="n">
+        <v>1</v>
+      </c>
+      <c r="C215" t="n">
+        <v>1</v>
+      </c>
+      <c r="D215" t="n">
+        <v>1</v>
+      </c>
+      <c r="E215" t="n">
+        <v>23.62766194234949</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>HiPro</t>
+        </is>
+      </c>
+      <c r="B216" t="n">
+        <v>1</v>
+      </c>
+      <c r="C216" t="n">
+        <v>1</v>
+      </c>
+      <c r="D216" t="n">
+        <v>1</v>
+      </c>
+      <c r="E216" t="inlineStr"/>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Hershey</t>
+        </is>
+      </c>
+      <c r="B217" t="n">
+        <v>1</v>
+      </c>
+      <c r="C217" t="n">
+        <v>1</v>
+      </c>
+      <c r="D217" t="n">
+        <v>1</v>
+      </c>
+      <c r="E217" t="n">
+        <v>19.07848055928269</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Haribo</t>
+        </is>
+      </c>
+      <c r="B218" t="n">
+        <v>1</v>
+      </c>
+      <c r="C218" t="n">
+        <v>1</v>
+      </c>
+      <c r="D218" t="n">
+        <v>1</v>
+      </c>
+      <c r="E218" t="inlineStr"/>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Haagen Daz</t>
+        </is>
+      </c>
+      <c r="B219" t="n">
+        <v>1</v>
+      </c>
+      <c r="C219" t="n">
+        <v>1</v>
+      </c>
+      <c r="D219" t="n">
+        <v>1</v>
+      </c>
+      <c r="E219" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>HOL Foods</t>
+        </is>
+      </c>
+      <c r="B220" t="n">
+        <v>1</v>
+      </c>
+      <c r="C220" t="n">
+        <v>1</v>
+      </c>
+      <c r="D220" t="n">
+        <v>1</v>
+      </c>
+      <c r="E220" t="n">
+        <v>14.42307692307692</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Snickers</t>
+        </is>
+      </c>
+      <c r="B221" t="n">
+        <v>1</v>
+      </c>
+      <c r="C221" t="n">
+        <v>1</v>
+      </c>
+      <c r="D221" t="n">
+        <v>1</v>
+      </c>
+      <c r="E221" t="n">
+        <v>40.99</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Goldfish</t>
+        </is>
+      </c>
+      <c r="B222" t="n">
+        <v>1</v>
+      </c>
+      <c r="C222" t="n">
+        <v>1</v>
+      </c>
+      <c r="D222" t="n">
+        <v>1</v>
+      </c>
+      <c r="E222" t="n">
+        <v>15.39664804469274</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Nerds</t>
+        </is>
+      </c>
+      <c r="B223" t="n">
+        <v>1</v>
+      </c>
+      <c r="C223" t="n">
+        <v>1</v>
+      </c>
+      <c r="D223" t="n">
+        <v>1</v>
+      </c>
+      <c r="E223" t="inlineStr"/>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Frito-Lay</t>
+        </is>
+      </c>
+      <c r="B224" t="n">
+        <v>1</v>
+      </c>
+      <c r="C224" t="n">
+        <v>1</v>
+      </c>
+      <c r="D224" t="n">
+        <v>1</v>
+      </c>
+      <c r="E224" t="inlineStr"/>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Fit Crunch</t>
+        </is>
+      </c>
+      <c r="B225" t="n">
+        <v>1</v>
+      </c>
+      <c r="C225" t="n">
+        <v>1</v>
+      </c>
+      <c r="D225" t="n">
+        <v>1</v>
+      </c>
+      <c r="E225" t="n">
+        <v>61.6</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
           <t>Kraft</t>
         </is>
       </c>
-      <c r="B213" t="n">
-        <v>1</v>
-      </c>
-      <c r="C213" t="n">
-        <v>1</v>
-      </c>
-      <c r="D213" t="n">
-        <v>1</v>
-      </c>
-      <c r="E213" t="n">
+      <c r="B226" t="n">
+        <v>1</v>
+      </c>
+      <c r="C226" t="n">
+        <v>1</v>
+      </c>
+      <c r="D226" t="n">
+        <v>1</v>
+      </c>
+      <c r="E226" t="n">
         <v>9.264432029795158</v>
       </c>
     </row>
@@ -9775,7 +10014,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Repeat</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -9854,17 +10093,17 @@
       <c r="AG29" t="inlineStr"/>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Repeat</t>
         </is>
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Repeat</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>unknown_galleta de avena vegan repeat</t>
+          <t>repeat_galleta de avena vegan repeat</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -9879,7 +10118,7 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>unknown_galleta de avena vegan repeat_0.04</t>
+          <t>repeat_galleta de avena vegan repeat_0.04</t>
         </is>
       </c>
       <c r="AN29" t="n">
@@ -9893,7 +10132,7 @@
       </c>
       <c r="AQ29" t="inlineStr">
         <is>
-          <t>unknown_avena_repeat_vegan</t>
+          <t>repeat_avena_repeat_vegan</t>
         </is>
       </c>
       <c r="AR29" t="n">
@@ -10115,7 +10354,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Repeat</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -10194,17 +10433,17 @@
       <c r="AG31" t="inlineStr"/>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Repeat</t>
         </is>
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Repeat</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>unknown_galleta de avena vegan repeat</t>
+          <t>repeat_galleta de avena vegan repeat</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -10219,7 +10458,7 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>unknown_galleta de avena vegan repeat_0.04</t>
+          <t>repeat_galleta de avena vegan repeat_0.04</t>
         </is>
       </c>
       <c r="AN31" t="n">
@@ -10233,7 +10472,7 @@
       </c>
       <c r="AQ31" t="inlineStr">
         <is>
-          <t>unknown_avena_repeat_vegan</t>
+          <t>repeat_avena_repeat_vegan</t>
         </is>
       </c>
       <c r="AR31" t="n">
@@ -12105,7 +12344,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>DBL</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -12184,17 +12423,17 @@
       <c r="AG43" t="inlineStr"/>
       <c r="AH43" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>DBL</t>
         </is>
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>DBL</t>
         </is>
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>unknown_galleta de chocolate chip vegana dbl</t>
+          <t>dbl_galleta de chocolate chip vegana dbl</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -12209,7 +12448,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>unknown_galleta de chocolate chip vegana dbl_0.07</t>
+          <t>dbl_galleta de chocolate chip vegana dbl_0.07</t>
         </is>
       </c>
       <c r="AN43" t="n">
@@ -12219,7 +12458,7 @@
       <c r="AP43" t="inlineStr"/>
       <c r="AQ43" t="inlineStr">
         <is>
-          <t>unknown_chip_chocolate_vegana</t>
+          <t>dbl_chip_chocolate_vegana</t>
         </is>
       </c>
       <c r="AR43" t="n">
@@ -12276,7 +12515,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>DBL</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -12355,17 +12594,17 @@
       <c r="AG44" t="inlineStr"/>
       <c r="AH44" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>DBL</t>
         </is>
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>DBL</t>
         </is>
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>unknown_galleta de chocolate chip vegana dbl</t>
+          <t>dbl_galleta de chocolate chip vegana dbl</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
@@ -12380,7 +12619,7 @@
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>unknown_galleta de chocolate chip vegana dbl_0.07</t>
+          <t>dbl_galleta de chocolate chip vegana dbl_0.07</t>
         </is>
       </c>
       <c r="AN44" t="n">
@@ -12390,7 +12629,7 @@
       <c r="AP44" t="inlineStr"/>
       <c r="AQ44" t="inlineStr">
         <is>
-          <t>unknown_chip_chocolate_vegana</t>
+          <t>dbl_chip_chocolate_vegana</t>
         </is>
       </c>
       <c r="AR44" t="n">
@@ -13129,7 +13368,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Repeat</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -13208,17 +13447,17 @@
       <c r="AG49" t="inlineStr"/>
       <c r="AH49" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Repeat</t>
         </is>
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Repeat</t>
         </is>
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>unknown_galleta de avena vegan repeat</t>
+          <t>repeat_galleta de avena vegan repeat</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -13233,7 +13472,7 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>unknown_galleta de avena vegan repeat_0.1</t>
+          <t>repeat_galleta de avena vegan repeat_0.1</t>
         </is>
       </c>
       <c r="AN49" t="n">
@@ -13247,7 +13486,7 @@
       </c>
       <c r="AQ49" t="inlineStr">
         <is>
-          <t>unknown_avena_repeat_vegan</t>
+          <t>repeat_avena_repeat_vegan</t>
         </is>
       </c>
       <c r="AR49" t="n">
@@ -13304,7 +13543,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Repeat</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -13383,17 +13622,17 @@
       <c r="AG50" t="inlineStr"/>
       <c r="AH50" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Repeat</t>
         </is>
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Repeat</t>
         </is>
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>unknown_galleta de avena vegan repeat</t>
+          <t>repeat_galleta de avena vegan repeat</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
@@ -13408,7 +13647,7 @@
       </c>
       <c r="AM50" t="inlineStr">
         <is>
-          <t>unknown_galleta de avena vegan repeat_0.1</t>
+          <t>repeat_galleta de avena vegan repeat_0.1</t>
         </is>
       </c>
       <c r="AN50" t="n">
@@ -13422,7 +13661,7 @@
       </c>
       <c r="AQ50" t="inlineStr">
         <is>
-          <t>unknown_avena_repeat_vegan</t>
+          <t>repeat_avena_repeat_vegan</t>
         </is>
       </c>
       <c r="AR50" t="n">
@@ -20239,7 +20478,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Sheila G's</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -20314,17 +20553,17 @@
       <c r="AG91" t="inlineStr"/>
       <c r="AH91" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Sheila G's</t>
         </is>
       </c>
       <c r="AI91" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Sheila G's</t>
         </is>
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>unknown_galletas brownie brittle dark chocolate sea salt sheila gs</t>
+          <t>sheila s_galletas brownie brittle dark chocolate sea salt sheila gs</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -20339,7 +20578,7 @@
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>unknown_galletas brownie brittle dark chocolate sea salt sheila gs_0.14</t>
+          <t>sheila s_galletas brownie brittle dark chocolate sea salt sheila gs_0.14</t>
         </is>
       </c>
       <c r="AN91" t="inlineStr"/>
@@ -20347,7 +20586,7 @@
       <c r="AP91" t="inlineStr"/>
       <c r="AQ91" t="inlineStr">
         <is>
-          <t>unknown_brittle_brownie_chocolate_dark</t>
+          <t>sheila s_brittle_brownie_chocolate_dark</t>
         </is>
       </c>
       <c r="AR91" t="n">
@@ -20404,7 +20643,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Sheila G's</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -20483,17 +20722,17 @@
       <c r="AG92" t="inlineStr"/>
       <c r="AH92" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Sheila G's</t>
         </is>
       </c>
       <c r="AI92" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Sheila G's</t>
         </is>
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>unknown_galletas brownie brittle chocolate chips sheila gs</t>
+          <t>sheila s_galletas brownie brittle chocolate chips sheila gs</t>
         </is>
       </c>
       <c r="AK92" t="inlineStr">
@@ -20508,7 +20747,7 @@
       </c>
       <c r="AM92" t="inlineStr">
         <is>
-          <t>unknown_galletas brownie brittle chocolate chips sheila gs_0.14</t>
+          <t>sheila s_galletas brownie brittle chocolate chips sheila gs_0.14</t>
         </is>
       </c>
       <c r="AN92" t="n">
@@ -20522,7 +20761,7 @@
       </c>
       <c r="AQ92" t="inlineStr">
         <is>
-          <t>unknown_brittle_brownie_chips_chocolate</t>
+          <t>sheila s_brittle_brownie_chips_chocolate</t>
         </is>
       </c>
       <c r="AR92" t="n">
@@ -20579,7 +20818,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Sheila G's</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -20654,17 +20893,17 @@
       <c r="AG93" t="inlineStr"/>
       <c r="AH93" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Sheila G's</t>
         </is>
       </c>
       <c r="AI93" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Sheila G's</t>
         </is>
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>unknown_galletas brownie brittle salted caramel sheila gs</t>
+          <t>sheila s_galletas brownie brittle salted caramel sheila gs</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -20679,7 +20918,7 @@
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>unknown_galletas brownie brittle salted caramel sheila gs_0.14</t>
+          <t>sheila s_galletas brownie brittle salted caramel sheila gs_0.14</t>
         </is>
       </c>
       <c r="AN93" t="inlineStr"/>
@@ -20687,7 +20926,7 @@
       <c r="AP93" t="inlineStr"/>
       <c r="AQ93" t="inlineStr">
         <is>
-          <t>unknown_brittle_brownie_caramel_salted</t>
+          <t>sheila s_brittle_brownie_caramel_salted</t>
         </is>
       </c>
       <c r="AR93" t="n">
@@ -23957,7 +24196,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Sheila G's</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -24036,17 +24275,17 @@
       <c r="AG113" t="inlineStr"/>
       <c r="AH113" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Sheila G's</t>
         </is>
       </c>
       <c r="AI113" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Sheila G's</t>
         </is>
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>unknown_galletas brownie brittle chocolate chips sheila gs</t>
+          <t>sheila s_galletas brownie brittle chocolate chips sheila gs</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -24061,7 +24300,7 @@
       </c>
       <c r="AM113" t="inlineStr">
         <is>
-          <t>unknown_galletas brownie brittle chocolate chips sheila gs_0.14</t>
+          <t>sheila s_galletas brownie brittle chocolate chips sheila gs_0.14</t>
         </is>
       </c>
       <c r="AN113" t="n">
@@ -24075,7 +24314,7 @@
       </c>
       <c r="AQ113" t="inlineStr">
         <is>
-          <t>unknown_brittle_brownie_chips_chocolate</t>
+          <t>sheila s_brittle_brownie_chips_chocolate</t>
         </is>
       </c>
       <c r="AR113" t="n">
@@ -24132,7 +24371,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Sheila G's</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -24207,17 +24446,17 @@
       <c r="AG114" t="inlineStr"/>
       <c r="AH114" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Sheila G's</t>
         </is>
       </c>
       <c r="AI114" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Sheila G's</t>
         </is>
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>unknown_galletas brownie brittle salted caramel sheila gs</t>
+          <t>sheila s_galletas brownie brittle salted caramel sheila gs</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
@@ -24232,7 +24471,7 @@
       </c>
       <c r="AM114" t="inlineStr">
         <is>
-          <t>unknown_galletas brownie brittle salted caramel sheila gs_0.14</t>
+          <t>sheila s_galletas brownie brittle salted caramel sheila gs_0.14</t>
         </is>
       </c>
       <c r="AN114" t="inlineStr"/>
@@ -24240,7 +24479,7 @@
       <c r="AP114" t="inlineStr"/>
       <c r="AQ114" t="inlineStr">
         <is>
-          <t>unknown_brittle_brownie_caramel_salted</t>
+          <t>sheila s_brittle_brownie_caramel_salted</t>
         </is>
       </c>
       <c r="AR114" t="n">
@@ -24297,7 +24536,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Sheila G's</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -24372,17 +24611,17 @@
       <c r="AG115" t="inlineStr"/>
       <c r="AH115" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Sheila G's</t>
         </is>
       </c>
       <c r="AI115" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Sheila G's</t>
         </is>
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>unknown_galletas brownie brittle dark chocolate sea salt sheila gs</t>
+          <t>sheila s_galletas brownie brittle dark chocolate sea salt sheila gs</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -24397,7 +24636,7 @@
       </c>
       <c r="AM115" t="inlineStr">
         <is>
-          <t>unknown_galletas brownie brittle dark chocolate sea salt sheila gs_0.14</t>
+          <t>sheila s_galletas brownie brittle dark chocolate sea salt sheila gs_0.14</t>
         </is>
       </c>
       <c r="AN115" t="inlineStr"/>
@@ -24405,7 +24644,7 @@
       <c r="AP115" t="inlineStr"/>
       <c r="AQ115" t="inlineStr">
         <is>
-          <t>unknown_brittle_brownie_chocolate_dark</t>
+          <t>sheila s_brittle_brownie_chocolate_dark</t>
         </is>
       </c>
       <c r="AR115" t="n">
@@ -46737,7 +46976,7 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>Ecovida</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -46816,17 +47055,17 @@
       <c r="AG247" t="inlineStr"/>
       <c r="AH247" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>Ecovida</t>
         </is>
       </c>
       <c r="AI247" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>Ecovida</t>
         </is>
       </c>
       <c r="AJ247" t="inlineStr">
         <is>
-          <t>lu_galleta de chocolate chips sin ecovida</t>
+          <t>ecovida_galleta de chocolate chips sin ecovida</t>
         </is>
       </c>
       <c r="AK247" t="inlineStr">
@@ -46841,7 +47080,7 @@
       </c>
       <c r="AM247" t="inlineStr">
         <is>
-          <t>lu_galleta de chocolate chips sin ecovida_0.15</t>
+          <t>ecovida_galleta de chocolate chips sin ecovida_0.15</t>
         </is>
       </c>
       <c r="AN247" t="n">
@@ -46855,7 +47094,7 @@
       </c>
       <c r="AQ247" t="inlineStr">
         <is>
-          <t>lu_chips_chocolate_ecovida</t>
+          <t>ecovida_chips_chocolate_ecovida</t>
         </is>
       </c>
       <c r="AR247" t="n">
@@ -46912,7 +47151,7 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>Ecovida</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -46991,17 +47230,17 @@
       <c r="AG248" t="inlineStr"/>
       <c r="AH248" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>Ecovida</t>
         </is>
       </c>
       <c r="AI248" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>Ecovida</t>
         </is>
       </c>
       <c r="AJ248" t="inlineStr">
         <is>
-          <t>lu_galleta ecovida sin coco</t>
+          <t>ecovida_galleta ecovida sin coco</t>
         </is>
       </c>
       <c r="AK248" t="inlineStr">
@@ -47016,7 +47255,7 @@
       </c>
       <c r="AM248" t="inlineStr">
         <is>
-          <t>lu_galleta ecovida sin coco_0.15</t>
+          <t>ecovida_galleta ecovida sin coco_0.15</t>
         </is>
       </c>
       <c r="AN248" t="n">
@@ -47030,7 +47269,7 @@
       </c>
       <c r="AQ248" t="inlineStr">
         <is>
-          <t>lu_coco_ecovida</t>
+          <t>ecovida_coco_ecovida</t>
         </is>
       </c>
       <c r="AR248" t="n">
@@ -47087,7 +47326,7 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>Ecovida</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -47166,17 +47405,17 @@
       <c r="AG249" t="inlineStr"/>
       <c r="AH249" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>Ecovida</t>
         </is>
       </c>
       <c r="AI249" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>Ecovida</t>
         </is>
       </c>
       <c r="AJ249" t="inlineStr">
         <is>
-          <t>lu_galleta sin berrie ecovida</t>
+          <t>ecovida_galleta sin berrie ecovida</t>
         </is>
       </c>
       <c r="AK249" t="inlineStr">
@@ -47191,7 +47430,7 @@
       </c>
       <c r="AM249" t="inlineStr">
         <is>
-          <t>lu_galleta sin berrie ecovida_0.15</t>
+          <t>ecovida_galleta sin berrie ecovida_0.15</t>
         </is>
       </c>
       <c r="AN249" t="n">
@@ -47205,7 +47444,7 @@
       </c>
       <c r="AQ249" t="inlineStr">
         <is>
-          <t>lu_berrie_ecovida</t>
+          <t>ecovida_berrie_ecovida</t>
         </is>
       </c>
       <c r="AR249" t="n">
@@ -51334,7 +51573,7 @@
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>Ecovida</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -51413,17 +51652,17 @@
       <c r="AG274" t="inlineStr"/>
       <c r="AH274" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>Ecovida</t>
         </is>
       </c>
       <c r="AI274" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>Ecovida</t>
         </is>
       </c>
       <c r="AJ274" t="inlineStr">
         <is>
-          <t>lu_galleta ecovida sin coco</t>
+          <t>ecovida_galleta ecovida sin coco</t>
         </is>
       </c>
       <c r="AK274" t="inlineStr">
@@ -51438,7 +51677,7 @@
       </c>
       <c r="AM274" t="inlineStr">
         <is>
-          <t>lu_galleta ecovida sin coco_0.15</t>
+          <t>ecovida_galleta ecovida sin coco_0.15</t>
         </is>
       </c>
       <c r="AN274" t="n">
@@ -51452,7 +51691,7 @@
       </c>
       <c r="AQ274" t="inlineStr">
         <is>
-          <t>lu_coco_ecovida</t>
+          <t>ecovida_coco_ecovida</t>
         </is>
       </c>
       <c r="AR274" t="n">
@@ -51509,7 +51748,7 @@
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>Ecovida</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
@@ -51588,17 +51827,17 @@
       <c r="AG275" t="inlineStr"/>
       <c r="AH275" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>Ecovida</t>
         </is>
       </c>
       <c r="AI275" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>Ecovida</t>
         </is>
       </c>
       <c r="AJ275" t="inlineStr">
         <is>
-          <t>lu_galleta sin berrie ecovida</t>
+          <t>ecovida_galleta sin berrie ecovida</t>
         </is>
       </c>
       <c r="AK275" t="inlineStr">
@@ -51613,7 +51852,7 @@
       </c>
       <c r="AM275" t="inlineStr">
         <is>
-          <t>lu_galleta sin berrie ecovida_0.15</t>
+          <t>ecovida_galleta sin berrie ecovida_0.15</t>
         </is>
       </c>
       <c r="AN275" t="n">
@@ -51627,7 +51866,7 @@
       </c>
       <c r="AQ275" t="inlineStr">
         <is>
-          <t>lu_berrie_ecovida</t>
+          <t>ecovida_berrie_ecovida</t>
         </is>
       </c>
       <c r="AR275" t="n">
@@ -55961,7 +56200,7 @@
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Sweet Ps</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
@@ -56040,17 +56279,17 @@
       <c r="AG301" t="inlineStr"/>
       <c r="AH301" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Sweet Ps</t>
         </is>
       </c>
       <c r="AI301" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Sweet Ps</t>
         </is>
       </c>
       <c r="AJ301" t="inlineStr">
         <is>
-          <t>unknown_mini brownies sweet ps</t>
+          <t>sweet ps_mini brownies sweet ps</t>
         </is>
       </c>
       <c r="AK301" t="inlineStr">
@@ -56065,7 +56304,7 @@
       </c>
       <c r="AM301" t="inlineStr">
         <is>
-          <t>unknown_mini brownies sweet ps_0.3</t>
+          <t>sweet ps_mini brownies sweet ps_0.3</t>
         </is>
       </c>
       <c r="AN301" t="n">
@@ -56079,7 +56318,7 @@
       </c>
       <c r="AQ301" t="inlineStr">
         <is>
-          <t>unknown_brownies_sweet</t>
+          <t>sweet ps_brownies_sweet</t>
         </is>
       </c>
       <c r="AR301" t="n">
@@ -56307,7 +56546,7 @@
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Sweet Ps</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
@@ -56386,17 +56625,17 @@
       <c r="AG303" t="inlineStr"/>
       <c r="AH303" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Sweet Ps</t>
         </is>
       </c>
       <c r="AI303" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Sweet Ps</t>
         </is>
       </c>
       <c r="AJ303" t="inlineStr">
         <is>
-          <t>unknown_mini brownies sweet ps</t>
+          <t>sweet ps_mini brownies sweet ps</t>
         </is>
       </c>
       <c r="AK303" t="inlineStr">
@@ -56411,7 +56650,7 @@
       </c>
       <c r="AM303" t="inlineStr">
         <is>
-          <t>unknown_mini brownies sweet ps_0.3</t>
+          <t>sweet ps_mini brownies sweet ps_0.3</t>
         </is>
       </c>
       <c r="AN303" t="n">
@@ -56425,7 +56664,7 @@
       </c>
       <c r="AQ303" t="inlineStr">
         <is>
-          <t>unknown_brownies_sweet</t>
+          <t>sweet ps_brownies_sweet</t>
         </is>
       </c>
       <c r="AR303" t="n">
@@ -56482,7 +56721,7 @@
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Mandul</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
@@ -56561,17 +56800,17 @@
       <c r="AG304" t="inlineStr"/>
       <c r="AH304" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Mandul</t>
         </is>
       </c>
       <c r="AI304" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Mandul</t>
         </is>
       </c>
       <c r="AJ304" t="inlineStr">
         <is>
-          <t>unknown_mini muffins choco chips mandul</t>
+          <t>mandul_mini muffins choco chips mandul</t>
         </is>
       </c>
       <c r="AK304" t="inlineStr">
@@ -56586,7 +56825,7 @@
       </c>
       <c r="AM304" t="inlineStr">
         <is>
-          <t>unknown_mini muffins choco chips mandul_0.2</t>
+          <t>mandul_mini muffins choco chips mandul_0.2</t>
         </is>
       </c>
       <c r="AN304" t="n">
@@ -56600,7 +56839,7 @@
       </c>
       <c r="AQ304" t="inlineStr">
         <is>
-          <t>unknown_chips_choco_mandul_muffins</t>
+          <t>mandul_chips_choco_mandul_muffins</t>
         </is>
       </c>
       <c r="AR304" t="n">
@@ -56828,7 +57067,7 @@
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Mandul</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
@@ -56907,17 +57146,17 @@
       <c r="AG306" t="inlineStr"/>
       <c r="AH306" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Mandul</t>
         </is>
       </c>
       <c r="AI306" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Mandul</t>
         </is>
       </c>
       <c r="AJ306" t="inlineStr">
         <is>
-          <t>unknown_mini muffins choco chips mandul</t>
+          <t>mandul_mini muffins choco chips mandul</t>
         </is>
       </c>
       <c r="AK306" t="inlineStr">
@@ -56932,7 +57171,7 @@
       </c>
       <c r="AM306" t="inlineStr">
         <is>
-          <t>unknown_mini muffins choco chips mandul_0.2</t>
+          <t>mandul_mini muffins choco chips mandul_0.2</t>
         </is>
       </c>
       <c r="AN306" t="n">
@@ -56946,7 +57185,7 @@
       </c>
       <c r="AQ306" t="inlineStr">
         <is>
-          <t>unknown_chips_choco_mandul_muffins</t>
+          <t>mandul_chips_choco_mandul_muffins</t>
         </is>
       </c>
       <c r="AR306" t="n">
@@ -57003,7 +57242,7 @@
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>DBL</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
@@ -57082,17 +57321,17 @@
       <c r="AG307" t="inlineStr"/>
       <c r="AH307" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>DBL</t>
         </is>
       </c>
       <c r="AI307" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>DBL</t>
         </is>
       </c>
       <c r="AJ307" t="inlineStr">
         <is>
-          <t>unknown_galleta de chocolate chip vegana dbl</t>
+          <t>dbl_galleta de chocolate chip vegana dbl</t>
         </is>
       </c>
       <c r="AK307" t="inlineStr">
@@ -57107,7 +57346,7 @@
       </c>
       <c r="AM307" t="inlineStr">
         <is>
-          <t>unknown_galleta de chocolate chip vegana dbl_0.34</t>
+          <t>dbl_galleta de chocolate chip vegana dbl_0.34</t>
         </is>
       </c>
       <c r="AN307" t="n">
@@ -57121,7 +57360,7 @@
       </c>
       <c r="AQ307" t="inlineStr">
         <is>
-          <t>unknown_chip_chocolate_vegana</t>
+          <t>dbl_chip_chocolate_vegana</t>
         </is>
       </c>
       <c r="AR307" t="n">
@@ -58023,7 +58262,7 @@
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>DBL</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
@@ -58102,17 +58341,17 @@
       <c r="AG313" t="inlineStr"/>
       <c r="AH313" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>DBL</t>
         </is>
       </c>
       <c r="AI313" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>DBL</t>
         </is>
       </c>
       <c r="AJ313" t="inlineStr">
         <is>
-          <t>unknown_galleta de chocolate chip vegana dbl</t>
+          <t>dbl_galleta de chocolate chip vegana dbl</t>
         </is>
       </c>
       <c r="AK313" t="inlineStr">
@@ -58127,7 +58366,7 @@
       </c>
       <c r="AM313" t="inlineStr">
         <is>
-          <t>unknown_galleta de chocolate chip vegana dbl_0.34</t>
+          <t>dbl_galleta de chocolate chip vegana dbl_0.34</t>
         </is>
       </c>
       <c r="AN313" t="n">
@@ -58141,7 +58380,7 @@
       </c>
       <c r="AQ313" t="inlineStr">
         <is>
-          <t>unknown_chip_chocolate_vegana</t>
+          <t>dbl_chip_chocolate_vegana</t>
         </is>
       </c>
       <c r="AR313" t="n">
@@ -60409,7 +60648,7 @@
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Mandul</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
@@ -60488,17 +60727,17 @@
       <c r="AG327" t="inlineStr"/>
       <c r="AH327" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Mandul</t>
         </is>
       </c>
       <c r="AI327" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Mandul</t>
         </is>
       </c>
       <c r="AJ327" t="inlineStr">
         <is>
-          <t>unknown_mini muffins rellenos de fresa mandul</t>
+          <t>mandul_mini muffins rellenos de fresa mandul</t>
         </is>
       </c>
       <c r="AK327" t="inlineStr">
@@ -60513,7 +60752,7 @@
       </c>
       <c r="AM327" t="inlineStr">
         <is>
-          <t>unknown_mini muffins rellenos de fresa mandul_0.21</t>
+          <t>mandul_mini muffins rellenos de fresa mandul_0.21</t>
         </is>
       </c>
       <c r="AN327" t="n">
@@ -60527,7 +60766,7 @@
       </c>
       <c r="AQ327" t="inlineStr">
         <is>
-          <t>unknown_fresa_mandul_muffins_rellenos</t>
+          <t>mandul_fresa_mandul_muffins_rellenos</t>
         </is>
       </c>
       <c r="AR327" t="n">
@@ -60584,7 +60823,7 @@
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Mandul</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
@@ -60663,17 +60902,17 @@
       <c r="AG328" t="inlineStr"/>
       <c r="AH328" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Mandul</t>
         </is>
       </c>
       <c r="AI328" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Mandul</t>
         </is>
       </c>
       <c r="AJ328" t="inlineStr">
         <is>
-          <t>unknown_mini muffins choco stars mandul</t>
+          <t>mandul_mini muffins choco stars mandul</t>
         </is>
       </c>
       <c r="AK328" t="inlineStr">
@@ -60688,7 +60927,7 @@
       </c>
       <c r="AM328" t="inlineStr">
         <is>
-          <t>unknown_mini muffins choco stars mandul_0.21</t>
+          <t>mandul_mini muffins choco stars mandul_0.21</t>
         </is>
       </c>
       <c r="AN328" t="n">
@@ -60702,7 +60941,7 @@
       </c>
       <c r="AQ328" t="inlineStr">
         <is>
-          <t>unknown_choco_mandul_muffins_stars</t>
+          <t>mandul_choco_mandul_muffins_stars</t>
         </is>
       </c>
       <c r="AR328" t="n">
@@ -61626,7 +61865,7 @@
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Mandul</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
@@ -61705,17 +61944,17 @@
       <c r="AG334" t="inlineStr"/>
       <c r="AH334" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Mandul</t>
         </is>
       </c>
       <c r="AI334" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Mandul</t>
         </is>
       </c>
       <c r="AJ334" t="inlineStr">
         <is>
-          <t>unknown_mini muffins choco stars mandul</t>
+          <t>mandul_mini muffins choco stars mandul</t>
         </is>
       </c>
       <c r="AK334" t="inlineStr">
@@ -61730,7 +61969,7 @@
       </c>
       <c r="AM334" t="inlineStr">
         <is>
-          <t>unknown_mini muffins choco stars mandul_0.21</t>
+          <t>mandul_mini muffins choco stars mandul_0.21</t>
         </is>
       </c>
       <c r="AN334" t="n">
@@ -61744,7 +61983,7 @@
       </c>
       <c r="AQ334" t="inlineStr">
         <is>
-          <t>unknown_choco_mandul_muffins_stars</t>
+          <t>mandul_choco_mandul_muffins_stars</t>
         </is>
       </c>
       <c r="AR334" t="n">
@@ -61801,7 +62040,7 @@
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Mandul</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
@@ -61880,17 +62119,17 @@
       <c r="AG335" t="inlineStr"/>
       <c r="AH335" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Mandul</t>
         </is>
       </c>
       <c r="AI335" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Mandul</t>
         </is>
       </c>
       <c r="AJ335" t="inlineStr">
         <is>
-          <t>unknown_mini muffins rellenos de fresa mandul</t>
+          <t>mandul_mini muffins rellenos de fresa mandul</t>
         </is>
       </c>
       <c r="AK335" t="inlineStr">
@@ -61905,7 +62144,7 @@
       </c>
       <c r="AM335" t="inlineStr">
         <is>
-          <t>unknown_mini muffins rellenos de fresa mandul_0.21</t>
+          <t>mandul_mini muffins rellenos de fresa mandul_0.21</t>
         </is>
       </c>
       <c r="AN335" t="n">
@@ -61919,7 +62158,7 @@
       </c>
       <c r="AQ335" t="inlineStr">
         <is>
-          <t>unknown_fresa_mandul_muffins_rellenos</t>
+          <t>mandul_fresa_mandul_muffins_rellenos</t>
         </is>
       </c>
       <c r="AR335" t="n">
@@ -62312,7 +62551,7 @@
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Sweet Ps</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
@@ -62391,17 +62630,17 @@
       <c r="AG338" t="inlineStr"/>
       <c r="AH338" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Sweet Ps</t>
         </is>
       </c>
       <c r="AI338" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Sweet Ps</t>
         </is>
       </c>
       <c r="AJ338" t="inlineStr">
         <is>
-          <t>unknown_cup cake de vainilla con chispas sweet ps</t>
+          <t>sweet ps_cup cake de vainilla con chispas sweet ps</t>
         </is>
       </c>
       <c r="AK338" t="inlineStr">
@@ -62416,7 +62655,7 @@
       </c>
       <c r="AM338" t="inlineStr">
         <is>
-          <t>unknown_cup cake de vainilla con chispas sweet ps_0.28</t>
+          <t>sweet ps_cup cake de vainilla con chispas sweet ps_0.28</t>
         </is>
       </c>
       <c r="AN338" t="n">
@@ -62430,7 +62669,7 @@
       </c>
       <c r="AQ338" t="inlineStr">
         <is>
-          <t>unknown_cake_chispas_sweet_vainilla</t>
+          <t>sweet ps_cake_chispas_sweet_vainilla</t>
         </is>
       </c>
       <c r="AR338" t="n">
@@ -62662,7 +62901,7 @@
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Sweet Ps</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
@@ -62741,17 +62980,17 @@
       <c r="AG340" t="inlineStr"/>
       <c r="AH340" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Sweet Ps</t>
         </is>
       </c>
       <c r="AI340" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Sweet Ps</t>
         </is>
       </c>
       <c r="AJ340" t="inlineStr">
         <is>
-          <t>unknown_cup cake de vainilla con chispas sweet ps</t>
+          <t>sweet ps_cup cake de vainilla con chispas sweet ps</t>
         </is>
       </c>
       <c r="AK340" t="inlineStr">
@@ -62766,7 +63005,7 @@
       </c>
       <c r="AM340" t="inlineStr">
         <is>
-          <t>unknown_cup cake de vainilla con chispas sweet ps_0.28</t>
+          <t>sweet ps_cup cake de vainilla con chispas sweet ps_0.28</t>
         </is>
       </c>
       <c r="AN340" t="n">
@@ -62780,7 +63019,7 @@
       </c>
       <c r="AQ340" t="inlineStr">
         <is>
-          <t>unknown_cake_chispas_sweet_vainilla</t>
+          <t>sweet ps_cake_chispas_sweet_vainilla</t>
         </is>
       </c>
       <c r="AR340" t="n">
@@ -64012,7 +64251,7 @@
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Ecovida</t>
         </is>
       </c>
       <c r="H348" t="inlineStr">
@@ -64091,17 +64330,17 @@
       <c r="AG348" t="inlineStr"/>
       <c r="AH348" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Ecovida</t>
         </is>
       </c>
       <c r="AI348" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Ecovida</t>
         </is>
       </c>
       <c r="AJ348" t="inlineStr">
         <is>
-          <t>unknown_galletas sin azucar rellenas de higo ecovida</t>
+          <t>ecovida_galletas sin azucar rellenas de higo ecovida</t>
         </is>
       </c>
       <c r="AK348" t="inlineStr">
@@ -64116,7 +64355,7 @@
       </c>
       <c r="AM348" t="inlineStr">
         <is>
-          <t>unknown_galletas sin azucar rellenas de higo ecovida_0.15</t>
+          <t>ecovida_galletas sin azucar rellenas de higo ecovida_0.15</t>
         </is>
       </c>
       <c r="AN348" t="n">
@@ -64130,7 +64369,7 @@
       </c>
       <c r="AQ348" t="inlineStr">
         <is>
-          <t>unknown_azucar_ecovida_higo_rellenas</t>
+          <t>ecovida_azucar_ecovida_higo_rellenas</t>
         </is>
       </c>
       <c r="AR348" t="n">
@@ -71934,7 +72173,7 @@
       </c>
       <c r="G394" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Ecovida</t>
         </is>
       </c>
       <c r="H394" t="inlineStr">
@@ -72013,17 +72252,17 @@
       <c r="AG394" t="inlineStr"/>
       <c r="AH394" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Ecovida</t>
         </is>
       </c>
       <c r="AI394" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Ecovida</t>
         </is>
       </c>
       <c r="AJ394" t="inlineStr">
         <is>
-          <t>unknown_galletas sin azucar rellenas de higo ecovida</t>
+          <t>ecovida_galletas sin azucar rellenas de higo ecovida</t>
         </is>
       </c>
       <c r="AK394" t="inlineStr">
@@ -72038,7 +72277,7 @@
       </c>
       <c r="AM394" t="inlineStr">
         <is>
-          <t>unknown_galletas sin azucar rellenas de higo ecovida_0.15</t>
+          <t>ecovida_galletas sin azucar rellenas de higo ecovida_0.15</t>
         </is>
       </c>
       <c r="AN394" t="n">
@@ -72052,7 +72291,7 @@
       </c>
       <c r="AQ394" t="inlineStr">
         <is>
-          <t>unknown_azucar_ecovida_higo_rellenas</t>
+          <t>ecovida_azucar_ecovida_higo_rellenas</t>
         </is>
       </c>
       <c r="AR394" t="n">
@@ -72109,7 +72348,7 @@
       </c>
       <c r="G395" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>BGourmet</t>
         </is>
       </c>
       <c r="H395" t="inlineStr">
@@ -72184,17 +72423,17 @@
       <c r="AG395" t="inlineStr"/>
       <c r="AH395" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>BGourmet</t>
         </is>
       </c>
       <c r="AI395" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>BGourmet</t>
         </is>
       </c>
       <c r="AJ395" t="inlineStr">
         <is>
-          <t>unknown_pan brioche chocolatechip bgourmet</t>
+          <t>bgourmet_pan brioche chocolatechip bgourmet</t>
         </is>
       </c>
       <c r="AK395" t="inlineStr">
@@ -72209,7 +72448,7 @@
       </c>
       <c r="AM395" t="inlineStr">
         <is>
-          <t>unknown_pan brioche chocolatechip bgourmet_0.4</t>
+          <t>bgourmet_pan brioche chocolatechip bgourmet_0.4</t>
         </is>
       </c>
       <c r="AN395" t="inlineStr"/>
@@ -72217,7 +72456,7 @@
       <c r="AP395" t="inlineStr"/>
       <c r="AQ395" t="inlineStr">
         <is>
-          <t>unknown_bgourmet_brioche_chocolatechip</t>
+          <t>bgourmet_bgourmet_brioche_chocolatechip</t>
         </is>
       </c>
       <c r="AR395" t="n">
@@ -72274,7 +72513,7 @@
       </c>
       <c r="G396" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>BGourmet</t>
         </is>
       </c>
       <c r="H396" t="inlineStr">
@@ -72349,17 +72588,17 @@
       <c r="AG396" t="inlineStr"/>
       <c r="AH396" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>BGourmet</t>
         </is>
       </c>
       <c r="AI396" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>BGourmet</t>
         </is>
       </c>
       <c r="AJ396" t="inlineStr">
         <is>
-          <t>unknown_pan brioche chocolatechip bgourmet</t>
+          <t>bgourmet_pan brioche chocolatechip bgourmet</t>
         </is>
       </c>
       <c r="AK396" t="inlineStr">
@@ -72374,7 +72613,7 @@
       </c>
       <c r="AM396" t="inlineStr">
         <is>
-          <t>unknown_pan brioche chocolatechip bgourmet_0.4</t>
+          <t>bgourmet_pan brioche chocolatechip bgourmet_0.4</t>
         </is>
       </c>
       <c r="AN396" t="inlineStr"/>
@@ -72382,7 +72621,7 @@
       <c r="AP396" t="inlineStr"/>
       <c r="AQ396" t="inlineStr">
         <is>
-          <t>unknown_bgourmet_brioche_chocolatechip</t>
+          <t>bgourmet_bgourmet_brioche_chocolatechip</t>
         </is>
       </c>
       <c r="AR396" t="n">
@@ -75549,7 +75788,7 @@
       </c>
       <c r="G415" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>BGourmet</t>
         </is>
       </c>
       <c r="H415" t="inlineStr">
@@ -75628,17 +75867,17 @@
       <c r="AG415" t="inlineStr"/>
       <c r="AH415" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>BGourmet</t>
         </is>
       </c>
       <c r="AI415" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>BGourmet</t>
         </is>
       </c>
       <c r="AJ415" t="inlineStr">
         <is>
-          <t>unknown_pan brioche lonjeado bgourmet</t>
+          <t>bgourmet_pan brioche lonjeado bgourmet</t>
         </is>
       </c>
       <c r="AK415" t="inlineStr">
@@ -75653,7 +75892,7 @@
       </c>
       <c r="AM415" t="inlineStr">
         <is>
-          <t>unknown_pan brioche lonjeado bgourmet_0.5</t>
+          <t>bgourmet_pan brioche lonjeado bgourmet_0.5</t>
         </is>
       </c>
       <c r="AN415" t="n">
@@ -75663,7 +75902,7 @@
       <c r="AP415" t="inlineStr"/>
       <c r="AQ415" t="inlineStr">
         <is>
-          <t>unknown_bgourmet_brioche_lonjeado</t>
+          <t>bgourmet_bgourmet_brioche_lonjeado</t>
         </is>
       </c>
       <c r="AR415" t="n">
@@ -76068,7 +76307,7 @@
       </c>
       <c r="G418" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>BGourmet</t>
         </is>
       </c>
       <c r="H418" t="inlineStr">
@@ -76147,17 +76386,17 @@
       <c r="AG418" t="inlineStr"/>
       <c r="AH418" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>BGourmet</t>
         </is>
       </c>
       <c r="AI418" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>BGourmet</t>
         </is>
       </c>
       <c r="AJ418" t="inlineStr">
         <is>
-          <t>unknown_pan brioche lonjeado bgourmet</t>
+          <t>bgourmet_pan brioche lonjeado bgourmet</t>
         </is>
       </c>
       <c r="AK418" t="inlineStr">
@@ -76172,7 +76411,7 @@
       </c>
       <c r="AM418" t="inlineStr">
         <is>
-          <t>unknown_pan brioche lonjeado bgourmet_0.5</t>
+          <t>bgourmet_pan brioche lonjeado bgourmet_0.5</t>
         </is>
       </c>
       <c r="AN418" t="n">
@@ -76182,7 +76421,7 @@
       <c r="AP418" t="inlineStr"/>
       <c r="AQ418" t="inlineStr">
         <is>
-          <t>unknown_bgourmet_brioche_lonjeado</t>
+          <t>bgourmet_bgourmet_brioche_lonjeado</t>
         </is>
       </c>
       <c r="AR418" t="n">

--- a/streamlit_data/regional_insights.xlsx
+++ b/streamlit_data/regional_insights.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E226"/>
+  <dimension ref="A1:E247"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>285</v>
+        <v>216</v>
       </c>
       <c r="C3" t="n">
         <v>3</v>
@@ -484,7 +484,7 @@
         <v>6</v>
       </c>
       <c r="E3" t="n">
-        <v>20.06214984603233</v>
+        <v>20.36031592181287</v>
       </c>
     </row>
     <row r="4">
@@ -642,39 +642,39 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Instorebakery</t>
+          <t>Hatuey</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>56</v>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>20.54408949352927</v>
+        <v>4.617555555555556</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Hatuey</t>
+          <t>Instorebakery</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>56</v>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E13" t="n">
-        <v>4.617555555555556</v>
+        <v>20.54408949352927</v>
       </c>
     </row>
     <row r="14">
@@ -813,7 +813,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sunshine Snacks</t>
+          <t>Fritolay</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -823,48 +823,48 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E21" t="n">
-        <v>20.92956623821305</v>
+        <v>24.18856987356913</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Betty Crocker</t>
+          <t>Sunshine Snacks</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>35</v>
       </c>
       <c r="C22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E22" t="n">
-        <v>11.50905500557616</v>
+        <v>20.92956623821305</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Fritolay</t>
+          <t>Betty Crocker</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>35</v>
       </c>
       <c r="C23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D23" t="n">
         <v>3</v>
       </c>
       <c r="E23" t="n">
-        <v>24.18856987356913</v>
+        <v>11.50905500557616</v>
       </c>
     </row>
     <row r="24">
@@ -1136,7 +1136,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Pepin</t>
+          <t>Pepperidge Farm</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -1146,29 +1146,29 @@
         <v>1</v>
       </c>
       <c r="D38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E38" t="n">
-        <v>3.923333333333334</v>
+        <v>19.8023205237686</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Bauducco</t>
+          <t>Pepin</t>
         </is>
       </c>
       <c r="B39" t="n">
         <v>18</v>
       </c>
       <c r="C39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D39" t="n">
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>14.2729343508003</v>
+        <v>3.923333333333334</v>
       </c>
     </row>
     <row r="40">
@@ -1193,20 +1193,20 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Pepperidge Farm</t>
+          <t>Bauducco</t>
         </is>
       </c>
       <c r="B41" t="n">
         <v>18</v>
       </c>
       <c r="C41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E41" t="n">
-        <v>19.8023205237686</v>
+        <v>14.2729343508003</v>
       </c>
     </row>
     <row r="42">
@@ -1250,7 +1250,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>El Charrito</t>
+          <t>Lenny &amp; Larry's</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -1260,16 +1260,16 @@
         <v>1</v>
       </c>
       <c r="D44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E44" t="n">
-        <v>4.845</v>
+        <v>26.45875</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Lenny &amp; Larry's</t>
+          <t>El Charrito</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -1279,10 +1279,10 @@
         <v>1</v>
       </c>
       <c r="D45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E45" t="n">
-        <v>26.45875</v>
+        <v>4.845</v>
       </c>
     </row>
     <row r="46">
@@ -1305,7 +1305,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Charles</t>
+          <t>Pepperidge</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -1315,16 +1315,16 @@
         <v>1</v>
       </c>
       <c r="D47" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E47" t="n">
-        <v>19.27125506072875</v>
+        <v>29.39239164449742</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Pepperidge</t>
+          <t>Charles</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -1334,10 +1334,10 @@
         <v>1</v>
       </c>
       <c r="D48" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E48" t="n">
-        <v>29.39239164449742</v>
+        <v>19.27125506072875</v>
       </c>
     </row>
     <row r="49">
@@ -1381,7 +1381,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Wow</t>
+          <t>Wasa</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -1391,16 +1391,16 @@
         <v>1</v>
       </c>
       <c r="D51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>9.45857142857143</v>
+        <v>20.93163482244135</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Wasa</t>
+          <t>Wala</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -1410,16 +1410,16 @@
         <v>1</v>
       </c>
       <c r="D52" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E52" t="n">
-        <v>20.93163482244135</v>
+        <v>5.640000000000001</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Wala</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -1429,16 +1429,16 @@
         <v>1</v>
       </c>
       <c r="D53" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E53" t="n">
-        <v>5.640000000000001</v>
+        <v>3.208571428571429</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Wow</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -1448,16 +1448,16 @@
         <v>1</v>
       </c>
       <c r="D54" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E54" t="n">
-        <v>3.208571428571429</v>
+        <v>9.45857142857143</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Bergen</t>
+          <t>Quadratini</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -1470,13 +1470,13 @@
         <v>1</v>
       </c>
       <c r="E55" t="n">
-        <v>11.83083333333333</v>
+        <v>25.69083333333333</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sweet Ps</t>
+          <t>Bergen</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -1489,7 +1489,7 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>15.17</v>
+        <v>11.83083333333333</v>
       </c>
     </row>
     <row r="57">
@@ -1514,7 +1514,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Quadratini</t>
+          <t>Sweet Ps</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -1527,26 +1527,26 @@
         <v>1</v>
       </c>
       <c r="E58" t="n">
-        <v>25.69083333333333</v>
+        <v>15.17</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Shoon</t>
+          <t>Noel</t>
         </is>
       </c>
       <c r="B59" t="n">
         <v>11</v>
       </c>
       <c r="C59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D59" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E59" t="n">
-        <v>23.68495475113122</v>
+        <v>19.31337392062075</v>
       </c>
     </row>
     <row r="60">
@@ -1571,20 +1571,20 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Noel</t>
+          <t>Shoon</t>
         </is>
       </c>
       <c r="B61" t="n">
         <v>11</v>
       </c>
       <c r="C61" t="n">
+        <v>1</v>
+      </c>
+      <c r="D61" t="n">
         <v>2</v>
       </c>
-      <c r="D61" t="n">
-        <v>3</v>
-      </c>
       <c r="E61" t="n">
-        <v>19.31337392062075</v>
+        <v>23.68495475113122</v>
       </c>
     </row>
     <row r="62">
@@ -1607,7 +1607,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Keebler</t>
+          <t>Doritos</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -1620,13 +1620,13 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>16.53</v>
+        <v>20.25820736467665</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Doritos</t>
+          <t>Keebler</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -1639,13 +1639,13 @@
         <v>2</v>
       </c>
       <c r="E64" t="n">
-        <v>20.25820736467665</v>
+        <v>16.53</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Pillsbury</t>
+          <t>Siete</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -1658,13 +1658,13 @@
         <v>2</v>
       </c>
       <c r="E65" t="n">
-        <v>7.764285714285714</v>
+        <v>35.46555757535778</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Festival</t>
+          <t>Bon</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -1677,87 +1677,89 @@
         <v>1</v>
       </c>
       <c r="E66" t="n">
-        <v>9.385016025641024</v>
+        <v>13.77</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Siete</t>
+          <t>Festival</t>
         </is>
       </c>
       <c r="B67" t="n">
         <v>9</v>
       </c>
       <c r="C67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E67" t="n">
-        <v>35.46555757535778</v>
+        <v>9.385016025641024</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Chips Ahoy</t>
+          <t>Cuetara</t>
         </is>
       </c>
       <c r="B68" t="n">
         <v>9</v>
       </c>
       <c r="C68" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D68" t="n">
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>12.99941707258641</v>
+        <v>10.41222222222222</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Cuetara</t>
+          <t>Pillsbury</t>
         </is>
       </c>
       <c r="B69" t="n">
         <v>9</v>
       </c>
       <c r="C69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>10.41222222222222</v>
+        <v>7.764285714285714</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Biskitop</t>
+          <t>Chips Ahoy</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D70" t="n">
-        <v>2</v>
-      </c>
-      <c r="E70" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E70" t="n">
+        <v>12.99941707258641</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Eggo</t>
+          <t>Biskitop</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -1767,16 +1769,14 @@
         <v>1</v>
       </c>
       <c r="D71" t="n">
-        <v>1</v>
-      </c>
-      <c r="E71" t="n">
-        <v>14.6121807037156</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="E71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Member's Selection</t>
+          <t>Renata</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -1786,54 +1786,54 @@
         <v>1</v>
       </c>
       <c r="D72" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>13.74</v>
+        <v>5.76</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Lavigne</t>
+          <t>Member's Selection</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C73" t="n">
         <v>1</v>
       </c>
       <c r="D73" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>9.161428571428571</v>
+        <v>13.74</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Walkers</t>
+          <t>Eggo</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C74" t="n">
         <v>1</v>
       </c>
       <c r="D74" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>97.43589743589745</v>
+        <v>14.6121807037156</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Holsum</t>
+          <t>Lavigne</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -1846,13 +1846,13 @@
         <v>1</v>
       </c>
       <c r="E75" t="n">
-        <v>7.78</v>
+        <v>9.161428571428571</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Biscotto</t>
+          <t>Holsum</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -1862,16 +1862,16 @@
         <v>1</v>
       </c>
       <c r="D76" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E76" t="n">
-        <v>25</v>
+        <v>7.78</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Nature'S Own</t>
+          <t>Ecovida</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -1884,13 +1884,13 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>7.755714285714285</v>
+        <v>21.75714285714286</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Golden</t>
+          <t>Nature'S Own</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -1900,9 +1900,11 @@
         <v>1</v>
       </c>
       <c r="D78" t="n">
-        <v>2</v>
-      </c>
-      <c r="E78" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E78" t="n">
+        <v>7.755714285714285</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -1924,7 +1926,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Crich</t>
+          <t>Walkers</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -1937,13 +1939,13 @@
         <v>2</v>
       </c>
       <c r="E80" t="n">
-        <v>13.94857142857143</v>
+        <v>97.43589743589745</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Ecovida</t>
+          <t>Mamut</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -1956,17 +1958,17 @@
         <v>1</v>
       </c>
       <c r="E81" t="n">
-        <v>21.75714285714286</v>
+        <v>15.69</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Laurieri</t>
+          <t>Biscotto</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C82" t="n">
         <v>1</v>
@@ -1975,17 +1977,17 @@
         <v>2</v>
       </c>
       <c r="E82" t="n">
-        <v>20.65978352354142</v>
+        <v>25</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Cadbury</t>
+          <t>Crich</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C83" t="n">
         <v>1</v>
@@ -1993,50 +1995,50 @@
       <c r="D83" t="n">
         <v>2</v>
       </c>
-      <c r="E83" t="inlineStr"/>
+      <c r="E83" t="n">
+        <v>13.94857142857143</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Sunshine</t>
+          <t>Golden</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C84" t="n">
         <v>1</v>
       </c>
       <c r="D84" t="n">
-        <v>1</v>
-      </c>
-      <c r="E84" t="n">
-        <v>9.488333333333333</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="E84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Costa</t>
+          <t>Schar</t>
         </is>
       </c>
       <c r="B85" t="n">
         <v>6</v>
       </c>
       <c r="C85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D85" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>14.64666666666667</v>
+        <v>24.18904950998269</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Spongy</t>
+          <t>Sheila G's</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -2049,32 +2051,32 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>7.990000000000001</v>
+        <v>34.93</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Schar</t>
+          <t>Costa</t>
         </is>
       </c>
       <c r="B87" t="n">
         <v>6</v>
       </c>
       <c r="C87" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D87" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E87" t="n">
-        <v>24.18904950998269</v>
+        <v>14.64666666666667</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Kugi</t>
+          <t>Mandul</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -2086,12 +2088,14 @@
       <c r="D88" t="n">
         <v>1</v>
       </c>
-      <c r="E88" t="inlineStr"/>
+      <c r="E88" t="n">
+        <v>18.36833333333334</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Bisco Pan</t>
+          <t>Kugi</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -2101,16 +2105,14 @@
         <v>1</v>
       </c>
       <c r="D89" t="n">
-        <v>2</v>
-      </c>
-      <c r="E89" t="n">
-        <v>5.82</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="E89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Sheila G's</t>
+          <t>Otis Spunkmeyer</t>
         </is>
       </c>
       <c r="B90" t="n">
@@ -2120,16 +2122,14 @@
         <v>1</v>
       </c>
       <c r="D90" t="n">
-        <v>1</v>
-      </c>
-      <c r="E90" t="n">
-        <v>34.93</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="E90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Mr Bakewell</t>
+          <t>Bisco Pan</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -2139,14 +2139,16 @@
         <v>1</v>
       </c>
       <c r="D91" t="n">
-        <v>1</v>
-      </c>
-      <c r="E91" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="E91" t="n">
+        <v>5.82</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Mandul</t>
+          <t>Spongy</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -2159,13 +2161,13 @@
         <v>1</v>
       </c>
       <c r="E92" t="n">
-        <v>18.36833333333334</v>
+        <v>7.990000000000001</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Otis Spunkmeyer</t>
+          <t>Laurieri</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -2177,16 +2179,18 @@
       <c r="D93" t="n">
         <v>2</v>
       </c>
-      <c r="E93" t="inlineStr"/>
+      <c r="E93" t="n">
+        <v>20.65978352354142</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Merba</t>
+          <t>Mr Bakewell</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C94" t="n">
         <v>1</v>
@@ -2199,30 +2203,28 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Stiratini</t>
+          <t>Cadbury</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C95" t="n">
         <v>1</v>
       </c>
       <c r="D95" t="n">
-        <v>1</v>
-      </c>
-      <c r="E95" t="n">
-        <v>17.42078051958985</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="E95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Tiffany</t>
+          <t>Sunshine</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C96" t="n">
         <v>1</v>
@@ -2230,50 +2232,48 @@
       <c r="D96" t="n">
         <v>1</v>
       </c>
-      <c r="E96" t="inlineStr"/>
+      <c r="E96" t="n">
+        <v>9.488333333333333</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Bagel Bites</t>
+          <t>Over The Top</t>
         </is>
       </c>
       <c r="B97" t="n">
         <v>5</v>
       </c>
       <c r="C97" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D97" t="n">
         <v>1</v>
       </c>
-      <c r="E97" t="n">
-        <v>14.76764878866199</v>
-      </c>
+      <c r="E97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Cheetos</t>
+          <t>Merba</t>
         </is>
       </c>
       <c r="B98" t="n">
         <v>5</v>
       </c>
       <c r="C98" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D98" t="n">
         <v>1</v>
       </c>
-      <c r="E98" t="n">
-        <v>23.77550530709329</v>
-      </c>
+      <c r="E98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Triskits</t>
+          <t>Hosttes</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -2285,31 +2285,33 @@
       <c r="D99" t="n">
         <v>1</v>
       </c>
-      <c r="E99" t="inlineStr"/>
+      <c r="E99" t="n">
+        <v>36.83418646645511</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Hosttes</t>
+          <t>Kiss</t>
         </is>
       </c>
       <c r="B100" t="n">
         <v>5</v>
       </c>
       <c r="C100" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D100" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E100" t="n">
-        <v>36.83418646645511</v>
+        <v>20.05506545869531</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Bolletje</t>
+          <t>La Dulcerita</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -2322,49 +2324,51 @@
         <v>2</v>
       </c>
       <c r="E101" t="n">
-        <v>29.40549939726599</v>
+        <v>14.22407288526729</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Over The Top</t>
+          <t>Nutella</t>
         </is>
       </c>
       <c r="B102" t="n">
         <v>5</v>
       </c>
       <c r="C102" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D102" t="n">
         <v>1</v>
       </c>
-      <c r="E102" t="inlineStr"/>
+      <c r="E102" t="n">
+        <v>15.46996215078755</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Nutella</t>
+          <t>Badia</t>
         </is>
       </c>
       <c r="B103" t="n">
         <v>5</v>
       </c>
       <c r="C103" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D103" t="n">
         <v>1</v>
       </c>
       <c r="E103" t="n">
-        <v>15.46996215078755</v>
+        <v>28.56294367711628</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>La Dulcerita</t>
+          <t>Triskits</t>
         </is>
       </c>
       <c r="B104" t="n">
@@ -2374,58 +2378,54 @@
         <v>1</v>
       </c>
       <c r="D104" t="n">
-        <v>2</v>
-      </c>
-      <c r="E104" t="n">
-        <v>14.22407288526729</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="E104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Kiss</t>
+          <t>Tiffany</t>
         </is>
       </c>
       <c r="B105" t="n">
         <v>5</v>
       </c>
       <c r="C105" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D105" t="n">
-        <v>3</v>
-      </c>
-      <c r="E105" t="n">
-        <v>20.05506545869531</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="E105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Badia</t>
+          <t>Bolletje</t>
         </is>
       </c>
       <c r="B106" t="n">
         <v>5</v>
       </c>
       <c r="C106" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D106" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E106" t="n">
-        <v>28.56294367711628</v>
+        <v>29.40549939726599</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>DBL</t>
+          <t>Stiratini</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C107" t="n">
         <v>1</v>
@@ -2434,51 +2434,51 @@
         <v>1</v>
       </c>
       <c r="E107" t="n">
-        <v>33.695</v>
+        <v>17.42078051958985</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Kinder</t>
+          <t>Bagel Bites</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C108" t="n">
         <v>2</v>
       </c>
       <c r="D108" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E108" t="n">
-        <v>9.291503578576814</v>
+        <v>14.76764878866199</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Repeat</t>
+          <t>Cheetos</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C109" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D109" t="n">
         <v>1</v>
       </c>
       <c r="E109" t="n">
-        <v>49.2325</v>
+        <v>23.77550530709329</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Dulcesol</t>
+          <t>Green Is My Thing</t>
         </is>
       </c>
       <c r="B110" t="n">
@@ -2490,14 +2490,12 @@
       <c r="D110" t="n">
         <v>1</v>
       </c>
-      <c r="E110" t="n">
-        <v>6.916666666666667</v>
-      </c>
+      <c r="E110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Mestemacher</t>
+          <t>DBL</t>
         </is>
       </c>
       <c r="B111" t="n">
@@ -2510,13 +2508,13 @@
         <v>1</v>
       </c>
       <c r="E111" t="n">
-        <v>5.7</v>
+        <v>33.695</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Keeber</t>
+          <t>Ovaltine</t>
         </is>
       </c>
       <c r="B112" t="n">
@@ -2526,16 +2524,16 @@
         <v>1</v>
       </c>
       <c r="D112" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E112" t="n">
-        <v>28.61772083892403</v>
+        <v>19.9445103354795</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Ovaltine</t>
+          <t>Lago</t>
         </is>
       </c>
       <c r="B113" t="n">
@@ -2548,13 +2546,13 @@
         <v>1</v>
       </c>
       <c r="E113" t="n">
-        <v>19.9445103354795</v>
+        <v>14.895</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Herrs</t>
+          <t>Repeat</t>
         </is>
       </c>
       <c r="B114" t="n">
@@ -2567,32 +2565,32 @@
         <v>1</v>
       </c>
       <c r="E114" t="n">
-        <v>37.30902864926393</v>
+        <v>49.2325</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Takis</t>
+          <t>Mestemacher</t>
         </is>
       </c>
       <c r="B115" t="n">
         <v>4</v>
       </c>
       <c r="C115" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D115" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E115" t="n">
-        <v>41.86</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Milka</t>
+          <t>Nestle</t>
         </is>
       </c>
       <c r="B116" t="n">
@@ -2602,35 +2600,35 @@
         <v>1</v>
       </c>
       <c r="D116" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E116" t="n">
-        <v>29.0725</v>
+        <v>41.70528266913809</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>BGourmet</t>
+          <t>Takis</t>
         </is>
       </c>
       <c r="B117" t="n">
         <v>4</v>
       </c>
       <c r="C117" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D117" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E117" t="n">
-        <v>14.2425</v>
+        <v>41.86</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Stonefire</t>
+          <t>Dulcesol</t>
         </is>
       </c>
       <c r="B118" t="n">
@@ -2643,30 +2641,32 @@
         <v>1</v>
       </c>
       <c r="E118" t="n">
-        <v>16.92</v>
+        <v>6.916666666666667</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Green Is My Thing</t>
+          <t>Glutino</t>
         </is>
       </c>
       <c r="B119" t="n">
         <v>4</v>
       </c>
       <c r="C119" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D119" t="n">
-        <v>1</v>
-      </c>
-      <c r="E119" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E119" t="n">
+        <v>19.41435404641845</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Snyder’S</t>
+          <t>Milka</t>
         </is>
       </c>
       <c r="B120" t="n">
@@ -2676,35 +2676,35 @@
         <v>1</v>
       </c>
       <c r="D120" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E120" t="n">
-        <v>21.8340355175269</v>
+        <v>29.0725</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Glutino</t>
+          <t>PopCorners</t>
         </is>
       </c>
       <c r="B121" t="n">
         <v>4</v>
       </c>
       <c r="C121" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D121" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E121" t="n">
-        <v>19.41435404641845</v>
+        <v>25.6825</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Nestle</t>
+          <t>Loacker</t>
         </is>
       </c>
       <c r="B122" t="n">
@@ -2714,20 +2714,20 @@
         <v>1</v>
       </c>
       <c r="D122" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E122" t="n">
-        <v>41.70528266913809</v>
+        <v>24.3</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Chobani</t>
+          <t>Pozuelo</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C123" t="n">
         <v>1</v>
@@ -2736,36 +2736,36 @@
         <v>1</v>
       </c>
       <c r="E123" t="n">
-        <v>25.58923192551497</v>
+        <v>6.06</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Verkade</t>
+          <t>Kinder</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C124" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D124" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E124" t="n">
-        <v>13.51789778605421</v>
+        <v>9.291503578576814</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Van Der Meulen</t>
+          <t>Stonefire</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C125" t="n">
         <v>1</v>
@@ -2774,34 +2774,36 @@
         <v>1</v>
       </c>
       <c r="E125" t="n">
-        <v>12.12155070255629</v>
+        <v>16.92</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Waitrose</t>
+          <t>BGourmet</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C126" t="n">
         <v>1</v>
       </c>
       <c r="D126" t="n">
-        <v>2</v>
-      </c>
-      <c r="E126" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E126" t="n">
+        <v>14.2425</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Elina</t>
+          <t>Quest</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C127" t="n">
         <v>1</v>
@@ -2810,34 +2812,36 @@
         <v>1</v>
       </c>
       <c r="E127" t="n">
-        <v>35.07692932225363</v>
+        <v>78.6225</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Del-E</t>
+          <t>Keeber</t>
         </is>
       </c>
       <c r="B128" t="n">
+        <v>4</v>
+      </c>
+      <c r="C128" t="n">
+        <v>1</v>
+      </c>
+      <c r="D128" t="n">
         <v>3</v>
       </c>
-      <c r="C128" t="n">
-        <v>1</v>
-      </c>
-      <c r="D128" t="n">
-        <v>2</v>
-      </c>
-      <c r="E128" t="inlineStr"/>
+      <c r="E128" t="n">
+        <v>28.61772083892403</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Confetti</t>
+          <t>Herrs</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C129" t="n">
         <v>1</v>
@@ -2845,16 +2849,18 @@
       <c r="D129" t="n">
         <v>1</v>
       </c>
-      <c r="E129" t="inlineStr"/>
+      <c r="E129" t="n">
+        <v>37.30902864926393</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Crix</t>
+          <t>Snyder’S</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C130" t="n">
         <v>1</v>
@@ -2863,17 +2869,17 @@
         <v>1</v>
       </c>
       <c r="E130" t="n">
-        <v>7.160318629656713</v>
+        <v>21.8340355175269</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Pizkas</t>
+          <t>Dante</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C131" t="n">
         <v>1</v>
@@ -2882,26 +2888,26 @@
         <v>1</v>
       </c>
       <c r="E131" t="n">
-        <v>4.146666666666667</v>
+        <v>7.470000000000001</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Verkade</t>
         </is>
       </c>
       <c r="B132" t="n">
         <v>3</v>
       </c>
       <c r="C132" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D132" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E132" t="n">
-        <v>24.31600957701516</v>
+        <v>13.51789778605421</v>
       </c>
     </row>
     <row r="133">
@@ -2924,7 +2930,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Totino's</t>
+          <t>Choco Wow</t>
         </is>
       </c>
       <c r="B134" t="n">
@@ -2937,13 +2943,13 @@
         <v>1</v>
       </c>
       <c r="E134" t="n">
-        <v>10.85144743680014</v>
+        <v>4.556666666666667</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Roomboter</t>
+          <t>Chobani</t>
         </is>
       </c>
       <c r="B135" t="n">
@@ -2953,16 +2959,16 @@
         <v>1</v>
       </c>
       <c r="D135" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E135" t="n">
-        <v>16.70555144365191</v>
+        <v>25.58923192551497</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Snyders</t>
+          <t>Waitrose</t>
         </is>
       </c>
       <c r="B136" t="n">
@@ -2972,14 +2978,14 @@
         <v>1</v>
       </c>
       <c r="D136" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Dux</t>
+          <t>Confetti</t>
         </is>
       </c>
       <c r="B137" t="n">
@@ -2996,7 +3002,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Flourish</t>
+          <t>Van Der Meulen</t>
         </is>
       </c>
       <c r="B138" t="n">
@@ -3008,35 +3014,37 @@
       <c r="D138" t="n">
         <v>1</v>
       </c>
-      <c r="E138" t="inlineStr"/>
+      <c r="E138" t="n">
+        <v>12.12155070255629</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Voortman</t>
+          <t>Roomboter</t>
         </is>
       </c>
       <c r="B139" t="n">
+        <v>3</v>
+      </c>
+      <c r="C139" t="n">
+        <v>1</v>
+      </c>
+      <c r="D139" t="n">
         <v>2</v>
       </c>
-      <c r="C139" t="n">
-        <v>1</v>
-      </c>
-      <c r="D139" t="n">
-        <v>1</v>
-      </c>
       <c r="E139" t="n">
-        <v>20.17345399698341</v>
+        <v>16.70555144365191</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Sara Lee</t>
+          <t>Crix</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C140" t="n">
         <v>1</v>
@@ -3045,17 +3053,17 @@
         <v>1</v>
       </c>
       <c r="E140" t="n">
-        <v>24.085</v>
+        <v>7.160318629656713</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Willie</t>
+          <t>Totino's</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C141" t="n">
         <v>1</v>
@@ -3063,16 +3071,18 @@
       <c r="D141" t="n">
         <v>1</v>
       </c>
-      <c r="E141" t="inlineStr"/>
+      <c r="E141" t="n">
+        <v>10.85144743680014</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Pico Bello</t>
+          <t>Snyders</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C142" t="n">
         <v>1</v>
@@ -3080,18 +3090,16 @@
       <c r="D142" t="n">
         <v>1</v>
       </c>
-      <c r="E142" t="n">
-        <v>21.08728168019017</v>
-      </c>
+      <c r="E142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Wheat Thins</t>
+          <t>Flourish</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C143" t="n">
         <v>1</v>
@@ -3099,18 +3107,16 @@
       <c r="D143" t="n">
         <v>1</v>
       </c>
-      <c r="E143" t="n">
-        <v>8.979888962508067</v>
-      </c>
+      <c r="E143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Ricola</t>
+          <t>Elina</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C144" t="n">
         <v>1</v>
@@ -3119,17 +3125,17 @@
         <v>1</v>
       </c>
       <c r="E144" t="n">
-        <v>7.351955307262569</v>
+        <v>35.07692932225363</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Royal Dansk</t>
+          <t>Pizkas</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C145" t="n">
         <v>1</v>
@@ -3138,17 +3144,17 @@
         <v>1</v>
       </c>
       <c r="E145" t="n">
-        <v>20.48</v>
+        <v>4.146666666666667</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Vigo</t>
+          <t>Dux</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C146" t="n">
         <v>1</v>
@@ -3156,52 +3162,52 @@
       <c r="D146" t="n">
         <v>1</v>
       </c>
-      <c r="E146" t="n">
-        <v>9.433248720978664</v>
-      </c>
+      <c r="E146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Werther’S</t>
+          <t>Town House</t>
         </is>
       </c>
       <c r="B147" t="n">
+        <v>3</v>
+      </c>
+      <c r="C147" t="n">
         <v>2</v>
       </c>
-      <c r="C147" t="n">
-        <v>1</v>
-      </c>
       <c r="D147" t="n">
-        <v>1</v>
-      </c>
-      <c r="E147" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="E147" t="n">
+        <v>24.31600957701516</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Soldanza</t>
+          <t>Del-E</t>
         </is>
       </c>
       <c r="B148" t="n">
+        <v>3</v>
+      </c>
+      <c r="C148" t="n">
+        <v>1</v>
+      </c>
+      <c r="D148" t="n">
         <v>2</v>
-      </c>
-      <c r="C148" t="n">
-        <v>1</v>
-      </c>
-      <c r="D148" t="n">
-        <v>1</v>
       </c>
       <c r="E148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Tuc</t>
+          <t>Lotus</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C149" t="n">
         <v>1</v>
@@ -3210,13 +3216,13 @@
         <v>1</v>
       </c>
       <c r="E149" t="n">
-        <v>7.575418994413408</v>
+        <v>19.15</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Twix</t>
+          <t>Vigo</t>
         </is>
       </c>
       <c r="B150" t="n">
@@ -3229,13 +3235,13 @@
         <v>1</v>
       </c>
       <c r="E150" t="n">
-        <v>25.28014847471393</v>
+        <v>9.433248720978664</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Agua Vivo</t>
+          <t>Voortman</t>
         </is>
       </c>
       <c r="B151" t="n">
@@ -3248,13 +3254,13 @@
         <v>1</v>
       </c>
       <c r="E151" t="n">
-        <v>12.445</v>
+        <v>20.17345399698341</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>dollys</t>
+          <t>Pico Bello</t>
         </is>
       </c>
       <c r="B152" t="n">
@@ -3267,13 +3273,13 @@
         <v>1</v>
       </c>
       <c r="E152" t="n">
-        <v>3.96</v>
+        <v>21.08728168019017</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Crunchmaster</t>
+          <t>Twix</t>
         </is>
       </c>
       <c r="B153" t="n">
@@ -3286,13 +3292,13 @@
         <v>1</v>
       </c>
       <c r="E153" t="n">
-        <v>51.37009840929231</v>
+        <v>25.28014847471393</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Danisha</t>
+          <t>Ricola</t>
         </is>
       </c>
       <c r="B154" t="n">
@@ -3304,12 +3310,14 @@
       <c r="D154" t="n">
         <v>1</v>
       </c>
-      <c r="E154" t="inlineStr"/>
+      <c r="E154" t="n">
+        <v>7.351955307262569</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Cole´s</t>
+          <t>Tuc</t>
         </is>
       </c>
       <c r="B155" t="n">
@@ -3322,13 +3330,13 @@
         <v>1</v>
       </c>
       <c r="E155" t="n">
-        <v>21.94025264317509</v>
+        <v>7.575418994413408</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Ita Abu</t>
+          <t>Werther’S</t>
         </is>
       </c>
       <c r="B156" t="n">
@@ -3345,7 +3353,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Hinged</t>
+          <t>Vaquita Rica</t>
         </is>
       </c>
       <c r="B157" t="n">
@@ -3357,14 +3365,12 @@
       <c r="D157" t="n">
         <v>1</v>
       </c>
-      <c r="E157" t="n">
-        <v>1.907848055928269</v>
-      </c>
+      <c r="E157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Gri Gri</t>
+          <t>Wheat Thins</t>
         </is>
       </c>
       <c r="B158" t="n">
@@ -3376,12 +3382,14 @@
       <c r="D158" t="n">
         <v>1</v>
       </c>
-      <c r="E158" t="inlineStr"/>
+      <c r="E158" t="n">
+        <v>8.979888962508067</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Dove</t>
+          <t>Willie</t>
         </is>
       </c>
       <c r="B159" t="n">
@@ -3393,14 +3401,12 @@
       <c r="D159" t="n">
         <v>1</v>
       </c>
-      <c r="E159" t="n">
-        <v>10.95146340976004</v>
-      </c>
+      <c r="E159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Glad</t>
+          <t>Soldanza</t>
         </is>
       </c>
       <c r="B160" t="n">
@@ -3417,7 +3423,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Dairy</t>
+          <t>Sara Lee</t>
         </is>
       </c>
       <c r="B161" t="n">
@@ -3429,12 +3435,14 @@
       <c r="D161" t="n">
         <v>1</v>
       </c>
-      <c r="E161" t="inlineStr"/>
+      <c r="E161" t="n">
+        <v>24.085</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Cheez</t>
+          <t>Royal Dansk</t>
         </is>
       </c>
       <c r="B162" t="n">
@@ -3446,12 +3454,14 @@
       <c r="D162" t="n">
         <v>1</v>
       </c>
-      <c r="E162" t="inlineStr"/>
+      <c r="E162" t="n">
+        <v>20.48</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Knotts</t>
+          <t>SuperMoist</t>
         </is>
       </c>
       <c r="B163" t="n">
@@ -3463,12 +3473,14 @@
       <c r="D163" t="n">
         <v>1</v>
       </c>
-      <c r="E163" t="inlineStr"/>
+      <c r="E163" t="n">
+        <v>11.36</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>La Tortilla Factory</t>
+          <t>dollys</t>
         </is>
       </c>
       <c r="B164" t="n">
@@ -3481,13 +3493,13 @@
         <v>1</v>
       </c>
       <c r="E164" t="n">
-        <v>21.71</v>
+        <v>3.96</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Lewis Bake Shop</t>
+          <t>New York Style</t>
         </is>
       </c>
       <c r="B165" t="n">
@@ -3500,13 +3512,13 @@
         <v>1</v>
       </c>
       <c r="E165" t="n">
-        <v>5.189283551419543</v>
+        <v>17.46</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Can Can</t>
+          <t>Agua Vivo</t>
         </is>
       </c>
       <c r="B166" t="n">
@@ -3519,13 +3531,13 @@
         <v>1</v>
       </c>
       <c r="E166" t="n">
-        <v>3.915</v>
+        <v>12.445</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Bisco</t>
+          <t>Glad</t>
         </is>
       </c>
       <c r="B167" t="n">
@@ -3537,14 +3549,12 @@
       <c r="D167" t="n">
         <v>1</v>
       </c>
-      <c r="E167" t="n">
-        <v>19.215</v>
-      </c>
+      <c r="E167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Mars</t>
+          <t>Dried</t>
         </is>
       </c>
       <c r="B168" t="n">
@@ -3554,14 +3564,14 @@
         <v>1</v>
       </c>
       <c r="D168" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Dried</t>
+          <t>Dove</t>
         </is>
       </c>
       <c r="B169" t="n">
@@ -3571,14 +3581,16 @@
         <v>1</v>
       </c>
       <c r="D169" t="n">
-        <v>2</v>
-      </c>
-      <c r="E169" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E169" t="n">
+        <v>10.95146340976004</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Beivita</t>
+          <t>Gri Gri</t>
         </is>
       </c>
       <c r="B170" t="n">
@@ -3590,21 +3602,19 @@
       <c r="D170" t="n">
         <v>1</v>
       </c>
-      <c r="E170" t="n">
-        <v>35.19230769230769</v>
-      </c>
+      <c r="E170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Nature Valley</t>
+          <t>Danisha</t>
         </is>
       </c>
       <c r="B171" t="n">
         <v>2</v>
       </c>
       <c r="C171" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D171" t="n">
         <v>1</v>
@@ -3614,7 +3624,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Hills</t>
+          <t>Dairy</t>
         </is>
       </c>
       <c r="B172" t="n">
@@ -3631,30 +3641,28 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Ferrero</t>
+          <t>Hills</t>
         </is>
       </c>
       <c r="B173" t="n">
         <v>2</v>
       </c>
       <c r="C173" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D173" t="n">
-        <v>2</v>
-      </c>
-      <c r="E173" t="n">
-        <v>48.37</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="E173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Triscuit</t>
+          <t>Hinged</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C174" t="n">
         <v>1</v>
@@ -3663,17 +3671,17 @@
         <v>1</v>
       </c>
       <c r="E174" t="n">
-        <v>21.76632743949854</v>
+        <v>1.907848055928269</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Odorex</t>
+          <t>Crunchmaster</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C175" t="n">
         <v>1</v>
@@ -3681,16 +3689,18 @@
       <c r="D175" t="n">
         <v>1</v>
       </c>
-      <c r="E175" t="inlineStr"/>
+      <c r="E175" t="n">
+        <v>51.37009840929231</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>DiGiorno</t>
+          <t>Cole´s</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C176" t="n">
         <v>1</v>
@@ -3699,17 +3709,17 @@
         <v>1</v>
       </c>
       <c r="E176" t="n">
-        <v>14.25891435863968</v>
+        <v>21.94025264317509</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Double Duty</t>
+          <t>Ita Abu</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C177" t="n">
         <v>1</v>
@@ -3722,11 +3732,11 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Ducales</t>
+          <t>Knotts</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C178" t="n">
         <v>1</v>
@@ -3734,56 +3744,54 @@
       <c r="D178" t="n">
         <v>1</v>
       </c>
-      <c r="E178" t="n">
-        <v>21.76632743949854</v>
-      </c>
+      <c r="E178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>El Corte Inglés</t>
+          <t>Cheez-It</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C179" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D179" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E179" t="n">
-        <v>8.85</v>
+        <v>24.93720782169088</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Toblerone</t>
+          <t>Ferrero</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C180" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D180" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E180" t="n">
-        <v>14.42655274400263</v>
+        <v>48.37</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Vegefarm</t>
+          <t>La Tortilla Factory</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C181" t="n">
         <v>1</v>
@@ -3792,17 +3800,17 @@
         <v>1</v>
       </c>
       <c r="E181" t="n">
-        <v>27.42714334124026</v>
+        <v>21.71</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Cusano´s</t>
+          <t>Cheez</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C182" t="n">
         <v>1</v>
@@ -3815,14 +3823,14 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Twizzlers</t>
+          <t>Nature Valley</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C183" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D183" t="n">
         <v>1</v>
@@ -3832,11 +3840,11 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Cloverhill</t>
+          <t>Muuu</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C184" t="n">
         <v>1</v>
@@ -3849,11 +3857,11 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Chowmein</t>
+          <t>Beivita</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C185" t="n">
         <v>1</v>
@@ -3861,16 +3869,18 @@
       <c r="D185" t="n">
         <v>1</v>
       </c>
-      <c r="E185" t="inlineStr"/>
+      <c r="E185" t="n">
+        <v>35.19230769230769</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Choppers</t>
+          <t>Mars</t>
         </is>
       </c>
       <c r="B186" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C186" t="n">
         <v>1</v>
@@ -3883,11 +3893,11 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Chokis</t>
+          <t>Can Can</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C187" t="n">
         <v>1</v>
@@ -3896,17 +3906,17 @@
         <v>1</v>
       </c>
       <c r="E187" t="n">
-        <v>11.44</v>
+        <v>3.915</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Cho Cho</t>
+          <t>Bisco</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C188" t="n">
         <v>1</v>
@@ -3914,16 +3924,18 @@
       <c r="D188" t="n">
         <v>1</v>
       </c>
-      <c r="E188" t="inlineStr"/>
+      <c r="E188" t="n">
+        <v>19.215</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Chiefeez</t>
+          <t>Lewis Bake Shop</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C189" t="n">
         <v>1</v>
@@ -3931,12 +3943,14 @@
       <c r="D189" t="n">
         <v>1</v>
       </c>
-      <c r="E189" t="inlineStr"/>
+      <c r="E189" t="n">
+        <v>5.189283551419543</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Chester</t>
+          <t>Chowmein</t>
         </is>
       </c>
       <c r="B190" t="n">
@@ -3953,7 +3967,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Bigelow</t>
+          <t>DiGiorno</t>
         </is>
       </c>
       <c r="B191" t="n">
@@ -3965,12 +3979,14 @@
       <c r="D191" t="n">
         <v>1</v>
       </c>
-      <c r="E191" t="inlineStr"/>
+      <c r="E191" t="n">
+        <v>14.25891435863968</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Becky's</t>
+          <t>Fernandes</t>
         </is>
       </c>
       <c r="B192" t="n">
@@ -3982,14 +3998,12 @@
       <c r="D192" t="n">
         <v>1</v>
       </c>
-      <c r="E192" t="n">
-        <v>19.37665392531608</v>
-      </c>
+      <c r="E192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Yasso</t>
+          <t>El Corte Inglés</t>
         </is>
       </c>
       <c r="B193" t="n">
@@ -4001,12 +4015,14 @@
       <c r="D193" t="n">
         <v>1</v>
       </c>
-      <c r="E193" t="inlineStr"/>
+      <c r="E193" t="n">
+        <v>8.85</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Fernandes</t>
+          <t>Ducales</t>
         </is>
       </c>
       <c r="B194" t="n">
@@ -4018,12 +4034,14 @@
       <c r="D194" t="n">
         <v>1</v>
       </c>
-      <c r="E194" t="inlineStr"/>
+      <c r="E194" t="n">
+        <v>21.76632743949854</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Give &amp; Go</t>
+          <t>Yasso</t>
         </is>
       </c>
       <c r="B195" t="n">
@@ -4040,7 +4058,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Sultana</t>
+          <t>Chiefeez</t>
         </is>
       </c>
       <c r="B196" t="n">
@@ -4052,14 +4070,12 @@
       <c r="D196" t="n">
         <v>1</v>
       </c>
-      <c r="E196" t="n">
-        <v>18.58472998137803</v>
-      </c>
+      <c r="E196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Hollandia</t>
+          <t>Becky's</t>
         </is>
       </c>
       <c r="B197" t="n">
@@ -4072,13 +4088,13 @@
         <v>1</v>
       </c>
       <c r="E197" t="n">
-        <v>52.34878150009826</v>
+        <v>19.37665392531608</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Ortega</t>
+          <t>Toblerone</t>
         </is>
       </c>
       <c r="B198" t="n">
@@ -4091,13 +4107,13 @@
         <v>1</v>
       </c>
       <c r="E198" t="n">
-        <v>10.91045974485786</v>
+        <v>14.42655274400263</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Oscar Mayer</t>
+          <t>Double Duty</t>
         </is>
       </c>
       <c r="B199" t="n">
@@ -4109,14 +4125,12 @@
       <c r="D199" t="n">
         <v>1</v>
       </c>
-      <c r="E199" t="n">
-        <v>21.70707121411719</v>
-      </c>
+      <c r="E199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Members Selection</t>
+          <t>Cho Cho</t>
         </is>
       </c>
       <c r="B200" t="n">
@@ -4133,7 +4147,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Mcvitie'S</t>
+          <t>Sultana</t>
         </is>
       </c>
       <c r="B201" t="n">
@@ -4146,13 +4160,13 @@
         <v>1</v>
       </c>
       <c r="E201" t="n">
-        <v>37.62485187066193</v>
+        <v>18.58472998137803</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Marie</t>
+          <t>Bigelow</t>
         </is>
       </c>
       <c r="B202" t="n">
@@ -4169,7 +4183,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Liga</t>
+          <t>Triscuit</t>
         </is>
       </c>
       <c r="B203" t="n">
@@ -4182,13 +4196,13 @@
         <v>1</v>
       </c>
       <c r="E203" t="n">
-        <v>10.58305138091117</v>
+        <v>21.76632743949854</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Pirucream</t>
+          <t>Cusano´s</t>
         </is>
       </c>
       <c r="B204" t="n">
@@ -4200,14 +4214,12 @@
       <c r="D204" t="n">
         <v>1</v>
       </c>
-      <c r="E204" t="n">
-        <v>20.53625219611713</v>
-      </c>
+      <c r="E204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Pirulin</t>
+          <t>Chester</t>
         </is>
       </c>
       <c r="B205" t="n">
@@ -4224,7 +4236,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>King's Hawaiian</t>
+          <t>Bridge</t>
         </is>
       </c>
       <c r="B206" t="n">
@@ -4236,12 +4248,14 @@
       <c r="D206" t="n">
         <v>1</v>
       </c>
-      <c r="E206" t="inlineStr"/>
+      <c r="E206" t="n">
+        <v>5.02</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Post</t>
+          <t>Chokis</t>
         </is>
       </c>
       <c r="B207" t="n">
@@ -4254,13 +4268,13 @@
         <v>1</v>
       </c>
       <c r="E207" t="n">
-        <v>7.51</v>
+        <v>11.44</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Kimberley's Bakeshoppe</t>
+          <t>Vegefarm</t>
         </is>
       </c>
       <c r="B208" t="n">
@@ -4272,12 +4286,14 @@
       <c r="D208" t="n">
         <v>1</v>
       </c>
-      <c r="E208" t="inlineStr"/>
+      <c r="E208" t="n">
+        <v>27.42714334124026</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Jos Poell</t>
+          <t>Twizzlers</t>
         </is>
       </c>
       <c r="B209" t="n">
@@ -4289,14 +4305,12 @@
       <c r="D209" t="n">
         <v>1</v>
       </c>
-      <c r="E209" t="n">
-        <v>25.38795779019243</v>
-      </c>
+      <c r="E209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Hostess</t>
+          <t>Cloverhill</t>
         </is>
       </c>
       <c r="B210" t="n">
@@ -4308,14 +4322,12 @@
       <c r="D210" t="n">
         <v>1</v>
       </c>
-      <c r="E210" t="n">
-        <v>20.82</v>
-      </c>
+      <c r="E210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Reynolds</t>
+          <t>Choppers</t>
         </is>
       </c>
       <c r="B211" t="n">
@@ -4332,7 +4344,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Stouffer's</t>
+          <t>Goldfish</t>
         </is>
       </c>
       <c r="B212" t="n">
@@ -4345,13 +4357,13 @@
         <v>1</v>
       </c>
       <c r="E212" t="n">
-        <v>27.47380304721075</v>
+        <v>15.39664804469274</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Holiday</t>
+          <t>Stouffer's</t>
         </is>
       </c>
       <c r="B213" t="n">
@@ -4363,12 +4375,14 @@
       <c r="D213" t="n">
         <v>1</v>
       </c>
-      <c r="E213" t="inlineStr"/>
+      <c r="E213" t="n">
+        <v>27.47380304721075</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Highland</t>
+          <t>Liga</t>
         </is>
       </c>
       <c r="B214" t="n">
@@ -4380,12 +4394,14 @@
       <c r="D214" t="n">
         <v>1</v>
       </c>
-      <c r="E214" t="inlineStr"/>
+      <c r="E214" t="n">
+        <v>10.58305138091117</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Santitas</t>
+          <t>Kimberley's Bakeshoppe</t>
         </is>
       </c>
       <c r="B215" t="n">
@@ -4397,14 +4413,12 @@
       <c r="D215" t="n">
         <v>1</v>
       </c>
-      <c r="E215" t="n">
-        <v>23.62766194234949</v>
-      </c>
+      <c r="E215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>HiPro</t>
+          <t>King's Hawaiian</t>
         </is>
       </c>
       <c r="B216" t="n">
@@ -4421,7 +4435,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Hershey</t>
+          <t>Post</t>
         </is>
       </c>
       <c r="B217" t="n">
@@ -4434,13 +4448,13 @@
         <v>1</v>
       </c>
       <c r="E217" t="n">
-        <v>19.07848055928269</v>
+        <v>7.51</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Haribo</t>
+          <t>Kraft</t>
         </is>
       </c>
       <c r="B218" t="n">
@@ -4452,12 +4466,14 @@
       <c r="D218" t="n">
         <v>1</v>
       </c>
-      <c r="E218" t="inlineStr"/>
+      <c r="E218" t="n">
+        <v>9.264432029795158</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Haagen Daz</t>
+          <t>Pirulin</t>
         </is>
       </c>
       <c r="B219" t="n">
@@ -4474,7 +4490,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>HOL Foods</t>
+          <t>Pirucream</t>
         </is>
       </c>
       <c r="B220" t="n">
@@ -4487,13 +4503,13 @@
         <v>1</v>
       </c>
       <c r="E220" t="n">
-        <v>14.42307692307692</v>
+        <v>20.53625219611713</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Snickers</t>
+          <t>Marie</t>
         </is>
       </c>
       <c r="B221" t="n">
@@ -4505,14 +4521,12 @@
       <c r="D221" t="n">
         <v>1</v>
       </c>
-      <c r="E221" t="n">
-        <v>40.99</v>
-      </c>
+      <c r="E221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Goldfish</t>
+          <t>Jos Poell</t>
         </is>
       </c>
       <c r="B222" t="n">
@@ -4525,13 +4539,13 @@
         <v>1</v>
       </c>
       <c r="E222" t="n">
-        <v>15.39664804469274</v>
+        <v>25.38795779019243</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Nerds</t>
+          <t>Mcvitie'S</t>
         </is>
       </c>
       <c r="B223" t="n">
@@ -4543,12 +4557,14 @@
       <c r="D223" t="n">
         <v>1</v>
       </c>
-      <c r="E223" t="inlineStr"/>
+      <c r="E223" t="n">
+        <v>37.62485187066193</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Frito-Lay</t>
+          <t>Members Selection</t>
         </is>
       </c>
       <c r="B224" t="n">
@@ -4565,7 +4581,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Fit Crunch</t>
+          <t>Mocano</t>
         </is>
       </c>
       <c r="B225" t="n">
@@ -4577,14 +4593,12 @@
       <c r="D225" t="n">
         <v>1</v>
       </c>
-      <c r="E225" t="n">
-        <v>61.6</v>
-      </c>
+      <c r="E225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Kraft</t>
+          <t>Oscar Mayer</t>
         </is>
       </c>
       <c r="B226" t="n">
@@ -4597,7 +4611,386 @@
         <v>1</v>
       </c>
       <c r="E226" t="n">
-        <v>9.264432029795158</v>
+        <v>21.70707121411719</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Ortega</t>
+        </is>
+      </c>
+      <c r="B227" t="n">
+        <v>1</v>
+      </c>
+      <c r="C227" t="n">
+        <v>1</v>
+      </c>
+      <c r="D227" t="n">
+        <v>1</v>
+      </c>
+      <c r="E227" t="n">
+        <v>10.91045974485786</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Nerds</t>
+        </is>
+      </c>
+      <c r="B228" t="n">
+        <v>1</v>
+      </c>
+      <c r="C228" t="n">
+        <v>1</v>
+      </c>
+      <c r="D228" t="n">
+        <v>1</v>
+      </c>
+      <c r="E228" t="inlineStr"/>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Jules Destrooper</t>
+        </is>
+      </c>
+      <c r="B229" t="n">
+        <v>1</v>
+      </c>
+      <c r="C229" t="n">
+        <v>1</v>
+      </c>
+      <c r="D229" t="n">
+        <v>1</v>
+      </c>
+      <c r="E229" t="n">
+        <v>39.61</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Hostess</t>
+        </is>
+      </c>
+      <c r="B230" t="n">
+        <v>1</v>
+      </c>
+      <c r="C230" t="n">
+        <v>1</v>
+      </c>
+      <c r="D230" t="n">
+        <v>1</v>
+      </c>
+      <c r="E230" t="n">
+        <v>20.82</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Fit Crunch</t>
+        </is>
+      </c>
+      <c r="B231" t="n">
+        <v>1</v>
+      </c>
+      <c r="C231" t="n">
+        <v>1</v>
+      </c>
+      <c r="D231" t="n">
+        <v>1</v>
+      </c>
+      <c r="E231" t="n">
+        <v>61.6</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Haagen Daz</t>
+        </is>
+      </c>
+      <c r="B232" t="n">
+        <v>1</v>
+      </c>
+      <c r="C232" t="n">
+        <v>1</v>
+      </c>
+      <c r="D232" t="n">
+        <v>1</v>
+      </c>
+      <c r="E232" t="inlineStr"/>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Frito-Lay</t>
+        </is>
+      </c>
+      <c r="B233" t="n">
+        <v>1</v>
+      </c>
+      <c r="C233" t="n">
+        <v>1</v>
+      </c>
+      <c r="D233" t="n">
+        <v>1</v>
+      </c>
+      <c r="E233" t="inlineStr"/>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Gavotte</t>
+        </is>
+      </c>
+      <c r="B234" t="n">
+        <v>1</v>
+      </c>
+      <c r="C234" t="n">
+        <v>1</v>
+      </c>
+      <c r="D234" t="n">
+        <v>1</v>
+      </c>
+      <c r="E234" t="n">
+        <v>29.15</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Give &amp; Go</t>
+        </is>
+      </c>
+      <c r="B235" t="n">
+        <v>1</v>
+      </c>
+      <c r="C235" t="n">
+        <v>1</v>
+      </c>
+      <c r="D235" t="n">
+        <v>1</v>
+      </c>
+      <c r="E235" t="inlineStr"/>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Odorex</t>
+        </is>
+      </c>
+      <c r="B236" t="n">
+        <v>1</v>
+      </c>
+      <c r="C236" t="n">
+        <v>1</v>
+      </c>
+      <c r="D236" t="n">
+        <v>1</v>
+      </c>
+      <c r="E236" t="inlineStr"/>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Snickers</t>
+        </is>
+      </c>
+      <c r="B237" t="n">
+        <v>1</v>
+      </c>
+      <c r="C237" t="n">
+        <v>1</v>
+      </c>
+      <c r="D237" t="n">
+        <v>1</v>
+      </c>
+      <c r="E237" t="n">
+        <v>40.99</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>HOL Foods</t>
+        </is>
+      </c>
+      <c r="B238" t="n">
+        <v>1</v>
+      </c>
+      <c r="C238" t="n">
+        <v>1</v>
+      </c>
+      <c r="D238" t="n">
+        <v>1</v>
+      </c>
+      <c r="E238" t="n">
+        <v>14.42307692307692</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Haribo</t>
+        </is>
+      </c>
+      <c r="B239" t="n">
+        <v>1</v>
+      </c>
+      <c r="C239" t="n">
+        <v>1</v>
+      </c>
+      <c r="D239" t="n">
+        <v>1</v>
+      </c>
+      <c r="E239" t="inlineStr"/>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>Hollandia</t>
+        </is>
+      </c>
+      <c r="B240" t="n">
+        <v>1</v>
+      </c>
+      <c r="C240" t="n">
+        <v>1</v>
+      </c>
+      <c r="D240" t="n">
+        <v>1</v>
+      </c>
+      <c r="E240" t="n">
+        <v>52.34878150009826</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Hershey</t>
+        </is>
+      </c>
+      <c r="B241" t="n">
+        <v>1</v>
+      </c>
+      <c r="C241" t="n">
+        <v>1</v>
+      </c>
+      <c r="D241" t="n">
+        <v>1</v>
+      </c>
+      <c r="E241" t="n">
+        <v>19.07848055928269</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Santitas</t>
+        </is>
+      </c>
+      <c r="B242" t="n">
+        <v>1</v>
+      </c>
+      <c r="C242" t="n">
+        <v>1</v>
+      </c>
+      <c r="D242" t="n">
+        <v>1</v>
+      </c>
+      <c r="E242" t="n">
+        <v>23.62766194234949</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>HiPro</t>
+        </is>
+      </c>
+      <c r="B243" t="n">
+        <v>1</v>
+      </c>
+      <c r="C243" t="n">
+        <v>1</v>
+      </c>
+      <c r="D243" t="n">
+        <v>1</v>
+      </c>
+      <c r="E243" t="inlineStr"/>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Highland</t>
+        </is>
+      </c>
+      <c r="B244" t="n">
+        <v>1</v>
+      </c>
+      <c r="C244" t="n">
+        <v>1</v>
+      </c>
+      <c r="D244" t="n">
+        <v>1</v>
+      </c>
+      <c r="E244" t="inlineStr"/>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Reynolds</t>
+        </is>
+      </c>
+      <c r="B245" t="n">
+        <v>1</v>
+      </c>
+      <c r="C245" t="n">
+        <v>1</v>
+      </c>
+      <c r="D245" t="n">
+        <v>1</v>
+      </c>
+      <c r="E245" t="inlineStr"/>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Holiday</t>
+        </is>
+      </c>
+      <c r="B246" t="n">
+        <v>1</v>
+      </c>
+      <c r="C246" t="n">
+        <v>1</v>
+      </c>
+      <c r="D246" t="n">
+        <v>1</v>
+      </c>
+      <c r="E246" t="inlineStr"/>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>AXA</t>
+        </is>
+      </c>
+      <c r="B247" t="n">
+        <v>1</v>
+      </c>
+      <c r="C247" t="n">
+        <v>1</v>
+      </c>
+      <c r="D247" t="n">
+        <v>1</v>
+      </c>
+      <c r="E247" t="n">
+        <v>33.5</v>
       </c>
     </row>
   </sheetData>
@@ -6441,7 +6834,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Quest</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -6520,17 +6913,17 @@
       <c r="AG8" t="inlineStr"/>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Quest</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Quest</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>unknown_barra de proteina sabor brownie de chocolate quest</t>
+          <t>quest_barra de proteina sabor brownie de chocolate quest</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -6545,7 +6938,7 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>unknown_barra de proteina sabor brownie de chocolate quest_0.06</t>
+          <t>quest_barra de proteina sabor brownie de chocolate quest_0.06</t>
         </is>
       </c>
       <c r="AN8" t="n">
@@ -6559,7 +6952,7 @@
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>unknown_barra_brownie_chocolate_proteina</t>
+          <t>quest_barra_brownie_chocolate_proteina</t>
         </is>
       </c>
       <c r="AR8" t="n">
@@ -6616,7 +7009,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Quest</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -6695,17 +7088,17 @@
       <c r="AG9" t="inlineStr"/>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Quest</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Quest</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>unknown_barra de proteina sabor brownie de chocolate quest</t>
+          <t>quest_barra de proteina sabor brownie de chocolate quest</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -6720,7 +7113,7 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>unknown_barra de proteina sabor brownie de chocolate quest_0.06</t>
+          <t>quest_barra de proteina sabor brownie de chocolate quest_0.06</t>
         </is>
       </c>
       <c r="AN9" t="n">
@@ -6734,7 +7127,7 @@
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>unknown_barra_brownie_chocolate_proteina</t>
+          <t>quest_barra_brownie_chocolate_proteina</t>
         </is>
       </c>
       <c r="AR9" t="n">
@@ -6791,7 +7184,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Quest</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -6870,17 +7263,17 @@
       <c r="AG10" t="inlineStr"/>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Quest</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Quest</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>unknown_barra de proteina sabor brownie de chocolate quest</t>
+          <t>quest_barra de proteina sabor brownie de chocolate quest</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -6895,7 +7288,7 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>unknown_barra de proteina sabor brownie de chocolate quest_0.06</t>
+          <t>quest_barra de proteina sabor brownie de chocolate quest_0.06</t>
         </is>
       </c>
       <c r="AN10" t="n">
@@ -6909,7 +7302,7 @@
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>unknown_barra_brownie_chocolate_proteina</t>
+          <t>quest_barra_brownie_chocolate_proteina</t>
         </is>
       </c>
       <c r="AR10" t="n">
@@ -6966,7 +7359,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Quest</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -7045,17 +7438,17 @@
       <c r="AG11" t="inlineStr"/>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Quest</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Quest</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>unknown_barra de proteina sabor brownie de chocolate quest</t>
+          <t>quest_barra de proteina sabor brownie de chocolate quest</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -7070,7 +7463,7 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>unknown_barra de proteina sabor brownie de chocolate quest_0.06</t>
+          <t>quest_barra de proteina sabor brownie de chocolate quest_0.06</t>
         </is>
       </c>
       <c r="AN11" t="n">
@@ -7084,7 +7477,7 @@
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>unknown_barra_brownie_chocolate_proteina</t>
+          <t>quest_barra_brownie_chocolate_proteina</t>
         </is>
       </c>
       <c r="AR11" t="n">
@@ -15935,7 +16328,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Jules Destrooper</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -16010,17 +16403,17 @@
       <c r="AG64" t="inlineStr"/>
       <c r="AH64" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Jules Destrooper</t>
         </is>
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Jules Destrooper</t>
         </is>
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>unknown_galleta de mantequilla jules destrooper</t>
+          <t>jules destrooper_galleta de mantequilla jules destrooper</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
@@ -16035,7 +16428,7 @@
       </c>
       <c r="AM64" t="inlineStr">
         <is>
-          <t>unknown_galleta de mantequilla jules destrooper_0.1</t>
+          <t>jules destrooper_galleta de mantequilla jules destrooper_0.1</t>
         </is>
       </c>
       <c r="AN64" t="inlineStr"/>
@@ -16043,7 +16436,7 @@
       <c r="AP64" t="inlineStr"/>
       <c r="AQ64" t="inlineStr">
         <is>
-          <t>unknown_destrooper_jules_mantequilla</t>
+          <t>jules destrooper_destrooper_jules_mantequilla</t>
         </is>
       </c>
       <c r="AR64" t="n">
@@ -25051,7 +25444,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>AXA</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -25130,17 +25523,17 @@
       <c r="AG118" t="inlineStr"/>
       <c r="AH118" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>AXA</t>
         </is>
       </c>
       <c r="AI118" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>AXA</t>
         </is>
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>unknown_galletas cookie n cream axa</t>
+          <t>axa_galletas cookie n cream axa</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
@@ -25155,7 +25548,7 @@
       </c>
       <c r="AM118" t="inlineStr">
         <is>
-          <t>unknown_galletas cookie n cream axa_0.14</t>
+          <t>axa_galletas cookie n cream axa_0.14</t>
         </is>
       </c>
       <c r="AN118" t="n">
@@ -25169,7 +25562,7 @@
       </c>
       <c r="AQ118" t="inlineStr">
         <is>
-          <t>unknown_cream</t>
+          <t>axa_cream</t>
         </is>
       </c>
       <c r="AR118" t="n">
@@ -32421,7 +32814,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Gavotte</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -32500,17 +32893,17 @@
       <c r="AG162" t="inlineStr"/>
       <c r="AH162" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Gavotte</t>
         </is>
       </c>
       <c r="AI162" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Gavotte</t>
         </is>
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>unknown_galleta gavotte dentelle</t>
+          <t>gavotte_galleta gavotte dentelle</t>
         </is>
       </c>
       <c r="AK162" t="inlineStr">
@@ -32525,7 +32918,7 @@
       </c>
       <c r="AM162" t="inlineStr">
         <is>
-          <t>unknown_galleta gavotte dentelle_0.12</t>
+          <t>gavotte_galleta gavotte dentelle_0.12</t>
         </is>
       </c>
       <c r="AN162" t="n">
@@ -32539,7 +32932,7 @@
       </c>
       <c r="AQ162" t="inlineStr">
         <is>
-          <t>unknown_dentelle_gavotte</t>
+          <t>gavotte_dentelle_gavotte</t>
         </is>
       </c>
       <c r="AR162" t="n">
@@ -44049,7 +44442,7 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>PopCorners</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -44128,17 +44521,17 @@
       <c r="AG230" t="inlineStr"/>
       <c r="AH230" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>PopCorners</t>
         </is>
       </c>
       <c r="AI230" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>PopCorners</t>
         </is>
       </c>
       <c r="AJ230" t="inlineStr">
         <is>
-          <t>unknown_tortillas chips kettle corn popcorners</t>
+          <t>popcorners_tortillas chips kettle corn popcorners</t>
         </is>
       </c>
       <c r="AK230" t="inlineStr">
@@ -44153,7 +44546,7 @@
       </c>
       <c r="AM230" t="inlineStr">
         <is>
-          <t>unknown_tortillas chips kettle corn popcorners_0.14</t>
+          <t>popcorners_tortillas chips kettle corn popcorners_0.14</t>
         </is>
       </c>
       <c r="AN230" t="n">
@@ -44167,7 +44560,7 @@
       </c>
       <c r="AQ230" t="inlineStr">
         <is>
-          <t>unknown_chips_corn_kettle_popcorners</t>
+          <t>popcorners_chips_corn_kettle_popcorners</t>
         </is>
       </c>
       <c r="AR230" t="n">
@@ -44224,7 +44617,7 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>PopCorners</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -44303,17 +44696,17 @@
       <c r="AG231" t="inlineStr"/>
       <c r="AH231" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>PopCorners</t>
         </is>
       </c>
       <c r="AI231" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>PopCorners</t>
         </is>
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>unknown_tortillas chips kettle corn popcorners</t>
+          <t>popcorners_tortillas chips kettle corn popcorners</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
@@ -44328,7 +44721,7 @@
       </c>
       <c r="AM231" t="inlineStr">
         <is>
-          <t>unknown_tortillas chips kettle corn popcorners_0.14</t>
+          <t>popcorners_tortillas chips kettle corn popcorners_0.14</t>
         </is>
       </c>
       <c r="AN231" t="n">
@@ -44342,7 +44735,7 @@
       </c>
       <c r="AQ231" t="inlineStr">
         <is>
-          <t>unknown_chips_corn_kettle_popcorners</t>
+          <t>popcorners_chips_corn_kettle_popcorners</t>
         </is>
       </c>
       <c r="AR231" t="n">
@@ -44399,7 +44792,7 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>PopCorners</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -44478,17 +44871,17 @@
       <c r="AG232" t="inlineStr"/>
       <c r="AH232" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>PopCorners</t>
         </is>
       </c>
       <c r="AI232" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>PopCorners</t>
         </is>
       </c>
       <c r="AJ232" t="inlineStr">
         <is>
-          <t>unknown_tortillas chips kettle corn popcorners</t>
+          <t>popcorners_tortillas chips kettle corn popcorners</t>
         </is>
       </c>
       <c r="AK232" t="inlineStr">
@@ -44503,7 +44896,7 @@
       </c>
       <c r="AM232" t="inlineStr">
         <is>
-          <t>unknown_tortillas chips kettle corn popcorners_0.14</t>
+          <t>popcorners_tortillas chips kettle corn popcorners_0.14</t>
         </is>
       </c>
       <c r="AN232" t="n">
@@ -44517,7 +44910,7 @@
       </c>
       <c r="AQ232" t="inlineStr">
         <is>
-          <t>unknown_chips_corn_kettle_popcorners</t>
+          <t>popcorners_chips_corn_kettle_popcorners</t>
         </is>
       </c>
       <c r="AR232" t="n">
@@ -44574,7 +44967,7 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>PopCorners</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -44653,17 +45046,17 @@
       <c r="AG233" t="inlineStr"/>
       <c r="AH233" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>PopCorners</t>
         </is>
       </c>
       <c r="AI233" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>PopCorners</t>
         </is>
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>unknown_tortillas chips kettle corn popcorners</t>
+          <t>popcorners_tortillas chips kettle corn popcorners</t>
         </is>
       </c>
       <c r="AK233" t="inlineStr">
@@ -44678,7 +45071,7 @@
       </c>
       <c r="AM233" t="inlineStr">
         <is>
-          <t>unknown_tortillas chips kettle corn popcorners_0.14</t>
+          <t>popcorners_tortillas chips kettle corn popcorners_0.14</t>
         </is>
       </c>
       <c r="AN233" t="n">
@@ -44692,7 +45085,7 @@
       </c>
       <c r="AQ233" t="inlineStr">
         <is>
-          <t>unknown_chips_corn_kettle_popcorners</t>
+          <t>popcorners_chips_corn_kettle_popcorners</t>
         </is>
       </c>
       <c r="AR233" t="n">
@@ -47988,7 +48381,7 @@
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Loacker</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -48067,17 +48460,17 @@
       <c r="AG253" t="inlineStr"/>
       <c r="AH253" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Loacker</t>
         </is>
       </c>
       <c r="AI253" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Loacker</t>
         </is>
       </c>
       <c r="AJ253" t="inlineStr">
         <is>
-          <t>unknown_galleta wafers loacker sabor a coconut</t>
+          <t>loacker_galleta wafers loacker sabor a coconut</t>
         </is>
       </c>
       <c r="AK253" t="inlineStr">
@@ -48092,7 +48485,7 @@
       </c>
       <c r="AM253" t="inlineStr">
         <is>
-          <t>unknown_galleta wafers loacker sabor a coconut_0.04</t>
+          <t>loacker_galleta wafers loacker sabor a coconut_0.04</t>
         </is>
       </c>
       <c r="AN253" t="n">
@@ -48106,7 +48499,7 @@
       </c>
       <c r="AQ253" t="inlineStr">
         <is>
-          <t>unknown_coconut_loacker_wafers</t>
+          <t>loacker_coconut_loacker_wafers</t>
         </is>
       </c>
       <c r="AR253" t="n">
@@ -48163,7 +48556,7 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Loacker</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -48242,17 +48635,17 @@
       <c r="AG254" t="inlineStr"/>
       <c r="AH254" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Loacker</t>
         </is>
       </c>
       <c r="AI254" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Loacker</t>
         </is>
       </c>
       <c r="AJ254" t="inlineStr">
         <is>
-          <t>unknown_galleta wafers loacker sabor a cremkakao</t>
+          <t>loacker_galleta wafers loacker sabor a cremkakao</t>
         </is>
       </c>
       <c r="AK254" t="inlineStr">
@@ -48267,7 +48660,7 @@
       </c>
       <c r="AM254" t="inlineStr">
         <is>
-          <t>unknown_galleta wafers loacker sabor a cremkakao_0.04</t>
+          <t>loacker_galleta wafers loacker sabor a cremkakao_0.04</t>
         </is>
       </c>
       <c r="AN254" t="n">
@@ -48281,7 +48674,7 @@
       </c>
       <c r="AQ254" t="inlineStr">
         <is>
-          <t>unknown_cremkakao_loacker_wafers</t>
+          <t>loacker_cremkakao_loacker_wafers</t>
         </is>
       </c>
       <c r="AR254" t="n">
@@ -48338,7 +48731,7 @@
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Loacker</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -48417,17 +48810,17 @@
       <c r="AG255" t="inlineStr"/>
       <c r="AH255" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Loacker</t>
         </is>
       </c>
       <c r="AI255" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Loacker</t>
         </is>
       </c>
       <c r="AJ255" t="inlineStr">
         <is>
-          <t>unknown_galleta wafers loacker sabor a napolitaner</t>
+          <t>loacker_galleta wafers loacker sabor a napolitaner</t>
         </is>
       </c>
       <c r="AK255" t="inlineStr">
@@ -48442,7 +48835,7 @@
       </c>
       <c r="AM255" t="inlineStr">
         <is>
-          <t>unknown_galleta wafers loacker sabor a napolitaner_0.04</t>
+          <t>loacker_galleta wafers loacker sabor a napolitaner_0.04</t>
         </is>
       </c>
       <c r="AN255" t="n">
@@ -48456,7 +48849,7 @@
       </c>
       <c r="AQ255" t="inlineStr">
         <is>
-          <t>unknown_loacker_napolitaner_wafers</t>
+          <t>loacker_loacker_napolitaner_wafers</t>
         </is>
       </c>
       <c r="AR255" t="n">
@@ -48513,7 +48906,7 @@
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Loacker</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -48588,17 +48981,17 @@
       <c r="AG256" t="inlineStr"/>
       <c r="AH256" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Loacker</t>
         </is>
       </c>
       <c r="AI256" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Loacker</t>
         </is>
       </c>
       <c r="AJ256" t="inlineStr">
         <is>
-          <t>unknown_galleta wafers loacker sabor a vainilla</t>
+          <t>loacker_galleta wafers loacker sabor a vainilla</t>
         </is>
       </c>
       <c r="AK256" t="inlineStr">
@@ -48613,7 +49006,7 @@
       </c>
       <c r="AM256" t="inlineStr">
         <is>
-          <t>unknown_galleta wafers loacker sabor a vainilla_0.04</t>
+          <t>loacker_galleta wafers loacker sabor a vainilla_0.04</t>
         </is>
       </c>
       <c r="AN256" t="inlineStr"/>
@@ -48621,7 +49014,7 @@
       <c r="AP256" t="inlineStr"/>
       <c r="AQ256" t="inlineStr">
         <is>
-          <t>unknown_loacker_vainilla_wafers</t>
+          <t>loacker_loacker_vainilla_wafers</t>
         </is>
       </c>
       <c r="AR256" t="n">
@@ -51231,7 +51624,7 @@
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Lotus</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
@@ -51310,17 +51703,17 @@
       <c r="AG272" t="inlineStr"/>
       <c r="AH272" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Lotus</t>
         </is>
       </c>
       <c r="AI272" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Lotus</t>
         </is>
       </c>
       <c r="AJ272" t="inlineStr">
         <is>
-          <t>unknown_galleta de mantequilla rellena de chocolate lotus</t>
+          <t>lotus_galleta de mantequilla rellena de chocolate lotus</t>
         </is>
       </c>
       <c r="AK272" t="inlineStr">
@@ -51335,7 +51728,7 @@
       </c>
       <c r="AM272" t="inlineStr">
         <is>
-          <t>unknown_galleta de mantequilla rellena de chocolate lotus_0.15</t>
+          <t>lotus_galleta de mantequilla rellena de chocolate lotus_0.15</t>
         </is>
       </c>
       <c r="AN272" t="n">
@@ -51345,7 +51738,7 @@
       <c r="AP272" t="inlineStr"/>
       <c r="AQ272" t="inlineStr">
         <is>
-          <t>unknown_chocolate_lotus_mantequilla</t>
+          <t>lotus_chocolate_lotus_mantequilla</t>
         </is>
       </c>
       <c r="AR272" t="n">
@@ -52434,7 +52827,7 @@
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Cheez-It</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
@@ -52509,17 +52902,17 @@
       <c r="AG279" t="inlineStr"/>
       <c r="AH279" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Cheez-It</t>
         </is>
       </c>
       <c r="AI279" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Kellanova</t>
         </is>
       </c>
       <c r="AJ279" t="inlineStr">
         <is>
-          <t>unknown_galleta snapd doble cheddar cheez it</t>
+          <t>cheez it_galleta snapd doble cheddar cheez it</t>
         </is>
       </c>
       <c r="AK279" t="inlineStr">
@@ -52534,7 +52927,7 @@
       </c>
       <c r="AM279" t="inlineStr">
         <is>
-          <t>unknown_galleta snapd doble cheddar cheez it_0.21</t>
+          <t>cheez it_galleta snapd doble cheddar cheez it_0.21</t>
         </is>
       </c>
       <c r="AN279" t="inlineStr"/>
@@ -52542,7 +52935,7 @@
       <c r="AP279" t="inlineStr"/>
       <c r="AQ279" t="inlineStr">
         <is>
-          <t>unknown_cheddar_cheez_doble_snapd</t>
+          <t>cheez it_cheddar_cheez_doble_snapd</t>
         </is>
       </c>
       <c r="AR279" t="n">
@@ -64756,7 +65149,7 @@
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>New York Style</t>
         </is>
       </c>
       <c r="H351" t="inlineStr">
@@ -64831,17 +65224,17 @@
       <c r="AG351" t="inlineStr"/>
       <c r="AH351" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>New York Style</t>
         </is>
       </c>
       <c r="AI351" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>New York Style</t>
         </is>
       </c>
       <c r="AJ351" t="inlineStr">
         <is>
-          <t>unknown_bagel crisps plain new york style</t>
+          <t>new york style_bagel crisps plain new york style</t>
         </is>
       </c>
       <c r="AK351" t="inlineStr">
@@ -64856,7 +65249,7 @@
       </c>
       <c r="AM351" t="inlineStr">
         <is>
-          <t>unknown_bagel crisps plain new york style_0.2</t>
+          <t>new york style_bagel crisps plain new york style_0.2</t>
         </is>
       </c>
       <c r="AN351" t="inlineStr"/>
@@ -64864,7 +65257,7 @@
       <c r="AP351" t="inlineStr"/>
       <c r="AQ351" t="inlineStr">
         <is>
-          <t>unknown_bagel_crisps_plain_style</t>
+          <t>new york style_bagel_crisps_plain_style</t>
         </is>
       </c>
       <c r="AR351" t="n">
@@ -64921,7 +65314,7 @@
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>New York Style</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
@@ -65000,17 +65393,17 @@
       <c r="AG352" t="inlineStr"/>
       <c r="AH352" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>New York Style</t>
         </is>
       </c>
       <c r="AI352" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>New York Style</t>
         </is>
       </c>
       <c r="AJ352" t="inlineStr">
         <is>
-          <t>unknown_bagel crisps sea salt new york style</t>
+          <t>new york style_bagel crisps sea salt new york style</t>
         </is>
       </c>
       <c r="AK352" t="inlineStr">
@@ -65025,7 +65418,7 @@
       </c>
       <c r="AM352" t="inlineStr">
         <is>
-          <t>unknown_bagel crisps sea salt new york style_0.2</t>
+          <t>new york style_bagel crisps sea salt new york style_0.2</t>
         </is>
       </c>
       <c r="AN352" t="n">
@@ -65035,7 +65428,7 @@
       <c r="AP352" t="inlineStr"/>
       <c r="AQ352" t="inlineStr">
         <is>
-          <t>unknown_bagel_crisps_salt_style</t>
+          <t>new york style_bagel_crisps_salt_style</t>
         </is>
       </c>
       <c r="AR352" t="n">
@@ -65772,7 +66165,7 @@
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Lotus</t>
         </is>
       </c>
       <c r="H357" t="inlineStr">
@@ -65851,17 +66244,17 @@
       <c r="AG357" t="inlineStr"/>
       <c r="AH357" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Lotus</t>
         </is>
       </c>
       <c r="AI357" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Lotus</t>
         </is>
       </c>
       <c r="AJ357" t="inlineStr">
         <is>
-          <t>unknown_galleta de mantequilla lotus</t>
+          <t>lotus_galleta de mantequilla lotus</t>
         </is>
       </c>
       <c r="AK357" t="inlineStr">
@@ -65876,7 +66269,7 @@
       </c>
       <c r="AM357" t="inlineStr">
         <is>
-          <t>unknown_galleta de mantequilla lotus_0.25</t>
+          <t>lotus_galleta de mantequilla lotus_0.25</t>
         </is>
       </c>
       <c r="AN357" t="n">
@@ -65890,7 +66283,7 @@
       </c>
       <c r="AQ357" t="inlineStr">
         <is>
-          <t>unknown_lotus_mantequilla</t>
+          <t>lotus_lotus_mantequilla</t>
         </is>
       </c>
       <c r="AR357" t="n">
@@ -65947,7 +66340,7 @@
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Lotus</t>
         </is>
       </c>
       <c r="H358" t="inlineStr">
@@ -66026,17 +66419,17 @@
       <c r="AG358" t="inlineStr"/>
       <c r="AH358" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Lotus</t>
         </is>
       </c>
       <c r="AI358" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Lotus</t>
         </is>
       </c>
       <c r="AJ358" t="inlineStr">
         <is>
-          <t>unknown_galleta de mantequilla lotus</t>
+          <t>lotus_galleta de mantequilla lotus</t>
         </is>
       </c>
       <c r="AK358" t="inlineStr">
@@ -66051,7 +66444,7 @@
       </c>
       <c r="AM358" t="inlineStr">
         <is>
-          <t>unknown_galleta de mantequilla lotus_0.25</t>
+          <t>lotus_galleta de mantequilla lotus_0.25</t>
         </is>
       </c>
       <c r="AN358" t="n">
@@ -66065,7 +66458,7 @@
       </c>
       <c r="AQ358" t="inlineStr">
         <is>
-          <t>unknown_lotus_mantequilla</t>
+          <t>lotus_lotus_mantequilla</t>
         </is>
       </c>
       <c r="AR358" t="n">
@@ -68544,7 +68937,7 @@
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Lago</t>
         </is>
       </c>
       <c r="H373" t="inlineStr">
@@ -68623,17 +69016,17 @@
       <c r="AG373" t="inlineStr"/>
       <c r="AH373" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Lago</t>
         </is>
       </c>
       <c r="AI373" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Lago</t>
         </is>
       </c>
       <c r="AJ373" t="inlineStr">
         <is>
-          <t>unknown_galleta wafers lago wafers mini party avellanas</t>
+          <t>lago_galleta wafers lago wafers mini party avellanas</t>
         </is>
       </c>
       <c r="AK373" t="inlineStr">
@@ -68648,7 +69041,7 @@
       </c>
       <c r="AM373" t="inlineStr">
         <is>
-          <t>unknown_galleta wafers lago wafers mini party avellanas_0.12</t>
+          <t>lago_galleta wafers lago wafers mini party avellanas_0.12</t>
         </is>
       </c>
       <c r="AN373" t="n">
@@ -68662,7 +69055,7 @@
       </c>
       <c r="AQ373" t="inlineStr">
         <is>
-          <t>unknown_avellanas_lago_party_wafers</t>
+          <t>lago_avellanas_lago_party_wafers</t>
         </is>
       </c>
       <c r="AR373" t="n">
@@ -68719,7 +69112,7 @@
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Lago</t>
         </is>
       </c>
       <c r="H374" t="inlineStr">
@@ -68798,17 +69191,17 @@
       <c r="AG374" t="inlineStr"/>
       <c r="AH374" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Lago</t>
         </is>
       </c>
       <c r="AI374" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Lago</t>
         </is>
       </c>
       <c r="AJ374" t="inlineStr">
         <is>
-          <t>unknown_galleta lago mini party cacao</t>
+          <t>lago_galleta lago mini party cacao</t>
         </is>
       </c>
       <c r="AK374" t="inlineStr">
@@ -68823,7 +69216,7 @@
       </c>
       <c r="AM374" t="inlineStr">
         <is>
-          <t>unknown_galleta lago mini party cacao_0.12</t>
+          <t>lago_galleta lago mini party cacao_0.12</t>
         </is>
       </c>
       <c r="AN374" t="n">
@@ -68837,7 +69230,7 @@
       </c>
       <c r="AQ374" t="inlineStr">
         <is>
-          <t>unknown_cacao_lago_party</t>
+          <t>lago_cacao_lago_party</t>
         </is>
       </c>
       <c r="AR374" t="n">
@@ -68894,7 +69287,7 @@
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Bon</t>
         </is>
       </c>
       <c r="H375" t="inlineStr">
@@ -68973,17 +69366,17 @@
       <c r="AG375" t="inlineStr"/>
       <c r="AH375" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Bon</t>
         </is>
       </c>
       <c r="AI375" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Bon</t>
         </is>
       </c>
       <c r="AJ375" t="inlineStr">
         <is>
-          <t>unknown_helados bon bizcocho</t>
+          <t>bon_helados bon bizcocho</t>
         </is>
       </c>
       <c r="AK375" t="inlineStr">
@@ -68998,7 +69391,7 @@
       </c>
       <c r="AM375" t="inlineStr">
         <is>
-          <t>unknown_helados bon bizcocho_0.26</t>
+          <t>bon_helados bon bizcocho_0.26</t>
         </is>
       </c>
       <c r="AN375" t="n">
@@ -69012,7 +69405,7 @@
       </c>
       <c r="AQ375" t="inlineStr">
         <is>
-          <t>unknown_bizcocho_helados</t>
+          <t>bon_bizcocho_helados</t>
         </is>
       </c>
       <c r="AR375" t="n">
@@ -69234,7 +69627,7 @@
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Mamut</t>
         </is>
       </c>
       <c r="H377" t="inlineStr">
@@ -69313,17 +69706,17 @@
       <c r="AG377" t="inlineStr"/>
       <c r="AH377" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Mamut</t>
         </is>
       </c>
       <c r="AI377" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Mamut</t>
         </is>
       </c>
       <c r="AJ377" t="inlineStr">
         <is>
-          <t>unknown_galletas de chocolate y malvavisco mamut</t>
+          <t>mamut_galletas de chocolate y malvavisco mamut</t>
         </is>
       </c>
       <c r="AK377" t="inlineStr">
@@ -69338,7 +69731,7 @@
       </c>
       <c r="AM377" t="inlineStr">
         <is>
-          <t>unknown_galletas de chocolate y malvavisco mamut_0.03</t>
+          <t>mamut_galletas de chocolate y malvavisco mamut_0.03</t>
         </is>
       </c>
       <c r="AN377" t="n">
@@ -69352,7 +69745,7 @@
       </c>
       <c r="AQ377" t="inlineStr">
         <is>
-          <t>unknown_chocolate_malvavisco_mamut</t>
+          <t>mamut_chocolate_malvavisco_mamut</t>
         </is>
       </c>
       <c r="AR377" t="n">
@@ -69409,7 +69802,7 @@
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Mamut</t>
         </is>
       </c>
       <c r="H378" t="inlineStr">
@@ -69488,17 +69881,17 @@
       <c r="AG378" t="inlineStr"/>
       <c r="AH378" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Mamut</t>
         </is>
       </c>
       <c r="AI378" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Mamut</t>
         </is>
       </c>
       <c r="AJ378" t="inlineStr">
         <is>
-          <t>unknown_galletas de chocolate y malvavisco mamut</t>
+          <t>mamut_galletas de chocolate y malvavisco mamut</t>
         </is>
       </c>
       <c r="AK378" t="inlineStr">
@@ -69513,7 +69906,7 @@
       </c>
       <c r="AM378" t="inlineStr">
         <is>
-          <t>unknown_galletas de chocolate y malvavisco mamut_0.03</t>
+          <t>mamut_galletas de chocolate y malvavisco mamut_0.03</t>
         </is>
       </c>
       <c r="AN378" t="n">
@@ -69527,7 +69920,7 @@
       </c>
       <c r="AQ378" t="inlineStr">
         <is>
-          <t>unknown_chocolate_malvavisco_mamut</t>
+          <t>mamut_chocolate_malvavisco_mamut</t>
         </is>
       </c>
       <c r="AR378" t="n">
@@ -69584,7 +69977,7 @@
       </c>
       <c r="G379" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Mamut</t>
         </is>
       </c>
       <c r="H379" t="inlineStr">
@@ -69663,17 +70056,17 @@
       <c r="AG379" t="inlineStr"/>
       <c r="AH379" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Mamut</t>
         </is>
       </c>
       <c r="AI379" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Mamut</t>
         </is>
       </c>
       <c r="AJ379" t="inlineStr">
         <is>
-          <t>unknown_galletas de chocolate y malvavisco mamut</t>
+          <t>mamut_galletas de chocolate y malvavisco mamut</t>
         </is>
       </c>
       <c r="AK379" t="inlineStr">
@@ -69688,7 +70081,7 @@
       </c>
       <c r="AM379" t="inlineStr">
         <is>
-          <t>unknown_galletas de chocolate y malvavisco mamut_0.03</t>
+          <t>mamut_galletas de chocolate y malvavisco mamut_0.03</t>
         </is>
       </c>
       <c r="AN379" t="n">
@@ -69702,7 +70095,7 @@
       </c>
       <c r="AQ379" t="inlineStr">
         <is>
-          <t>unknown_chocolate_malvavisco_mamut</t>
+          <t>mamut_chocolate_malvavisco_mamut</t>
         </is>
       </c>
       <c r="AR379" t="n">
@@ -69934,7 +70327,7 @@
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Mamut</t>
         </is>
       </c>
       <c r="H381" t="inlineStr">
@@ -70013,17 +70406,17 @@
       <c r="AG381" t="inlineStr"/>
       <c r="AH381" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Mamut</t>
         </is>
       </c>
       <c r="AI381" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Mamut</t>
         </is>
       </c>
       <c r="AJ381" t="inlineStr">
         <is>
-          <t>unknown_galletas de chocolate y malvavisco mamut</t>
+          <t>mamut_galletas de chocolate y malvavisco mamut</t>
         </is>
       </c>
       <c r="AK381" t="inlineStr">
@@ -70038,7 +70431,7 @@
       </c>
       <c r="AM381" t="inlineStr">
         <is>
-          <t>unknown_galletas de chocolate y malvavisco mamut_0.03</t>
+          <t>mamut_galletas de chocolate y malvavisco mamut_0.03</t>
         </is>
       </c>
       <c r="AN381" t="n">
@@ -70052,7 +70445,7 @@
       </c>
       <c r="AQ381" t="inlineStr">
         <is>
-          <t>unknown_chocolate_malvavisco_mamut</t>
+          <t>mamut_chocolate_malvavisco_mamut</t>
         </is>
       </c>
       <c r="AR381" t="n">
@@ -70109,7 +70502,7 @@
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Mamut</t>
         </is>
       </c>
       <c r="H382" t="inlineStr">
@@ -70188,17 +70581,17 @@
       <c r="AG382" t="inlineStr"/>
       <c r="AH382" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Mamut</t>
         </is>
       </c>
       <c r="AI382" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Mamut</t>
         </is>
       </c>
       <c r="AJ382" t="inlineStr">
         <is>
-          <t>unknown_galletas de chocolate y malvavisco mamut</t>
+          <t>mamut_galletas de chocolate y malvavisco mamut</t>
         </is>
       </c>
       <c r="AK382" t="inlineStr">
@@ -70213,7 +70606,7 @@
       </c>
       <c r="AM382" t="inlineStr">
         <is>
-          <t>unknown_galletas de chocolate y malvavisco mamut_0.03</t>
+          <t>mamut_galletas de chocolate y malvavisco mamut_0.03</t>
         </is>
       </c>
       <c r="AN382" t="n">
@@ -70227,7 +70620,7 @@
       </c>
       <c r="AQ382" t="inlineStr">
         <is>
-          <t>unknown_chocolate_malvavisco_mamut</t>
+          <t>mamut_chocolate_malvavisco_mamut</t>
         </is>
       </c>
       <c r="AR382" t="n">
@@ -71318,7 +71711,7 @@
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Mamut</t>
         </is>
       </c>
       <c r="H389" t="inlineStr">
@@ -71397,17 +71790,17 @@
       <c r="AG389" t="inlineStr"/>
       <c r="AH389" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Mamut</t>
         </is>
       </c>
       <c r="AI389" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Mamut</t>
         </is>
       </c>
       <c r="AJ389" t="inlineStr">
         <is>
-          <t>unknown_galletas de chocolate y malvavisco mamut</t>
+          <t>mamut_galletas de chocolate y malvavisco mamut</t>
         </is>
       </c>
       <c r="AK389" t="inlineStr">
@@ -71422,7 +71815,7 @@
       </c>
       <c r="AM389" t="inlineStr">
         <is>
-          <t>unknown_galletas de chocolate y malvavisco mamut_0.03</t>
+          <t>mamut_galletas de chocolate y malvavisco mamut_0.03</t>
         </is>
       </c>
       <c r="AN389" t="n">
@@ -71436,7 +71829,7 @@
       </c>
       <c r="AQ389" t="inlineStr">
         <is>
-          <t>unknown_chocolate_malvavisco_mamut</t>
+          <t>mamut_chocolate_malvavisco_mamut</t>
         </is>
       </c>
       <c r="AR389" t="n">
@@ -71493,7 +71886,7 @@
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Mamut</t>
         </is>
       </c>
       <c r="H390" t="inlineStr">
@@ -71572,17 +71965,17 @@
       <c r="AG390" t="inlineStr"/>
       <c r="AH390" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Mamut</t>
         </is>
       </c>
       <c r="AI390" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Mamut</t>
         </is>
       </c>
       <c r="AJ390" t="inlineStr">
         <is>
-          <t>unknown_galletas de chocolate y malvavisco mamut</t>
+          <t>mamut_galletas de chocolate y malvavisco mamut</t>
         </is>
       </c>
       <c r="AK390" t="inlineStr">
@@ -71597,7 +71990,7 @@
       </c>
       <c r="AM390" t="inlineStr">
         <is>
-          <t>unknown_galletas de chocolate y malvavisco mamut_0.03</t>
+          <t>mamut_galletas de chocolate y malvavisco mamut_0.03</t>
         </is>
       </c>
       <c r="AN390" t="n">
@@ -71611,7 +72004,7 @@
       </c>
       <c r="AQ390" t="inlineStr">
         <is>
-          <t>unknown_chocolate_malvavisco_mamut</t>
+          <t>mamut_chocolate_malvavisco_mamut</t>
         </is>
       </c>
       <c r="AR390" t="n">
@@ -71833,7 +72226,7 @@
       </c>
       <c r="G392" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Bon</t>
         </is>
       </c>
       <c r="H392" t="inlineStr">
@@ -71912,17 +72305,17 @@
       <c r="AG392" t="inlineStr"/>
       <c r="AH392" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Bon</t>
         </is>
       </c>
       <c r="AI392" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Bon</t>
         </is>
       </c>
       <c r="AJ392" t="inlineStr">
         <is>
-          <t>unknown_helados bon bizcocho</t>
+          <t>bon_helados bon bizcocho</t>
         </is>
       </c>
       <c r="AK392" t="inlineStr">
@@ -71937,7 +72330,7 @@
       </c>
       <c r="AM392" t="inlineStr">
         <is>
-          <t>unknown_helados bon bizcocho_0.26</t>
+          <t>bon_helados bon bizcocho_0.26</t>
         </is>
       </c>
       <c r="AN392" t="n">
@@ -71951,7 +72344,7 @@
       </c>
       <c r="AQ392" t="inlineStr">
         <is>
-          <t>unknown_bizcocho_helados</t>
+          <t>bon_bizcocho_helados</t>
         </is>
       </c>
       <c r="AR392" t="n">
@@ -78033,7 +78426,7 @@
       </c>
       <c r="G428" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Lago</t>
         </is>
       </c>
       <c r="H428" t="inlineStr">
@@ -78114,17 +78507,17 @@
       <c r="AG428" t="inlineStr"/>
       <c r="AH428" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Lago</t>
         </is>
       </c>
       <c r="AI428" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Lago</t>
         </is>
       </c>
       <c r="AJ428" t="inlineStr">
         <is>
-          <t>unknown_galleta wafers lago poker con avellanas 5 und</t>
+          <t>lago_galleta wafers lago poker con avellanas 5 und</t>
         </is>
       </c>
       <c r="AK428" t="inlineStr">
@@ -78139,7 +78532,7 @@
       </c>
       <c r="AM428" t="inlineStr">
         <is>
-          <t>unknown_galleta wafers lago poker con avellanas 5 und_0.22</t>
+          <t>lago_galleta wafers lago poker con avellanas 5 und_0.22</t>
         </is>
       </c>
       <c r="AN428" t="n">
@@ -78153,7 +78546,7 @@
       </c>
       <c r="AQ428" t="inlineStr">
         <is>
-          <t>unknown_avellanas_lago_poker_wafers</t>
+          <t>lago_avellanas_lago_poker_wafers</t>
         </is>
       </c>
       <c r="AR428" t="n">
@@ -78210,7 +78603,7 @@
       </c>
       <c r="G429" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Lago</t>
         </is>
       </c>
       <c r="H429" t="inlineStr">
@@ -78289,17 +78682,17 @@
       <c r="AG429" t="inlineStr"/>
       <c r="AH429" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Lago</t>
         </is>
       </c>
       <c r="AI429" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Lago</t>
         </is>
       </c>
       <c r="AJ429" t="inlineStr">
         <is>
-          <t>unknown_galleta lago mini party cacao</t>
+          <t>lago_galleta lago mini party cacao</t>
         </is>
       </c>
       <c r="AK429" t="inlineStr">
@@ -78314,7 +78707,7 @@
       </c>
       <c r="AM429" t="inlineStr">
         <is>
-          <t>unknown_galleta lago mini party cacao_0.12</t>
+          <t>lago_galleta lago mini party cacao_0.12</t>
         </is>
       </c>
       <c r="AN429" t="n">
@@ -78328,7 +78721,7 @@
       </c>
       <c r="AQ429" t="inlineStr">
         <is>
-          <t>unknown_cacao_lago_party</t>
+          <t>lago_cacao_lago_party</t>
         </is>
       </c>
       <c r="AR429" t="n">

--- a/streamlit_data/regional_insights.xlsx
+++ b/streamlit_data/regional_insights.xlsx
@@ -39535,7 +39535,7 @@
       </c>
       <c r="AV181" t="inlineStr">
         <is>
-          <t>unknown_hotdog_buns</t>
+          <t>exclude_from_benchmark</t>
         </is>
       </c>
       <c r="AW181" t="n">
